--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R6dc4f19ab5064e6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Reeb40dc6399c4d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R72b231d551574e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R1a7e77d5a83a4094"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,12 +433,12 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L82),2)</x:f>
-        <x:v>75.08</x:v>
+        <x:f>ROUND(SUM(L11:L85),2)</x:f>
+        <x:v>75.13</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
-        <x:v>BOM updated 2026-10-05 with U19; all stock/prices are listing snapshots.</x:v>
+        <x:v>BOM updated 2026-10-05 with active USB auxiliary mux; stock/prices are listing snapshots or marked unverified.</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
@@ -461,12 +461,12 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M82),2)</x:f>
+        <x:f>ROUND(SUM(M11:M85),2)</x:f>
         <x:v>94.01</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
-        <x:v>MOQ orders consolidated by MPN; repeat rows show order quantity0.</x:v>
+        <x:v>MOQ orders consolidated by MPN; repeat rows show order quantity 0.</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
       <x:c r="I5" s="1"/>
@@ -493,7 +493,7 @@
       </x:c>
       <x:c r="F6" s="1"/>
       <x:c r="G6" s="1" t="str">
-        <x:v>Partial subtotal excludes unpriced parts, pack, switches, speakers and open audio selections; not full product cost.</x:v>
+        <x:v>Partial subtotal excludes unpriced parts, unverified stock, pack, switches, speakers and open audio selections; not full product cost.</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
       <x:c r="I6" s="1"/>
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D11,$F$11:$F$82),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D11,$F$11:$F$85),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D12,$F$11:$F$82),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D12,$F$11:$F$85),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -782,7 +782,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="14" t="n">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D13,$F$11:$F$82),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D13,$F$11:$F$85),G13)/H13,0)*H13))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="6" t="n">
@@ -842,7 +842,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D14,$F$11:$F$82),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D14,$F$11:$F$85),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -902,7 +902,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D15,$F$11:$F$82),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D15,$F$11:$F$85),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -962,7 +962,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D16,$F$11:$F$82),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D16,$F$11:$F$85),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1022,7 +1022,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D17,$F$11:$F$82),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D17,$F$11:$F$85),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1082,7 +1082,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D18,$F$11:$F$82),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D18,$F$11:$F$85),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1142,7 +1142,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D19,$F$11:$F$82),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D19,$F$11:$F$85),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1202,7 +1202,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D20,$F$11:$F$82),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D20,$F$11:$F$85),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1262,7 +1262,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D21,$F$11:$F$82),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D21,$F$11:$F$85),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1322,7 +1322,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="1" t="n">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D22,$F$11:$F$82),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D22,$F$11:$F$85),G22)/H22,0)*H22))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J22" s="1" t="n">
@@ -1382,7 +1382,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D23,$F$11:$F$82),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D23,$F$11:$F$85),G23)/H23,0)*H23))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1442,7 +1442,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D24,$F$11:$F$82),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D24,$F$11:$F$85),G24)/H24,0)*H24))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1502,7 +1502,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D25,$F$11:$F$82),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D25,$F$11:$F$85),G25)/H25,0)*H25))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1562,7 +1562,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D26,$F$11:$F$82),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D26,$F$11:$F$85),G26)/H26,0)*H26))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1622,7 +1622,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D27,$F$11:$F$82),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D27,$F$11:$F$85),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1682,7 +1682,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D28,$F$11:$F$82),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D28,$F$11:$F$85),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1742,7 +1742,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I29" s="1" t="n">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D29,$F$11:$F$82),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D29,$F$11:$F$85),G29)/H29,0)*H29))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J29" s="1" t="n">
@@ -1802,7 +1802,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D30,$F$11:$F$82),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D30,$F$11:$F$85),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1862,7 +1862,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D31,$F$11:$F$82),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D31,$F$11:$F$85),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1924,7 +1924,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D32,$F$11:$F$82),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D32,$F$11:$F$85),G32)/H32,0)*H32))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1984,7 +1984,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D33,$F$11:$F$82),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D33,$F$11:$F$85),G33)/H33,0)*H33))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -2044,7 +2044,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D34,$F$11:$F$82),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D34,$F$11:$F$85),G34)/H34,0)*H34))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2103,7 +2103,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D35,$F$11:$F$82),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D35,$F$11:$F$85),G35)/H35,0)*H35))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2163,7 +2163,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I36" t="n">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D36,$F$11:$F$82),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D36,$F$11:$F$85),G36)/H36,0)*H36))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J36" t="n">
@@ -2223,7 +2223,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D37,$F$11:$F$82),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D37,$F$11:$F$85),G37)/H37,0)*H37))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2283,7 +2283,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D38,$F$11:$F$82),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D38,$F$11:$F$85),G38)/H38,0)*H38))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2343,7 +2343,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D39,$F$11:$F$82),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D39,$F$11:$F$85),G39)/H39,0)*H39))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2403,7 +2403,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D40,$F$11:$F$82),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D40,$F$11:$F$85),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2463,7 +2463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D41,$F$11:$F$82),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D41,$F$11:$F$85),G41)/H41,0)*H41))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2523,7 +2523,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D42,$F$11:$F$82),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D42,$F$11:$F$85),G42)/H42,0)*H42))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2575,7 +2575,7 @@
       <x:c r="G43"/>
       <x:c r="H43"/>
       <x:c r="I43" t="str">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D43,$F$11:$F$82),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D43,$F$11:$F$85),G43)/H43,0)*H43))</x:f>
       </x:c>
       <x:c r="J43"/>
       <x:c r="K43" s="26"/>
@@ -2620,7 +2620,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D44,$F$11:$F$82),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D44,$F$11:$F$85),G44)/H44,0)*H44))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2680,7 +2680,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D45,$F$11:$F$82),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D45,$F$11:$F$85),G45)/H45,0)*H45))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2740,7 +2740,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D46,$F$11:$F$82),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D46,$F$11:$F$85),G46)/H46,0)*H46))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2800,7 +2800,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D47,$F$11:$F$82),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D47,$F$11:$F$85),G47)/H47,0)*H47))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2862,7 +2862,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D48,$F$11:$F$82),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D48,$F$11:$F$85),G48)/H48,0)*H48))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2921,7 +2921,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D49,$F$11:$F$82),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D49,$F$11:$F$85),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2981,7 +2981,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D50,$F$11:$F$82),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D50,$F$11:$F$85),G50)/H50,0)*H50))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -3041,7 +3041,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D51,$F$11:$F$82),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D51,$F$11:$F$85),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3101,7 +3101,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D52,$F$11:$F$82),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D52,$F$11:$F$85),G52)/H52,0)*H52))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3161,7 +3161,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D53,$F$11:$F$82),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D53,$F$11:$F$85),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3210,7 +3210,7 @@
       <x:c r="G54"/>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D54,$F$11:$F$82),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D54,$F$11:$F$85),G54)/H54,0)*H54))</x:f>
       </x:c>
       <x:c r="J54"/>
       <x:c r="K54" s="26"/>
@@ -3245,7 +3245,7 @@
       <x:c r="G55"/>
       <x:c r="H55"/>
       <x:c r="I55" t="str">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D55,$F$11:$F$82),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D55,$F$11:$F$85),G55)/H55,0)*H55))</x:f>
       </x:c>
       <x:c r="J55"/>
       <x:c r="K55" s="26"/>
@@ -3280,7 +3280,7 @@
       <x:c r="G56"/>
       <x:c r="H56"/>
       <x:c r="I56" t="str">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D56,$F$11:$F$82),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D56,$F$11:$F$85),G56)/H56,0)*H56))</x:f>
       </x:c>
       <x:c r="J56"/>
       <x:c r="K56" s="26"/>
@@ -3315,7 +3315,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D57,$F$11:$F$82),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D57,$F$11:$F$85),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3360,7 +3360,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D58,$F$11:$F$82),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D58,$F$11:$F$85),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3396,7 +3396,7 @@
     </x:row>
     <x:row r="59" ht="36" customHeight="1">
       <x:c r="A59" s="25" t="str">
-        <x:v>C122, C123</x:v>
+        <x:v>C122, C123, C124, C125</x:v>
       </x:c>
       <x:c r="B59" s="25" t="str">
         <x:v>AO LDO 1uF X7R 10V capacitors</x:v>
@@ -3411,7 +3411,7 @@
         <x:v>C92806</x:v>
       </x:c>
       <x:c r="F59" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G59" t="n">
         <x:v>50</x:v>
@@ -3420,7 +3420,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D59,$F$11:$F$82),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D59,$F$11:$F$85),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3431,7 +3431,7 @@
       </x:c>
       <x:c r="L59" s="27" t="n">
         <x:f>IF(K59="","",ROUND(F59*K59,4))</x:f>
-        <x:v>0.0462</x:v>
+        <x:v>0.0924</x:v>
       </x:c>
       <x:c r="M59" s="27" t="n">
         <x:f>IF(OR(K59="",I59="",N59=""),"",IF(N59&gt;=I59,ROUND(I59*K59,4),""))</x:f>
@@ -3480,7 +3480,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D60,$F$11:$F$82),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D60,$F$11:$F$85),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3539,7 +3539,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D61,$F$11:$F$82),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D61,$F$11:$F$85),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3599,7 +3599,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D62,$F$11:$F$82),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D62,$F$11:$F$85),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3658,7 +3658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D63,$F$11:$F$82),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D63,$F$11:$F$85),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3720,7 +3720,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D64,$F$11:$F$82),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D64,$F$11:$F$85),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3779,7 +3779,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D65,$F$11:$F$82),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D65,$F$11:$F$85),G65)/H65,0)*H65))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3839,7 +3839,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D66,$F$11:$F$82),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D66,$F$11:$F$85),G66)/H66,0)*H66))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3897,7 +3897,7 @@
       <x:c r="G67"/>
       <x:c r="H67"/>
       <x:c r="I67" t="str">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D67,$F$11:$F$82),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D67,$F$11:$F$85),G67)/H67,0)*H67))</x:f>
       </x:c>
       <x:c r="J67"/>
       <x:c r="K67" s="26"/>
@@ -3944,7 +3944,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D68,$F$11:$F$82),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D68,$F$11:$F$85),G68)/H68,0)*H68))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4003,7 +4003,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D69,$F$11:$F$82),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D69,$F$11:$F$85),G69)/H69,0)*H69))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4063,7 +4063,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D70,$F$11:$F$82),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D70,$F$11:$F$85),G70)/H70,0)*H70))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4125,7 +4125,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D71,$F$11:$F$82),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D71,$F$11:$F$85),G71)/H71,0)*H71))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4187,7 +4187,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I72" t="n">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D72,$F$11:$F$82),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D72,$F$11:$F$85),G72)/H72,0)*H72))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J72" t="n">
@@ -4247,7 +4247,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D73,$F$11:$F$82),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D73,$F$11:$F$85),G73)/H73,0)*H73))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4307,7 +4307,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D74,$F$11:$F$82),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D74,$F$11:$F$85),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4366,7 +4366,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D75,$F$11:$F$82),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D75,$F$11:$F$85),G75)/H75,0)*H75))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4425,7 +4425,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D76,$F$11:$F$82),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D76,$F$11:$F$85),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4485,7 +4485,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D77,$F$11:$F$82),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D77,$F$11:$F$85),G77)/H77,0)*H77))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4545,7 +4545,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D78,$F$11:$F$82),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D78,$F$11:$F$85),G78)/H78,0)*H78))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4605,7 +4605,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D79,$F$11:$F$82),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D79,$F$11:$F$85),G79)/H79,0)*H79))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4664,7 +4664,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D80,$F$11:$F$82),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D80,$F$11:$F$85),G80)/H80,0)*H80))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4723,7 +4723,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D81,$F$11:$F$82),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D81,$F$11:$F$85),G81)/H81,0)*H81))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4763,7 +4763,7 @@
         <x:v>U19</x:v>
       </x:c>
       <x:c r="B82" s="21" t="str">
-        <x:v>USB PD controller 5.0V VDD LDO</x:v>
+        <x:v>USB auxiliary 5V / PD controller VDD LDO</x:v>
       </x:c>
       <x:c r="C82" s="21" t="str">
         <x:v>Texas Instruments</x:v>
@@ -4784,7 +4784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$82,D82,$F$11:$F$82),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D82,$F$11:$F$85),G82)/H82,0)*H82))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4820,78 +4820,174 @@
         <x:v>https://www.lcsc.com/product-detail/C3751394.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
-      <x:c r="A83" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B83"/>
-      <x:c r="C83"/>
-      <x:c r="D83"/>
-      <x:c r="E83"/>
-      <x:c r="F83"/>
+    <x:row r="83" ht="48" customHeight="1">
+      <x:c r="A83" s="21" t="str">
+        <x:v>U20</x:v>
+      </x:c>
+      <x:c r="B83" s="21" t="str">
+        <x:v>USB and system logic priority mux</x:v>
+      </x:c>
+      <x:c r="C83" s="21" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="D83" s="21" t="str">
+        <x:v>TPS2116DRLR</x:v>
+      </x:c>
+      <x:c r="E83" s="21" t="str">
+        <x:v>C3235557</x:v>
+      </x:c>
+      <x:c r="F83" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G83"/>
       <x:c r="H83"/>
-      <x:c r="I83"/>
+      <x:c r="I83" t="str">
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D83,$F$11:$F$85),G83)/H83,0)*H83))</x:f>
+      </x:c>
       <x:c r="J83"/>
-      <x:c r="K83"/>
-      <x:c r="L83"/>
-      <x:c r="M83"/>
+      <x:c r="K83" s="26"/>
+      <x:c r="L83" s="27" t="str">
+        <x:f>IF(K83="","",ROUND(F83*K83,4))</x:f>
+      </x:c>
+      <x:c r="M83" s="27" t="str">
+        <x:f>IF(OR(K83="",I83="",N83=""),"",IF(N83&gt;=I83,ROUND(I83*K83,4),""))</x:f>
+      </x:c>
       <x:c r="N83"/>
-      <x:c r="O83"/>
-      <x:c r="P83"/>
+      <x:c r="O83" t="str">
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P83" s="16"/>
       <x:c r="Q83"/>
-      <x:c r="R83"/>
-      <x:c r="S83"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
-      </x:c>
-      <x:c r="B84"/>
-      <x:c r="C84"/>
-      <x:c r="D84"/>
-      <x:c r="E84"/>
-      <x:c r="F84"/>
-      <x:c r="G84"/>
-      <x:c r="H84"/>
-      <x:c r="I84"/>
-      <x:c r="J84"/>
-      <x:c r="K84"/>
-      <x:c r="L84"/>
-      <x:c r="M84"/>
+      <x:c r="R83" s="21" t="str">
+        <x:v>Selected MPN/LCSC mapping; current stock and price not verified.</x:v>
+      </x:c>
+      <x:c r="S83" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C3235557.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="48" customHeight="1">
+      <x:c r="A84" s="21" t="str">
+        <x:v>R124</x:v>
+      </x:c>
+      <x:c r="B84" s="21" t="str">
+        <x:v>180k 1% USB-priority threshold divider resistor</x:v>
+      </x:c>
+      <x:c r="C84" s="21" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D84" s="21" t="str">
+        <x:v>RC0603FR-07180KL</x:v>
+      </x:c>
+      <x:c r="E84" s="21" t="str">
+        <x:v>C123419</x:v>
+      </x:c>
+      <x:c r="F84" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I84" t="n">
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D84,$F$11:$F$85),G84)/H84,0)*H84))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K84" s="26" t="n">
+        <x:v>0.0012</x:v>
+      </x:c>
+      <x:c r="L84" s="27" t="n">
+        <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
+        <x:v>0.0012</x:v>
+      </x:c>
+      <x:c r="M84" s="27" t="str">
+        <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
+      </x:c>
       <x:c r="N84"/>
-      <x:c r="O84"/>
-      <x:c r="P84"/>
-      <x:c r="Q84"/>
-      <x:c r="R84"/>
-      <x:c r="S84"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
-      </x:c>
-      <x:c r="B85"/>
-      <x:c r="C85"/>
-      <x:c r="D85"/>
-      <x:c r="E85"/>
-      <x:c r="F85"/>
-      <x:c r="G85"/>
-      <x:c r="H85"/>
-      <x:c r="I85"/>
-      <x:c r="J85"/>
-      <x:c r="K85"/>
-      <x:c r="L85"/>
-      <x:c r="M85"/>
-      <x:c r="N85"/>
-      <x:c r="O85"/>
-      <x:c r="P85"/>
-      <x:c r="Q85"/>
-      <x:c r="R85"/>
-      <x:c r="S85"/>
+      <x:c r="O84" t="str">
+        <x:v>Stock unverified; price snapshot</x:v>
+      </x:c>
+      <x:c r="P84" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q84" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R84" s="21" t="str">
+        <x:v>Observed listing tier: $0.0012 at MOQ100. Product page may be stale; stock is unverified.</x:v>
+      </x:c>
+      <x:c r="S84" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="48" customHeight="1">
+      <x:c r="A85" s="21" t="str">
+        <x:v>R125</x:v>
+      </x:c>
+      <x:c r="B85" s="21" t="str">
+        <x:v>100k PR1 divider resistor</x:v>
+      </x:c>
+      <x:c r="C85" s="21" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D85" s="21" t="str">
+        <x:v>RC0603FR-07100KL</x:v>
+      </x:c>
+      <x:c r="E85" s="21" t="str">
+        <x:v>C14675</x:v>
+      </x:c>
+      <x:c r="F85" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H85" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I85" t="n">
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D85,$F$11:$F$85),G85)/H85,0)*H85))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K85" s="26" t="n">
+        <x:v>0.0036</x:v>
+      </x:c>
+      <x:c r="L85" s="27" t="n">
+        <x:f>IF(K85="","",ROUND(F85*K85,4))</x:f>
+        <x:v>0.0036</x:v>
+      </x:c>
+      <x:c r="M85" s="27" t="str">
+        <x:f>IF(OR(K85="",I85="",N85=""),"",IF(N85&gt;=I85,ROUND(I85*K85,4),""))</x:f>
+      </x:c>
+      <x:c r="N85" t="n">
+        <x:v>7813400</x:v>
+      </x:c>
+      <x:c r="O85" t="str">
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P85" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q85" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R85" s="21" t="str">
+        <x:v>Reuse same selected MPN/LCSC mapping as existing 100k BOM rows; no additional MOQ order.</x:v>
+      </x:c>
+      <x:c r="S85" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>J1: 16-pin right angle. Displayed discount price.</x:v>
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
       <x:c r="B86"/>
       <x:c r="C86"/>
@@ -4914,7 +5010,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>J2, J3: J2 HEAD_OUT, J3 AUX_IN. Switched stereo jack. Displayed discount price.</x:v>
+        <x:v>U2: Only 4 available in page snapshot.</x:v>
       </x:c>
       <x:c r="B87"/>
       <x:c r="C87"/>
@@ -4937,7 +5033,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>D1: TI dual-channel USB2 data ESD. No required VBUS connection.</x:v>
+        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
       </x:c>
       <x:c r="B88"/>
       <x:c r="C88"/>
@@ -4957,6 +5053,75 @@
       <x:c r="Q88"/>
       <x:c r="R88"/>
       <x:c r="S88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
+      <x:c r="J89"/>
+      <x:c r="K89"/>
+      <x:c r="L89"/>
+      <x:c r="M89"/>
+      <x:c r="N89"/>
+      <x:c r="O89"/>
+      <x:c r="P89"/>
+      <x:c r="Q89"/>
+      <x:c r="R89"/>
+      <x:c r="S89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>U2: Only 4 available in page snapshot.</x:v>
+      </x:c>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
+      <x:c r="J90"/>
+      <x:c r="K90"/>
+      <x:c r="L90"/>
+      <x:c r="M90"/>
+      <x:c r="N90"/>
+      <x:c r="O90"/>
+      <x:c r="P90"/>
+      <x:c r="Q90"/>
+      <x:c r="R90"/>
+      <x:c r="S90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+      </x:c>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
+      <x:c r="J91"/>
+      <x:c r="K91"/>
+      <x:c r="L91"/>
+      <x:c r="M91"/>
+      <x:c r="N91"/>
+      <x:c r="O91"/>
+      <x:c r="P91"/>
+      <x:c r="Q91"/>
+      <x:c r="R91"/>
+      <x:c r="S91"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R72b231d551574e9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R1a7e77d5a83a4094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf4cdf102b5cd4efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R96104e32cb3f4b10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,12 +433,12 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L85),2)</x:f>
-        <x:v>75.13</x:v>
+        <x:f>ROUND(SUM(L11:L87),2)</x:f>
+        <x:v>75.61</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
-        <x:v>BOM updated 2026-10-05 with active USB auxiliary mux; stock/prices are listing snapshots or marked unverified.</x:v>
+        <x:v>BOM updated 2026-10-05 with gauge undervoltage supervisor and isolation controls; stock/prices are listing snapshots.</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M85),2)</x:f>
-        <x:v>94.01</x:v>
+        <x:f>ROUND(SUM(M11:M87),2)</x:f>
+        <x:v>95.01</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D11,$F$11:$F$85),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D11,$F$11:$F$87),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D12,$F$11:$F$85),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D12,$F$11:$F$87),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -782,7 +782,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="14" t="n">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D13,$F$11:$F$85),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D13,$F$11:$F$87),G13)/H13,0)*H13))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="6" t="n">
@@ -842,7 +842,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D14,$F$11:$F$85),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D14,$F$11:$F$87),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -902,7 +902,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D15,$F$11:$F$85),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D15,$F$11:$F$87),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -962,7 +962,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D16,$F$11:$F$85),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D16,$F$11:$F$87),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1022,7 +1022,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D17,$F$11:$F$85),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D17,$F$11:$F$87),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1082,7 +1082,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D18,$F$11:$F$85),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D18,$F$11:$F$87),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1142,7 +1142,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D19,$F$11:$F$85),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D19,$F$11:$F$87),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1202,7 +1202,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D20,$F$11:$F$85),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D20,$F$11:$F$87),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1262,7 +1262,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D21,$F$11:$F$85),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D21,$F$11:$F$87),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1322,7 +1322,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="1" t="n">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D22,$F$11:$F$85),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D22,$F$11:$F$87),G22)/H22,0)*H22))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J22" s="1" t="n">
@@ -1382,7 +1382,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D23,$F$11:$F$85),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D23,$F$11:$F$87),G23)/H23,0)*H23))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1442,7 +1442,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D24,$F$11:$F$85),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D24,$F$11:$F$87),G24)/H24,0)*H24))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1502,7 +1502,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D25,$F$11:$F$85),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D25,$F$11:$F$87),G25)/H25,0)*H25))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1538,10 +1538,10 @@
     </x:row>
     <x:row r="26" ht="36" customHeight="1">
       <x:c r="A26" s="22" t="str">
-        <x:v>Q100</x:v>
+        <x:v>Q100, Q104</x:v>
       </x:c>
       <x:c r="B26" s="22" t="str">
-        <x:v>Charge-enable NMOS</x:v>
+        <x:v>Charger CE and gauge-enable NMOS</x:v>
       </x:c>
       <x:c r="C26" s="22" t="str">
         <x:v>Nexperia</x:v>
@@ -1553,7 +1553,7 @@
         <x:v>C65189</x:v>
       </x:c>
       <x:c r="F26" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G26" s="1" t="n">
         <x:v>20</x:v>
@@ -1562,7 +1562,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D26,$F$11:$F$85),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D26,$F$11:$F$87),G26)/H26,0)*H26))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1573,7 +1573,7 @@
       </x:c>
       <x:c r="L26" s="31" t="n">
         <x:f>IF(K26="","",ROUND(F26*K26,4))</x:f>
-        <x:v>0.0183</x:v>
+        <x:v>0.0366</x:v>
       </x:c>
       <x:c r="M26" s="31" t="n">
         <x:f>IF(OR(K26="",I26="",N26=""),"",IF(N26&gt;=I26,ROUND(I26*K26,4),""))</x:f>
@@ -1622,7 +1622,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D27,$F$11:$F$85),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D27,$F$11:$F$87),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1682,7 +1682,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D28,$F$11:$F$85),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D28,$F$11:$F$87),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1742,7 +1742,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I29" s="1" t="n">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D29,$F$11:$F$85),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D29,$F$11:$F$87),G29)/H29,0)*H29))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J29" s="1" t="n">
@@ -1802,7 +1802,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D30,$F$11:$F$85),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D30,$F$11:$F$87),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1862,7 +1862,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D31,$F$11:$F$85),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D31,$F$11:$F$87),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1924,7 +1924,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D32,$F$11:$F$85),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D32,$F$11:$F$87),G32)/H32,0)*H32))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1984,7 +1984,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D33,$F$11:$F$85),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D33,$F$11:$F$87),G33)/H33,0)*H33))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -2044,7 +2044,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D34,$F$11:$F$85),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D34,$F$11:$F$87),G34)/H34,0)*H34))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2103,7 +2103,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D35,$F$11:$F$85),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D35,$F$11:$F$87),G35)/H35,0)*H35))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2163,7 +2163,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I36" t="n">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D36,$F$11:$F$85),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D36,$F$11:$F$87),G36)/H36,0)*H36))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J36" t="n">
@@ -2223,7 +2223,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D37,$F$11:$F$85),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D37,$F$11:$F$87),G37)/H37,0)*H37))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2283,7 +2283,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D38,$F$11:$F$85),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D38,$F$11:$F$87),G38)/H38,0)*H38))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2343,7 +2343,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D39,$F$11:$F$85),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D39,$F$11:$F$87),G39)/H39,0)*H39))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2403,7 +2403,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D40,$F$11:$F$85),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D40,$F$11:$F$87),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2463,7 +2463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D41,$F$11:$F$85),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D41,$F$11:$F$87),G41)/H41,0)*H41))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2523,7 +2523,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D42,$F$11:$F$85),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D42,$F$11:$F$87),G42)/H42,0)*H42))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2575,7 +2575,7 @@
       <x:c r="G43"/>
       <x:c r="H43"/>
       <x:c r="I43" t="str">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D43,$F$11:$F$85),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D43,$F$11:$F$87),G43)/H43,0)*H43))</x:f>
       </x:c>
       <x:c r="J43"/>
       <x:c r="K43" s="26"/>
@@ -2620,7 +2620,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D44,$F$11:$F$85),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D44,$F$11:$F$87),G44)/H44,0)*H44))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2680,7 +2680,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D45,$F$11:$F$85),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D45,$F$11:$F$87),G45)/H45,0)*H45))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2740,7 +2740,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D46,$F$11:$F$85),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D46,$F$11:$F$87),G46)/H46,0)*H46))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2800,7 +2800,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D47,$F$11:$F$85),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D47,$F$11:$F$87),G47)/H47,0)*H47))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2862,7 +2862,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D48,$F$11:$F$85),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D48,$F$11:$F$87),G48)/H48,0)*H48))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2921,7 +2921,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D49,$F$11:$F$85),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D49,$F$11:$F$87),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2981,7 +2981,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D50,$F$11:$F$85),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D50,$F$11:$F$87),G50)/H50,0)*H50))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -3041,7 +3041,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D51,$F$11:$F$85),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D51,$F$11:$F$87),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3101,7 +3101,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D52,$F$11:$F$85),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D52,$F$11:$F$87),G52)/H52,0)*H52))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3161,7 +3161,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D53,$F$11:$F$85),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D53,$F$11:$F$87),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3210,7 +3210,7 @@
       <x:c r="G54"/>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D54,$F$11:$F$85),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D54,$F$11:$F$87),G54)/H54,0)*H54))</x:f>
       </x:c>
       <x:c r="J54"/>
       <x:c r="K54" s="26"/>
@@ -3245,7 +3245,7 @@
       <x:c r="G55"/>
       <x:c r="H55"/>
       <x:c r="I55" t="str">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D55,$F$11:$F$85),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D55,$F$11:$F$87),G55)/H55,0)*H55))</x:f>
       </x:c>
       <x:c r="J55"/>
       <x:c r="K55" s="26"/>
@@ -3280,7 +3280,7 @@
       <x:c r="G56"/>
       <x:c r="H56"/>
       <x:c r="I56" t="str">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D56,$F$11:$F$85),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D56,$F$11:$F$87),G56)/H56,0)*H56))</x:f>
       </x:c>
       <x:c r="J56"/>
       <x:c r="K56" s="26"/>
@@ -3315,7 +3315,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D57,$F$11:$F$85),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D57,$F$11:$F$87),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3336,10 +3336,10 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
-        <x:v>100nF / 10V-or-higher 0603 decoupling</x:v>
+        <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
       </x:c>
       <x:c r="C58" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
@@ -3351,7 +3351,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3360,7 +3360,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D58,$F$11:$F$85),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D58,$F$11:$F$87),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3371,7 +3371,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.0777</x:v>
+        <x:v>0.0888</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3420,7 +3420,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D59,$F$11:$F$85),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D59,$F$11:$F$87),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3480,7 +3480,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D60,$F$11:$F$85),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D60,$F$11:$F$87),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3539,7 +3539,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D61,$F$11:$F$85),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D61,$F$11:$F$87),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3599,7 +3599,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D62,$F$11:$F$85),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D62,$F$11:$F$87),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3658,7 +3658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D63,$F$11:$F$85),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D63,$F$11:$F$87),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3720,7 +3720,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D64,$F$11:$F$85),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D64,$F$11:$F$87),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3779,7 +3779,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D65,$F$11:$F$85),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D65,$F$11:$F$87),G65)/H65,0)*H65))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3839,7 +3839,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D66,$F$11:$F$85),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D66,$F$11:$F$87),G66)/H66,0)*H66))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3897,7 +3897,7 @@
       <x:c r="G67"/>
       <x:c r="H67"/>
       <x:c r="I67" t="str">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D67,$F$11:$F$85),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D67,$F$11:$F$87),G67)/H67,0)*H67))</x:f>
       </x:c>
       <x:c r="J67"/>
       <x:c r="K67" s="26"/>
@@ -3944,7 +3944,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D68,$F$11:$F$85),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D68,$F$11:$F$87),G68)/H68,0)*H68))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4003,7 +4003,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D69,$F$11:$F$85),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D69,$F$11:$F$87),G69)/H69,0)*H69))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4063,7 +4063,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D70,$F$11:$F$85),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D70,$F$11:$F$87),G70)/H70,0)*H70))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4125,7 +4125,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D71,$F$11:$F$85),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D71,$F$11:$F$87),G71)/H71,0)*H71))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4187,7 +4187,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I72" t="n">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D72,$F$11:$F$85),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D72,$F$11:$F$87),G72)/H72,0)*H72))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J72" t="n">
@@ -4247,7 +4247,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D73,$F$11:$F$85),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D73,$F$11:$F$87),G73)/H73,0)*H73))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4307,7 +4307,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D74,$F$11:$F$85),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D74,$F$11:$F$87),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4366,7 +4366,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D75,$F$11:$F$85),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D75,$F$11:$F$87),G75)/H75,0)*H75))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4425,7 +4425,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D76,$F$11:$F$85),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D76,$F$11:$F$87),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4485,7 +4485,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D77,$F$11:$F$85),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D77,$F$11:$F$87),G77)/H77,0)*H77))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4545,7 +4545,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D78,$F$11:$F$85),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D78,$F$11:$F$87),G78)/H78,0)*H78))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4605,7 +4605,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D79,$F$11:$F$85),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D79,$F$11:$F$87),G79)/H79,0)*H79))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4664,7 +4664,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D80,$F$11:$F$85),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D80,$F$11:$F$87),G80)/H80,0)*H80))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4723,7 +4723,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D81,$F$11:$F$85),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D81,$F$11:$F$87),G81)/H81,0)*H81))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4784,7 +4784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D82,$F$11:$F$85),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D82,$F$11:$F$87),G82)/H82,0)*H82))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4842,7 +4842,7 @@
       <x:c r="G83"/>
       <x:c r="H83"/>
       <x:c r="I83" t="str">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D83,$F$11:$F$85),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D83,$F$11:$F$87),G83)/H83,0)*H83))</x:f>
       </x:c>
       <x:c r="J83"/>
       <x:c r="K83" s="26"/>
@@ -4891,7 +4891,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D84,$F$11:$F$85),G84)/H84,0)*H84))</x:f>
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D84,$F$11:$F$87),G84)/H84,0)*H84))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J84" t="n">
@@ -4950,7 +4950,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D85,$F$11:$F$85),G85)/H85,0)*H85))</x:f>
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D85,$F$11:$F$87),G85)/H85,0)*H85))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" t="n">
@@ -4985,55 +4985,129 @@
         <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
-      <x:c r="A86" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B86"/>
-      <x:c r="C86"/>
-      <x:c r="D86"/>
-      <x:c r="E86"/>
-      <x:c r="F86"/>
-      <x:c r="G86"/>
-      <x:c r="H86"/>
-      <x:c r="I86"/>
-      <x:c r="J86"/>
-      <x:c r="K86"/>
-      <x:c r="L86"/>
-      <x:c r="M86"/>
-      <x:c r="N86"/>
-      <x:c r="O86"/>
-      <x:c r="P86"/>
-      <x:c r="Q86"/>
-      <x:c r="R86"/>
-      <x:c r="S86"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
-      </x:c>
-      <x:c r="B87"/>
-      <x:c r="C87"/>
-      <x:c r="D87"/>
-      <x:c r="E87"/>
-      <x:c r="F87"/>
-      <x:c r="G87"/>
-      <x:c r="H87"/>
-      <x:c r="I87"/>
-      <x:c r="J87"/>
-      <x:c r="K87"/>
-      <x:c r="L87"/>
-      <x:c r="M87"/>
-      <x:c r="N87"/>
-      <x:c r="O87"/>
-      <x:c r="P87"/>
-      <x:c r="Q87"/>
-      <x:c r="R87"/>
-      <x:c r="S87"/>
+    <x:row r="86" ht="54" customHeight="1">
+      <x:c r="A86" s="21" t="str">
+        <x:v>U21</x:v>
+      </x:c>
+      <x:c r="B86" s="21" t="str">
+        <x:v>Gauge undervoltage supervisor</x:v>
+      </x:c>
+      <x:c r="C86" s="21" t="str">
+        <x:v>Texas Instruments</x:v>
+      </x:c>
+      <x:c r="D86" s="21" t="str">
+        <x:v>TPS3839G33DBZR</x:v>
+      </x:c>
+      <x:c r="E86" s="21" t="str">
+        <x:v>C485802</x:v>
+      </x:c>
+      <x:c r="F86" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I86" t="n">
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D86,$F$11:$F$87),G86)/H86,0)*H86))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" s="26" t="n">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="L86" s="27" t="n">
+        <x:f>IF(K86="","",ROUND(F86*K86,4))</x:f>
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="M86" s="27" t="n">
+        <x:f>IF(OR(K86="",I86="",N86=""),"",IF(N86&gt;=I86,ROUND(I86*K86,4),""))</x:f>
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="N86" t="n">
+        <x:v>3444</x:v>
+      </x:c>
+      <x:c r="O86" t="str">
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P86" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q86" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R86" s="21"/>
+      <x:c r="S86" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C485802.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="54" customHeight="1">
+      <x:c r="A87" s="21" t="str">
+        <x:v>R126, R127</x:v>
+      </x:c>
+      <x:c r="B87" s="21" t="str">
+        <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
+      </x:c>
+      <x:c r="C87" s="21" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D87" s="21" t="str">
+        <x:v>RC0603FR-071ML</x:v>
+      </x:c>
+      <x:c r="E87" s="21" t="str">
+        <x:v>C105578</x:v>
+      </x:c>
+      <x:c r="F87" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G87" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H87" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I87" t="n">
+        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D87,$F$11:$F$87),G87)/H87,0)*H87))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J87" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K87" s="26" t="n">
+        <x:v>0.0056</x:v>
+      </x:c>
+      <x:c r="L87" s="27" t="n">
+        <x:f>IF(K87="","",ROUND(F87*K87,4))</x:f>
+        <x:v>0.0112</x:v>
+      </x:c>
+      <x:c r="M87" s="27" t="n">
+        <x:f>IF(OR(K87="",I87="",N87=""),"",IF(N87&gt;=I87,ROUND(I87*K87,4),""))</x:f>
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="N87" t="n">
+        <x:v>359600</x:v>
+      </x:c>
+      <x:c r="O87" t="str">
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P87" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q87" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R87" s="21"/>
+      <x:c r="S87" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C105578.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
       <x:c r="B88"/>
       <x:c r="C88"/>
@@ -5056,7 +5130,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+        <x:v>U2: Only 4 available in page snapshot.</x:v>
       </x:c>
       <x:c r="B89"/>
       <x:c r="C89"/>
@@ -5079,7 +5153,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
+        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
       </x:c>
       <x:c r="B90"/>
       <x:c r="C90"/>
@@ -5102,7 +5176,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
       <x:c r="B91"/>
       <x:c r="C91"/>
@@ -5122,6 +5196,52 @@
       <x:c r="Q91"/>
       <x:c r="R91"/>
       <x:c r="S91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>U2: Only 4 available in page snapshot.</x:v>
+      </x:c>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
+      <x:c r="J92"/>
+      <x:c r="K92"/>
+      <x:c r="L92"/>
+      <x:c r="M92"/>
+      <x:c r="N92"/>
+      <x:c r="O92"/>
+      <x:c r="P92"/>
+      <x:c r="Q92"/>
+      <x:c r="R92"/>
+      <x:c r="S92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+      </x:c>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
+      <x:c r="J93"/>
+      <x:c r="K93"/>
+      <x:c r="L93"/>
+      <x:c r="M93"/>
+      <x:c r="N93"/>
+      <x:c r="O93"/>
+      <x:c r="P93"/>
+      <x:c r="Q93"/>
+      <x:c r="R93"/>
+      <x:c r="S93"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf4cdf102b5cd4efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R96104e32cb3f4b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rcfe5ef04d251472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rc7f5797f957e4915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate fixes" sheetId="3" r:id="R38e0c34ddca84d82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6003,4 +6004,261 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Reference (candidate)</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Function</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Manufacturer</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>MPN</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>LCSC part</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Fitted qty</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>MOQ</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>Unit USD (tier)</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>Stock qty (2026-10-05 listing)</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>Footprint</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>TPS25730D CVBUS 4.7uF/50V X7R 1210 (was 1uF)</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>CL32B475KBUYNNE</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>C170099</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>0.1367</x:v>
+      </x:c>
+      <x:c r="I2" t="n">
+        <x:v>57880</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>DesktopSpeaker:PD_C_1210</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>Alt: GRM32ER71H475KA88L C86052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>C6</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>TPS25730D CLDO_3V3 22uF/10V X7R 0805 (was 10uF)</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>GRM21BZ71A226ME15L</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>C907991</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>0.2543</x:v>
+      </x:c>
+      <x:c r="I3" t="n">
+        <x:v>132900</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>DesktopSpeaker:PD_C_0805</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>Same MPN as SYS caps</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>C113, C114, C115</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>BQ25792 VBUS/PMID/SYS 100nF/50V X7R 0402 bypass</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>GRM155R71H104KE14D</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>C77020</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="I4" t="n">
+        <x:v>777000</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>DesktopSpeaker:PD_C_0402 (new, ai-files/candidates/PD_C_0402.kicad_mod)</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>Replaces mismatched CL21B104KBCNNNC (0805)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>D7</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>TPS25730D VBUS-to-GND Schottky (TI 8.5)</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Diodes Incorporated</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>1N5819HW-7-F</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>C82544</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H5" t="n">
+        <x:v>0.057</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>137330</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>DesktopSpeaker:PD_D_SOD123</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>40V/1A SOD-123; IR max ~1 mA at 40V, lower at 20V; alt B5819W SL C8598</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>R14, R15, R18</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>TPS25730D I2C SDA/SCL pull-ups to LDO_3V3 (R14,R15); pin 36 to GND (R18) 10k 1%</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>RC0603FR-0710KL</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>C98220</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>0.0034</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>7736700</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>DesktopSpeaker:PD_R_0603</x:v>
+      </x:c>
+      <x:c r="K6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>R16, R17, R103</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>TPS25730D PLUG_EVENT/SINK_EN 100k pull-ups (R16,R17); BQ25792 R103 CE pull-up now 100k (was 10k)</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>RC0603FR-07100KL</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>C14675</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>0.0026</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>7987300</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>DesktopSpeaker:PD_R_0603</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>R103 stays in Selected BOM row "R103, R106" as 10k until integration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Candidate-only rows; not in Selected BOM subtotals. Prices/stock are LCSC listing snapshots (2026-10-05). LCSC URL = https://www.lcsc.com/product-detail/&lt;LCSC part&gt;.html</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rcfe5ef04d251472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rc7f5797f957e4915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate fixes" sheetId="3" r:id="R38e0c34ddca84d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R84b5439466b04a39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R775214754f27435f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,12 +433,12 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L87),2)</x:f>
-        <x:v>75.61</x:v>
+        <x:f>ROUND(SUM(L11:L76),2)</x:f>
+        <x:v>67.28</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
-        <x:v>BOM updated 2026-10-05 with gauge undervoltage supervisor and isolation controls; stock/prices are listing snapshots.</x:v>
+        <x:v>BOM updated 2026-10-05: TPS25730D USB_PD and BQ25792 charger integrated; stock/prices are listing snapshots or marked unverified.</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
@@ -462,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M87),2)</x:f>
-        <x:v>95.01</x:v>
+        <x:f>ROUND(SUM(M11:M76),2)</x:f>
+        <x:v>83.81</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -663,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D11,$F$11:$F$87),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D11,$F$11:$F$76),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -723,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D12,$F$11:$F$87),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D12,$F$11:$F$76),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -762,59 +761,44 @@
         <x:v>U4</x:v>
       </x:c>
       <x:c r="B13" s="22" t="str">
-        <x:v>Battery charger</x:v>
+        <x:v>Battery charger, 5-20 V 1S buck-boost</x:v>
       </x:c>
       <x:c r="C13" s="22" t="str">
         <x:v>TI</x:v>
       </x:c>
       <x:c r="D13" s="22" t="str">
-        <x:v>BQ25895RTWR</x:v>
+        <x:v>BQ25792RQMR</x:v>
       </x:c>
       <x:c r="E13" s="22" t="str">
-        <x:v>C80200</x:v>
+        <x:v>C2862876</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="14" t="n">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D13,$F$11:$F$87),G13)/H13,0)*H13))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J13" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K13" s="28" t="n">
-        <x:v>2.1402</x:v>
-      </x:c>
-      <x:c r="L13" s="30" t="n">
+      <x:c r="G13" s="13"/>
+      <x:c r="H13" s="13"/>
+      <x:c r="I13" s="14" t="str">
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D13,$F$11:$F$76),G13)/H13,0)*H13))</x:f>
+      </x:c>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="28"/>
+      <x:c r="L13" s="30" t="str">
         <x:f>IF(K13="","",ROUND(F13*K13,4))</x:f>
-        <x:v>2.1402</x:v>
-      </x:c>
-      <x:c r="M13" s="30" t="n">
+      </x:c>
+      <x:c r="M13" s="30" t="str">
         <x:f>IF(OR(K13="",I13="",N13=""),"",IF(N13&gt;=I13,ROUND(I13*K13,4),""))</x:f>
-        <x:v>2.1402</x:v>
-      </x:c>
-      <x:c r="N13" s="7" t="n">
-        <x:v>4508</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N13" s="7"/>
       <x:c r="O13" s="1" t="str">
-        <x:v>In stock</x:v>
-      </x:c>
-      <x:c r="P13" s="4" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="Q13" s="1" t="str">
-        <x:v>today</x:v>
-      </x:c>
-      <x:c r="R13" s="1"/>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P13" s="4"/>
+      <x:c r="Q13" s="1"/>
+      <x:c r="R13" s="1" t="str">
+        <x:v>Replaces BQ25895. Review snapshot: US$2.0489 (1+), 4,970 in stock; not re-verified at this BOM freeze, so excluded from priced subtotal.</x:v>
+      </x:c>
       <x:c r="S13" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C80200.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2862876.html</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
@@ -843,7 +827,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D14,$F$11:$F$87),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D14,$F$11:$F$76),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -903,7 +887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D15,$F$11:$F$87),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D15,$F$11:$F$76),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -963,7 +947,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D16,$F$11:$F$87),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D16,$F$11:$F$76),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1023,7 +1007,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D17,$F$11:$F$87),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D17,$F$11:$F$76),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1083,7 +1067,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D18,$F$11:$F$87),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D18,$F$11:$F$76),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1143,7 +1127,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D19,$F$11:$F$87),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D19,$F$11:$F$76),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1203,7 +1187,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D20,$F$11:$F$87),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D20,$F$11:$F$76),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1263,7 +1247,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D21,$F$11:$F$87),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D21,$F$11:$F$76),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1302,79 +1286,64 @@
         <x:v>U11</x:v>
       </x:c>
       <x:c r="B22" s="22" t="str">
-        <x:v>USB PD controller</x:v>
+        <x:v>USB-C PD 5-20 V sink controller</x:v>
       </x:c>
       <x:c r="C22" s="22" t="str">
-        <x:v>ST</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D22" s="22" t="str">
-        <x:v>STUSB4500QTR</x:v>
+        <x:v>TPS25730DREFR</x:v>
       </x:c>
       <x:c r="E22" s="22" t="str">
-        <x:v>C2678061</x:v>
+        <x:v>C22438973</x:v>
       </x:c>
       <x:c r="F22" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G22" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="n">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D22,$F$11:$F$87),G22)/H22,0)*H22))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K22" s="28" t="n">
-        <x:v>2.6826</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+      <x:c r="I22" s="1" t="str">
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D22,$F$11:$F$76),G22)/H22,0)*H22))</x:f>
+      </x:c>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="28"/>
+      <x:c r="L22" s="31" t="str">
         <x:f>IF(K22="","",ROUND(F22*K22,4))</x:f>
-        <x:v>2.6826</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
+      </x:c>
+      <x:c r="M22" s="31" t="str">
         <x:f>IF(OR(K22="",I22="",N22=""),"",IF(N22&gt;=I22,ROUND(I22*K22,4),""))</x:f>
-        <x:v>2.6826</x:v>
-      </x:c>
-      <x:c r="N22" s="7" t="n">
-        <x:v>4877</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N22" s="7"/>
       <x:c r="O22" s="1" t="str">
-        <x:v>Snapshot</x:v>
-      </x:c>
-      <x:c r="P22" s="4" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="Q22" s="1" t="str">
-        <x:v>today</x:v>
-      </x:c>
-      <x:c r="R22" s="1"/>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P22" s="4"/>
+      <x:c r="Q22" s="1"/>
+      <x:c r="R22" s="1" t="str">
+        <x:v>Replaces STUSB4500 and Q1/Q2/U18/U19-front-end parts. Review snapshot: US$3.0105 (1+), 381 in stock; not re-verified.</x:v>
+      </x:c>
       <x:c r="S22" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2678061.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C22438973.html</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="36" customHeight="1">
       <x:c r="A23" s="24" t="str">
-        <x:v>Q1, Q2</x:v>
+        <x:v>U12</x:v>
       </x:c>
       <x:c r="B23" s="22" t="str">
-        <x:v>PD reverse-blocking PMOS</x:v>
+        <x:v>3.0 V always-on LDO</x:v>
       </x:c>
       <x:c r="C23" s="22" t="str">
-        <x:v>ST</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D23" s="22" t="str">
-        <x:v>STL9P3LLH6</x:v>
+        <x:v>TPS7A0230PDBVR</x:v>
       </x:c>
       <x:c r="E23" s="22" t="str">
-        <x:v>C2969828</x:v>
+        <x:v>C3747031</x:v>
       </x:c>
       <x:c r="F23" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="1" t="n">
         <x:v>1</x:v>
@@ -1383,25 +1352,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D23,$F$11:$F$87),G23)/H23,0)*H23))</x:f>
-        <x:v>2</x:v>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D23,$F$11:$F$76),G23)/H23,0)*H23))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K23" s="28" t="n">
-        <x:v>1.0781</x:v>
+        <x:v>0.4515</x:v>
       </x:c>
       <x:c r="L23" s="31" t="n">
         <x:f>IF(K23="","",ROUND(F23*K23,4))</x:f>
-        <x:v>2.1562</x:v>
+        <x:v>0.4515</x:v>
       </x:c>
       <x:c r="M23" s="31" t="n">
         <x:f>IF(OR(K23="",I23="",N23=""),"",IF(N23&gt;=I23,ROUND(I23*K23,4),""))</x:f>
-        <x:v>2.1562</x:v>
+        <x:v>0.4515</x:v>
       </x:c>
       <x:c r="N23" s="7" t="n">
-        <x:v>829</x:v>
+        <x:v>37473</x:v>
       </x:c>
       <x:c r="O23" s="1" t="str">
         <x:v>Snapshot</x:v>
@@ -1410,178 +1379,178 @@
         <x:v>46299</x:v>
       </x:c>
       <x:c r="Q23" s="1" t="str">
-        <x:v>3 months ago</x:v>
+        <x:v>today</x:v>
       </x:c>
       <x:c r="R23" s="1"/>
       <x:c r="S23" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2969828.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3747031.html</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
       <x:c r="A24" s="22" t="str">
-        <x:v>U12</x:v>
+        <x:v>U13, U16, U17</x:v>
       </x:c>
       <x:c r="B24" s="22" t="str">
-        <x:v>3.0 V always-on LDO</x:v>
+        <x:v>Low-current gauge signal isolation</x:v>
       </x:c>
       <x:c r="C24" s="22" t="str">
         <x:v>TI</x:v>
       </x:c>
       <x:c r="D24" s="22" t="str">
-        <x:v>TPS7A0230PDBVR</x:v>
+        <x:v>TS5A3167DBVR</x:v>
       </x:c>
       <x:c r="E24" s="22" t="str">
-        <x:v>C3747031</x:v>
+        <x:v>C128416</x:v>
       </x:c>
       <x:c r="F24" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G24" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H24" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D24,$F$11:$F$87),G24)/H24,0)*H24))</x:f>
-        <x:v>1</x:v>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D24,$F$11:$F$76),G24)/H24,0)*H24))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K24" s="28" t="n">
-        <x:v>0.4515</x:v>
+        <x:v>0.3187</x:v>
       </x:c>
       <x:c r="L24" s="31" t="n">
         <x:f>IF(K24="","",ROUND(F24*K24,4))</x:f>
-        <x:v>0.4515</x:v>
+        <x:v>0.9561</x:v>
       </x:c>
       <x:c r="M24" s="31" t="n">
         <x:f>IF(OR(K24="",I24="",N24=""),"",IF(N24&gt;=I24,ROUND(I24*K24,4),""))</x:f>
-        <x:v>0.4515</x:v>
+        <x:v>1.5935</x:v>
       </x:c>
       <x:c r="N24" s="7" t="n">
-        <x:v>37473</x:v>
+        <x:v>11755</x:v>
       </x:c>
       <x:c r="O24" s="1" t="str">
-        <x:v>Snapshot</x:v>
+        <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P24" s="4" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="Q24" s="1" t="str">
-        <x:v>today</x:v>
+        <x:v>2026-10-04</x:v>
       </x:c>
       <x:c r="R24" s="1"/>
       <x:c r="S24" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3747031.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C128416.html</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="36" customHeight="1">
       <x:c r="A25" s="22" t="str">
-        <x:v>U13, U16, U17</x:v>
+        <x:v>Q100, Q101, Q102, Q104</x:v>
       </x:c>
       <x:c r="B25" s="22" t="str">
-        <x:v>Low-current gauge signal isolation</x:v>
+        <x:v>Charger CE, ILIM_HIZ and gauge-enable NMOS</x:v>
       </x:c>
       <x:c r="C25" s="22" t="str">
-        <x:v>TI</x:v>
+        <x:v>Nexperia</x:v>
       </x:c>
       <x:c r="D25" s="22" t="str">
-        <x:v>TS5A3167DBVR</x:v>
+        <x:v>2N7002,215</x:v>
       </x:c>
       <x:c r="E25" s="22" t="str">
-        <x:v>C128416</x:v>
+        <x:v>C65189</x:v>
       </x:c>
       <x:c r="F25" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G25" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H25" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D25,$F$11:$F$87),G25)/H25,0)*H25))</x:f>
-        <x:v>5</x:v>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D25,$F$11:$F$76),G25)/H25,0)*H25))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K25" s="28" t="n">
-        <x:v>0.3187</x:v>
+        <x:v>0.0183</x:v>
       </x:c>
       <x:c r="L25" s="31" t="n">
         <x:f>IF(K25="","",ROUND(F25*K25,4))</x:f>
-        <x:v>0.9561</x:v>
+        <x:v>0.0732</x:v>
       </x:c>
       <x:c r="M25" s="31" t="n">
         <x:f>IF(OR(K25="",I25="",N25=""),"",IF(N25&gt;=I25,ROUND(I25*K25,4),""))</x:f>
-        <x:v>1.5935</x:v>
+        <x:v>0.366</x:v>
       </x:c>
       <x:c r="N25" s="7" t="n">
-        <x:v>11755</x:v>
+        <x:v>274640</x:v>
       </x:c>
       <x:c r="O25" s="1" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P25" s="4" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q25" s="1" t="str">
-        <x:v>2026-10-04</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R25" s="1"/>
       <x:c r="S25" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C128416.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C65189.html</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="36" customHeight="1">
       <x:c r="A26" s="22" t="str">
-        <x:v>Q100, Q104</x:v>
+        <x:v>D5</x:v>
       </x:c>
       <x:c r="B26" s="22" t="str">
-        <x:v>Charger CE and gauge-enable NMOS</x:v>
+        <x:v>USB-C CC protection</x:v>
       </x:c>
       <x:c r="C26" s="22" t="str">
-        <x:v>Nexperia</x:v>
+        <x:v>ST</x:v>
       </x:c>
       <x:c r="D26" s="22" t="str">
-        <x:v>2N7002,215</x:v>
+        <x:v>ESDA25L</x:v>
       </x:c>
       <x:c r="E26" s="22" t="str">
-        <x:v>C65189</x:v>
+        <x:v>C95343</x:v>
       </x:c>
       <x:c r="F26" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="1" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H26" s="1" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D26,$F$11:$F$87),G26)/H26,0)*H26))</x:f>
-        <x:v>20</x:v>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D26,$F$11:$F$76),G26)/H26,0)*H26))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K26" s="28" t="n">
-        <x:v>0.0183</x:v>
+        <x:v>0.0971</x:v>
       </x:c>
       <x:c r="L26" s="31" t="n">
         <x:f>IF(K26="","",ROUND(F26*K26,4))</x:f>
-        <x:v>0.0366</x:v>
+        <x:v>0.0971</x:v>
       </x:c>
       <x:c r="M26" s="31" t="n">
         <x:f>IF(OR(K26="",I26="",N26=""),"",IF(N26&gt;=I26,ROUND(I26*K26,4),""))</x:f>
-        <x:v>0.366</x:v>
+        <x:v>0.4855</x:v>
       </x:c>
       <x:c r="N26" s="7" t="n">
-        <x:v>274640</x:v>
+        <x:v>1955</x:v>
       </x:c>
       <x:c r="O26" s="1" t="str">
         <x:v>Snapshot</x:v>
@@ -1590,28 +1559,28 @@
         <x:v>46299</x:v>
       </x:c>
       <x:c r="Q26" s="1" t="str">
-        <x:v>today</x:v>
+        <x:v>2 months ago</x:v>
       </x:c>
       <x:c r="R26" s="1"/>
       <x:c r="S26" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C65189.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C95343.html</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="36" customHeight="1">
       <x:c r="A27" s="22" t="str">
-        <x:v>D5</x:v>
+        <x:v>D6</x:v>
       </x:c>
       <x:c r="B27" s="22" t="str">
-        <x:v>USB-C CC protection</x:v>
+        <x:v>Raw VBUS 22V standoff TVS</x:v>
       </x:c>
       <x:c r="C27" s="22" t="str">
-        <x:v>ST</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D27" s="22" t="str">
-        <x:v>ESDA25L</x:v>
+        <x:v>TVS2200DRVR</x:v>
       </x:c>
       <x:c r="E27" s="22" t="str">
-        <x:v>C95343</x:v>
+        <x:v>C523793</x:v>
       </x:c>
       <x:c r="F27" s="22" t="n">
         <x:v>1</x:v>
@@ -1623,55 +1592,55 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D27,$F$11:$F$87),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D27,$F$11:$F$76),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K27" s="28" t="n">
-        <x:v>0.0971</x:v>
+        <x:v>0.4672</x:v>
       </x:c>
       <x:c r="L27" s="31" t="n">
         <x:f>IF(K27="","",ROUND(F27*K27,4))</x:f>
-        <x:v>0.0971</x:v>
+        <x:v>0.4672</x:v>
       </x:c>
       <x:c r="M27" s="31" t="n">
         <x:f>IF(OR(K27="",I27="",N27=""),"",IF(N27&gt;=I27,ROUND(I27*K27,4),""))</x:f>
-        <x:v>0.4855</x:v>
+        <x:v>2.336</x:v>
       </x:c>
       <x:c r="N27" s="7" t="n">
-        <x:v>1955</x:v>
+        <x:v>3285</x:v>
       </x:c>
       <x:c r="O27" s="1" t="str">
-        <x:v>Snapshot</x:v>
+        <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P27" s="4" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="Q27" s="1" t="str">
-        <x:v>2 months ago</x:v>
+        <x:v>2026-10-04</x:v>
       </x:c>
       <x:c r="R27" s="1"/>
       <x:c r="S27" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C95343.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C523793.html</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="36" customHeight="1">
       <x:c r="A28" s="22" t="str">
-        <x:v>D6</x:v>
+        <x:v>L1</x:v>
       </x:c>
       <x:c r="B28" s="22" t="str">
-        <x:v>Raw VBUS 22V standoff TVS</x:v>
+        <x:v>Charger inductor</x:v>
       </x:c>
       <x:c r="C28" s="22" t="str">
-        <x:v>TI</x:v>
+        <x:v>Bourns</x:v>
       </x:c>
       <x:c r="D28" s="22" t="str">
-        <x:v>TVS2200DRVR</x:v>
+        <x:v>SRN6045TA-2R2Y</x:v>
       </x:c>
       <x:c r="E28" s="22" t="str">
-        <x:v>C523793</x:v>
+        <x:v>C1332316</x:v>
       </x:c>
       <x:c r="F28" s="22" t="n">
         <x:v>1</x:v>
@@ -1683,103 +1652,88 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D28,$F$11:$F$87),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D28,$F$11:$F$76),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K28" s="28" t="n">
-        <x:v>0.4672</x:v>
+        <x:v>0.2261</x:v>
       </x:c>
       <x:c r="L28" s="31" t="n">
         <x:f>IF(K28="","",ROUND(F28*K28,4))</x:f>
-        <x:v>0.4672</x:v>
+        <x:v>0.2261</x:v>
       </x:c>
       <x:c r="M28" s="31" t="n">
         <x:f>IF(OR(K28="",I28="",N28=""),"",IF(N28&gt;=I28,ROUND(I28*K28,4),""))</x:f>
-        <x:v>2.336</x:v>
+        <x:v>1.1305</x:v>
       </x:c>
       <x:c r="N28" s="7" t="n">
-        <x:v>3285</x:v>
+        <x:v>2980</x:v>
       </x:c>
       <x:c r="O28" s="1" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Snapshot</x:v>
       </x:c>
       <x:c r="P28" s="4" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="Q28" s="1" t="str">
-        <x:v>2026-10-04</x:v>
+        <x:v>5 days ago</x:v>
       </x:c>
       <x:c r="R28" s="1"/>
       <x:c r="S28" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C523793.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C1332316.html</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="36" customHeight="1">
       <x:c r="A29" s="22" t="str">
-        <x:v>L1</x:v>
+        <x:v>Q103</x:v>
       </x:c>
       <x:c r="B29" s="22" t="str">
-        <x:v>Charger inductor</x:v>
+        <x:v>Ship FET (pack disconnect)</x:v>
       </x:c>
       <x:c r="C29" s="22" t="str">
-        <x:v>Bourns</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D29" s="22" t="str">
-        <x:v>SRN6045TA-2R2Y</x:v>
+        <x:v>CSD17579Q3A</x:v>
       </x:c>
       <x:c r="E29" s="22" t="str">
-        <x:v>C1332316</x:v>
+        <x:v>C97376</x:v>
       </x:c>
       <x:c r="F29" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I29" s="1" t="n">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D29,$F$11:$F$87),G29)/H29,0)*H29))</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K29" s="28" t="n">
-        <x:v>0.2261</x:v>
-      </x:c>
-      <x:c r="L29" s="31" t="n">
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+      <x:c r="I29" s="1" t="str">
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D29,$F$11:$F$76),G29)/H29,0)*H29))</x:f>
+      </x:c>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="28"/>
+      <x:c r="L29" s="31" t="str">
         <x:f>IF(K29="","",ROUND(F29*K29,4))</x:f>
-        <x:v>0.2261</x:v>
-      </x:c>
-      <x:c r="M29" s="31" t="n">
+      </x:c>
+      <x:c r="M29" s="31" t="str">
         <x:f>IF(OR(K29="",I29="",N29=""),"",IF(N29&gt;=I29,ROUND(I29*K29,4),""))</x:f>
-        <x:v>1.1305</x:v>
-      </x:c>
-      <x:c r="N29" s="7" t="n">
-        <x:v>2980</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N29" s="7"/>
       <x:c r="O29" s="1" t="str">
-        <x:v>Snapshot</x:v>
-      </x:c>
-      <x:c r="P29" s="4" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="Q29" s="1" t="str">
-        <x:v>5 days ago</x:v>
-      </x:c>
-      <x:c r="R29" s="1"/>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P29" s="4"/>
+      <x:c r="Q29" s="1"/>
+      <x:c r="R29" s="1" t="str">
+        <x:v>Price/stock not verified.</x:v>
+      </x:c>
       <x:c r="S29" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1332316.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C97376.html</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="96" customHeight="1">
       <x:c r="A30" s="22" t="str">
-        <x:v>C104, C105, C107, C140, C141, C142, C150, C152, C153, C154</x:v>
+        <x:v>C6, C104, C105, C107, C140, C141, C142, C150, C152, C153, C154</x:v>
       </x:c>
       <x:c r="B30" s="22" t="str">
         <x:v>Charger / regulated-rail 22uF bulk capacitors</x:v>
@@ -1794,7 +1748,7 @@
         <x:v>C907991</x:v>
       </x:c>
       <x:c r="F30" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="1" t="n">
         <x:v>5</x:v>
@@ -1803,7 +1757,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D30,$F$11:$F$87),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D30,$F$11:$F$76),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1814,7 +1768,7 @@
       </x:c>
       <x:c r="L30" s="31" t="n">
         <x:f>IF(K30="","",ROUND(F30*K30,4))</x:f>
-        <x:v>2.543</x:v>
+        <x:v>2.7973</x:v>
       </x:c>
       <x:c r="M30" s="31" t="n">
         <x:f>IF(OR(K30="",I30="",N30=""),"",IF(N30&gt;=I30,ROUND(I30*K30,4),""))</x:f>
@@ -1863,7 +1817,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D31,$F$11:$F$87),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D31,$F$11:$F$76),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1901,49 +1855,49 @@
     </x:row>
     <x:row r="32" ht="36" customHeight="1">
       <x:c r="A32" s="25" t="str">
-        <x:v>C1, C3</x:v>
+        <x:v>C2</x:v>
       </x:c>
       <x:c r="B32" s="25" t="str">
-        <x:v>PD 1uF X7R 10V capacitors</x:v>
+        <x:v>TPS25730D CVBUS 4.7uF / 50V X7R 1210</x:v>
       </x:c>
       <x:c r="C32" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D32" s="25" t="str">
-        <x:v>CL21B105KBFNNNE</x:v>
+        <x:v>CL32B475KBUYNNE</x:v>
       </x:c>
       <x:c r="E32" s="25" t="str">
-        <x:v>C28323</x:v>
+        <x:v>C170099</x:v>
       </x:c>
       <x:c r="F32" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D32,$F$11:$F$87),G32)/H32,0)*H32))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D32,$F$11:$F$76),G32)/H32,0)*H32))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K32" s="26" t="n">
-        <x:v>0.0403</x:v>
+        <x:v>0.1367</x:v>
       </x:c>
       <x:c r="L32" s="27" t="n">
         <x:f>IF(K32="","",ROUND(F32*K32,4))</x:f>
-        <x:v>0.0806</x:v>
+        <x:v>0.1367</x:v>
       </x:c>
       <x:c r="M32" s="27" t="n">
         <x:f>IF(OR(K32="",I32="",N32=""),"",IF(N32&gt;=I32,ROUND(I32*K32,4),""))</x:f>
-        <x:v>0.403</x:v>
+        <x:v>0.6835</x:v>
       </x:c>
       <x:c r="N32" t="n">
-        <x:v>1363910</x:v>
+        <x:v>57880</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>Listing snapshot</x:v>
@@ -1954,56 +1908,58 @@
       <x:c r="Q32" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R32"/>
+      <x:c r="R32" t="str">
+        <x:v>Alt: GRM32ER71H475KA88L C86052</x:v>
+      </x:c>
       <x:c r="S32" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C170099.html</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C2</x:v>
+        <x:v>C184</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
-        <x:v>100nF / 50V capacitor</x:v>
+        <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
       </x:c>
       <x:c r="C33" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D33" s="25" t="str">
-        <x:v>CL21B104KBCNNNC</x:v>
+        <x:v>CL21B105KBFNNNE</x:v>
       </x:c>
       <x:c r="E33" s="25" t="str">
-        <x:v>C1711</x:v>
+        <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D33,$F$11:$F$87),G33)/H33,0)*H33))</x:f>
-        <x:v>20</x:v>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D33,$F$11:$F$76),G33)/H33,0)*H33))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J33" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K33" s="26" t="n">
-        <x:v>0.0159</x:v>
+        <x:v>0.0403</x:v>
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.0159</x:v>
+        <x:v>0.0403</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
-        <x:v>0.318</x:v>
+        <x:v>0.403</x:v>
       </x:c>
       <x:c r="N33" t="n">
-        <x:v>854600</x:v>
+        <x:v>1363910</x:v>
       </x:c>
       <x:c r="O33" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2014,29 +1970,31 @@
       <x:c r="Q33" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R33"/>
+      <x:c r="R33" t="str">
+        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven.</x:v>
+      </x:c>
       <x:c r="S33" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1711.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="25" t="str">
-        <x:v>C4, C6, C180</x:v>
+        <x:v>C5</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
-        <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
+        <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
       </x:c>
       <x:c r="C34" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D34" s="25" t="str">
-        <x:v>CL21B105KBFNNNE</x:v>
+        <x:v>CL31B475KBHNNNE</x:v>
       </x:c>
       <x:c r="E34" s="25" t="str">
-        <x:v>C28323</x:v>
+        <x:v>C51205</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>10</x:v>
@@ -2045,24 +2003,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D34,$F$11:$F$87),G34)/H34,0)*H34))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D34,$F$11:$F$76),G34)/H34,0)*H34))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K34" s="26" t="n">
-        <x:v>0.0403</x:v>
+        <x:v>0.0759</x:v>
       </x:c>
       <x:c r="L34" s="27" t="n">
         <x:f>IF(K34="","",ROUND(F34*K34,4))</x:f>
-        <x:v>0.1209</x:v>
-      </x:c>
-      <x:c r="M34" s="27" t="str">
+        <x:v>0.0759</x:v>
+      </x:c>
+      <x:c r="M34" s="27" t="n">
         <x:f>IF(OR(K34="",I34="",N34=""),"",IF(N34&gt;=I34,ROUND(I34*K34,4),""))</x:f>
+        <x:v>0.759</x:v>
       </x:c>
       <x:c r="N34" t="n">
-        <x:v>1363910</x:v>
+        <x:v>302170</x:v>
       </x:c>
       <x:c r="O34" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2075,174 +2034,126 @@
       </x:c>
       <x:c r="R34"/>
       <x:c r="S34" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C51205.html</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="36" customHeight="1">
       <x:c r="A35" s="25" t="str">
-        <x:v>C5</x:v>
+        <x:v>R10</x:v>
       </x:c>
       <x:c r="B35" s="25" t="str">
-        <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
-      </x:c>
-      <x:c r="C35" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D35" s="25" t="str">
-        <x:v>CL31B475KBHNNNE</x:v>
-      </x:c>
-      <x:c r="E35" s="25" t="str">
-        <x:v>C51205</x:v>
-      </x:c>
+        <x:v>PD 200k 1% resistor (MPN open)</x:v>
+      </x:c>
+      <x:c r="C35" s="25"/>
+      <x:c r="D35" s="25"/>
+      <x:c r="E35" s="25"/>
       <x:c r="F35" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G35" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H35" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D35,$F$11:$F$87),G35)/H35,0)*H35))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J35" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K35" s="26" t="n">
-        <x:v>0.0759</x:v>
-      </x:c>
-      <x:c r="L35" s="27" t="n">
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+      <x:c r="I35" t="str">
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D35,$F$11:$F$76),G35)/H35,0)*H35))</x:f>
+      </x:c>
+      <x:c r="J35"/>
+      <x:c r="K35" s="26"/>
+      <x:c r="L35" s="27" t="str">
         <x:f>IF(K35="","",ROUND(F35*K35,4))</x:f>
-        <x:v>0.0759</x:v>
-      </x:c>
-      <x:c r="M35" s="27" t="n">
+      </x:c>
+      <x:c r="M35" s="27" t="str">
         <x:f>IF(OR(K35="",I35="",N35=""),"",IF(N35&gt;=I35,ROUND(I35*K35,4),""))</x:f>
-        <x:v>0.759</x:v>
-      </x:c>
-      <x:c r="N35" t="n">
-        <x:v>302170</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N35"/>
       <x:c r="O35" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P35" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q35" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R35"/>
-      <x:c r="S35" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C51205.html</x:v>
-      </x:c>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P35" s="16"/>
+      <x:c r="Q35"/>
+      <x:c r="R35" t="str">
+        <x:v>Sheet value 200k 1%; MPN/LCSC unselected.</x:v>
+      </x:c>
+      <x:c r="S35"/>
     </x:row>
     <x:row r="36" ht="36" customHeight="1">
       <x:c r="A36" s="25" t="str">
-        <x:v>R1</x:v>
+        <x:v>J4</x:v>
       </x:c>
       <x:c r="B36" s="25" t="str">
-        <x:v>PD 470R resistor</x:v>
-      </x:c>
-      <x:c r="C36" s="25" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D36" s="25" t="str">
-        <x:v>RC0603FR-07470RL</x:v>
-      </x:c>
-      <x:c r="E36" s="25" t="str">
-        <x:v>C114669</x:v>
-      </x:c>
+        <x:v>PD I2C service header</x:v>
+      </x:c>
+      <x:c r="C36" s="25"/>
+      <x:c r="D36" s="25"/>
+      <x:c r="E36" s="25"/>
       <x:c r="F36" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G36" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H36" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I36" t="n">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D36,$F$11:$F$87),G36)/H36,0)*H36))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J36" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K36" s="26" t="n">
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="L36" s="27" t="n">
+      <x:c r="G36"/>
+      <x:c r="H36"/>
+      <x:c r="I36" t="str">
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D36,$F$11:$F$76),G36)/H36,0)*H36))</x:f>
+      </x:c>
+      <x:c r="J36"/>
+      <x:c r="K36" s="26"/>
+      <x:c r="L36" s="27" t="str">
         <x:f>IF(K36="","",ROUND(F36*K36,4))</x:f>
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="M36" s="27" t="n">
+      </x:c>
+      <x:c r="M36" s="27" t="str">
         <x:f>IF(OR(K36="",I36="",N36=""),"",IF(N36&gt;=I36,ROUND(I36*K36,4),""))</x:f>
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="N36" t="n">
-        <x:v>1090800</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N36"/>
       <x:c r="O36" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P36" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q36" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>MPN open</x:v>
+      </x:c>
+      <x:c r="P36" s="16"/>
+      <x:c r="Q36"/>
       <x:c r="R36"/>
-      <x:c r="S36" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114669.html</x:v>
-      </x:c>
+      <x:c r="S36"/>
     </x:row>
     <x:row r="37" ht="36" customHeight="1">
       <x:c r="A37" s="25" t="str">
-        <x:v>R2</x:v>
+        <x:v>C100, C101, C108, C111, C112</x:v>
       </x:c>
       <x:c r="B37" s="25" t="str">
-        <x:v>1k resistor</x:v>
+        <x:v>BQ25792 VBUS/PMID 10uF / 50V X7R 1210 bank</x:v>
       </x:c>
       <x:c r="C37" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D37" s="25" t="str">
-        <x:v>RC0603FR-071KL</x:v>
+        <x:v>CL32B106KBJNNNE</x:v>
       </x:c>
       <x:c r="E37" s="25" t="str">
-        <x:v>C22548</x:v>
+        <x:v>C138687</x:v>
       </x:c>
       <x:c r="F37" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D37,$F$11:$F$87),G37)/H37,0)*H37))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D37,$F$11:$F$76),G37)/H37,0)*H37))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="26" t="n">
-        <x:v>0.0037</x:v>
+        <x:v>0.1571</x:v>
       </x:c>
       <x:c r="L37" s="27" t="n">
         <x:f>IF(K37="","",ROUND(F37*K37,4))</x:f>
-        <x:v>0.0037</x:v>
+        <x:v>0.7855</x:v>
       </x:c>
       <x:c r="M37" s="27" t="n">
         <x:f>IF(OR(K37="",I37="",N37=""),"",IF(N37&gt;=I37,ROUND(I37*K37,4),""))</x:f>
-        <x:v>0.37</x:v>
+        <x:v>0.7855</x:v>
       </x:c>
       <x:c r="N37" t="n">
-        <x:v>10309000</x:v>
+        <x:v>183897</x:v>
       </x:c>
       <x:c r="O37" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2253,56 +2164,58 @@
       <x:c r="Q37" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R37"/>
+      <x:c r="R37" t="str">
+        <x:v>Review snapshot 2026-10-05; effective capacitance at bias per bq25792 ceramic review.</x:v>
+      </x:c>
       <x:c r="S37" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C22548.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138687.html</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="25" t="str">
-        <x:v>R6, R9</x:v>
+        <x:v>C102, C109, C181, C185</x:v>
       </x:c>
       <x:c r="B38" s="25" t="str">
-        <x:v>PD 4.7k resistors</x:v>
+        <x:v>10uF / 10V X7R 0805 capacitors (charger REGN/PD CVIN_3V3)</x:v>
       </x:c>
       <x:c r="C38" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D38" s="25" t="str">
-        <x:v>RC0603FR-074K7L</x:v>
+        <x:v>CL21B106KPQNNNE</x:v>
       </x:c>
       <x:c r="E38" s="25" t="str">
-        <x:v>C99782</x:v>
+        <x:v>C32635</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D38,$F$11:$F$87),G38)/H38,0)*H38))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D38,$F$11:$F$76),G38)/H38,0)*H38))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J38" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K38" s="26" t="n">
-        <x:v>0.0011</x:v>
+        <x:v>0.093</x:v>
       </x:c>
       <x:c r="L38" s="27" t="n">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v>0.0022</x:v>
+        <x:v>0.372</x:v>
       </x:c>
       <x:c r="M38" s="27" t="n">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
-        <x:v>0.11</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="N38" t="n">
-        <x:v>1575400</x:v>
+        <x:v>230700</x:v>
       </x:c>
       <x:c r="O38" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2315,54 +2228,54 @@
       </x:c>
       <x:c r="R38"/>
       <x:c r="S38" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C99782.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="25" t="str">
-        <x:v>R10, R55</x:v>
+        <x:v>C103, C110</x:v>
       </x:c>
       <x:c r="B39" s="25" t="str">
-        <x:v>PD 100k resistors</x:v>
+        <x:v>47nF X7R / 50V bootstrap capacitors</x:v>
       </x:c>
       <x:c r="C39" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D39" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>CC0603KRX7R9BB473</x:v>
       </x:c>
       <x:c r="E39" s="25" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C107093</x:v>
       </x:c>
       <x:c r="F39" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D39,$F$11:$F$87),G39)/H39,0)*H39))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D39,$F$11:$F$76),G39)/H39,0)*H39))</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K39" s="26" t="n">
-        <x:v>0.0036</x:v>
+        <x:v>0.0077</x:v>
       </x:c>
       <x:c r="L39" s="27" t="n">
         <x:f>IF(K39="","",ROUND(F39*K39,4))</x:f>
-        <x:v>0.0072</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
       <x:c r="M39" s="27" t="n">
         <x:f>IF(OR(K39="",I39="",N39=""),"",IF(N39&gt;=I39,ROUND(I39*K39,4),""))</x:f>
-        <x:v>0.36</x:v>
+        <x:v>0.385</x:v>
       </x:c>
       <x:c r="N39" t="n">
-        <x:v>7813400</x:v>
+        <x:v>1537650</x:v>
       </x:c>
       <x:c r="O39" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2375,27 +2288,27 @@
       </x:c>
       <x:c r="R39"/>
       <x:c r="S39" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C107093.html</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="36" customHeight="1">
       <x:c r="A40" s="25" t="str">
-        <x:v>R11</x:v>
+        <x:v>C113, C114, C115</x:v>
       </x:c>
       <x:c r="B40" s="25" t="str">
-        <x:v>PD 22k resistor</x:v>
+        <x:v>BQ25792 VBUS/PMID/SYS 100nF/50V X7R 0402 bypass</x:v>
       </x:c>
       <x:c r="C40" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D40" s="25" t="str">
-        <x:v>RC0603FR-0722KL</x:v>
+        <x:v>GRM155R71H104KE14D</x:v>
       </x:c>
       <x:c r="E40" s="25" t="str">
-        <x:v>C114065</x:v>
+        <x:v>C77020</x:v>
       </x:c>
       <x:c r="F40" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G40" t="n">
         <x:v>100</x:v>
@@ -2404,25 +2317,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D40,$F$11:$F$87),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D40,$F$11:$F$76),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K40" s="26" t="n">
-        <x:v>0.0017</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="L40" s="27" t="n">
         <x:f>IF(K40="","",ROUND(F40*K40,4))</x:f>
-        <x:v>0.0017</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="M40" s="27" t="n">
         <x:f>IF(OR(K40="",I40="",N40=""),"",IF(N40&gt;=I40,ROUND(I40*K40,4),""))</x:f>
-        <x:v>0.17</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="N40" t="n">
-        <x:v>644600</x:v>
+        <x:v>777000</x:v>
       </x:c>
       <x:c r="O40" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2433,56 +2346,58 @@
       <x:c r="Q40" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R40"/>
+      <x:c r="R40" t="str">
+        <x:v>Footprint DesktopSpeaker:PD_C_0402 (no 3D model)</x:v>
+      </x:c>
       <x:c r="S40" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114065.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="36" customHeight="1">
       <x:c r="A41" s="25" t="str">
-        <x:v>R13</x:v>
+        <x:v>D7</x:v>
       </x:c>
       <x:c r="B41" s="25" t="str">
-        <x:v>PD 100R resistor</x:v>
+        <x:v>TPS25730D VBUS-to-GND Schottky</x:v>
       </x:c>
       <x:c r="C41" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Diodes Incorporated</x:v>
       </x:c>
       <x:c r="D41" s="25" t="str">
-        <x:v>RC0603FR-07100RL</x:v>
+        <x:v>1N5819HW-7-F</x:v>
       </x:c>
       <x:c r="E41" s="25" t="str">
-        <x:v>C105588</x:v>
+        <x:v>C82544</x:v>
       </x:c>
       <x:c r="F41" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D41,$F$11:$F$87),G41)/H41,0)*H41))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D41,$F$11:$F$76),G41)/H41,0)*H41))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K41" s="26" t="n">
-        <x:v>0.0024</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="L41" s="27" t="n">
         <x:f>IF(K41="","",ROUND(F41*K41,4))</x:f>
-        <x:v>0.0024</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="M41" s="27" t="n">
         <x:f>IF(OR(K41="",I41="",N41=""),"",IF(N41&gt;=I41,ROUND(I41*K41,4),""))</x:f>
-        <x:v>0.24</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="N41" t="n">
-        <x:v>2943700</x:v>
+        <x:v>137330</x:v>
       </x:c>
       <x:c r="O41" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2493,153 +2408,154 @@
       <x:c r="Q41" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R41"/>
+      <x:c r="R41" t="str">
+        <x:v>40V/1A SOD-123; leakage not bench-checked; alt B5819W SL C8598</x:v>
+      </x:c>
       <x:c r="S41" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105588.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C82544.html</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="36" customHeight="1">
       <x:c r="A42" s="25" t="str">
-        <x:v>D4</x:v>
+        <x:v>C182, C183</x:v>
       </x:c>
       <x:c r="B42" s="25" t="str">
-        <x:v>PD support diode; 1N4148W type</x:v>
-      </x:c>
-      <x:c r="C42" s="25" t="str">
-        <x:v>Diodes Incorporated</x:v>
-      </x:c>
-      <x:c r="D42" s="25" t="str">
-        <x:v>1N4148W-7-F</x:v>
-      </x:c>
-      <x:c r="E42" s="25" t="str">
-        <x:v>C83528</x:v>
-      </x:c>
+        <x:v>TPS25730D CC1/CC2 330pF C0G filters (MPN open)</x:v>
+      </x:c>
+      <x:c r="C42" s="25"/>
+      <x:c r="D42" s="25"/>
+      <x:c r="E42" s="25"/>
       <x:c r="F42" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G42" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H42" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D42,$F$11:$F$87),G42)/H42,0)*H42))</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J42" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K42" s="26" t="n">
-        <x:v>0.0293</x:v>
-      </x:c>
-      <x:c r="L42" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
+      <x:c r="I42" t="str">
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D42,$F$11:$F$76),G42)/H42,0)*H42))</x:f>
+      </x:c>
+      <x:c r="J42"/>
+      <x:c r="K42" s="26"/>
+      <x:c r="L42" s="27" t="str">
         <x:f>IF(K42="","",ROUND(F42*K42,4))</x:f>
-        <x:v>0.0293</x:v>
-      </x:c>
-      <x:c r="M42" s="27" t="n">
+      </x:c>
+      <x:c r="M42" s="27" t="str">
         <x:f>IF(OR(K42="",I42="",N42=""),"",IF(N42&gt;=I42,ROUND(I42*K42,4),""))</x:f>
-        <x:v>0.586</x:v>
-      </x:c>
-      <x:c r="N42" t="n">
-        <x:v>231360</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N42"/>
       <x:c r="O42" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P42" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q42" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P42" s="16"/>
+      <x:c r="Q42"/>
       <x:c r="R42" t="str">
-        <x:v>In stock 231,360; $0.0293 at MOQ 20. Datasheet: 100V VRRM, SOD-123, 300mA, low leakage.</x:v>
-      </x:c>
-      <x:c r="S42" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C83528.html</x:v>
-      </x:c>
+        <x:v>Unselected 0603 C0G part.</x:v>
+      </x:c>
+      <x:c r="S42"/>
     </x:row>
     <x:row r="43" ht="36" customHeight="1">
       <x:c r="A43" s="25" t="str">
-        <x:v>J4</x:v>
+        <x:v>C106</x:v>
       </x:c>
       <x:c r="B43" s="25" t="str">
-        <x:v>PD I2C service header</x:v>
-      </x:c>
-      <x:c r="C43" s="25"/>
-      <x:c r="D43" s="25"/>
-      <x:c r="E43" s="25"/>
+        <x:v>Charger BAT 22uF / 10V capacitor</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D43" s="25" t="str">
+        <x:v>GRM21BZ71A226ME15L</x:v>
+      </x:c>
+      <x:c r="E43" s="25" t="str">
+        <x:v>C907991</x:v>
+      </x:c>
       <x:c r="F43" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G43"/>
-      <x:c r="H43"/>
-      <x:c r="I43" t="str">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D43,$F$11:$F$87),G43)/H43,0)*H43))</x:f>
-      </x:c>
-      <x:c r="J43"/>
-      <x:c r="K43" s="26"/>
-      <x:c r="L43" s="27" t="str">
+      <x:c r="G43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D43,$F$11:$F$76),G43)/H43,0)*H43))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K43" s="26" t="n">
+        <x:v>0.2543</x:v>
+      </x:c>
+      <x:c r="L43" s="27" t="n">
         <x:f>IF(K43="","",ROUND(F43*K43,4))</x:f>
+        <x:v>0.2543</x:v>
       </x:c>
       <x:c r="M43" s="27" t="str">
         <x:f>IF(OR(K43="",I43="",N43=""),"",IF(N43&gt;=I43,ROUND(I43*K43,4),""))</x:f>
       </x:c>
-      <x:c r="N43"/>
+      <x:c r="N43" t="n">
+        <x:v>146915</x:v>
+      </x:c>
       <x:c r="O43" t="str">
-        <x:v>MPN open</x:v>
-      </x:c>
-      <x:c r="P43" s="16"/>
-      <x:c r="Q43"/>
+        <x:v>Selected; price/stock open</x:v>
+      </x:c>
+      <x:c r="P43" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
       <x:c r="R43"/>
-      <x:c r="S43"/>
+      <x:c r="S43" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="36" customHeight="1">
       <x:c r="A44" s="25" t="str">
-        <x:v>C100</x:v>
+        <x:v>R100</x:v>
       </x:c>
       <x:c r="B44" s="25" t="str">
-        <x:v>Charger 2.2uF / 25V capacitor</x:v>
+        <x:v>Charger 5.23k resistor</x:v>
       </x:c>
       <x:c r="C44" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>SAE</x:v>
       </x:c>
       <x:c r="D44" s="25" t="str">
-        <x:v>CL21B225KBYNNNE</x:v>
+        <x:v>1RC0603F5231</x:v>
       </x:c>
       <x:c r="E44" s="25" t="str">
-        <x:v>C2762602</x:v>
+        <x:v>C54531489</x:v>
       </x:c>
       <x:c r="F44" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D44,$F$11:$F$87),G44)/H44,0)*H44))</x:f>
-        <x:v>5</x:v>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D44,$F$11:$F$76),G44)/H44,0)*H44))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K44" s="26" t="n">
-        <x:v>0.1052</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="L44" s="27" t="n">
         <x:f>IF(K44="","",ROUND(F44*K44,4))</x:f>
-        <x:v>0.1052</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="M44" s="27" t="n">
         <x:f>IF(OR(K44="",I44="",N44=""),"",IF(N44&gt;=I44,ROUND(I44*K44,4),""))</x:f>
-        <x:v>0.526</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="N44" t="n">
-        <x:v>73810</x:v>
+        <x:v>9900</x:v>
       </x:c>
       <x:c r="O44" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2652,54 +2568,54 @@
       </x:c>
       <x:c r="R44"/>
       <x:c r="S44" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2762602.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C54531489.html</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="36" customHeight="1">
       <x:c r="A45" s="25" t="str">
-        <x:v>C101</x:v>
+        <x:v>R101</x:v>
       </x:c>
       <x:c r="B45" s="25" t="str">
-        <x:v>Charger PMID 22uF / 25V capacitor</x:v>
+        <x:v>Charger 30.1k resistor</x:v>
       </x:c>
       <x:c r="C45" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>SAE</x:v>
       </x:c>
       <x:c r="D45" s="25" t="str">
-        <x:v>CL32B226KAJNNNE</x:v>
+        <x:v>1RC0603F3012</x:v>
       </x:c>
       <x:c r="E45" s="25" t="str">
-        <x:v>C309062</x:v>
+        <x:v>C54531365</x:v>
       </x:c>
       <x:c r="F45" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D45,$F$11:$F$87),G45)/H45,0)*H45))</x:f>
-        <x:v>2</x:v>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D45,$F$11:$F$76),G45)/H45,0)*H45))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K45" s="26" t="n">
-        <x:v>0.3569</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="L45" s="27" t="n">
         <x:f>IF(K45="","",ROUND(F45*K45,4))</x:f>
-        <x:v>0.3569</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="M45" s="27" t="n">
         <x:f>IF(OR(K45="",I45="",N45=""),"",IF(N45&gt;=I45,ROUND(I45*K45,4),""))</x:f>
-        <x:v>0.7138</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="N45" t="n">
-        <x:v>96346</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="O45" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2712,54 +2628,54 @@
       </x:c>
       <x:c r="R45"/>
       <x:c r="S45" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C309062.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C54531365.html</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="36" customHeight="1">
       <x:c r="A46" s="25" t="str">
-        <x:v>C102</x:v>
+        <x:v>R102</x:v>
       </x:c>
       <x:c r="B46" s="25" t="str">
-        <x:v>Charger 10uF / 10V capacitor</x:v>
+        <x:v>Charger 4.7k resistor</x:v>
       </x:c>
       <x:c r="C46" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D46" s="25" t="str">
-        <x:v>CL21B106KPQNNNE</x:v>
+        <x:v>RC0603FR-074K7L</x:v>
       </x:c>
       <x:c r="E46" s="25" t="str">
-        <x:v>C32635</x:v>
+        <x:v>C99782</x:v>
       </x:c>
       <x:c r="F46" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H46" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D46,$F$11:$F$87),G46)/H46,0)*H46))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D46,$F$11:$F$76),G46)/H46,0)*H46))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K46" s="26" t="n">
-        <x:v>0.093</x:v>
+        <x:v>0.0011</x:v>
       </x:c>
       <x:c r="L46" s="27" t="n">
         <x:f>IF(K46="","",ROUND(F46*K46,4))</x:f>
-        <x:v>0.093</x:v>
+        <x:v>0.0011</x:v>
       </x:c>
       <x:c r="M46" s="27" t="n">
         <x:f>IF(OR(K46="",I46="",N46=""),"",IF(N46&gt;=I46,ROUND(I46*K46,4),""))</x:f>
-        <x:v>0.93</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="N46" t="n">
-        <x:v>230700</x:v>
+        <x:v>1575400</x:v>
       </x:c>
       <x:c r="O46" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2772,55 +2688,52 @@
       </x:c>
       <x:c r="R46"/>
       <x:c r="S46" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C99782.html</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="36" customHeight="1">
       <x:c r="A47" s="25" t="str">
-        <x:v>C103</x:v>
+        <x:v>R108</x:v>
       </x:c>
       <x:c r="B47" s="25" t="str">
-        <x:v>Charger 47nF X7R / 10V minimum bootstrap capacitor</x:v>
+        <x:v>Charger 180k threshold resistor</x:v>
       </x:c>
       <x:c r="C47" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D47" s="25" t="str">
-        <x:v>CC0603KRX7R9BB473</x:v>
+        <x:v>RC0603FR-07180KL</x:v>
       </x:c>
       <x:c r="E47" s="25" t="str">
-        <x:v>C107093</x:v>
+        <x:v>C123419</x:v>
       </x:c>
       <x:c r="F47" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H47" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D47,$F$11:$F$87),G47)/H47,0)*H47))</x:f>
-        <x:v>50</x:v>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D47,$F$11:$F$76),G47)/H47,0)*H47))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K47" s="26" t="n">
-        <x:v>0.0077</x:v>
+        <x:v>0.0012</x:v>
       </x:c>
       <x:c r="L47" s="27" t="n">
         <x:f>IF(K47="","",ROUND(F47*K47,4))</x:f>
-        <x:v>0.0077</x:v>
-      </x:c>
-      <x:c r="M47" s="27" t="n">
+        <x:v>0.0012</x:v>
+      </x:c>
+      <x:c r="M47" s="27" t="str">
         <x:f>IF(OR(K47="",I47="",N47=""),"",IF(N47&gt;=I47,ROUND(I47*K47,4),""))</x:f>
-        <x:v>0.385</x:v>
-      </x:c>
-      <x:c r="N47" t="n">
-        <x:v>1537650</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N47"/>
       <x:c r="O47" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
@@ -2830,60 +2743,59 @@
       <x:c r="Q47" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R47" t="str">
-        <x:v>In stock 1,537,650; $0.0077 at MOQ 50. Exact 47nF 50V X7R ±10%, 0603. Datasheet has no guaranteed DC-bias curve.</x:v>
-      </x:c>
+      <x:c r="R47"/>
       <x:c r="S47" t="str">
-        <x:v>https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603KRX7R9BB473_C107093.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="36" customHeight="1">
       <x:c r="A48" s="25" t="str">
-        <x:v>C106</x:v>
+        <x:v>R112</x:v>
       </x:c>
       <x:c r="B48" s="25" t="str">
-        <x:v>Charger BAT 22uF / 10V capacitor</x:v>
+        <x:v>Charger 100R resistor</x:v>
       </x:c>
       <x:c r="C48" s="25" t="str">
-        <x:v>Murata</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D48" s="25" t="str">
-        <x:v>GRM21BZ71A226ME15L</x:v>
+        <x:v>RC0603FR-07100RL</x:v>
       </x:c>
       <x:c r="E48" s="25" t="str">
-        <x:v>C907991</x:v>
+        <x:v>C105588</x:v>
       </x:c>
       <x:c r="F48" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H48" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D48,$F$11:$F$87),G48)/H48,0)*H48))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D48,$F$11:$F$76),G48)/H48,0)*H48))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K48" s="26" t="n">
-        <x:v>0.2543</x:v>
+        <x:v>0.0024</x:v>
       </x:c>
       <x:c r="L48" s="27" t="n">
         <x:f>IF(K48="","",ROUND(F48*K48,4))</x:f>
-        <x:v>0.2543</x:v>
-      </x:c>
-      <x:c r="M48" s="27" t="str">
+        <x:v>0.0024</x:v>
+      </x:c>
+      <x:c r="M48" s="27" t="n">
         <x:f>IF(OR(K48="",I48="",N48=""),"",IF(N48&gt;=I48,ROUND(I48*K48,4),""))</x:f>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="N48" t="n">
-        <x:v>146915</x:v>
+        <x:v>2943700</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>Selected; price/stock open</x:v>
+        <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P48" s="16" t="n">
         <x:v>46300</x:v>
@@ -2893,24 +2805,24 @@
       </x:c>
       <x:c r="R48"/>
       <x:c r="S48" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C105588.html</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="36" customHeight="1">
       <x:c r="A49" s="25" t="str">
-        <x:v>R100</x:v>
+        <x:v>R106</x:v>
       </x:c>
       <x:c r="B49" s="25" t="str">
-        <x:v>Charger 5.23k resistor</x:v>
+        <x:v>Charger INT pull-up 10k</x:v>
       </x:c>
       <x:c r="C49" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D49" s="25" t="str">
-        <x:v>1RC0603F5231</x:v>
+        <x:v>RC0603FR-0710KL</x:v>
       </x:c>
       <x:c r="E49" s="25" t="str">
-        <x:v>C54531489</x:v>
+        <x:v>C98220</x:v>
       </x:c>
       <x:c r="F49" s="25" t="n">
         <x:v>1</x:v>
@@ -2922,25 +2834,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D49,$F$11:$F$87),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D49,$F$11:$F$76),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K49" s="26" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.0035</x:v>
       </x:c>
       <x:c r="L49" s="27" t="n">
         <x:f>IF(K49="","",ROUND(F49*K49,4))</x:f>
-        <x:v>0.002</x:v>
+        <x:v>0.0035</x:v>
       </x:c>
       <x:c r="M49" s="27" t="n">
         <x:f>IF(OR(K49="",I49="",N49=""),"",IF(N49&gt;=I49,ROUND(I49*K49,4),""))</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="N49" t="n">
-        <x:v>9900</x:v>
+        <x:v>11102500</x:v>
       </x:c>
       <x:c r="O49" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2953,27 +2865,27 @@
       </x:c>
       <x:c r="R49"/>
       <x:c r="S49" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531489.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="25" t="str">
-        <x:v>R101</x:v>
+        <x:v>R11, R13, R14, R15, R18</x:v>
       </x:c>
       <x:c r="B50" s="25" t="str">
-        <x:v>Charger 30.1k resistor</x:v>
+        <x:v>TPS25730D 10k 1% resistors (CC/ADC, I2C pull-ups R14/R15, pin 36 R18)</x:v>
       </x:c>
       <x:c r="C50" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D50" s="25" t="str">
-        <x:v>1RC0603F3012</x:v>
+        <x:v>RC0603FR-0710KL</x:v>
       </x:c>
       <x:c r="E50" s="25" t="str">
-        <x:v>C54531365</x:v>
+        <x:v>C98220</x:v>
       </x:c>
       <x:c r="F50" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>100</x:v>
@@ -2982,25 +2894,24 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D50,$F$11:$F$87),G50)/H50,0)*H50))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D50,$F$11:$F$76),G50)/H50,0)*H50))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K50" s="26" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.0034</x:v>
       </x:c>
       <x:c r="L50" s="27" t="n">
         <x:f>IF(K50="","",ROUND(F50*K50,4))</x:f>
-        <x:v>0.002</x:v>
-      </x:c>
-      <x:c r="M50" s="27" t="n">
+        <x:v>0.017</x:v>
+      </x:c>
+      <x:c r="M50" s="27" t="str">
         <x:f>IF(OR(K50="",I50="",N50=""),"",IF(N50&gt;=I50,ROUND(I50*K50,4),""))</x:f>
-        <x:v>0.2</x:v>
       </x:c>
       <x:c r="N50" t="n">
-        <x:v>3700</x:v>
+        <x:v>7736700</x:v>
       </x:c>
       <x:c r="O50" t="str">
         <x:v>Listing snapshot</x:v>
@@ -3013,24 +2924,24 @@
       </x:c>
       <x:c r="R50"/>
       <x:c r="S50" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531365.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="36" customHeight="1">
       <x:c r="A51" s="25" t="str">
-        <x:v>R102</x:v>
+        <x:v>R107</x:v>
       </x:c>
       <x:c r="B51" s="25" t="str">
-        <x:v>Charger 220R ILIM resistor</x:v>
+        <x:v>Charger 100k resistor</x:v>
       </x:c>
       <x:c r="C51" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D51" s="25" t="str">
-        <x:v>RC0603FR-07220RL</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="E51" s="25" t="str">
-        <x:v>C107696</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="F51" s="25" t="n">
         <x:v>1</x:v>
@@ -3042,25 +2953,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D51,$F$11:$F$87),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D51,$F$11:$F$76),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K51" s="26" t="n">
-        <x:v>0.0012</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="L51" s="27" t="n">
         <x:f>IF(K51="","",ROUND(F51*K51,4))</x:f>
-        <x:v>0.0012</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="M51" s="27" t="n">
         <x:f>IF(OR(K51="",I51="",N51=""),"",IF(N51&gt;=I51,ROUND(I51*K51,4),""))</x:f>
-        <x:v>0.12</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="N51" t="n">
-        <x:v>484600</x:v>
+        <x:v>7813400</x:v>
       </x:c>
       <x:c r="O51" t="str">
         <x:v>Listing snapshot</x:v>
@@ -3073,27 +2984,27 @@
       </x:c>
       <x:c r="R51"/>
       <x:c r="S51" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C107696.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="36" customHeight="1">
       <x:c r="A52" s="25" t="str">
-        <x:v>R103, R106</x:v>
+        <x:v>R12, R16, R17</x:v>
       </x:c>
       <x:c r="B52" s="25" t="str">
-        <x:v>Charger 10k resistors</x:v>
+        <x:v>TPS25730D 100k pull-ups / VIN_3V3 resistor</x:v>
       </x:c>
       <x:c r="C52" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D52" s="25" t="str">
-        <x:v>RC0603FR-0710KL</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="E52" s="25" t="str">
-        <x:v>C98220</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="F52" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G52" t="n">
         <x:v>100</x:v>
@@ -3102,25 +3013,24 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D52,$F$11:$F$87),G52)/H52,0)*H52))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D52,$F$11:$F$76),G52)/H52,0)*H52))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K52" s="26" t="n">
-        <x:v>0.0035</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="L52" s="27" t="n">
         <x:f>IF(K52="","",ROUND(F52*K52,4))</x:f>
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="M52" s="27" t="n">
+        <x:v>0.0108</x:v>
+      </x:c>
+      <x:c r="M52" s="27" t="str">
         <x:f>IF(OR(K52="",I52="",N52=""),"",IF(N52&gt;=I52,ROUND(I52*K52,4),""))</x:f>
-        <x:v>0.35</x:v>
       </x:c>
       <x:c r="N52" t="n">
-        <x:v>11102500</x:v>
+        <x:v>7813400</x:v>
       </x:c>
       <x:c r="O52" t="str">
         <x:v>Listing snapshot</x:v>
@@ -3133,15 +3043,15 @@
       </x:c>
       <x:c r="R52"/>
       <x:c r="S52" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="36" customHeight="1">
       <x:c r="A53" s="25" t="str">
-        <x:v>R107</x:v>
+        <x:v>R103, R109, R110, R111</x:v>
       </x:c>
       <x:c r="B53" s="25" t="str">
-        <x:v>Charger 100k resistor</x:v>
+        <x:v>Charger 100k pull-up/down resistors</x:v>
       </x:c>
       <x:c r="C53" s="25" t="str">
         <x:v>YAGEO</x:v>
@@ -3153,7 +3063,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F53" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G53" t="n">
         <x:v>100</x:v>
@@ -3162,7 +3072,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D53,$F$11:$F$87),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D53,$F$11:$F$76),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3173,7 +3083,7 @@
       </x:c>
       <x:c r="L53" s="27" t="n">
         <x:f>IF(K53="","",ROUND(F53*K53,4))</x:f>
-        <x:v>0.0036</x:v>
+        <x:v>0.0144</x:v>
       </x:c>
       <x:c r="M53" s="27" t="str">
         <x:f>IF(OR(K53="",I53="",N53=""),"",IF(N53&gt;=I53,ROUND(I53*K53,4),""))</x:f>
@@ -3211,7 +3121,7 @@
       <x:c r="G54"/>
       <x:c r="H54"/>
       <x:c r="I54" t="str">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D54,$F$11:$F$87),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D54,$F$11:$F$76),G54)/H54,0)*H54))</x:f>
       </x:c>
       <x:c r="J54"/>
       <x:c r="K54" s="26"/>
@@ -3246,7 +3156,7 @@
       <x:c r="G55"/>
       <x:c r="H55"/>
       <x:c r="I55" t="str">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D55,$F$11:$F$87),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D55,$F$11:$F$76),G55)/H55,0)*H55))</x:f>
       </x:c>
       <x:c r="J55"/>
       <x:c r="K55" s="26"/>
@@ -3281,7 +3191,7 @@
       <x:c r="G56"/>
       <x:c r="H56"/>
       <x:c r="I56" t="str">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D56,$F$11:$F$87),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D56,$F$11:$F$76),G56)/H56,0)*H56))</x:f>
       </x:c>
       <x:c r="J56"/>
       <x:c r="K56" s="26"/>
@@ -3316,7 +3226,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D57,$F$11:$F$87),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D57,$F$11:$F$76),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3361,7 +3271,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D58,$F$11:$F$87),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D58,$F$11:$F$76),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3421,7 +3331,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D59,$F$11:$F$87),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D59,$F$11:$F$76),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3481,7 +3391,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D60,$F$11:$F$87),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D60,$F$11:$F$76),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3540,7 +3450,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D61,$F$11:$F$87),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D61,$F$11:$F$76),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3600,7 +3510,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D62,$F$11:$F$87),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D62,$F$11:$F$76),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3659,7 +3569,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D63,$F$11:$F$87),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D63,$F$11:$F$76),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3721,7 +3631,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D64,$F$11:$F$87),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D64,$F$11:$F$76),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3756,213 +3666,233 @@
     </x:row>
     <x:row r="65" ht="36" customHeight="1">
       <x:c r="A65" s="25" t="str">
-        <x:v>U18</x:v>
+        <x:v>R140</x:v>
       </x:c>
       <x:c r="B65" s="25" t="str">
-        <x:v>USB input hardware overvoltage cutoff</x:v>
+        <x:v>78.7k 1% codec feedback divider resistor</x:v>
       </x:c>
       <x:c r="C65" s="25" t="str">
-        <x:v>TI</x:v>
+        <x:v>SAE</x:v>
       </x:c>
       <x:c r="D65" s="25" t="str">
-        <x:v>TPS26600PWPR</x:v>
+        <x:v>1RC0603F7872</x:v>
       </x:c>
       <x:c r="E65" s="25" t="str">
-        <x:v>C544399</x:v>
+        <x:v>C54531588</x:v>
       </x:c>
       <x:c r="F65" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H65" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D65,$F$11:$F$87),G65)/H65,0)*H65))</x:f>
-        <x:v>1</x:v>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D65,$F$11:$F$76),G65)/H65,0)*H65))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K65" s="26" t="n">
-        <x:v>1.6339</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="L65" s="27" t="n">
         <x:f>IF(K65="","",ROUND(F65*K65,4))</x:f>
-        <x:v>1.6339</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="M65" s="27" t="n">
         <x:f>IF(OR(K65="",I65="",N65=""),"",IF(N65&gt;=I65,ROUND(I65*K65,4),""))</x:f>
-        <x:v>1.6339</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="N65" t="n">
-        <x:v>4931</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="O65" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P65" s="16" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q65" t="str">
-        <x:v>2026-10-04</x:v>
-      </x:c>
-      <x:c r="R65"/>
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R65" t="str">
+        <x:v>In stock 4,700; tier $0.002 at 100+. Datasheet confirms 0603, ±1%, ±100ppm/°C and −55 to +155°C.</x:v>
+      </x:c>
       <x:c r="S65" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C544399.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C54531588.html</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="36" customHeight="1">
       <x:c r="A66" s="25" t="str">
-        <x:v>D7, D9</x:v>
+        <x:v>R141</x:v>
       </x:c>
       <x:c r="B66" s="25" t="str">
-        <x:v>PMOS gate 12V clamp</x:v>
+        <x:v>9.1k 1% codec feedback divider resistor</x:v>
       </x:c>
       <x:c r="C66" s="25" t="str">
-        <x:v>Diodes Incorporated</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D66" s="25" t="str">
-        <x:v>BZT52C12-7-F</x:v>
+        <x:v>RC0603FR-079K1L</x:v>
       </x:c>
       <x:c r="E66" s="25" t="str">
-        <x:v>C124196</x:v>
+        <x:v>C114639</x:v>
       </x:c>
       <x:c r="F66" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D66,$F$11:$F$87),G66)/H66,0)*H66))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D66,$F$11:$F$76),G66)/H66,0)*H66))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
-        <x:v>10</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K66" s="26" t="n">
-        <x:v>0.0771</x:v>
+        <x:v>0.0034</x:v>
       </x:c>
       <x:c r="L66" s="27" t="n">
         <x:f>IF(K66="","",ROUND(F66*K66,4))</x:f>
-        <x:v>0.1542</x:v>
+        <x:v>0.0034</x:v>
       </x:c>
       <x:c r="M66" s="27" t="n">
         <x:f>IF(OR(K66="",I66="",N66=""),"",IF(N66&gt;=I66,ROUND(I66*K66,4),""))</x:f>
-        <x:v>0.771</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="N66" t="n">
-        <x:v>26150</x:v>
+        <x:v>296500</x:v>
       </x:c>
       <x:c r="O66" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P66" s="16" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q66" t="str">
-        <x:v>2026-10-04</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R66" t="str">
-        <x:v>D7 and D9 use the same clamp; retained the existing 2026-10-04 listing snapshot price and MOQ.</x:v>
+        <x:v>In stock 296,500; tier $0.0034 at 100+. 0603, ±1%, ±100ppm/°C, −55 to +155°C. Distinct MPN from R151.</x:v>
       </x:c>
       <x:c r="S66" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C124196.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C114639.html</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="36" customHeight="1">
       <x:c r="A67" s="25" t="str">
-        <x:v>D8</x:v>
+        <x:v>R150</x:v>
       </x:c>
       <x:c r="B67" s="25" t="str">
-        <x:v>Protected VBUS clamp; manufacturer-specific</x:v>
+        <x:v>604k 1% feedback resistor</x:v>
       </x:c>
       <x:c r="C67" s="25" t="str">
-        <x:v>Taiwan Semiconductor</x:v>
+        <x:v>FOJAN</x:v>
       </x:c>
       <x:c r="D67" s="25" t="str">
-        <x:v>SMA6J10A M2G</x:v>
+        <x:v>FRC0603F6043TS</x:v>
       </x:c>
       <x:c r="E67" s="25" t="str">
-        <x:v>C2444429</x:v>
+        <x:v>C2933246</x:v>
       </x:c>
       <x:c r="F67" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G67"/>
-      <x:c r="H67"/>
-      <x:c r="I67" t="str">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D67,$F$11:$F$87),G67)/H67,0)*H67))</x:f>
-      </x:c>
-      <x:c r="J67"/>
-      <x:c r="K67" s="26"/>
-      <x:c r="L67" s="27" t="str">
+      <x:c r="G67" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H67" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I67" t="n">
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D67,$F$11:$F$76),G67)/H67,0)*H67))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J67" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K67" s="26" t="n">
+        <x:v>0.0025</x:v>
+      </x:c>
+      <x:c r="L67" s="27" t="n">
         <x:f>IF(K67="","",ROUND(F67*K67,4))</x:f>
-      </x:c>
-      <x:c r="M67" s="27" t="str">
+        <x:v>0.0025</x:v>
+      </x:c>
+      <x:c r="M67" s="27" t="n">
         <x:f>IF(OR(K67="",I67="",N67=""),"",IF(N67&gt;=I67,ROUND(I67*K67,4),""))</x:f>
-      </x:c>
-      <x:c r="N67"/>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="N67" t="n">
+        <x:v>54400</x:v>
+      </x:c>
       <x:c r="O67" t="str">
-        <x:v>Stock/price unverified</x:v>
-      </x:c>
-      <x:c r="P67" s="16"/>
-      <x:c r="Q67"/>
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P67" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q67" t="str">
+        <x:v>2026-10-05</x:v>
+      </x:c>
       <x:c r="R67"/>
       <x:c r="S67" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2444429.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2933246.html</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="36" customHeight="1">
       <x:c r="A68" s="25" t="str">
-        <x:v>C10</x:v>
+        <x:v>R151</x:v>
       </x:c>
       <x:c r="B68" s="25" t="str">
-        <x:v>100nF / 25V capacitor</x:v>
+        <x:v>91k 1% feedback resistor</x:v>
       </x:c>
       <x:c r="C68" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D68" s="25" t="str">
-        <x:v>CL21B104KBCNNNC</x:v>
+        <x:v>AC0603FR-0791KL</x:v>
       </x:c>
       <x:c r="E68" s="25" t="str">
-        <x:v>C1711</x:v>
+        <x:v>C228098</x:v>
       </x:c>
       <x:c r="F68" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G68" t="n">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H68" t="n">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D68,$F$11:$F$87),G68)/H68,0)*H68))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D68,$F$11:$F$76),G68)/H68,0)*H68))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K68" s="26" t="n">
-        <x:v>0.0159</x:v>
+        <x:v>0.0061</x:v>
       </x:c>
       <x:c r="L68" s="27" t="n">
         <x:f>IF(K68="","",ROUND(F68*K68,4))</x:f>
-        <x:v>0.0159</x:v>
-      </x:c>
-      <x:c r="M68" s="27" t="str">
+        <x:v>0.0061</x:v>
+      </x:c>
+      <x:c r="M68" s="27" t="n">
         <x:f>IF(OR(K68="",I68="",N68=""),"",IF(N68&gt;=I68,ROUND(I68*K68,4),""))</x:f>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="N68" t="n">
-        <x:v>854600</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="O68" t="str">
         <x:v>Listing snapshot</x:v>
@@ -3975,54 +3905,53 @@
       </x:c>
       <x:c r="R68"/>
       <x:c r="S68" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1711.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C228098.html</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R4</x:v>
+        <x:v>R152, R153, R154</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
-        <x:v>3.3k1206 discharge resistor; thermal/pulse qualification open</x:v>
+        <x:v>100k EN / MODE / bleeder resistors</x:v>
       </x:c>
       <x:c r="C69" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D69" s="25" t="str">
-        <x:v>RC1206FR-073K3L</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="E69" s="25" t="str">
-        <x:v>C137292</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G69" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H69" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D69,$F$11:$F$87),G69)/H69,0)*H69))</x:f>
-        <x:v>50</x:v>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D69,$F$11:$F$76),G69)/H69,0)*H69))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K69" s="26" t="n">
-        <x:v>0.0104</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0104</x:v>
-      </x:c>
-      <x:c r="M69" s="27" t="n">
+        <x:v>0.0108</x:v>
+      </x:c>
+      <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
-        <x:v>0.52</x:v>
       </x:c>
       <x:c r="N69" t="n">
-        <x:v>264700</x:v>
+        <x:v>7813400</x:v>
       </x:c>
       <x:c r="O69" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4035,24 +3964,24 @@
       </x:c>
       <x:c r="R69"/>
       <x:c r="S69" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C137292.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="36" customHeight="1">
       <x:c r="A70" s="25" t="str">
-        <x:v>R140</x:v>
+        <x:v>R142</x:v>
       </x:c>
       <x:c r="B70" s="25" t="str">
-        <x:v>78.7k 1% codec feedback divider resistor</x:v>
+        <x:v>100k EN pulldown resistor</x:v>
       </x:c>
       <x:c r="C70" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D70" s="25" t="str">
-        <x:v>1RC0603F7872</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="E70" s="25" t="str">
-        <x:v>C54531588</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="F70" s="25" t="n">
         <x:v>1</x:v>
@@ -4064,25 +3993,24 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D70,$F$11:$F$87),G70)/H70,0)*H70))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D70,$F$11:$F$76),G70)/H70,0)*H70))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K70" s="26" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="L70" s="27" t="n">
         <x:f>IF(K70="","",ROUND(F70*K70,4))</x:f>
-        <x:v>0.002</x:v>
-      </x:c>
-      <x:c r="M70" s="27" t="n">
+        <x:v>0.0036</x:v>
+      </x:c>
+      <x:c r="M70" s="27" t="str">
         <x:f>IF(OR(K70="",I70="",N70=""),"",IF(N70&gt;=I70,ROUND(I70*K70,4),""))</x:f>
-        <x:v>0.2</x:v>
       </x:c>
       <x:c r="N70" t="n">
-        <x:v>4700</x:v>
+        <x:v>7813400</x:v>
       </x:c>
       <x:c r="O70" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4094,57 +4022,57 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R70" t="str">
-        <x:v>In stock 4,700; tier $0.002 at 100+. Datasheet confirms 0603, ±1%, ±100ppm/°C and −55 to +155°C.</x:v>
+        <x:v>Existing selected resistor; separated from R141 after divider value change.</x:v>
       </x:c>
       <x:c r="S70" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531588.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="36" customHeight="1">
       <x:c r="A71" s="25" t="str">
-        <x:v>R141</x:v>
+        <x:v>U19</x:v>
       </x:c>
       <x:c r="B71" s="25" t="str">
-        <x:v>9.1k 1% codec feedback divider resistor</x:v>
+        <x:v>USB auxiliary 5V / PD controller VDD LDO</x:v>
       </x:c>
       <x:c r="C71" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D71" s="25" t="str">
-        <x:v>RC0603FR-079K1L</x:v>
+        <x:v>TPS7B8450QWDRBRQ1</x:v>
       </x:c>
       <x:c r="E71" s="25" t="str">
-        <x:v>C114639</x:v>
+        <x:v>C3751394</x:v>
       </x:c>
       <x:c r="F71" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G71" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H71" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D71,$F$11:$F$87),G71)/H71,0)*H71))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D71,$F$11:$F$76),G71)/H71,0)*H71))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K71" s="26" t="n">
-        <x:v>0.0034</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="L71" s="27" t="n">
         <x:f>IF(K71="","",ROUND(F71*K71,4))</x:f>
-        <x:v>0.0034</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="M71" s="27" t="n">
         <x:f>IF(OR(K71="",I71="",N71=""),"",IF(N71&gt;=I71,ROUND(I71*K71,4),""))</x:f>
-        <x:v>0.34</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="N71" t="n">
-        <x:v>296500</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O71" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4156,87 +4084,72 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R71" t="str">
-        <x:v>In stock 296,500; tier $0.0034 at 100+. 0603, ±1%, ±100ppm/°C, −55 to +155°C. Distinct MPN from R151.</x:v>
+        <x:v>LCSC snapshot 2026-10-05: 1 pc in stock; $1.3452 at 1+, MOQ/multiple 1 (standard pack 3000; LCSC allows single-piece purchase). Stock is thin and may sell before ordering. TI TPS7B84-Q1: fixed 5V, 150mA, 40V input; startup/surge/dropout and thermal qualification open. Datasheet: ../datasheets/TPS7B84-Q1.pdf.</x:v>
       </x:c>
       <x:c r="S71" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114639.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3751394.html</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="36" customHeight="1">
       <x:c r="A72" s="25" t="str">
-        <x:v>R150</x:v>
+        <x:v>U20</x:v>
       </x:c>
       <x:c r="B72" s="25" t="str">
-        <x:v>604k 1% feedback resistor</x:v>
+        <x:v>USB and system logic priority mux</x:v>
       </x:c>
       <x:c r="C72" s="25" t="str">
-        <x:v>FOJAN</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D72" s="25" t="str">
-        <x:v>FRC0603F6043TS</x:v>
+        <x:v>TPS2116DRLR</x:v>
       </x:c>
       <x:c r="E72" s="25" t="str">
-        <x:v>C2933246</x:v>
+        <x:v>C3235557</x:v>
       </x:c>
       <x:c r="F72" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G72" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H72" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I72" t="n">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D72,$F$11:$F$87),G72)/H72,0)*H72))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J72" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K72" s="26" t="n">
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="L72" s="27" t="n">
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72" t="str">
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D72,$F$11:$F$76),G72)/H72,0)*H72))</x:f>
+      </x:c>
+      <x:c r="J72"/>
+      <x:c r="K72" s="26"/>
+      <x:c r="L72" s="27" t="str">
         <x:f>IF(K72="","",ROUND(F72*K72,4))</x:f>
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="M72" s="27" t="n">
+      </x:c>
+      <x:c r="M72" s="27" t="str">
         <x:f>IF(OR(K72="",I72="",N72=""),"",IF(N72&gt;=I72,ROUND(I72*K72,4),""))</x:f>
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="N72" t="n">
-        <x:v>54400</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N72"/>
       <x:c r="O72" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P72" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q72" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R72"/>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P72" s="16"/>
+      <x:c r="Q72"/>
+      <x:c r="R72" t="str">
+        <x:v>Selected MPN/LCSC mapping; current stock and price not verified.</x:v>
+      </x:c>
       <x:c r="S72" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2933246.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3235557.html</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="36" customHeight="1">
       <x:c r="A73" s="25" t="str">
-        <x:v>R151</x:v>
+        <x:v>R124</x:v>
       </x:c>
       <x:c r="B73" s="25" t="str">
-        <x:v>91k 1% feedback resistor</x:v>
+        <x:v>180k 1% USB-priority threshold divider resistor</x:v>
       </x:c>
       <x:c r="C73" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D73" s="25" t="str">
-        <x:v>AC0603FR-0791KL</x:v>
+        <x:v>RC0603FR-07180KL</x:v>
       </x:c>
       <x:c r="E73" s="25" t="str">
-        <x:v>C228098</x:v>
+        <x:v>C123419</x:v>
       </x:c>
       <x:c r="F73" s="25" t="n">
         <x:v>1</x:v>
@@ -4248,28 +4161,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D73,$F$11:$F$87),G73)/H73,0)*H73))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D73,$F$11:$F$76),G73)/H73,0)*H73))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K73" s="26" t="n">
-        <x:v>0.0061</x:v>
+        <x:v>0.0012</x:v>
       </x:c>
       <x:c r="L73" s="27" t="n">
         <x:f>IF(K73="","",ROUND(F73*K73,4))</x:f>
-        <x:v>0.0061</x:v>
-      </x:c>
-      <x:c r="M73" s="27" t="n">
+        <x:v>0.0012</x:v>
+      </x:c>
+      <x:c r="M73" s="27" t="str">
         <x:f>IF(OR(K73="",I73="",N73=""),"",IF(N73&gt;=I73,ROUND(I73*K73,4),""))</x:f>
-        <x:v>0.61</x:v>
-      </x:c>
-      <x:c r="N73" t="n">
-        <x:v>700</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N73"/>
       <x:c r="O73" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Stock unverified; price snapshot</x:v>
       </x:c>
       <x:c r="P73" s="16" t="n">
         <x:v>46300</x:v>
@@ -4277,17 +4187,19 @@
       <x:c r="Q73" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R73"/>
+      <x:c r="R73" t="str">
+        <x:v>Observed listing tier: $0.0012 at MOQ100. Product page may be stale; stock is unverified.</x:v>
+      </x:c>
       <x:c r="S73" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C228098.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="36" customHeight="1">
       <x:c r="A74" s="25" t="str">
-        <x:v>R152, R153, R154</x:v>
+        <x:v>R125</x:v>
       </x:c>
       <x:c r="B74" s="25" t="str">
-        <x:v>100k EN / MODE / bleeder resistors</x:v>
+        <x:v>100k PR1 divider resistor</x:v>
       </x:c>
       <x:c r="C74" s="25" t="str">
         <x:v>YAGEO</x:v>
@@ -4299,7 +4211,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F74" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G74" t="n">
         <x:v>100</x:v>
@@ -4308,7 +4220,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D74,$F$11:$F$87),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D74,$F$11:$F$76),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4319,7 +4231,7 @@
       </x:c>
       <x:c r="L74" s="27" t="n">
         <x:f>IF(K74="","",ROUND(F74*K74,4))</x:f>
-        <x:v>0.0108</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="M74" s="27" t="str">
         <x:f>IF(OR(K74="",I74="",N74=""),"",IF(N74&gt;=I74,ROUND(I74*K74,4),""))</x:f>
@@ -4336,55 +4248,58 @@
       <x:c r="Q74" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R74"/>
+      <x:c r="R74" t="str">
+        <x:v>Reuse same selected MPN/LCSC mapping as existing 100k BOM rows; no additional MOQ order.</x:v>
+      </x:c>
       <x:c r="S74" t="str">
         <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="36" customHeight="1">
       <x:c r="A75" s="25" t="str">
-        <x:v>R180</x:v>
+        <x:v>U21</x:v>
       </x:c>
       <x:c r="B75" s="25" t="str">
-        <x:v>100k 1% OVP divider resistor</x:v>
+        <x:v>Gauge undervoltage supervisor</x:v>
       </x:c>
       <x:c r="C75" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D75" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>TPS3839G33DBZR</x:v>
       </x:c>
       <x:c r="E75" s="25" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C485802</x:v>
       </x:c>
       <x:c r="F75" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G75" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H75" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D75,$F$11:$F$87),G75)/H75,0)*H75))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D75,$F$11:$F$76),G75)/H75,0)*H75))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K75" s="26" t="n">
-        <x:v>0.0036</x:v>
+        <x:v>0.439</x:v>
       </x:c>
       <x:c r="L75" s="27" t="n">
         <x:f>IF(K75="","",ROUND(F75*K75,4))</x:f>
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="M75" s="27" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="M75" s="27" t="n">
         <x:f>IF(OR(K75="",I75="",N75=""),"",IF(N75&gt;=I75,ROUND(I75*K75,4),""))</x:f>
+        <x:v>0.439</x:v>
       </x:c>
       <x:c r="N75" t="n">
-        <x:v>7813400</x:v>
+        <x:v>3444</x:v>
       </x:c>
       <x:c r="O75" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4397,27 +4312,27 @@
       </x:c>
       <x:c r="R75"/>
       <x:c r="S75" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C485802.html</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
       <x:c r="A76" s="25" t="str">
-        <x:v>R181</x:v>
+        <x:v>R126, R127</x:v>
       </x:c>
       <x:c r="B76" s="25" t="str">
-        <x:v>12.1k 1% OVP divider resistor</x:v>
+        <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
       </x:c>
       <x:c r="C76" s="25" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D76" s="25" t="str">
-        <x:v>RC0603FR-0712K1L</x:v>
+        <x:v>RC0603FR-071ML</x:v>
       </x:c>
       <x:c r="E76" s="25" t="str">
-        <x:v>C123417</x:v>
+        <x:v>C105578</x:v>
       </x:c>
       <x:c r="F76" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G76" t="n">
         <x:v>100</x:v>
@@ -4426,25 +4341,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D76,$F$11:$F$87),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D76,$F$11:$F$76),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K76" s="26" t="n">
-        <x:v>0.0031</x:v>
+        <x:v>0.0056</x:v>
       </x:c>
       <x:c r="L76" s="27" t="n">
         <x:f>IF(K76="","",ROUND(F76*K76,4))</x:f>
-        <x:v>0.0031</x:v>
+        <x:v>0.0112</x:v>
       </x:c>
       <x:c r="M76" s="27" t="n">
         <x:f>IF(OR(K76="",I76="",N76=""),"",IF(N76&gt;=I76,ROUND(I76*K76,4),""))</x:f>
-        <x:v>0.31</x:v>
+        <x:v>0.56</x:v>
       </x:c>
       <x:c r="N76" t="n">
-        <x:v>135800</x:v>
+        <x:v>359600</x:v>
       </x:c>
       <x:c r="O76" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4457,659 +4372,250 @@
       </x:c>
       <x:c r="R76"/>
       <x:c r="S76" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C123417.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C105578.html</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="36" customHeight="1">
-      <x:c r="A77" s="25" t="str">
-        <x:v>R182</x:v>
-      </x:c>
-      <x:c r="B77" s="25" t="str">
-        <x:v>5.36k 1% current-limit resistor</x:v>
-      </x:c>
-      <x:c r="C77" s="25" t="str">
-        <x:v>FOJAN</x:v>
-      </x:c>
-      <x:c r="D77" s="25" t="str">
-        <x:v>FRC0603F5361TS</x:v>
-      </x:c>
-      <x:c r="E77" s="25" t="str">
-        <x:v>C2930112</x:v>
-      </x:c>
-      <x:c r="F77" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G77" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H77" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D77,$F$11:$F$87),G77)/H77,0)*H77))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J77" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K77" s="26" t="n">
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="L77" s="27" t="n">
-        <x:f>IF(K77="","",ROUND(F77*K77,4))</x:f>
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="M77" s="27" t="n">
-        <x:f>IF(OR(K77="",I77="",N77=""),"",IF(N77&gt;=I77,ROUND(I77*K77,4),""))</x:f>
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="N77" t="n">
-        <x:v>33100</x:v>
-      </x:c>
-      <x:c r="O77" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P77" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q77" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+      <x:c r="A77" s="25"/>
+      <x:c r="B77" s="25"/>
+      <x:c r="C77" s="25"/>
+      <x:c r="D77" s="25"/>
+      <x:c r="E77" s="25"/>
+      <x:c r="F77" s="25"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
+      <x:c r="J77"/>
+      <x:c r="K77" s="26"/>
+      <x:c r="L77" s="27"/>
+      <x:c r="M77" s="27"/>
+      <x:c r="N77"/>
+      <x:c r="O77"/>
+      <x:c r="P77" s="16"/>
+      <x:c r="Q77"/>
       <x:c r="R77"/>
-      <x:c r="S77" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2930112.html</x:v>
-      </x:c>
+      <x:c r="S77"/>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="21" t="str">
-        <x:v>C181</x:v>
-      </x:c>
-      <x:c r="B78" s="21" t="str">
-        <x:v>eFuse startup-ramp 22nF50VX7R0603</x:v>
-      </x:c>
-      <x:c r="C78" s="21" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D78" s="21" t="str">
-        <x:v>CL10B223KB8NNNC</x:v>
-      </x:c>
-      <x:c r="E78" s="21" t="str">
-        <x:v>C21122</x:v>
-      </x:c>
-      <x:c r="F78" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G78" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H78" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D78,$F$11:$F$87),G78)/H78,0)*H78))</x:f>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J78" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K78" s="26" t="n">
-        <x:v>0.0084</x:v>
-      </x:c>
-      <x:c r="L78" s="27" t="n">
-        <x:f>IF(K78="","",ROUND(F78*K78,4))</x:f>
-        <x:v>0.0084</x:v>
-      </x:c>
-      <x:c r="M78" s="27" t="n">
-        <x:f>IF(OR(K78="",I78="",N78=""),"",IF(N78&gt;=I78,ROUND(I78*K78,4),""))</x:f>
-        <x:v>0.42</x:v>
-      </x:c>
-      <x:c r="N78" t="n">
-        <x:v>316900</x:v>
-      </x:c>
-      <x:c r="O78" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P78" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q78" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
+      <x:c r="B78" s="21"/>
+      <x:c r="C78" s="21"/>
+      <x:c r="D78" s="21"/>
+      <x:c r="E78" s="21"/>
+      <x:c r="F78" s="21"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+      <x:c r="J78"/>
+      <x:c r="K78" s="26"/>
+      <x:c r="L78" s="27"/>
+      <x:c r="M78" s="27"/>
+      <x:c r="N78"/>
+      <x:c r="O78"/>
+      <x:c r="P78" s="16"/>
+      <x:c r="Q78"/>
       <x:c r="R78"/>
-      <x:c r="S78" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C21122.html</x:v>
-      </x:c>
+      <x:c r="S78"/>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="21" t="str">
-        <x:v>C108</x:v>
-      </x:c>
-      <x:c r="B79" s="21" t="str">
-        <x:v>Additional PMID22uF25V1210</x:v>
-      </x:c>
-      <x:c r="C79" s="21" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D79" s="21" t="str">
-        <x:v>CL32B226KAJNNNE</x:v>
-      </x:c>
-      <x:c r="E79" s="21" t="str">
-        <x:v>C309062</x:v>
-      </x:c>
-      <x:c r="F79" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G79" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H79" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D79,$F$11:$F$87),G79)/H79,0)*H79))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J79" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K79" s="26" t="n">
-        <x:v>0.3569</x:v>
-      </x:c>
-      <x:c r="L79" s="27" t="n">
-        <x:f>IF(K79="","",ROUND(F79*K79,4))</x:f>
-        <x:v>0.3569</x:v>
-      </x:c>
-      <x:c r="M79" s="27" t="str">
-        <x:f>IF(OR(K79="",I79="",N79=""),"",IF(N79&gt;=I79,ROUND(I79*K79,4),""))</x:f>
-      </x:c>
-      <x:c r="N79" t="n">
-        <x:v>96346</x:v>
-      </x:c>
-      <x:c r="O79" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P79" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q79" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>U2: Only 4 available in page snapshot.</x:v>
+      </x:c>
+      <x:c r="B79" s="21"/>
+      <x:c r="C79" s="21"/>
+      <x:c r="D79" s="21"/>
+      <x:c r="E79" s="21"/>
+      <x:c r="F79" s="21"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+      <x:c r="J79"/>
+      <x:c r="K79" s="26"/>
+      <x:c r="L79" s="27"/>
+      <x:c r="M79" s="27"/>
+      <x:c r="N79"/>
+      <x:c r="O79"/>
+      <x:c r="P79" s="16"/>
+      <x:c r="Q79"/>
       <x:c r="R79"/>
-      <x:c r="S79" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C309062.html</x:v>
-      </x:c>
+      <x:c r="S79"/>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="21" t="str">
-        <x:v>C109</x:v>
-      </x:c>
-      <x:c r="B80" s="21" t="str">
-        <x:v>Additional REGN10uF10V0805</x:v>
-      </x:c>
-      <x:c r="C80" s="21" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D80" s="21" t="str">
-        <x:v>CL21B106KPQNNNE</x:v>
-      </x:c>
-      <x:c r="E80" s="21" t="str">
-        <x:v>C32635</x:v>
-      </x:c>
-      <x:c r="F80" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G80" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H80" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D80,$F$11:$F$87),G80)/H80,0)*H80))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J80" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K80" s="26" t="n">
-        <x:v>0.093</x:v>
-      </x:c>
-      <x:c r="L80" s="27" t="n">
-        <x:f>IF(K80="","",ROUND(F80*K80,4))</x:f>
-        <x:v>0.093</x:v>
-      </x:c>
-      <x:c r="M80" s="27" t="str">
-        <x:f>IF(OR(K80="",I80="",N80=""),"",IF(N80&gt;=I80,ROUND(I80*K80,4),""))</x:f>
-      </x:c>
-      <x:c r="N80" t="n">
-        <x:v>230700</x:v>
-      </x:c>
-      <x:c r="O80" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P80" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q80" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+      </x:c>
+      <x:c r="B80" s="21"/>
+      <x:c r="C80" s="21"/>
+      <x:c r="D80" s="21"/>
+      <x:c r="E80" s="21"/>
+      <x:c r="F80" s="21"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
+      <x:c r="J80"/>
+      <x:c r="K80" s="26"/>
+      <x:c r="L80" s="27"/>
+      <x:c r="M80" s="27"/>
+      <x:c r="N80"/>
+      <x:c r="O80"/>
+      <x:c r="P80" s="16"/>
+      <x:c r="Q80"/>
       <x:c r="R80"/>
-      <x:c r="S80" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
-      </x:c>
+      <x:c r="S80"/>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
-      <x:c r="A81" s="21" t="str">
-        <x:v>R142</x:v>
-      </x:c>
-      <x:c r="B81" s="21" t="str">
-        <x:v>100k EN pulldown resistor</x:v>
-      </x:c>
-      <x:c r="C81" s="21" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D81" s="21" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E81" s="21" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
-      <x:c r="F81" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D81,$F$11:$F$87),G81)/H81,0)*H81))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K81" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L81" s="27" t="n">
-        <x:f>IF(K81="","",ROUND(F81*K81,4))</x:f>
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="M81" s="27" t="str">
-        <x:f>IF(OR(K81="",I81="",N81=""),"",IF(N81&gt;=I81,ROUND(I81*K81,4),""))</x:f>
-      </x:c>
-      <x:c r="N81" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
-      <x:c r="O81" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P81" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q81" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R81" t="str">
-        <x:v>Existing selected resistor; separated from R141 after divider value change.</x:v>
-      </x:c>
-      <x:c r="S81" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+      <x:c r="A81" t="str">
+        <x:v>U4/U11/Q103 prices are review-time snapshots or unverified; C2/C6/D7/R10/C182/C183 per candidate review; TPS25730D 5-20 V integration 2026-10-05.</x:v>
+      </x:c>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
+      <x:c r="J81"/>
+      <x:c r="K81"/>
+      <x:c r="L81"/>
+      <x:c r="M81"/>
+      <x:c r="N81"/>
+      <x:c r="O81"/>
+      <x:c r="P81"/>
+      <x:c r="Q81"/>
+      <x:c r="R81"/>
+      <x:c r="S81"/>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
-      <x:c r="A82" s="21" t="str">
-        <x:v>U19</x:v>
-      </x:c>
-      <x:c r="B82" s="21" t="str">
-        <x:v>USB auxiliary 5V / PD controller VDD LDO</x:v>
-      </x:c>
-      <x:c r="C82" s="21" t="str">
-        <x:v>Texas Instruments</x:v>
-      </x:c>
-      <x:c r="D82" s="21" t="str">
-        <x:v>TPS7B8450QWDRBRQ1</x:v>
-      </x:c>
-      <x:c r="E82" s="21" t="str">
-        <x:v>C3751394</x:v>
-      </x:c>
-      <x:c r="F82" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G82" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H82" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D82,$F$11:$F$87),G82)/H82,0)*H82))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J82" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K82" s="26" t="n">
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="L82" s="27" t="n">
-        <x:f>IF(K82="","",ROUND(F82*K82,4))</x:f>
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="M82" s="27" t="n">
-        <x:f>IF(OR(K82="",I82="",N82=""),"",IF(N82&gt;=I82,ROUND(I82*K82,4),""))</x:f>
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="N82" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O82" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P82" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q82" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R82" t="str">
-        <x:v>LCSC snapshot 2026-10-05: 1 pc in stock; $1.3452 at 1+, MOQ/multiple 1 (standard pack 3000; LCSC allows single-piece purchase). Stock is thin and may sell before ordering. TI TPS7B84-Q1: fixed 5V, 150mA, 40V input; startup/surge/dropout and thermal qualification open. Datasheet: ../datasheets/TPS7B84-Q1.pdf.</x:v>
-      </x:c>
-      <x:c r="S82" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3751394.html</x:v>
-      </x:c>
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
+      <x:c r="J82"/>
+      <x:c r="K82"/>
+      <x:c r="L82"/>
+      <x:c r="M82"/>
+      <x:c r="N82"/>
+      <x:c r="O82"/>
+      <x:c r="P82"/>
+      <x:c r="Q82"/>
+      <x:c r="R82"/>
+      <x:c r="S82"/>
     </x:row>
     <x:row r="83" ht="48" customHeight="1">
-      <x:c r="A83" s="21" t="str">
-        <x:v>U20</x:v>
-      </x:c>
-      <x:c r="B83" s="21" t="str">
-        <x:v>USB and system logic priority mux</x:v>
-      </x:c>
-      <x:c r="C83" s="21" t="str">
-        <x:v>Texas Instruments</x:v>
-      </x:c>
-      <x:c r="D83" s="21" t="str">
-        <x:v>TPS2116DRLR</x:v>
-      </x:c>
-      <x:c r="E83" s="21" t="str">
-        <x:v>C3235557</x:v>
-      </x:c>
-      <x:c r="F83" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83"/>
-      <x:c r="I83" t="str">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D83,$F$11:$F$87),G83)/H83,0)*H83))</x:f>
-      </x:c>
+      <x:c r="I83"/>
       <x:c r="J83"/>
-      <x:c r="K83" s="26"/>
-      <x:c r="L83" s="27" t="str">
-        <x:f>IF(K83="","",ROUND(F83*K83,4))</x:f>
-      </x:c>
-      <x:c r="M83" s="27" t="str">
-        <x:f>IF(OR(K83="",I83="",N83=""),"",IF(N83&gt;=I83,ROUND(I83*K83,4),""))</x:f>
-      </x:c>
+      <x:c r="K83"/>
+      <x:c r="L83"/>
+      <x:c r="M83"/>
       <x:c r="N83"/>
-      <x:c r="O83" t="str">
-        <x:v>Stock/price unverified</x:v>
-      </x:c>
-      <x:c r="P83" s="16"/>
+      <x:c r="O83"/>
+      <x:c r="P83"/>
       <x:c r="Q83"/>
-      <x:c r="R83" s="21" t="str">
-        <x:v>Selected MPN/LCSC mapping; current stock and price not verified.</x:v>
-      </x:c>
-      <x:c r="S83" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3235557.html</x:v>
-      </x:c>
+      <x:c r="R83"/>
+      <x:c r="S83"/>
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
-      <x:c r="A84" s="21" t="str">
-        <x:v>R124</x:v>
-      </x:c>
-      <x:c r="B84" s="21" t="str">
-        <x:v>180k 1% USB-priority threshold divider resistor</x:v>
-      </x:c>
-      <x:c r="C84" s="21" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D84" s="21" t="str">
-        <x:v>RC0603FR-07180KL</x:v>
-      </x:c>
-      <x:c r="E84" s="21" t="str">
-        <x:v>C123419</x:v>
-      </x:c>
-      <x:c r="F84" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D84,$F$11:$F$87),G84)/H84,0)*H84))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K84" s="26" t="n">
-        <x:v>0.0012</x:v>
-      </x:c>
-      <x:c r="L84" s="27" t="n">
-        <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
-        <x:v>0.0012</x:v>
-      </x:c>
-      <x:c r="M84" s="27" t="str">
-        <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
-      </x:c>
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
+      <x:c r="J84"/>
+      <x:c r="K84"/>
+      <x:c r="L84"/>
+      <x:c r="M84"/>
       <x:c r="N84"/>
-      <x:c r="O84" t="str">
-        <x:v>Stock unverified; price snapshot</x:v>
-      </x:c>
-      <x:c r="P84" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q84" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R84" s="21" t="str">
-        <x:v>Observed listing tier: $0.0012 at MOQ100. Product page may be stale; stock is unverified.</x:v>
-      </x:c>
-      <x:c r="S84" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
-      </x:c>
+      <x:c r="O84"/>
+      <x:c r="P84"/>
+      <x:c r="Q84"/>
+      <x:c r="R84"/>
+      <x:c r="S84"/>
     </x:row>
     <x:row r="85" ht="48" customHeight="1">
-      <x:c r="A85" s="21" t="str">
-        <x:v>R125</x:v>
-      </x:c>
-      <x:c r="B85" s="21" t="str">
-        <x:v>100k PR1 divider resistor</x:v>
-      </x:c>
-      <x:c r="C85" s="21" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D85" s="21" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E85" s="21" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
-      <x:c r="F85" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G85" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H85" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D85,$F$11:$F$87),G85)/H85,0)*H85))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J85" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K85" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L85" s="27" t="n">
-        <x:f>IF(K85="","",ROUND(F85*K85,4))</x:f>
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="M85" s="27" t="str">
-        <x:f>IF(OR(K85="",I85="",N85=""),"",IF(N85&gt;=I85,ROUND(I85*K85,4),""))</x:f>
-      </x:c>
-      <x:c r="N85" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
-      <x:c r="O85" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P85" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q85" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R85" s="21" t="str">
-        <x:v>Reuse same selected MPN/LCSC mapping as existing 100k BOM rows; no additional MOQ order.</x:v>
-      </x:c>
-      <x:c r="S85" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
+      <x:c r="H85"/>
+      <x:c r="I85"/>
+      <x:c r="J85"/>
+      <x:c r="K85"/>
+      <x:c r="L85"/>
+      <x:c r="M85"/>
+      <x:c r="N85"/>
+      <x:c r="O85"/>
+      <x:c r="P85"/>
+      <x:c r="Q85"/>
+      <x:c r="R85"/>
+      <x:c r="S85"/>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
-      <x:c r="A86" s="21" t="str">
-        <x:v>U21</x:v>
-      </x:c>
-      <x:c r="B86" s="21" t="str">
-        <x:v>Gauge undervoltage supervisor</x:v>
-      </x:c>
-      <x:c r="C86" s="21" t="str">
-        <x:v>Texas Instruments</x:v>
-      </x:c>
-      <x:c r="D86" s="21" t="str">
-        <x:v>TPS3839G33DBZR</x:v>
-      </x:c>
-      <x:c r="E86" s="21" t="str">
-        <x:v>C485802</x:v>
-      </x:c>
-      <x:c r="F86" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G86" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H86" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I86" t="n">
-        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D86,$F$11:$F$87),G86)/H86,0)*H86))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J86" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K86" s="26" t="n">
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="L86" s="27" t="n">
-        <x:f>IF(K86="","",ROUND(F86*K86,4))</x:f>
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="M86" s="27" t="n">
-        <x:f>IF(OR(K86="",I86="",N86=""),"",IF(N86&gt;=I86,ROUND(I86*K86,4),""))</x:f>
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="N86" t="n">
-        <x:v>3444</x:v>
-      </x:c>
-      <x:c r="O86" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P86" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q86" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R86" s="21"/>
-      <x:c r="S86" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C485802.html</x:v>
-      </x:c>
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
+      <x:c r="H86"/>
+      <x:c r="I86"/>
+      <x:c r="J86"/>
+      <x:c r="K86"/>
+      <x:c r="L86"/>
+      <x:c r="M86"/>
+      <x:c r="N86"/>
+      <x:c r="O86"/>
+      <x:c r="P86"/>
+      <x:c r="Q86"/>
+      <x:c r="R86"/>
+      <x:c r="S86"/>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87" s="21" t="str">
-        <x:v>R126, R127</x:v>
-      </x:c>
-      <x:c r="B87" s="21" t="str">
-        <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
-      </x:c>
-      <x:c r="C87" s="21" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D87" s="21" t="str">
-        <x:v>RC0603FR-071ML</x:v>
-      </x:c>
-      <x:c r="E87" s="21" t="str">
-        <x:v>C105578</x:v>
-      </x:c>
-      <x:c r="F87" s="21" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G87" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H87" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I87" t="n">
-        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$87,D87,$F$11:$F$87),G87)/H87,0)*H87))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J87" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K87" s="26" t="n">
-        <x:v>0.0056</x:v>
-      </x:c>
-      <x:c r="L87" s="27" t="n">
-        <x:f>IF(K87="","",ROUND(F87*K87,4))</x:f>
-        <x:v>0.0112</x:v>
-      </x:c>
-      <x:c r="M87" s="27" t="n">
-        <x:f>IF(OR(K87="",I87="",N87=""),"",IF(N87&gt;=I87,ROUND(I87*K87,4),""))</x:f>
-        <x:v>0.56</x:v>
-      </x:c>
-      <x:c r="N87" t="n">
-        <x:v>359600</x:v>
-      </x:c>
-      <x:c r="O87" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P87" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q87" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R87" s="21"/>
-      <x:c r="S87" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105578.html</x:v>
-      </x:c>
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
+      <x:c r="J87"/>
+      <x:c r="K87"/>
+      <x:c r="L87"/>
+      <x:c r="M87"/>
+      <x:c r="N87"/>
+      <x:c r="O87"/>
+      <x:c r="P87"/>
+      <x:c r="Q87"/>
+      <x:c r="R87"/>
+      <x:c r="S87"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A88"/>
       <x:c r="B88"/>
       <x:c r="C88"/>
       <x:c r="D88"/>
@@ -5130,9 +4636,7 @@
       <x:c r="S88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
-      </x:c>
+      <x:c r="A89"/>
       <x:c r="B89"/>
       <x:c r="C89"/>
       <x:c r="D89"/>
@@ -5153,9 +4657,7 @@
       <x:c r="S89"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
-      </x:c>
+      <x:c r="A90"/>
       <x:c r="B90"/>
       <x:c r="C90"/>
       <x:c r="D90"/>
@@ -5176,9 +4678,7 @@
       <x:c r="S90"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A91"/>
       <x:c r="B91"/>
       <x:c r="C91"/>
       <x:c r="D91"/>
@@ -5199,9 +4699,7 @@
       <x:c r="S91"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
-      </x:c>
+      <x:c r="A92"/>
       <x:c r="B92"/>
       <x:c r="C92"/>
       <x:c r="D92"/>
@@ -5222,9 +4720,7 @@
       <x:c r="S92"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
-      </x:c>
+      <x:c r="A93"/>
       <x:c r="B93"/>
       <x:c r="C93"/>
       <x:c r="D93"/>
@@ -6004,261 +5500,4 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
-        <x:v>Reference (candidate)</x:v>
-      </x:c>
-      <x:c r="B1" t="str">
-        <x:v>Function</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>Manufacturer</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>MPN</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>LCSC part</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>Fitted qty</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>MOQ</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>Unit USD (tier)</x:v>
-      </x:c>
-      <x:c r="I1" t="str">
-        <x:v>Stock qty (2026-10-05 listing)</x:v>
-      </x:c>
-      <x:c r="J1" t="str">
-        <x:v>Footprint</x:v>
-      </x:c>
-      <x:c r="K1" t="str">
-        <x:v>Note</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>C2</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>TPS25730D CVBUS 4.7uF/50V X7R 1210 (was 1uF)</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>CL32B475KBUYNNE</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>C170099</x:v>
-      </x:c>
-      <x:c r="F2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H2" t="n">
-        <x:v>0.1367</x:v>
-      </x:c>
-      <x:c r="I2" t="n">
-        <x:v>57880</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>DesktopSpeaker:PD_C_1210</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>Alt: GRM32ER71H475KA88L C86052</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>C6</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>TPS25730D CLDO_3V3 22uF/10V X7R 0805 (was 10uF)</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Murata</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>GRM21BZ71A226ME15L</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>C907991</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" t="n">
-        <x:v>0.2543</x:v>
-      </x:c>
-      <x:c r="I3" t="n">
-        <x:v>132900</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>DesktopSpeaker:PD_C_0805</x:v>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>Same MPN as SYS caps</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>C113, C114, C115</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>BQ25792 VBUS/PMID/SYS 100nF/50V X7R 0402 bypass</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Murata</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>GRM155R71H104KE14D</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>C77020</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G4" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H4" t="n">
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="I4" t="n">
-        <x:v>777000</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>DesktopSpeaker:PD_C_0402 (new, ai-files/candidates/PD_C_0402.kicad_mod)</x:v>
-      </x:c>
-      <x:c r="K4" t="str">
-        <x:v>Replaces mismatched CL21B104KBCNNNC (0805)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>D7</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>TPS25730D VBUS-to-GND Schottky (TI 8.5)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Diodes Incorporated</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>1N5819HW-7-F</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>C82544</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H5" t="n">
-        <x:v>0.057</x:v>
-      </x:c>
-      <x:c r="I5" t="n">
-        <x:v>137330</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>DesktopSpeaker:PD_D_SOD123</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>40V/1A SOD-123; IR max ~1 mA at 40V, lower at 20V; alt B5819W SL C8598</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>R14, R15, R18</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>TPS25730D I2C SDA/SCL pull-ups to LDO_3V3 (R14,R15); pin 36 to GND (R18) 10k 1%</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>RC0603FR-0710KL</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>C98220</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H6" t="n">
-        <x:v>0.0034</x:v>
-      </x:c>
-      <x:c r="I6" t="n">
-        <x:v>7736700</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>DesktopSpeaker:PD_R_0603</x:v>
-      </x:c>
-      <x:c r="K6" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>R16, R17, R103</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>TPS25730D PLUG_EVENT/SINK_EN 100k pull-ups (R16,R17); BQ25792 R103 CE pull-up now 100k (was 10k)</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H7" t="n">
-        <x:v>0.0026</x:v>
-      </x:c>
-      <x:c r="I7" t="n">
-        <x:v>7987300</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>DesktopSpeaker:PD_R_0603</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>R103 stays in Selected BOM row "R103, R106" as 10k until integration</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Candidate-only rows; not in Selected BOM subtotals. Prices/stock are LCSC listing snapshots (2026-10-05). LCSC URL = https://www.lcsc.com/product-detail/&lt;LCSC part&gt;.html</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R84b5439466b04a39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R775214754f27435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Ra3b864060822466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rdef7aa4a7fd24139"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4470,23 +4470,48 @@
         <x:v>U4/U11/Q103 prices are review-time snapshots or unverified; C2/C6/D7/R10/C182/C183 per candidate review; TPS25730D 5-20 V integration 2026-10-05.</x:v>
       </x:c>
       <x:c r="B81"/>
-      <x:c r="C81"/>
-      <x:c r="D81"/>
-      <x:c r="E81"/>
+      <x:c r="C81" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>CL10C331JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>C1578</x:v>
+      </x:c>
       <x:c r="F81"/>
-      <x:c r="G81"/>
-      <x:c r="H81"/>
-      <x:c r="I81"/>
-      <x:c r="J81"/>
-      <x:c r="K81"/>
+      <x:c r="G81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I81" t="n">
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$100,D81,$F$11:$F$100),G81)/H81,0)*H81))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K81" t="n">
+        <x:v>0.0089</x:v>
+      </x:c>
       <x:c r="L81"/>
       <x:c r="M81"/>
-      <x:c r="N81"/>
-      <x:c r="O81"/>
-      <x:c r="P81"/>
-      <x:c r="Q81"/>
+      <x:c r="N81" t="str"/>
+      <x:c r="O81" t="str">
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P81" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q81" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
       <x:c r="R81"/>
-      <x:c r="S81"/>
+      <x:c r="S81" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C1578.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Ra3b864060822466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rdef7aa4a7fd24139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Re8f2831317b74255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R1c330fc6c0864148"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
         <x:f>ROUND(SUM(L11:L76),2)</x:f>
-        <x:v>67.28</x:v>
+        <x:v>68.79</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -462,7 +462,7 @@
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
         <x:f>ROUND(SUM(M11:M76),2)</x:f>
-        <x:v>83.81</x:v>
+        <x:v>84.99</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -3112,33 +3112,60 @@
       <x:c r="B54" s="25" t="str">
         <x:v>Three-contact protected pack connector</x:v>
       </x:c>
-      <x:c r="C54" s="25"/>
-      <x:c r="D54" s="25"/>
-      <x:c r="E54" s="25"/>
+      <x:c r="C54" s="25" t="str">
+        <x:v>Molex</x:v>
+      </x:c>
+      <x:c r="D54" s="25" t="str">
+        <x:v>43650-0300</x:v>
+      </x:c>
+      <x:c r="E54" s="25" t="str">
+        <x:v>C503478</x:v>
+      </x:c>
       <x:c r="F54" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G54"/>
-      <x:c r="H54"/>
-      <x:c r="I54" t="str">
+      <x:c r="G54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I54" t="n">
         <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D54,$F$11:$F$76),G54)/H54,0)*H54))</x:f>
-      </x:c>
-      <x:c r="J54"/>
-      <x:c r="K54" s="26"/>
-      <x:c r="L54" s="27" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K54" s="26" t="n">
+        <x:v>0.5485</x:v>
+      </x:c>
+      <x:c r="L54" s="27" t="n">
         <x:f>IF(K54="","",ROUND(F54*K54,4))</x:f>
-      </x:c>
-      <x:c r="M54" s="27" t="str">
+        <x:v>0.5485</x:v>
+      </x:c>
+      <x:c r="M54" s="27" t="n">
         <x:f>IF(OR(K54="",I54="",N54=""),"",IF(N54&gt;=I54,ROUND(I54*K54,4),""))</x:f>
-      </x:c>
-      <x:c r="N54"/>
+        <x:v>0.5485</x:v>
+      </x:c>
+      <x:c r="N54" t="n">
+        <x:v>9368</x:v>
+      </x:c>
       <x:c r="O54" t="str">
-        <x:v>MPN open</x:v>
-      </x:c>
-      <x:c r="P54" s="16"/>
-      <x:c r="Q54"/>
-      <x:c r="R54"/>
-      <x:c r="S54"/>
+        <x:v>Listing snapshot, unverified</x:v>
+      </x:c>
+      <x:c r="P54" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q54" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R54" t="str">
+        <x:v>Selected 2026-10-06: Micro-Fit 3.0 3-pos right-angle header, 8.5 A/contact (LCSC listing); mates 43645-0300 housing + 43030 crimps (not yet in BOM). LCSC datasheet file is an LXW 5 A drawing; use Molex PS-43650. Price/stock from 2026-10-06 LCSC page, not a quote.</x:v>
+      </x:c>
+      <x:c r="S54" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C503478.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="36" customHeight="1">
       <x:c r="A55" s="25" t="str">
@@ -3147,33 +3174,60 @@
       <x:c r="B55" s="25" t="str">
         <x:v>QON wake pushbutton</x:v>
       </x:c>
-      <x:c r="C55" s="25"/>
-      <x:c r="D55" s="25"/>
-      <x:c r="E55" s="25"/>
+      <x:c r="C55" s="25" t="str">
+        <x:v>TE Connectivity</x:v>
+      </x:c>
+      <x:c r="D55" s="25" t="str">
+        <x:v>1977066-1</x:v>
+      </x:c>
+      <x:c r="E55" s="25" t="str">
+        <x:v>C2972219</x:v>
+      </x:c>
       <x:c r="F55" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G55"/>
-      <x:c r="H55"/>
-      <x:c r="I55" t="str">
+      <x:c r="G55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I55" t="n">
         <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D55,$F$11:$F$76),G55)/H55,0)*H55))</x:f>
-      </x:c>
-      <x:c r="J55"/>
-      <x:c r="K55" s="26"/>
-      <x:c r="L55" s="27" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K55" s="26" t="n">
+        <x:v>0.6291</x:v>
+      </x:c>
+      <x:c r="L55" s="27" t="n">
         <x:f>IF(K55="","",ROUND(F55*K55,4))</x:f>
-      </x:c>
-      <x:c r="M55" s="27" t="str">
+        <x:v>0.6291</x:v>
+      </x:c>
+      <x:c r="M55" s="27" t="n">
         <x:f>IF(OR(K55="",I55="",N55=""),"",IF(N55&gt;=I55,ROUND(I55*K55,4),""))</x:f>
-      </x:c>
-      <x:c r="N55"/>
+        <x:v>0.6291</x:v>
+      </x:c>
+      <x:c r="N55" t="n">
+        <x:v>2009</x:v>
+      </x:c>
       <x:c r="O55" t="str">
-        <x:v>MPN open</x:v>
-      </x:c>
-      <x:c r="P55" s="16"/>
-      <x:c r="Q55"/>
-      <x:c r="R55"/>
-      <x:c r="S55"/>
+        <x:v>Listing snapshot, unverified</x:v>
+      </x:c>
+      <x:c r="P55" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q55" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R55" t="str">
+        <x:v>Selected 2026-10-06: right-angle SMT tact, 50 mA @12 V. LCSC number confirmed. Price/stock from LCSC page 2026-10-06, not a quote.</x:v>
+      </x:c>
+      <x:c r="S55" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C2972219.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="36" customHeight="1">
       <x:c r="A56" s="25" t="str">
@@ -3182,33 +3236,59 @@
       <x:c r="B56" s="25" t="str">
         <x:v>Pack-positive disconnect switch</x:v>
       </x:c>
-      <x:c r="C56" s="25"/>
-      <x:c r="D56" s="25"/>
-      <x:c r="E56" s="25"/>
+      <x:c r="C56" s="25" t="str">
+        <x:v>SHOU HAN</x:v>
+      </x:c>
+      <x:c r="D56" s="25" t="str">
+        <x:v>KCD1-201-R</x:v>
+      </x:c>
+      <x:c r="E56" s="25" t="str">
+        <x:v>C5884429</x:v>
+      </x:c>
       <x:c r="F56" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G56"/>
-      <x:c r="H56"/>
-      <x:c r="I56" t="str">
+      <x:c r="G56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I56" t="n">
         <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D56,$F$11:$F$76),G56)/H56,0)*H56))</x:f>
-      </x:c>
-      <x:c r="J56"/>
-      <x:c r="K56" s="26"/>
-      <x:c r="L56" s="27" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K56" s="26" t="n">
+        <x:v>0.338</x:v>
+      </x:c>
+      <x:c r="L56" s="27" t="n">
         <x:f>IF(K56="","",ROUND(F56*K56,4))</x:f>
+        <x:v>0.338</x:v>
       </x:c>
       <x:c r="M56" s="27" t="str">
         <x:f>IF(OR(K56="",I56="",N56=""),"",IF(N56&gt;=I56,ROUND(I56*K56,4),""))</x:f>
       </x:c>
-      <x:c r="N56"/>
+      <x:c r="N56" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="O56" t="str">
-        <x:v>MPN open</x:v>
-      </x:c>
-      <x:c r="P56" s="16"/>
-      <x:c r="Q56"/>
-      <x:c r="R56"/>
-      <x:c r="S56"/>
+        <x:v>Listing snapshot, unverified</x:v>
+      </x:c>
+      <x:c r="P56" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q56" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R56" t="str">
+        <x:v>Selected 2026-10-06: 20 mm round SPST rocker, 10 A @12 VDC (datasheet), 6 A 250 VAC. LCSC stock 0 at 2026-10-06: availability and 3-terminal mapping UNVERIFIED; peak 15-20 A exceeds rating, see HANDOVER.</x:v>
+      </x:c>
+      <x:c r="S56" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C5884429.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="36" customHeight="1">
       <x:c r="A57" s="25" t="str">

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Re8f2831317b74255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R1c330fc6c0864148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R251dda92d91f4db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R31fc1f4fda48428b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L76),2)</x:f>
-        <x:v>68.79</x:v>
+        <x:f>ROUND(SUM(L11:L78),2)</x:f>
+        <x:v>68.9</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M76),2)</x:f>
-        <x:v>84.99</x:v>
+        <x:f>ROUND(SUM(M11:M78),2)</x:f>
+        <x:v>85.55</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D11,$F$11:$F$76),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D11,$F$11:$F$78),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D12,$F$11:$F$76),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D12,$F$11:$F$78),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -778,7 +778,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D13,$F$11:$F$76),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D13,$F$11:$F$78),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -827,7 +827,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D14,$F$11:$F$76),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D14,$F$11:$F$78),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -887,7 +887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D15,$F$11:$F$76),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D15,$F$11:$F$78),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -947,7 +947,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D16,$F$11:$F$76),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D16,$F$11:$F$78),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1007,7 +1007,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D17,$F$11:$F$76),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D17,$F$11:$F$78),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1067,7 +1067,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D18,$F$11:$F$76),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D18,$F$11:$F$78),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1127,7 +1127,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D19,$F$11:$F$76),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D19,$F$11:$F$78),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1187,7 +1187,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D20,$F$11:$F$76),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D20,$F$11:$F$78),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1247,7 +1247,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D21,$F$11:$F$76),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D21,$F$11:$F$78),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1303,7 +1303,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D22,$F$11:$F$76),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D22,$F$11:$F$78),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1352,7 +1352,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D23,$F$11:$F$76),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D23,$F$11:$F$78),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1412,7 +1412,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D24,$F$11:$F$76),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D24,$F$11:$F$78),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1472,7 +1472,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D25,$F$11:$F$76),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D25,$F$11:$F$78),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1532,7 +1532,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D26,$F$11:$F$76),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D26,$F$11:$F$78),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1592,7 +1592,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D27,$F$11:$F$76),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D27,$F$11:$F$78),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1652,7 +1652,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D28,$F$11:$F$76),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D28,$F$11:$F$78),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1708,7 +1708,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D29,$F$11:$F$76),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D29,$F$11:$F$78),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1757,7 +1757,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D30,$F$11:$F$76),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D30,$F$11:$F$78),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1817,7 +1817,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D31,$F$11:$F$76),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D31,$F$11:$F$78),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1879,7 +1879,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D32,$F$11:$F$76),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D32,$F$11:$F$78),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1941,7 +1941,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D33,$F$11:$F$76),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D33,$F$11:$F$78),G33)/H33,0)*H33))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -2003,7 +2003,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D34,$F$11:$F$76),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D34,$F$11:$F$78),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2042,37 +2042,57 @@
         <x:v>R10</x:v>
       </x:c>
       <x:c r="B35" s="25" t="str">
-        <x:v>PD 200k 1% resistor (MPN open)</x:v>
-      </x:c>
-      <x:c r="C35" s="25"/>
-      <x:c r="D35" s="25"/>
-      <x:c r="E35" s="25"/>
+        <x:v>PD 200k 1% resistor</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D35" s="25" t="str">
+        <x:v>RC0603FR-07200KL</x:v>
+      </x:c>
+      <x:c r="E35" s="25" t="str">
+        <x:v>C105604</x:v>
+      </x:c>
       <x:c r="F35" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-      <x:c r="I35" t="str">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D35,$F$11:$F$76),G35)/H35,0)*H35))</x:f>
-      </x:c>
-      <x:c r="J35"/>
-      <x:c r="K35" s="26"/>
-      <x:c r="L35" s="27" t="str">
+      <x:c r="G35" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D35,$F$11:$F$78),G35)/H35,0)*H35))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K35" s="26" t="n">
+        <x:v>0.0024</x:v>
+      </x:c>
+      <x:c r="L35" s="27" t="n">
         <x:f>IF(K35="","",ROUND(F35*K35,4))</x:f>
+        <x:v>0.0024</x:v>
       </x:c>
       <x:c r="M35" s="27" t="str">
         <x:f>IF(OR(K35="",I35="",N35=""),"",IF(N35&gt;=I35,ROUND(I35*K35,4),""))</x:f>
       </x:c>
       <x:c r="N35"/>
       <x:c r="O35" t="str">
-        <x:v>Stock/price unverified</x:v>
-      </x:c>
-      <x:c r="P35" s="16"/>
-      <x:c r="Q35"/>
-      <x:c r="R35" t="str">
-        <x:v>Sheet value 200k 1%; MPN/LCSC unselected.</x:v>
-      </x:c>
-      <x:c r="S35"/>
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P35" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q35" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R35" t="str"/>
+      <x:c r="S35" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C105604.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="36" customHeight="1">
       <x:c r="A36" s="25" t="str">
@@ -2090,7 +2110,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D36,$F$11:$F$76),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D36,$F$11:$F$78),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2135,7 +2155,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D37,$F$11:$F$76),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D37,$F$11:$F$78),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2197,7 +2217,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D38,$F$11:$F$76),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D38,$F$11:$F$78),G38)/H38,0)*H38))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2257,7 +2277,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D39,$F$11:$F$76),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D39,$F$11:$F$78),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2317,7 +2337,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D40,$F$11:$F$76),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D40,$F$11:$F$78),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2379,7 +2399,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D41,$F$11:$F$76),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D41,$F$11:$F$78),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2420,37 +2440,57 @@
         <x:v>C182, C183</x:v>
       </x:c>
       <x:c r="B42" s="25" t="str">
-        <x:v>TPS25730D CC1/CC2 330pF C0G filters (MPN open)</x:v>
-      </x:c>
-      <x:c r="C42" s="25"/>
-      <x:c r="D42" s="25"/>
-      <x:c r="E42" s="25"/>
+        <x:v>TPS25730D CC1/CC2 330pF C0G filters</x:v>
+      </x:c>
+      <x:c r="C42" s="25" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D42" s="25" t="str">
+        <x:v>CL10C331JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E42" s="25" t="str">
+        <x:v>C1578</x:v>
+      </x:c>
       <x:c r="F42" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G42"/>
-      <x:c r="H42"/>
-      <x:c r="I42" t="str">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D42,$F$11:$F$76),G42)/H42,0)*H42))</x:f>
-      </x:c>
-      <x:c r="J42"/>
-      <x:c r="K42" s="26"/>
-      <x:c r="L42" s="27" t="str">
+      <x:c r="G42" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D42,$F$11:$F$78),G42)/H42,0)*H42))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K42" s="26" t="n">
+        <x:v>0.0089</x:v>
+      </x:c>
+      <x:c r="L42" s="27" t="n">
         <x:f>IF(K42="","",ROUND(F42*K42,4))</x:f>
+        <x:v>0.0178</x:v>
       </x:c>
       <x:c r="M42" s="27" t="str">
         <x:f>IF(OR(K42="",I42="",N42=""),"",IF(N42&gt;=I42,ROUND(I42*K42,4),""))</x:f>
       </x:c>
       <x:c r="N42"/>
       <x:c r="O42" t="str">
-        <x:v>Stock/price unverified</x:v>
-      </x:c>
-      <x:c r="P42" s="16"/>
-      <x:c r="Q42"/>
-      <x:c r="R42" t="str">
-        <x:v>Unselected 0603 C0G part.</x:v>
-      </x:c>
-      <x:c r="S42"/>
+        <x:v>Listing snapshot</x:v>
+      </x:c>
+      <x:c r="P42" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R42" t="str"/>
+      <x:c r="S42" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C1578.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="36" customHeight="1">
       <x:c r="A43" s="25" t="str">
@@ -2478,7 +2518,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D43,$F$11:$F$76),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D43,$F$11:$F$78),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2537,7 +2577,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D44,$F$11:$F$76),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D44,$F$11:$F$78),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2597,7 +2637,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D45,$F$11:$F$76),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D45,$F$11:$F$78),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2657,7 +2697,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D46,$F$11:$F$76),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D46,$F$11:$F$78),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2717,7 +2757,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D47,$F$11:$F$76),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D47,$F$11:$F$78),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2774,7 +2814,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D48,$F$11:$F$76),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D48,$F$11:$F$78),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2834,7 +2874,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D49,$F$11:$F$76),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D49,$F$11:$F$78),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2894,7 +2934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D50,$F$11:$F$76),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D50,$F$11:$F$78),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2953,7 +2993,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D51,$F$11:$F$76),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D51,$F$11:$F$78),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3013,7 +3053,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D52,$F$11:$F$76),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D52,$F$11:$F$78),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3072,7 +3112,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D53,$F$11:$F$76),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D53,$F$11:$F$78),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3131,7 +3171,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D54,$F$11:$F$76),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D54,$F$11:$F$78),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3193,7 +3233,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D55,$F$11:$F$76),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D55,$F$11:$F$78),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3255,7 +3295,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D56,$F$11:$F$76),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D56,$F$11:$F$78),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3306,7 +3346,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D57,$F$11:$F$76),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D57,$F$11:$F$78),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3327,7 +3367,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3342,7 +3382,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3351,7 +3391,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D58,$F$11:$F$76),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D58,$F$11:$F$78),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3362,7 +3402,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.0888</x:v>
+        <x:v>0.111</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3411,7 +3451,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D59,$F$11:$F$76),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D59,$F$11:$F$78),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3471,7 +3511,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D60,$F$11:$F$76),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D60,$F$11:$F$78),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3530,7 +3570,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D61,$F$11:$F$76),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D61,$F$11:$F$78),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3590,7 +3630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D62,$F$11:$F$76),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D62,$F$11:$F$78),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3649,7 +3689,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D63,$F$11:$F$76),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D63,$F$11:$F$78),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3711,7 +3751,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D64,$F$11:$F$76),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D64,$F$11:$F$78),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3770,7 +3810,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D65,$F$11:$F$76),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D65,$F$11:$F$78),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3832,7 +3872,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D66,$F$11:$F$76),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D66,$F$11:$F$78),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3894,7 +3934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D67,$F$11:$F$76),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D67,$F$11:$F$78),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3954,7 +3994,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D68,$F$11:$F$76),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D68,$F$11:$F$78),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -3990,10 +4030,10 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154</x:v>
+        <x:v>R152, R153, R154, R160</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
-        <x:v>100k EN / MODE / bleeder resistors</x:v>
+        <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
       </x:c>
       <x:c r="C69" s="25" t="str">
         <x:v>YAGEO</x:v>
@@ -4005,7 +4045,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4014,7 +4054,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D69,$F$11:$F$76),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D69,$F$11:$F$78),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4025,7 +4065,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0108</x:v>
+        <x:v>0.0144</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4073,7 +4113,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D70,$F$11:$F$76),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D70,$F$11:$F$78),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4134,7 +4174,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D71,$F$11:$F$76),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D71,$F$11:$F$78),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4192,7 +4232,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D72,$F$11:$F$76),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D72,$F$11:$F$78),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4241,7 +4281,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D73,$F$11:$F$76),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D73,$F$11:$F$78),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4300,7 +4340,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D74,$F$11:$F$76),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D74,$F$11:$F$78),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4361,7 +4401,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D75,$F$11:$F$76),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D75,$F$11:$F$78),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4421,7 +4461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$76,D76,$F$11:$F$76),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D76,$F$11:$F$78),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4456,53 +4496,131 @@
       </x:c>
     </x:row>
     <x:row r="77" ht="36" customHeight="1">
-      <x:c r="A77" s="25"/>
-      <x:c r="B77" s="25"/>
-      <x:c r="C77" s="25"/>
-      <x:c r="D77" s="25"/>
-      <x:c r="E77" s="25"/>
-      <x:c r="F77" s="25"/>
-      <x:c r="G77"/>
-      <x:c r="H77"/>
-      <x:c r="I77"/>
-      <x:c r="J77"/>
-      <x:c r="K77" s="26"/>
-      <x:c r="L77" s="27"/>
-      <x:c r="M77" s="27"/>
-      <x:c r="N77"/>
-      <x:c r="O77"/>
-      <x:c r="P77" s="16"/>
-      <x:c r="Q77"/>
-      <x:c r="R77"/>
-      <x:c r="S77"/>
+      <x:c r="A77" s="25" t="str">
+        <x:v>C161</x:v>
+      </x:c>
+      <x:c r="B77" s="25" t="str">
+        <x:v>MCU VDD/VDDA 4.7uF bulk (DS12992 fig. 13)</x:v>
+      </x:c>
+      <x:c r="C77" s="25" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D77" s="25" t="str">
+        <x:v>CL10A475KO8NNNC</x:v>
+      </x:c>
+      <x:c r="E77" s="25" t="str">
+        <x:v>C19666</x:v>
+      </x:c>
+      <x:c r="F77" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I77" t="n">
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D77,$F$11:$F$78),G77)/H77,0)*H77))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K77" s="26" t="n">
+        <x:v>0.0298</x:v>
+      </x:c>
+      <x:c r="L77" s="27" t="n">
+        <x:f>IF(K77="","",ROUND(F77*K77,4))</x:f>
+        <x:v>0.0298</x:v>
+      </x:c>
+      <x:c r="M77" s="27" t="n">
+        <x:f>IF(OR(K77="",I77="",N77=""),"",IF(N77&gt;=I77,ROUND(I77*K77,4),""))</x:f>
+        <x:v>0.298</x:v>
+      </x:c>
+      <x:c r="N77" t="n">
+        <x:v>138390</x:v>
+      </x:c>
+      <x:c r="O77" t="str">
+        <x:v>Listing snapshot, 2026-10-06</x:v>
+      </x:c>
+      <x:c r="P77" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q77" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R77" t="str">
+        <x:v>LCSC listing 4.7uF/16V X5R 0603; DC-bias derating at 3.0 V not checked.</x:v>
+      </x:c>
+      <x:c r="S77" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C19666.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="21" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B78" s="21"/>
-      <x:c r="C78" s="21"/>
-      <x:c r="D78" s="21"/>
-      <x:c r="E78" s="21"/>
-      <x:c r="F78" s="21"/>
-      <x:c r="G78"/>
-      <x:c r="H78"/>
-      <x:c r="I78"/>
-      <x:c r="J78"/>
-      <x:c r="K78" s="26"/>
-      <x:c r="L78" s="27"/>
-      <x:c r="M78" s="27"/>
-      <x:c r="N78"/>
-      <x:c r="O78"/>
-      <x:c r="P78" s="16"/>
-      <x:c r="Q78"/>
-      <x:c r="R78"/>
-      <x:c r="S78"/>
+        <x:v>J6</x:v>
+      </x:c>
+      <x:c r="B78" s="21" t="str">
+        <x:v>MCU SWD header 1x5 2.54 mm</x:v>
+      </x:c>
+      <x:c r="C78" s="21" t="str">
+        <x:v>XYECONN</x:v>
+      </x:c>
+      <x:c r="D78" s="21" t="str">
+        <x:v>XY-MTP254-1X5</x:v>
+      </x:c>
+      <x:c r="E78" s="21" t="str">
+        <x:v>C54110162</x:v>
+      </x:c>
+      <x:c r="F78" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H78" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I78" t="n">
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D78,$F$11:$F$78),G78)/H78,0)*H78))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J78" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K78" s="26" t="n">
+        <x:v>0.0267</x:v>
+      </x:c>
+      <x:c r="L78" s="27" t="n">
+        <x:f>IF(K78="","",ROUND(F78*K78,4))</x:f>
+        <x:v>0.0267</x:v>
+      </x:c>
+      <x:c r="M78" s="27" t="n">
+        <x:f>IF(OR(K78="",I78="",N78=""),"",IF(N78&gt;=I78,ROUND(I78*K78,4),""))</x:f>
+        <x:v>0.267</x:v>
+      </x:c>
+      <x:c r="N78" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="O78" t="str">
+        <x:v>Listing snapshot, 2026-10-06</x:v>
+      </x:c>
+      <x:c r="P78" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q78" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R78" t="str">
+        <x:v>1x5 straight THT header; footprint PinHeader_1x05_P2.54mm_Vertical (stock KiCad STEP). Pin order 1 SWDIO 2 SWCLK 3 NRST 4 3V_AO 5 GND.</x:v>
+      </x:c>
+      <x:c r="S78" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C54110162.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
-      <x:c r="A79" s="21" t="str">
-        <x:v>U2: Only 4 available in page snapshot.</x:v>
-      </x:c>
+      <x:c r="A79" s="21"/>
       <x:c r="B79" s="21"/>
       <x:c r="C79" s="21"/>
       <x:c r="D79" s="21"/>
@@ -4524,7 +4642,7 @@
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="21" t="str">
-        <x:v>U6, U7: Refreshed full product page differs from older cached prices.</x:v>
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
       <x:c r="B80" s="21"/>
       <x:c r="C80" s="21"/>
@@ -4546,55 +4664,30 @@
       <x:c r="S80"/>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
-      <x:c r="A81" t="str">
-        <x:v>U4/U11/Q103 prices are review-time snapshots or unverified; C2/C6/D7/R10/C182/C183 per candidate review; TPS25730D 5-20 V integration 2026-10-05.</x:v>
-      </x:c>
+      <x:c r="A81"/>
       <x:c r="B81"/>
-      <x:c r="C81" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D81" t="str">
-        <x:v>CL10C331JB8NNNC</x:v>
-      </x:c>
-      <x:c r="E81" t="str">
-        <x:v>C1578</x:v>
-      </x:c>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
       <x:c r="F81"/>
-      <x:c r="G81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$100,D81,$F$11:$F$100),G81)/H81,0)*H81))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K81" t="n">
-        <x:v>0.0089</x:v>
-      </x:c>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81" t="str"/>
+      <x:c r="J81"/>
+      <x:c r="K81"/>
       <x:c r="L81"/>
       <x:c r="M81"/>
-      <x:c r="N81" t="str"/>
-      <x:c r="O81" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P81" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q81" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
+      <x:c r="N81"/>
+      <x:c r="O81"/>
+      <x:c r="P81"/>
+      <x:c r="Q81"/>
       <x:c r="R81"/>
-      <x:c r="S81" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1578.html</x:v>
-      </x:c>
+      <x:c r="S81"/>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
-      <x:c r="A82"/>
+      <x:c r="A82" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B82"/>
       <x:c r="C82"/>
       <x:c r="D82"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R251dda92d91f4db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R31fc1f4fda48428b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf292f786c25747fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R48a4253aa4534ae6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L78),2)</x:f>
-        <x:v>68.9</x:v>
+        <x:f>ROUND(SUM(L11:L83),2)</x:f>
+        <x:v>69.49</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M78),2)</x:f>
-        <x:v>85.55</x:v>
+        <x:f>ROUND(SUM(M11:M83),2)</x:f>
+        <x:v>86.01</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D11,$F$11:$F$78),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D11,$F$11:$F$83),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D12,$F$11:$F$78),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D12,$F$11:$F$83),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -778,7 +778,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D13,$F$11:$F$78),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D13,$F$11:$F$83),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -827,7 +827,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D14,$F$11:$F$78),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D14,$F$11:$F$83),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -887,7 +887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D15,$F$11:$F$78),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D15,$F$11:$F$83),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -947,7 +947,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D16,$F$11:$F$78),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D16,$F$11:$F$83),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1007,7 +1007,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D17,$F$11:$F$78),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D17,$F$11:$F$83),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1067,7 +1067,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D18,$F$11:$F$78),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D18,$F$11:$F$83),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1127,7 +1127,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D19,$F$11:$F$78),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D19,$F$11:$F$83),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1187,7 +1187,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D20,$F$11:$F$78),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D20,$F$11:$F$83),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1247,7 +1247,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D21,$F$11:$F$78),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D21,$F$11:$F$83),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1303,7 +1303,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D22,$F$11:$F$78),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D22,$F$11:$F$83),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1352,7 +1352,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D23,$F$11:$F$78),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D23,$F$11:$F$83),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1412,7 +1412,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D24,$F$11:$F$78),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D24,$F$11:$F$83),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1472,7 +1472,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D25,$F$11:$F$78),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D25,$F$11:$F$83),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1532,7 +1532,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D26,$F$11:$F$78),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D26,$F$11:$F$83),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1592,7 +1592,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D27,$F$11:$F$78),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D27,$F$11:$F$83),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1652,7 +1652,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D28,$F$11:$F$78),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D28,$F$11:$F$83),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1708,7 +1708,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D29,$F$11:$F$78),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D29,$F$11:$F$83),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1757,7 +1757,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D30,$F$11:$F$78),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D30,$F$11:$F$83),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1817,7 +1817,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D31,$F$11:$F$78),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D31,$F$11:$F$83),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1879,7 +1879,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D32,$F$11:$F$78),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D32,$F$11:$F$83),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1917,7 +1917,7 @@
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184</x:v>
+        <x:v>C184, C170, C171, C172, C173, C174</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
         <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
@@ -1932,7 +1932,7 @@
         <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>10</x:v>
@@ -1941,7 +1941,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D33,$F$11:$F$78),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D33,$F$11:$F$83),G33)/H33,0)*H33))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -1952,7 +1952,7 @@
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.0403</x:v>
+        <x:v>0.2418</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
@@ -1979,7 +1979,7 @@
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="25" t="str">
-        <x:v>C5</x:v>
+        <x:v>C5, C186, C187</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
         <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
@@ -1994,7 +1994,7 @@
         <x:v>C51205</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>10</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D34,$F$11:$F$78),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D34,$F$11:$F$83),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2014,7 +2014,7 @@
       </x:c>
       <x:c r="L34" s="27" t="n">
         <x:f>IF(K34="","",ROUND(F34*K34,4))</x:f>
-        <x:v>0.0759</x:v>
+        <x:v>0.2277</x:v>
       </x:c>
       <x:c r="M34" s="27" t="n">
         <x:f>IF(OR(K34="",I34="",N34=""),"",IF(N34&gt;=I34,ROUND(I34*K34,4),""))</x:f>
@@ -2063,7 +2063,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D35,$F$11:$F$78),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D35,$F$11:$F$83),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2110,7 +2110,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D36,$F$11:$F$78),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D36,$F$11:$F$83),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2155,7 +2155,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D37,$F$11:$F$78),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D37,$F$11:$F$83),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2193,7 +2193,7 @@
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="25" t="str">
-        <x:v>C102, C109, C181, C185</x:v>
+        <x:v>C102, C109, C181, C185, C175, C176</x:v>
       </x:c>
       <x:c r="B38" s="25" t="str">
         <x:v>10uF / 10V X7R 0805 capacitors (charger REGN/PD CVIN_3V3)</x:v>
@@ -2208,7 +2208,7 @@
         <x:v>C32635</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G38" t="n">
         <x:v>10</x:v>
@@ -2217,7 +2217,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D38,$F$11:$F$78),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D38,$F$11:$F$83),G38)/H38,0)*H38))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2228,7 +2228,7 @@
       </x:c>
       <x:c r="L38" s="27" t="n">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v>0.372</x:v>
+        <x:v>0.558</x:v>
       </x:c>
       <x:c r="M38" s="27" t="n">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
@@ -2277,7 +2277,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D39,$F$11:$F$78),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D39,$F$11:$F$83),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2337,7 +2337,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D40,$F$11:$F$78),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D40,$F$11:$F$83),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2399,7 +2399,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D41,$F$11:$F$78),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D41,$F$11:$F$83),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2461,7 +2461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D42,$F$11:$F$78),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D42,$F$11:$F$83),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2518,7 +2518,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D43,$F$11:$F$78),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D43,$F$11:$F$83),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2577,7 +2577,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D44,$F$11:$F$78),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D44,$F$11:$F$83),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2637,7 +2637,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D45,$F$11:$F$78),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D45,$F$11:$F$83),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2697,7 +2697,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D46,$F$11:$F$78),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D46,$F$11:$F$83),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2757,7 +2757,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D47,$F$11:$F$78),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D47,$F$11:$F$83),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2814,7 +2814,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D48,$F$11:$F$78),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D48,$F$11:$F$83),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2874,7 +2874,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D49,$F$11:$F$78),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D49,$F$11:$F$83),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2934,7 +2934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D50,$F$11:$F$78),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D50,$F$11:$F$83),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2993,7 +2993,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D51,$F$11:$F$78),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D51,$F$11:$F$83),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3053,7 +3053,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D52,$F$11:$F$78),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D52,$F$11:$F$83),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3112,7 +3112,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D53,$F$11:$F$78),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D53,$F$11:$F$83),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3171,7 +3171,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D54,$F$11:$F$78),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D54,$F$11:$F$83),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3233,7 +3233,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D55,$F$11:$F$78),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D55,$F$11:$F$83),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3295,7 +3295,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D56,$F$11:$F$78),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D56,$F$11:$F$83),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3346,7 +3346,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D57,$F$11:$F$78),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D57,$F$11:$F$83),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3391,7 +3391,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D58,$F$11:$F$78),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D58,$F$11:$F$83),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3451,7 +3451,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D59,$F$11:$F$78),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D59,$F$11:$F$83),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3511,7 +3511,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D60,$F$11:$F$78),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D60,$F$11:$F$83),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3570,7 +3570,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D61,$F$11:$F$78),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D61,$F$11:$F$83),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3630,7 +3630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D62,$F$11:$F$78),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D62,$F$11:$F$83),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3689,7 +3689,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D63,$F$11:$F$78),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D63,$F$11:$F$83),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3751,7 +3751,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D64,$F$11:$F$78),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D64,$F$11:$F$83),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3810,7 +3810,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D65,$F$11:$F$78),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D65,$F$11:$F$83),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3872,7 +3872,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D66,$F$11:$F$78),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D66,$F$11:$F$83),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3934,7 +3934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D67,$F$11:$F$78),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D67,$F$11:$F$83),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3994,7 +3994,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D68,$F$11:$F$78),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D68,$F$11:$F$83),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4030,7 +4030,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4045,7 +4045,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4054,7 +4054,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D69,$F$11:$F$78),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D69,$F$11:$F$83),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4065,7 +4065,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0144</x:v>
+        <x:v>0.0216</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4113,7 +4113,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D70,$F$11:$F$78),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D70,$F$11:$F$83),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4174,7 +4174,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D71,$F$11:$F$78),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D71,$F$11:$F$83),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4232,7 +4232,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D72,$F$11:$F$78),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D72,$F$11:$F$83),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4281,7 +4281,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D73,$F$11:$F$78),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D73,$F$11:$F$83),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4340,7 +4340,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D74,$F$11:$F$78),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D74,$F$11:$F$83),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4401,7 +4401,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D75,$F$11:$F$78),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D75,$F$11:$F$83),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4437,7 +4437,7 @@
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
       <x:c r="A76" s="25" t="str">
-        <x:v>R126, R127</x:v>
+        <x:v>R126, R127, R174</x:v>
       </x:c>
       <x:c r="B76" s="25" t="str">
         <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
@@ -4452,7 +4452,7 @@
         <x:v>C105578</x:v>
       </x:c>
       <x:c r="F76" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G76" t="n">
         <x:v>100</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D76,$F$11:$F$78),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D76,$F$11:$F$83),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4472,7 +4472,7 @@
       </x:c>
       <x:c r="L76" s="27" t="n">
         <x:f>IF(K76="","",ROUND(F76*K76,4))</x:f>
-        <x:v>0.0112</x:v>
+        <x:v>0.0168</x:v>
       </x:c>
       <x:c r="M76" s="27" t="n">
         <x:f>IF(OR(K76="",I76="",N76=""),"",IF(N76&gt;=I76,ROUND(I76*K76,4),""))</x:f>
@@ -4521,7 +4521,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D77,$F$11:$F$78),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D77,$F$11:$F$83),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4583,7 +4583,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$78,D78,$F$11:$F$78),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D78,$F$11:$F$83),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4620,113 +4620,288 @@
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
-      <x:c r="A79" s="21"/>
-      <x:c r="B79" s="21"/>
-      <x:c r="C79" s="21"/>
-      <x:c r="D79" s="21"/>
-      <x:c r="E79" s="21"/>
-      <x:c r="F79" s="21"/>
-      <x:c r="G79"/>
-      <x:c r="H79"/>
-      <x:c r="I79"/>
-      <x:c r="J79"/>
-      <x:c r="K79" s="26"/>
-      <x:c r="L79" s="27"/>
-      <x:c r="M79" s="27"/>
-      <x:c r="N79"/>
-      <x:c r="O79"/>
-      <x:c r="P79" s="16"/>
-      <x:c r="Q79"/>
-      <x:c r="R79"/>
-      <x:c r="S79"/>
+      <x:c r="A79" s="21" t="str">
+        <x:v>Y170</x:v>
+      </x:c>
+      <x:c r="B79" s="21" t="str">
+        <x:v>12 MHz crystal for PCM2902C (3225-4P, CL 20 pF, +/-10 ppm)</x:v>
+      </x:c>
+      <x:c r="C79" s="21" t="str">
+        <x:v>YXC</x:v>
+      </x:c>
+      <x:c r="D79" s="21" t="str">
+        <x:v>X322512MSB4SI</x:v>
+      </x:c>
+      <x:c r="E79" s="21" t="str">
+        <x:v>C9002</x:v>
+      </x:c>
+      <x:c r="F79" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H79" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I79" t="n">
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D79,$F$11:$F$83),G79)/H79,0)*H79))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J79" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K79" s="26" t="n">
+        <x:v>0.0371</x:v>
+      </x:c>
+      <x:c r="L79" s="27" t="n">
+        <x:f>IF(K79="","",ROUND(F79*K79,4))</x:f>
+        <x:v>0.0371</x:v>
+      </x:c>
+      <x:c r="M79" s="27" t="n">
+        <x:f>IF(OR(K79="",I79="",N79=""),"",IF(N79&gt;=I79,ROUND(I79*K79,4),""))</x:f>
+        <x:v>0.371</x:v>
+      </x:c>
+      <x:c r="N79" t="n">
+        <x:v>312110</x:v>
+      </x:c>
+      <x:c r="O79" t="str">
+        <x:v>Listing snapshot, 2026-10-06</x:v>
+      </x:c>
+      <x:c r="P79" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q79" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R79" t="str">
+        <x:v>Search-result snapshot; datasheet not retrieved. Pads 1/3 crystal, 2/4 GND assumed (generic 3225-4P) - verify. 22 pF load caps give ~14 pF CL, below the 20 pF rating: tune at bring-up.</x:v>
+      </x:c>
+      <x:c r="S79" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C9002.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="21" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B80" s="21"/>
-      <x:c r="C80" s="21"/>
-      <x:c r="D80" s="21"/>
-      <x:c r="E80" s="21"/>
-      <x:c r="F80" s="21"/>
-      <x:c r="G80"/>
-      <x:c r="H80"/>
-      <x:c r="I80"/>
-      <x:c r="J80"/>
+        <x:v>C177, C178</x:v>
+      </x:c>
+      <x:c r="B80" s="21" t="str">
+        <x:v>Crystal load capacitors 22 pF C0G 0603</x:v>
+      </x:c>
+      <x:c r="C80" s="21" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D80" s="21" t="str">
+        <x:v>CL10C220JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E80" s="21" t="str">
+        <x:v>C1653</x:v>
+      </x:c>
+      <x:c r="F80" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G80" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H80" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I80" t="n">
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D80,$F$11:$F$83),G80)/H80,0)*H80))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J80" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="K80" s="26"/>
-      <x:c r="L80" s="27"/>
-      <x:c r="M80" s="27"/>
+      <x:c r="L80" s="27" t="str">
+        <x:f>IF(K80="","",ROUND(F80*K80,4))</x:f>
+      </x:c>
+      <x:c r="M80" s="27" t="str">
+        <x:f>IF(OR(K80="",I80="",N80=""),"",IF(N80&gt;=I80,ROUND(I80*K80,4),""))</x:f>
+      </x:c>
       <x:c r="N80"/>
-      <x:c r="O80"/>
-      <x:c r="P80" s="16"/>
-      <x:c r="Q80"/>
-      <x:c r="R80"/>
-      <x:c r="S80"/>
+      <x:c r="O80" t="str">
+        <x:v>LCSC number from search result; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P80" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q80" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R80" t="str">
+        <x:v>DS: 10-33 pF depending on crystal.</x:v>
+      </x:c>
+      <x:c r="S80" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C1653.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
-      <x:c r="A81"/>
-      <x:c r="B81"/>
-      <x:c r="C81"/>
-      <x:c r="D81"/>
-      <x:c r="E81"/>
-      <x:c r="F81"/>
-      <x:c r="G81"/>
-      <x:c r="H81"/>
-      <x:c r="I81" t="str"/>
-      <x:c r="J81"/>
+      <x:c r="A81" t="str">
+        <x:v>R170</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>PCM2902C VBUS filter 2.2 ohm 1% 0603</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>RC0603FR-072R2L</x:v>
+      </x:c>
+      <x:c r="E81" t="str"/>
+      <x:c r="F81" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I81" t="n">
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D81,$F$11:$F$83),G81)/H81,0)*H81))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J81" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="K81"/>
-      <x:c r="L81"/>
-      <x:c r="M81"/>
+      <x:c r="L81" t="str">
+        <x:f>IF(K81="","",ROUND(F81*K81,4))</x:f>
+      </x:c>
+      <x:c r="M81" t="str">
+        <x:f>IF(OR(K81="",I81="",N81=""),"",IF(N81&gt;=I81,ROUND(I81*K81,4),""))</x:f>
+      </x:c>
       <x:c r="N81"/>
-      <x:c r="O81"/>
-      <x:c r="P81"/>
-      <x:c r="Q81"/>
-      <x:c r="R81"/>
-      <x:c r="S81"/>
+      <x:c r="O81" t="str">
+        <x:v>LCSC number not found</x:v>
+      </x:c>
+      <x:c r="P81" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q81" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R81" t="str">
+        <x:v>Part number follows the family; LCSC code and price still to be looked up.</x:v>
+      </x:c>
+      <x:c r="S81" t="str"/>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B82"/>
-      <x:c r="C82"/>
-      <x:c r="D82"/>
-      <x:c r="E82"/>
-      <x:c r="F82"/>
-      <x:c r="G82"/>
-      <x:c r="H82"/>
-      <x:c r="I82"/>
-      <x:c r="J82"/>
+        <x:v>R171, R172</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>USB D+/D- 22 ohm series resistors 0603</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>RC0603FR-0722RL</x:v>
+      </x:c>
+      <x:c r="E82" t="str"/>
+      <x:c r="F82" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G82" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H82" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I82" t="n">
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D82,$F$11:$F$83),G82)/H82,0)*H82))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J82" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="K82"/>
-      <x:c r="L82"/>
-      <x:c r="M82"/>
+      <x:c r="L82" t="str">
+        <x:f>IF(K82="","",ROUND(F82*K82,4))</x:f>
+      </x:c>
+      <x:c r="M82" t="str">
+        <x:f>IF(OR(K82="",I82="",N82=""),"",IF(N82&gt;=I82,ROUND(I82*K82,4),""))</x:f>
+      </x:c>
       <x:c r="N82"/>
-      <x:c r="O82"/>
-      <x:c r="P82"/>
-      <x:c r="Q82"/>
-      <x:c r="R82"/>
-      <x:c r="S82"/>
+      <x:c r="O82" t="str">
+        <x:v>LCSC number not found</x:v>
+      </x:c>
+      <x:c r="P82" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q82" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R82" t="str">
+        <x:v>Alternative seen in search: UNI-ROYAL 0603WAJ0220T5E / C1203 (22 ohm, 5%).</x:v>
+      </x:c>
+      <x:c r="S82" t="str"/>
     </x:row>
     <x:row r="83" ht="48" customHeight="1">
-      <x:c r="A83"/>
-      <x:c r="B83"/>
-      <x:c r="C83"/>
-      <x:c r="D83"/>
-      <x:c r="E83"/>
-      <x:c r="F83"/>
-      <x:c r="G83"/>
-      <x:c r="H83"/>
-      <x:c r="I83"/>
-      <x:c r="J83"/>
-      <x:c r="K83"/>
-      <x:c r="L83"/>
-      <x:c r="M83"/>
-      <x:c r="N83"/>
-      <x:c r="O83"/>
-      <x:c r="P83"/>
-      <x:c r="Q83"/>
-      <x:c r="R83"/>
-      <x:c r="S83"/>
+      <x:c r="A83" t="str">
+        <x:v>R173</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>D+ pull-up 1.5 kohm 1% 0603 (to VDDI)</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>RC0603FR-071K5L</x:v>
+      </x:c>
+      <x:c r="E83" t="str">
+        <x:v>C114668</x:v>
+      </x:c>
+      <x:c r="F83" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H83" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I83" t="n">
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D83,$F$11:$F$83),G83)/H83,0)*H83))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J83" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K83" t="n">
+        <x:v>0.0009</x:v>
+      </x:c>
+      <x:c r="L83" t="n">
+        <x:f>IF(K83="","",ROUND(F83*K83,4))</x:f>
+        <x:v>0.0009</x:v>
+      </x:c>
+      <x:c r="M83" t="n">
+        <x:f>IF(OR(K83="",I83="",N83=""),"",IF(N83&gt;=I83,ROUND(I83*K83,4),""))</x:f>
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="N83" t="n">
+        <x:v>507200</x:v>
+      </x:c>
+      <x:c r="O83" t="str">
+        <x:v>Listing snapshot, 2026-10-06</x:v>
+      </x:c>
+      <x:c r="P83" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q83" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R83" t="str">
+        <x:v>Search-result price/stock.</x:v>
+      </x:c>
+      <x:c r="S83" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C114668.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
       <x:c r="A84"/>
@@ -4750,7 +4925,9 @@
       <x:c r="S84"/>
     </x:row>
     <x:row r="85" ht="48" customHeight="1">
-      <x:c r="A85"/>
+      <x:c r="A85" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B85"/>
       <x:c r="C85"/>
       <x:c r="D85"/>
@@ -4792,7 +4969,9 @@
       <x:c r="S86"/>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87"/>
+      <x:c r="A87" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B87"/>
       <x:c r="C87"/>
       <x:c r="D87"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf292f786c25747fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R48a4253aa4534ae6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf99eb1f3366647af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R45b8aee9a936483b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
         <x:f>ROUND(SUM(L11:L83),2)</x:f>
-        <x:v>69.49</x:v>
+        <x:v>69.46</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -462,7 +462,7 @@
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
         <x:f>ROUND(SUM(M11:M83),2)</x:f>
-        <x:v>86.01</x:v>
+        <x:v>85.75</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -4562,16 +4562,16 @@
         <x:v>J6</x:v>
       </x:c>
       <x:c r="B78" s="21" t="str">
-        <x:v>MCU SWD header 1x5 2.54 mm</x:v>
+        <x:v>MCU SWD header 1x4 2.54 mm (J7 Tag-Connect TC2030 is PCB pads only, no BOM part)</x:v>
       </x:c>
       <x:c r="C78" s="21" t="str">
-        <x:v>XYECONN</x:v>
+        <x:v>Ckmtw</x:v>
       </x:c>
       <x:c r="D78" s="21" t="str">
-        <x:v>XY-MTP254-1X5</x:v>
+        <x:v>B-2100S04P-A110</x:v>
       </x:c>
       <x:c r="E78" s="21" t="str">
-        <x:v>C54110162</x:v>
+        <x:v>C124378</x:v>
       </x:c>
       <x:c r="F78" s="21" t="n">
         <x:v>1</x:v>
@@ -4589,22 +4589,16 @@
       <x:c r="J78" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K78" s="26" t="n">
-        <x:v>0.0267</x:v>
-      </x:c>
-      <x:c r="L78" s="27" t="n">
+      <x:c r="K78" s="26"/>
+      <x:c r="L78" s="27" t="str">
         <x:f>IF(K78="","",ROUND(F78*K78,4))</x:f>
-        <x:v>0.0267</x:v>
-      </x:c>
-      <x:c r="M78" s="27" t="n">
+      </x:c>
+      <x:c r="M78" s="27" t="str">
         <x:f>IF(OR(K78="",I78="",N78=""),"",IF(N78&gt;=I78,ROUND(I78*K78,4),""))</x:f>
-        <x:v>0.267</x:v>
-      </x:c>
-      <x:c r="N78" t="n">
-        <x:v>1830</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N78"/>
       <x:c r="O78" t="str">
-        <x:v>Listing snapshot, 2026-10-06</x:v>
+        <x:v>LCSC number from search; price/stock unverified</x:v>
       </x:c>
       <x:c r="P78" s="16" t="n">
         <x:v>46300</x:v>
@@ -4613,10 +4607,10 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R78" t="str">
-        <x:v>1x5 straight THT header; footprint PinHeader_1x05_P2.54mm_Vertical (stock KiCad STEP). Pin order 1 SWDIO 2 SWCLK 3 NRST 4 3V_AO 5 GND.</x:v>
+        <x:v>1x4 straight THT header; footprint PinHeader_1x04_P2.54mm_Vertical (stock KiCad STEP). Pin order 1 SWDIO 2 SWCLK 3 NRST 4 GND. Programmer cable TC2030-IDC (legged footprint J7) is a tool, not fitted.</x:v>
       </x:c>
       <x:c r="S78" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54110162.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C124378.html</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
@@ -4675,7 +4669,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R79" t="str">
-        <x:v>Search-result snapshot; datasheet not retrieved. Pads 1/3 crystal, 2/4 GND assumed (generic 3225-4P) - verify. 22 pF load caps give ~14 pF CL, below the 20 pF rating: tune at bring-up.</x:v>
+        <x:v>Search-result snapshot; datasheet not retrieved. Pads 1/3 crystal, 2/4 GND assumed (generic 3225-4P) - verify. 33 pF load caps (C177/C178) give ~19.5 pF effective CL incl. stray, vs 20 pF rating.</x:v>
       </x:c>
       <x:c r="S79" t="str">
         <x:v>https://www.lcsc.com/product-detail/C9002.html</x:v>
@@ -4686,16 +4680,16 @@
         <x:v>C177, C178</x:v>
       </x:c>
       <x:c r="B80" s="21" t="str">
-        <x:v>Crystal load capacitors 22 pF C0G 0603</x:v>
+        <x:v>Crystal load capacitors 33 pF C0G 0603</x:v>
       </x:c>
       <x:c r="C80" s="21" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D80" s="21" t="str">
-        <x:v>CL10C220JB8NNNC</x:v>
+        <x:v>CL10C330JB8NNNC</x:v>
       </x:c>
       <x:c r="E80" s="21" t="str">
-        <x:v>C1653</x:v>
+        <x:v>C1663</x:v>
       </x:c>
       <x:c r="F80" s="21" t="n">
         <x:v>2</x:v>
@@ -4722,7 +4716,7 @@
       </x:c>
       <x:c r="N80"/>
       <x:c r="O80" t="str">
-        <x:v>LCSC number from search result; price/stock unverified</x:v>
+        <x:v>Search snapshot: from ~0.0026 USD, ~517,700 in stock (unverified)</x:v>
       </x:c>
       <x:c r="P80" s="16" t="n">
         <x:v>46300</x:v>
@@ -4731,10 +4725,10 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R80" t="str">
-        <x:v>DS: 10-33 pF depending on crystal.</x:v>
+        <x:v>33 pF + ~3 pF stray each side gives ~19.5 pF effective vs 20 pF crystal rating (DS: 10-33 pF).</x:v>
       </x:c>
       <x:c r="S80" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1653.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C1663.html</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
@@ -4750,7 +4744,9 @@
       <x:c r="D81" t="str">
         <x:v>RC0603FR-072R2L</x:v>
       </x:c>
-      <x:c r="E81" t="str"/>
+      <x:c r="E81" t="str">
+        <x:v>C112307</x:v>
+      </x:c>
       <x:c r="F81" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4776,7 +4772,7 @@
       </x:c>
       <x:c r="N81"/>
       <x:c r="O81" t="str">
-        <x:v>LCSC number not found</x:v>
+        <x:v>LCSC number from JLCPCB/LCSC listing; price/stock unverified</x:v>
       </x:c>
       <x:c r="P81" t="n">
         <x:v>46300</x:v>
@@ -4785,9 +4781,11 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R81" t="str">
-        <x:v>Part number follows the family; LCSC code and price still to be looked up.</x:v>
-      </x:c>
-      <x:c r="S81" t="str"/>
+        <x:v>Yageo RC0603FR-072R2L, 2.2 ohm 1% 0603.</x:v>
+      </x:c>
+      <x:c r="S81" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C112307.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" t="str">
@@ -4802,7 +4800,9 @@
       <x:c r="D82" t="str">
         <x:v>RC0603FR-0722RL</x:v>
       </x:c>
-      <x:c r="E82" t="str"/>
+      <x:c r="E82" t="str">
+        <x:v>C107701</x:v>
+      </x:c>
       <x:c r="F82" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4828,7 +4828,7 @@
       </x:c>
       <x:c r="N82"/>
       <x:c r="O82" t="str">
-        <x:v>LCSC number not found</x:v>
+        <x:v>Search snapshot: from ~0.0018 USD, ~216,200 in stock (unverified)</x:v>
       </x:c>
       <x:c r="P82" t="n">
         <x:v>46300</x:v>
@@ -4837,9 +4837,11 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R82" t="str">
-        <x:v>Alternative seen in search: UNI-ROYAL 0603WAJ0220T5E / C1203 (22 ohm, 5%).</x:v>
-      </x:c>
-      <x:c r="S82" t="str"/>
+        <x:v>Yageo RC0603FR-0722RL, 22 ohm 1% 0603.</x:v>
+      </x:c>
+      <x:c r="S82" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C107701.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="48" customHeight="1">
       <x:c r="A83" t="str">

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rf99eb1f3366647af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R45b8aee9a936483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R04e63c59fac44743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rb27476c5454d4687"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L83),2)</x:f>
-        <x:v>69.46</x:v>
+        <x:f>ROUND(SUM(L11:L85),2)</x:f>
+        <x:v>69.82</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M83),2)</x:f>
-        <x:v>85.75</x:v>
+        <x:f>ROUND(SUM(M11:M85),2)</x:f>
+        <x:v>85.86</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D11,$F$11:$F$83),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D11,$F$11:$F$85),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D12,$F$11:$F$83),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D12,$F$11:$F$85),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -778,7 +778,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D13,$F$11:$F$83),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D13,$F$11:$F$85),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -827,7 +827,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D14,$F$11:$F$83),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D14,$F$11:$F$85),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -887,7 +887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D15,$F$11:$F$83),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D15,$F$11:$F$85),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -947,7 +947,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D16,$F$11:$F$83),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D16,$F$11:$F$85),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1007,7 +1007,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D17,$F$11:$F$83),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D17,$F$11:$F$85),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1067,7 +1067,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D18,$F$11:$F$83),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D18,$F$11:$F$85),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1127,7 +1127,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D19,$F$11:$F$83),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D19,$F$11:$F$85),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1187,7 +1187,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D20,$F$11:$F$83),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D20,$F$11:$F$85),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1247,7 +1247,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D21,$F$11:$F$83),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D21,$F$11:$F$85),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1303,7 +1303,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D22,$F$11:$F$83),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D22,$F$11:$F$85),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1352,7 +1352,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D23,$F$11:$F$83),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D23,$F$11:$F$85),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1412,7 +1412,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D24,$F$11:$F$83),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D24,$F$11:$F$85),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1472,7 +1472,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D25,$F$11:$F$83),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D25,$F$11:$F$85),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1532,7 +1532,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D26,$F$11:$F$83),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D26,$F$11:$F$85),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1592,7 +1592,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D27,$F$11:$F$83),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D27,$F$11:$F$85),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1652,7 +1652,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D28,$F$11:$F$83),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D28,$F$11:$F$85),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1708,7 +1708,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D29,$F$11:$F$83),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D29,$F$11:$F$85),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1757,7 +1757,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D30,$F$11:$F$83),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D30,$F$11:$F$85),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1817,7 +1817,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D31,$F$11:$F$83),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D31,$F$11:$F$85),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1879,7 +1879,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D32,$F$11:$F$83),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D32,$F$11:$F$85),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1917,7 +1917,7 @@
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184, C170, C171, C172, C173, C174</x:v>
+        <x:v>C184, C170, C171, C172, C173, C174, C192, C193</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
         <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
@@ -1932,7 +1932,7 @@
         <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>10</x:v>
@@ -1941,7 +1941,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D33,$F$11:$F$83),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D33,$F$11:$F$85),G33)/H33,0)*H33))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -1952,7 +1952,7 @@
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.2418</x:v>
+        <x:v>0.3224</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
@@ -1979,7 +1979,7 @@
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="25" t="str">
-        <x:v>C5, C186, C187</x:v>
+        <x:v>C5, C186, C187, C194, C195</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
         <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
@@ -1994,7 +1994,7 @@
         <x:v>C51205</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>10</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D34,$F$11:$F$83),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D34,$F$11:$F$85),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2014,7 +2014,7 @@
       </x:c>
       <x:c r="L34" s="27" t="n">
         <x:f>IF(K34="","",ROUND(F34*K34,4))</x:f>
-        <x:v>0.2277</x:v>
+        <x:v>0.3795</x:v>
       </x:c>
       <x:c r="M34" s="27" t="n">
         <x:f>IF(OR(K34="",I34="",N34=""),"",IF(N34&gt;=I34,ROUND(I34*K34,4),""))</x:f>
@@ -2063,7 +2063,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D35,$F$11:$F$83),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D35,$F$11:$F$85),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2110,7 +2110,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D36,$F$11:$F$83),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D36,$F$11:$F$85),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2155,7 +2155,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D37,$F$11:$F$83),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D37,$F$11:$F$85),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2193,7 +2193,7 @@
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="25" t="str">
-        <x:v>C102, C109, C181, C185, C175, C176</x:v>
+        <x:v>C102, C109, C181, C185, C175, C176, C190</x:v>
       </x:c>
       <x:c r="B38" s="25" t="str">
         <x:v>10uF / 10V X7R 0805 capacitors (charger REGN/PD CVIN_3V3)</x:v>
@@ -2208,7 +2208,7 @@
         <x:v>C32635</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G38" t="n">
         <x:v>10</x:v>
@@ -2217,7 +2217,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D38,$F$11:$F$83),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D38,$F$11:$F$85),G38)/H38,0)*H38))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2228,7 +2228,7 @@
       </x:c>
       <x:c r="L38" s="27" t="n">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v>0.558</x:v>
+        <x:v>0.651</x:v>
       </x:c>
       <x:c r="M38" s="27" t="n">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
@@ -2277,7 +2277,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D39,$F$11:$F$83),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D39,$F$11:$F$85),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2337,7 +2337,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D40,$F$11:$F$83),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D40,$F$11:$F$85),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2399,7 +2399,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D41,$F$11:$F$83),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D41,$F$11:$F$85),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2461,7 +2461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D42,$F$11:$F$83),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D42,$F$11:$F$85),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2518,7 +2518,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D43,$F$11:$F$83),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D43,$F$11:$F$85),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2577,7 +2577,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D44,$F$11:$F$83),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D44,$F$11:$F$85),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2637,7 +2637,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D45,$F$11:$F$83),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D45,$F$11:$F$85),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2697,7 +2697,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D46,$F$11:$F$83),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D46,$F$11:$F$85),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2757,7 +2757,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D47,$F$11:$F$83),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D47,$F$11:$F$85),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2814,7 +2814,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D48,$F$11:$F$83),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D48,$F$11:$F$85),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2874,7 +2874,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D49,$F$11:$F$83),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D49,$F$11:$F$85),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2910,7 +2910,7 @@
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="25" t="str">
-        <x:v>R11, R13, R14, R15, R18</x:v>
+        <x:v>R11, R13, R14, R15, R18, R182, R183</x:v>
       </x:c>
       <x:c r="B50" s="25" t="str">
         <x:v>TPS25730D 10k 1% resistors (CC/ADC, I2C pull-ups R14/R15, pin 36 R18)</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>C98220</x:v>
       </x:c>
       <x:c r="F50" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>100</x:v>
@@ -2934,7 +2934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D50,$F$11:$F$83),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D50,$F$11:$F$85),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2945,7 +2945,7 @@
       </x:c>
       <x:c r="L50" s="27" t="n">
         <x:f>IF(K50="","",ROUND(F50*K50,4))</x:f>
-        <x:v>0.017</x:v>
+        <x:v>0.0238</x:v>
       </x:c>
       <x:c r="M50" s="27" t="str">
         <x:f>IF(OR(K50="",I50="",N50=""),"",IF(N50&gt;=I50,ROUND(I50*K50,4),""))</x:f>
@@ -2993,7 +2993,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D51,$F$11:$F$83),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D51,$F$11:$F$85),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3053,7 +3053,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D52,$F$11:$F$83),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D52,$F$11:$F$85),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3112,7 +3112,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D53,$F$11:$F$83),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D53,$F$11:$F$85),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3171,7 +3171,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D54,$F$11:$F$83),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D54,$F$11:$F$85),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3233,7 +3233,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D55,$F$11:$F$83),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D55,$F$11:$F$85),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3295,7 +3295,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D56,$F$11:$F$83),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D56,$F$11:$F$85),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3346,7 +3346,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D57,$F$11:$F$83),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D57,$F$11:$F$85),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3367,7 +3367,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3382,7 +3382,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3391,7 +3391,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D58,$F$11:$F$83),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D58,$F$11:$F$85),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3402,7 +3402,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.111</x:v>
+        <x:v>0.1221</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3451,7 +3451,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D59,$F$11:$F$83),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D59,$F$11:$F$85),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3511,7 +3511,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D60,$F$11:$F$83),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D60,$F$11:$F$85),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3570,7 +3570,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D61,$F$11:$F$83),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D61,$F$11:$F$85),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3630,7 +3630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D62,$F$11:$F$83),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D62,$F$11:$F$85),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3689,7 +3689,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D63,$F$11:$F$83),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D63,$F$11:$F$85),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3751,7 +3751,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D64,$F$11:$F$83),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D64,$F$11:$F$85),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3810,7 +3810,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D65,$F$11:$F$83),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D65,$F$11:$F$85),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3872,7 +3872,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D66,$F$11:$F$83),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D66,$F$11:$F$85),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3934,7 +3934,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D67,$F$11:$F$83),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D67,$F$11:$F$85),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3994,7 +3994,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D68,$F$11:$F$83),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D68,$F$11:$F$85),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4030,7 +4030,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4045,7 +4045,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4054,7 +4054,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D69,$F$11:$F$83),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D69,$F$11:$F$85),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4065,7 +4065,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0216</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4113,7 +4113,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D70,$F$11:$F$83),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D70,$F$11:$F$85),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4174,7 +4174,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D71,$F$11:$F$83),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D71,$F$11:$F$85),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4232,7 +4232,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D72,$F$11:$F$83),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D72,$F$11:$F$85),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4281,7 +4281,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D73,$F$11:$F$83),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D73,$F$11:$F$85),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4340,7 +4340,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D74,$F$11:$F$83),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D74,$F$11:$F$85),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4401,7 +4401,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D75,$F$11:$F$83),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D75,$F$11:$F$85),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4461,7 +4461,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D76,$F$11:$F$83),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D76,$F$11:$F$85),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4521,7 +4521,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D77,$F$11:$F$83),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D77,$F$11:$F$85),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4583,7 +4583,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D78,$F$11:$F$83),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D78,$F$11:$F$85),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4639,7 +4639,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D79,$F$11:$F$83),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D79,$F$11:$F$85),G79)/H79,0)*H79))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4701,7 +4701,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D80,$F$11:$F$83),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D80,$F$11:$F$85),G80)/H80,0)*H80))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4757,7 +4757,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D81,$F$11:$F$83),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D81,$F$11:$F$85),G81)/H81,0)*H81))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4813,7 +4813,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D82,$F$11:$F$83),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D82,$F$11:$F$85),G82)/H82,0)*H82))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4869,7 +4869,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$83,D83,$F$11:$F$83),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D83,$F$11:$F$85),G83)/H83,0)*H83))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" t="n">
@@ -4906,48 +4906,122 @@
       </x:c>
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
-      <x:c r="A84"/>
-      <x:c r="B84"/>
-      <x:c r="C84"/>
-      <x:c r="D84"/>
-      <x:c r="E84"/>
-      <x:c r="F84"/>
-      <x:c r="G84"/>
-      <x:c r="H84"/>
-      <x:c r="I84"/>
-      <x:c r="J84"/>
-      <x:c r="K84"/>
-      <x:c r="L84"/>
-      <x:c r="M84"/>
-      <x:c r="N84"/>
-      <x:c r="O84"/>
-      <x:c r="P84"/>
-      <x:c r="Q84"/>
-      <x:c r="R84"/>
-      <x:c r="S84"/>
+      <x:c r="A84" t="str">
+        <x:v>R185, R186, R187</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>BM83 RST_N series (R185) and UART_TXD / P0_0 TX_IND series (R186, R187) 1 kohm 1% 0603</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>RC0603FR-071KL</x:v>
+      </x:c>
+      <x:c r="E84" t="str">
+        <x:v>C22548</x:v>
+      </x:c>
+      <x:c r="F84" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I84" t="n">
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D84,$F$11:$F$85),G84)/H84,0)*H84))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J84" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K84" t="n">
+        <x:v>0.0011</x:v>
+      </x:c>
+      <x:c r="L84" t="n">
+        <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
+        <x:v>0.0033</x:v>
+      </x:c>
+      <x:c r="M84" t="n">
+        <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="N84" t="n">
+        <x:v>9947200</x:v>
+      </x:c>
+      <x:c r="O84" t="str">
+        <x:v>Search-result price/stock, 2026-10-06</x:v>
+      </x:c>
+      <x:c r="P84" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q84" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R84" t="str">
+        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified.</x:v>
+      </x:c>
+      <x:c r="S84" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C22548.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="48" customHeight="1">
       <x:c r="A85" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B85"/>
-      <x:c r="C85"/>
-      <x:c r="D85"/>
-      <x:c r="E85"/>
-      <x:c r="F85"/>
-      <x:c r="G85"/>
-      <x:c r="H85"/>
-      <x:c r="I85"/>
-      <x:c r="J85"/>
+        <x:v>J8</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>BM83 test/programming header 1x5 2.54 mm (RST_N, P3_4, UART RX/TX, GND)</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>XYECONN</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>XY-MTP254-1X5</x:v>
+      </x:c>
+      <x:c r="E85" t="str">
+        <x:v>C54110162</x:v>
+      </x:c>
+      <x:c r="F85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H85" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I85" t="n">
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D85,$F$11:$F$85),G85)/H85,0)*H85))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J85" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="K85"/>
-      <x:c r="L85"/>
-      <x:c r="M85"/>
+      <x:c r="L85" t="str">
+        <x:f>IF(K85="","",ROUND(F85*K85,4))</x:f>
+      </x:c>
+      <x:c r="M85" t="str">
+        <x:f>IF(OR(K85="",I85="",N85=""),"",IF(N85&gt;=I85,ROUND(I85*K85,4),""))</x:f>
+      </x:c>
       <x:c r="N85"/>
-      <x:c r="O85"/>
-      <x:c r="P85"/>
-      <x:c r="Q85"/>
-      <x:c r="R85"/>
-      <x:c r="S85"/>
+      <x:c r="O85" t="str">
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P85" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q85" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R85" t="str">
+        <x:v>Bluetooth sheet; part number carried from the earlier 1x5 SWD header selection, not re-verified.</x:v>
+      </x:c>
+      <x:c r="S85" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C54110162.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86"/>
@@ -5015,7 +5089,9 @@
       <x:c r="S88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89"/>
+      <x:c r="A89" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B89"/>
       <x:c r="C89"/>
       <x:c r="D89"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R04e63c59fac44743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rb27476c5454d4687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R02056123ae4e4edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R9ded64ac860b489a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L85),2)</x:f>
-        <x:v>69.82</x:v>
+        <x:f>ROUND(SUM(L11:L86),2)</x:f>
+        <x:v>69.18</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M85),2)</x:f>
-        <x:v>85.86</x:v>
+        <x:f>ROUND(SUM(M11:M86),2)</x:f>
+        <x:v>85.21</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D11,$F$11:$F$85),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D11,$F$11:$F$86),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -701,16 +701,16 @@
         <x:v>U3</x:v>
       </x:c>
       <x:c r="B12" s="22" t="str">
-        <x:v>System control</x:v>
+        <x:v>System control (LQFP64; 128 KB flash, 36 KB RAM)</x:v>
       </x:c>
       <x:c r="C12" s="22" t="str">
         <x:v>ST</x:v>
       </x:c>
       <x:c r="D12" s="22" t="str">
-        <x:v>STM32G031K8T6</x:v>
+        <x:v>STM32G071RBT6</x:v>
       </x:c>
       <x:c r="E12" s="22" t="str">
-        <x:v>C432203</x:v>
+        <x:v>C432213</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
         <x:v>1</x:v>
@@ -722,38 +722,40 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D12,$F$11:$F$85),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D12,$F$11:$F$86),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K12" s="28" t="n">
-        <x:v>3.107</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="L12" s="30" t="n">
         <x:f>IF(K12="","",ROUND(F12*K12,4))</x:f>
-        <x:v>3.107</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="M12" s="30" t="n">
         <x:f>IF(OR(K12="",I12="",N12=""),"",IF(N12&gt;=I12,ROUND(I12*K12,4),""))</x:f>
-        <x:v>3.107</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="N12" s="7" t="n">
-        <x:v>299</x:v>
+        <x:v>1597</x:v>
       </x:c>
       <x:c r="O12" s="1" t="str">
-        <x:v>In stock</x:v>
+        <x:v>Search snapshot 2026-10-06 (architecture doc); verify at order</x:v>
       </x:c>
       <x:c r="P12" s="4" t="n">
-        <x:v>46297</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q12" s="1" t="str">
-        <x:v>today</x:v>
-      </x:c>
-      <x:c r="R12" s="1"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R12" s="1" t="str">
+        <x:v>Replaces STM32G031K8T6 (C432203): audio chain needs about 46 GPIO. Price/stock not re-verified.</x:v>
+      </x:c>
       <x:c r="S12" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C432203.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C432213.html</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
@@ -778,7 +780,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D13,$F$11:$F$85),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D13,$F$11:$F$86),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -827,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D14,$F$11:$F$85),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D14,$F$11:$F$86),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -887,7 +889,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D15,$F$11:$F$85),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D15,$F$11:$F$86),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -947,7 +949,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D16,$F$11:$F$85),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D16,$F$11:$F$86),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1007,7 +1009,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D17,$F$11:$F$85),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D17,$F$11:$F$86),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1067,7 +1069,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D18,$F$11:$F$85),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D18,$F$11:$F$86),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1127,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D19,$F$11:$F$85),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D19,$F$11:$F$86),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1187,7 +1189,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D20,$F$11:$F$85),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D20,$F$11:$F$86),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1247,7 +1249,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D21,$F$11:$F$85),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D21,$F$11:$F$86),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1303,7 +1305,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D22,$F$11:$F$85),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D22,$F$11:$F$86),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1352,7 +1354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D23,$F$11:$F$85),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D23,$F$11:$F$86),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1412,7 +1414,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D24,$F$11:$F$85),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D24,$F$11:$F$86),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1472,7 +1474,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D25,$F$11:$F$85),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D25,$F$11:$F$86),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1532,7 +1534,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D26,$F$11:$F$85),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D26,$F$11:$F$86),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1592,7 +1594,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D27,$F$11:$F$85),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D27,$F$11:$F$86),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1652,7 +1654,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D28,$F$11:$F$85),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D28,$F$11:$F$86),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1708,7 +1710,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D29,$F$11:$F$85),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D29,$F$11:$F$86),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1757,7 +1759,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D30,$F$11:$F$85),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D30,$F$11:$F$86),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1817,7 +1819,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D31,$F$11:$F$85),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D31,$F$11:$F$86),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1879,7 +1881,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D32,$F$11:$F$85),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D32,$F$11:$F$86),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1941,7 +1943,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D33,$F$11:$F$85),G33)/H33,0)*H33))</x:f>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D33,$F$11:$F$86),G33)/H33,0)*H33))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J33" t="n">
@@ -2003,7 +2005,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D34,$F$11:$F$85),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D34,$F$11:$F$86),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2063,7 +2065,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D35,$F$11:$F$85),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D35,$F$11:$F$86),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2110,7 +2112,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D36,$F$11:$F$85),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D36,$F$11:$F$86),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2155,7 +2157,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D37,$F$11:$F$85),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D37,$F$11:$F$86),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2217,7 +2219,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D38,$F$11:$F$85),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D38,$F$11:$F$86),G38)/H38,0)*H38))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2277,7 +2279,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D39,$F$11:$F$85),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D39,$F$11:$F$86),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2337,7 +2339,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D40,$F$11:$F$85),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D40,$F$11:$F$86),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2399,7 +2401,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D41,$F$11:$F$85),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D41,$F$11:$F$86),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2461,7 +2463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D42,$F$11:$F$85),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D42,$F$11:$F$86),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2518,7 +2520,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D43,$F$11:$F$85),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D43,$F$11:$F$86),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2577,7 +2579,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D44,$F$11:$F$85),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D44,$F$11:$F$86),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2637,7 +2639,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D45,$F$11:$F$85),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D45,$F$11:$F$86),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2697,7 +2699,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D46,$F$11:$F$85),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D46,$F$11:$F$86),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2757,7 +2759,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D47,$F$11:$F$85),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D47,$F$11:$F$86),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2814,7 +2816,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D48,$F$11:$F$85),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D48,$F$11:$F$86),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2874,7 +2876,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D49,$F$11:$F$85),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D49,$F$11:$F$86),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2934,7 +2936,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D50,$F$11:$F$85),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D50,$F$11:$F$86),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2993,7 +2995,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D51,$F$11:$F$85),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D51,$F$11:$F$86),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3053,7 +3055,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D52,$F$11:$F$85),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D52,$F$11:$F$86),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3112,7 +3114,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D53,$F$11:$F$85),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D53,$F$11:$F$86),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3171,7 +3173,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D54,$F$11:$F$85),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D54,$F$11:$F$86),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3233,7 +3235,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D55,$F$11:$F$85),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D55,$F$11:$F$86),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3295,7 +3297,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D56,$F$11:$F$85),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D56,$F$11:$F$86),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3346,7 +3348,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D57,$F$11:$F$85),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D57,$F$11:$F$86),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3367,7 +3369,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3382,7 +3384,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3391,7 +3393,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D58,$F$11:$F$85),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D58,$F$11:$F$86),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3402,7 +3404,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.1221</x:v>
+        <x:v>0.1332</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3451,7 +3453,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D59,$F$11:$F$85),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D59,$F$11:$F$86),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3511,7 +3513,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D60,$F$11:$F$85),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D60,$F$11:$F$86),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3570,7 +3572,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D61,$F$11:$F$85),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D61,$F$11:$F$86),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3630,7 +3632,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D62,$F$11:$F$85),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D62,$F$11:$F$86),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3689,7 +3691,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D63,$F$11:$F$85),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D63,$F$11:$F$86),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3751,7 +3753,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D64,$F$11:$F$85),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D64,$F$11:$F$86),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3810,7 +3812,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D65,$F$11:$F$85),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D65,$F$11:$F$86),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3872,7 +3874,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D66,$F$11:$F$85),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D66,$F$11:$F$86),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3934,7 +3936,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D67,$F$11:$F$85),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D67,$F$11:$F$86),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3994,7 +3996,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D68,$F$11:$F$85),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D68,$F$11:$F$86),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4030,7 +4032,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4045,7 +4047,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4054,7 +4056,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D69,$F$11:$F$85),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D69,$F$11:$F$86),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4065,7 +4067,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0324</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4113,7 +4115,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D70,$F$11:$F$85),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D70,$F$11:$F$86),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4174,7 +4176,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D71,$F$11:$F$85),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D71,$F$11:$F$86),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4232,7 +4234,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D72,$F$11:$F$85),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D72,$F$11:$F$86),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4281,7 +4283,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D73,$F$11:$F$85),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D73,$F$11:$F$86),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4340,7 +4342,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D74,$F$11:$F$85),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D74,$F$11:$F$86),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4401,7 +4403,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D75,$F$11:$F$85),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D75,$F$11:$F$86),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4461,7 +4463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D76,$F$11:$F$85),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D76,$F$11:$F$86),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4521,7 +4523,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D77,$F$11:$F$85),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D77,$F$11:$F$86),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4583,7 +4585,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D78,$F$11:$F$85),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D78,$F$11:$F$86),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4639,7 +4641,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D79,$F$11:$F$85),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D79,$F$11:$F$86),G79)/H79,0)*H79))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4701,7 +4703,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D80,$F$11:$F$85),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D80,$F$11:$F$86),G80)/H80,0)*H80))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4757,7 +4759,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D81,$F$11:$F$85),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D81,$F$11:$F$86),G81)/H81,0)*H81))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4813,7 +4815,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D82,$F$11:$F$85),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D82,$F$11:$F$86),G82)/H82,0)*H82))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4869,7 +4871,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D83,$F$11:$F$85),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D83,$F$11:$F$86),G83)/H83,0)*H83))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" t="n">
@@ -4931,7 +4933,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D84,$F$11:$F$85),G84)/H84,0)*H84))</x:f>
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D84,$F$11:$F$86),G84)/H84,0)*H84))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J84" t="n">
@@ -4993,7 +4995,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$85,D85,$F$11:$F$85),G85)/H85,0)*H85))</x:f>
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D85,$F$11:$F$86),G85)/H85,0)*H85))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J85" t="n">
@@ -5024,30 +5026,63 @@
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
-      <x:c r="A86"/>
-      <x:c r="B86"/>
-      <x:c r="C86"/>
-      <x:c r="D86"/>
-      <x:c r="E86"/>
-      <x:c r="F86"/>
-      <x:c r="G86"/>
-      <x:c r="H86"/>
-      <x:c r="I86"/>
-      <x:c r="J86"/>
+      <x:c r="A86" t="str">
+        <x:v>C164</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>MCU VREF+ 1uF (DS12232 fig. 13)</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>CL10A105KB8NNNC</x:v>
+      </x:c>
+      <x:c r="E86" t="str">
+        <x:v>C15849</x:v>
+      </x:c>
+      <x:c r="F86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I86" t="n">
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D86,$F$11:$F$86),G86)/H86,0)*H86))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J86" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="K86"/>
-      <x:c r="L86"/>
-      <x:c r="M86"/>
+      <x:c r="L86" t="str">
+        <x:f>IF(K86="","",ROUND(F86*K86,4))</x:f>
+      </x:c>
+      <x:c r="M86" t="str">
+        <x:f>IF(OR(K86="",I86="",N86=""),"",IF(N86&gt;=I86,ROUND(I86*K86,4),""))</x:f>
+      </x:c>
       <x:c r="N86"/>
-      <x:c r="O86"/>
-      <x:c r="P86"/>
-      <x:c r="Q86"/>
-      <x:c r="R86"/>
-      <x:c r="S86"/>
+      <x:c r="O86" t="str">
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P86" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q86" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R86" t="str">
+        <x:v>LCSC code from memory of the Samsung 1uF 0603 family; verify code, voltage rating and DC-bias at order.</x:v>
+      </x:c>
+      <x:c r="S86" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C15849.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A87"/>
       <x:c r="B87"/>
       <x:c r="C87"/>
       <x:c r="D87"/>
@@ -5068,7 +5103,9 @@
       <x:c r="S87"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88"/>
+      <x:c r="A88" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B88"/>
       <x:c r="C88"/>
       <x:c r="D88"/>
@@ -5089,9 +5126,7 @@
       <x:c r="S88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A89"/>
       <x:c r="B89"/>
       <x:c r="C89"/>
       <x:c r="D89"/>
@@ -5112,7 +5147,9 @@
       <x:c r="S89"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90"/>
+      <x:c r="A90" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B90"/>
       <x:c r="C90"/>
       <x:c r="D90"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R02056123ae4e4edd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R9ded64ac860b489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R25686a9d28eb4ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rbc74c9e2df1842a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L86),2)</x:f>
-        <x:v>69.18</x:v>
+        <x:f>ROUND(SUM(L11:L97),2)</x:f>
+        <x:v>69.85</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M86),2)</x:f>
-        <x:v>85.21</x:v>
+        <x:f>ROUND(SUM(M11:M97),2)</x:f>
+        <x:v>86.54</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D11,$F$11:$F$86),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D11,$F$11:$F$97),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D12,$F$11:$F$86),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D12,$F$11:$F$97),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -780,7 +780,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D13,$F$11:$F$86),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D13,$F$11:$F$97),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -829,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D14,$F$11:$F$86),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D14,$F$11:$F$97),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -889,7 +889,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D15,$F$11:$F$86),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D15,$F$11:$F$97),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -949,7 +949,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D16,$F$11:$F$86),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D16,$F$11:$F$97),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1009,7 +1009,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D17,$F$11:$F$86),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D17,$F$11:$F$97),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1069,7 +1069,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D18,$F$11:$F$86),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D18,$F$11:$F$97),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1129,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D19,$F$11:$F$86),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D19,$F$11:$F$97),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1189,7 +1189,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D20,$F$11:$F$86),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D20,$F$11:$F$97),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1249,7 +1249,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D21,$F$11:$F$86),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D21,$F$11:$F$97),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1305,7 +1305,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D22,$F$11:$F$86),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D22,$F$11:$F$97),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1354,7 +1354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D23,$F$11:$F$86),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D23,$F$11:$F$97),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1414,7 +1414,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D24,$F$11:$F$86),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D24,$F$11:$F$97),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1474,7 +1474,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D25,$F$11:$F$86),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D25,$F$11:$F$97),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1534,7 +1534,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D26,$F$11:$F$86),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D26,$F$11:$F$97),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1594,7 +1594,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D27,$F$11:$F$86),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D27,$F$11:$F$97),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1654,7 +1654,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D28,$F$11:$F$86),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D28,$F$11:$F$97),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1710,7 +1710,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D29,$F$11:$F$86),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D29,$F$11:$F$97),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1759,7 +1759,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D30,$F$11:$F$86),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D30,$F$11:$F$97),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1819,7 +1819,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D31,$F$11:$F$86),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D31,$F$11:$F$97),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1881,7 +1881,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D32,$F$11:$F$86),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D32,$F$11:$F$97),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1919,7 +1919,7 @@
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184, C170, C171, C172, C173, C174, C192, C193</x:v>
+        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
         <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
@@ -1934,7 +1934,7 @@
         <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>10</x:v>
@@ -1943,8 +1943,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D33,$F$11:$F$86),G33)/H33,0)*H33))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D33,$F$11:$F$97),G33)/H33,0)*H33))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J33" t="n">
         <x:v>10</x:v>
@@ -1954,11 +1954,11 @@
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.3224</x:v>
+        <x:v>0.5642</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
-        <x:v>0.403</x:v>
+        <x:v>0.806</x:v>
       </x:c>
       <x:c r="N33" t="n">
         <x:v>1363910</x:v>
@@ -2005,7 +2005,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D34,$F$11:$F$86),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D34,$F$11:$F$97),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2065,7 +2065,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D35,$F$11:$F$86),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D35,$F$11:$F$97),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2112,7 +2112,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D36,$F$11:$F$86),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D36,$F$11:$F$97),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2157,7 +2157,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D37,$F$11:$F$86),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D37,$F$11:$F$97),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2195,7 +2195,7 @@
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="25" t="str">
-        <x:v>C102, C109, C181, C185, C175, C176, C190</x:v>
+        <x:v>C102, C109, C181, C185, C175, C176, C190, C214, C216, C218, C223</x:v>
       </x:c>
       <x:c r="B38" s="25" t="str">
         <x:v>10uF / 10V X7R 0805 capacitors (charger REGN/PD CVIN_3V3)</x:v>
@@ -2210,7 +2210,7 @@
         <x:v>C32635</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G38" t="n">
         <x:v>10</x:v>
@@ -2219,8 +2219,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D38,$F$11:$F$86),G38)/H38,0)*H38))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D38,$F$11:$F$97),G38)/H38,0)*H38))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J38" t="n">
         <x:v>10</x:v>
@@ -2230,11 +2230,11 @@
       </x:c>
       <x:c r="L38" s="27" t="n">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v>0.651</x:v>
+        <x:v>1.023</x:v>
       </x:c>
       <x:c r="M38" s="27" t="n">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
-        <x:v>0.93</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="N38" t="n">
         <x:v>230700</x:v>
@@ -2279,7 +2279,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D39,$F$11:$F$86),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D39,$F$11:$F$97),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2339,7 +2339,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D40,$F$11:$F$86),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D40,$F$11:$F$97),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2401,7 +2401,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D41,$F$11:$F$86),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D41,$F$11:$F$97),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2463,7 +2463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D42,$F$11:$F$86),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D42,$F$11:$F$97),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2520,7 +2520,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D43,$F$11:$F$86),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D43,$F$11:$F$97),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2579,7 +2579,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D44,$F$11:$F$86),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D44,$F$11:$F$97),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2639,7 +2639,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D45,$F$11:$F$86),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D45,$F$11:$F$97),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2699,7 +2699,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D46,$F$11:$F$86),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D46,$F$11:$F$97),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2759,7 +2759,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D47,$F$11:$F$86),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D47,$F$11:$F$97),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2816,7 +2816,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D48,$F$11:$F$86),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D48,$F$11:$F$97),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2876,7 +2876,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D49,$F$11:$F$86),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D49,$F$11:$F$97),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2936,7 +2936,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D50,$F$11:$F$86),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D50,$F$11:$F$97),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2995,7 +2995,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D51,$F$11:$F$86),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D51,$F$11:$F$97),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3055,7 +3055,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D52,$F$11:$F$86),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D52,$F$11:$F$97),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3114,7 +3114,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D53,$F$11:$F$86),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D53,$F$11:$F$97),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3173,7 +3173,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D54,$F$11:$F$86),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D54,$F$11:$F$97),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3235,7 +3235,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D55,$F$11:$F$86),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D55,$F$11:$F$97),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3297,7 +3297,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D56,$F$11:$F$86),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D56,$F$11:$F$97),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3348,7 +3348,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D57,$F$11:$F$86),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D57,$F$11:$F$97),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3369,7 +3369,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3384,7 +3384,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3393,7 +3393,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D58,$F$11:$F$86),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D58,$F$11:$F$97),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3404,7 +3404,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.1332</x:v>
+        <x:v>0.1776</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3453,7 +3453,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D59,$F$11:$F$86),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D59,$F$11:$F$97),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3513,7 +3513,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D60,$F$11:$F$86),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D60,$F$11:$F$97),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3572,7 +3572,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D61,$F$11:$F$86),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D61,$F$11:$F$97),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3632,7 +3632,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D62,$F$11:$F$86),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D62,$F$11:$F$97),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3691,7 +3691,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D63,$F$11:$F$86),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D63,$F$11:$F$97),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3753,7 +3753,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D64,$F$11:$F$86),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D64,$F$11:$F$97),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3812,7 +3812,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D65,$F$11:$F$86),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D65,$F$11:$F$97),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3874,7 +3874,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D66,$F$11:$F$86),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D66,$F$11:$F$97),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3936,7 +3936,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D67,$F$11:$F$86),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D67,$F$11:$F$97),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3996,7 +3996,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D68,$F$11:$F$86),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D68,$F$11:$F$97),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4032,7 +4032,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4047,7 +4047,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D69,$F$11:$F$86),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D69,$F$11:$F$97),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4067,7 +4067,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.036</x:v>
+        <x:v>0.0432</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4115,7 +4115,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D70,$F$11:$F$86),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D70,$F$11:$F$97),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4176,7 +4176,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D71,$F$11:$F$86),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D71,$F$11:$F$97),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4234,7 +4234,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D72,$F$11:$F$86),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D72,$F$11:$F$97),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4283,7 +4283,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D73,$F$11:$F$86),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D73,$F$11:$F$97),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4342,7 +4342,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D74,$F$11:$F$86),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D74,$F$11:$F$97),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4403,7 +4403,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D75,$F$11:$F$86),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D75,$F$11:$F$97),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4463,7 +4463,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D76,$F$11:$F$86),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D76,$F$11:$F$97),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4523,7 +4523,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D77,$F$11:$F$86),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D77,$F$11:$F$97),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4585,7 +4585,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D78,$F$11:$F$86),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D78,$F$11:$F$97),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4641,7 +4641,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D79,$F$11:$F$86),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D79,$F$11:$F$97),G79)/H79,0)*H79))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4703,7 +4703,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D80,$F$11:$F$86),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D80,$F$11:$F$97),G80)/H80,0)*H80))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4759,7 +4759,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D81,$F$11:$F$86),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D81,$F$11:$F$97),G81)/H81,0)*H81))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4815,7 +4815,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D82,$F$11:$F$86),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D82,$F$11:$F$97),G82)/H82,0)*H82))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4871,7 +4871,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D83,$F$11:$F$86),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D83,$F$11:$F$97),G83)/H83,0)*H83))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" t="n">
@@ -4933,7 +4933,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D84,$F$11:$F$86),G84)/H84,0)*H84))</x:f>
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D84,$F$11:$F$97),G84)/H84,0)*H84))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J84" t="n">
@@ -4995,7 +4995,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D85,$F$11:$F$86),G85)/H85,0)*H85))</x:f>
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D85,$F$11:$F$97),G85)/H85,0)*H85))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J85" t="n">
@@ -5051,7 +5051,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I86" t="n">
-        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$86,D86,$F$11:$F$86),G86)/H86,0)*H86))</x:f>
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D86,$F$11:$F$97),G86)/H86,0)*H86))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J86" t="n">
@@ -5082,155 +5082,684 @@
       </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87"/>
-      <x:c r="B87"/>
-      <x:c r="C87"/>
-      <x:c r="D87"/>
-      <x:c r="E87"/>
-      <x:c r="F87"/>
-      <x:c r="G87"/>
-      <x:c r="H87"/>
-      <x:c r="I87"/>
-      <x:c r="J87"/>
+      <x:c r="A87" t="str">
+        <x:v>U24</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>Audio ADC 4:1 input, I2S master (TSSOP-30)</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>TI</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>PCM1862DBTR</x:v>
+      </x:c>
+      <x:c r="E87" t="str">
+        <x:v>C544647</x:v>
+      </x:c>
+      <x:c r="F87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I87" t="n">
+        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D87,$F$11:$F$97),G87)/H87,0)*H87))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J87" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K87"/>
-      <x:c r="L87"/>
-      <x:c r="M87"/>
+      <x:c r="L87" t="str">
+        <x:f>IF(K87="","",ROUND(F87*K87,4))</x:f>
+      </x:c>
+      <x:c r="M87" t="str">
+        <x:f>IF(OR(K87="",I87="",N87=""),"",IF(N87&gt;=I87,ROUND(I87*K87,4),""))</x:f>
+      </x:c>
       <x:c r="N87"/>
-      <x:c r="O87"/>
-      <x:c r="P87"/>
-      <x:c r="Q87"/>
-      <x:c r="R87"/>
-      <x:c r="S87"/>
+      <x:c r="O87" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P87" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q87" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R87" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet SLAS831D.</x:v>
+      </x:c>
+      <x:c r="S87" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C544647.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B88"/>
-      <x:c r="C88"/>
-      <x:c r="D88"/>
-      <x:c r="E88"/>
-      <x:c r="F88"/>
-      <x:c r="G88"/>
-      <x:c r="H88"/>
-      <x:c r="I88"/>
-      <x:c r="J88"/>
+        <x:v>U22</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>3V3_AUDIO 300 mA ultra-low-noise LDO</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>TI</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>TPS7A2033PDBVR</x:v>
+      </x:c>
+      <x:c r="E88" t="str">
+        <x:v>C2862740</x:v>
+      </x:c>
+      <x:c r="F88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I88" t="n">
+        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D88,$F$11:$F$97),G88)/H88,0)*H88))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J88" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K88"/>
-      <x:c r="L88"/>
-      <x:c r="M88"/>
+      <x:c r="L88" t="str">
+        <x:f>IF(K88="","",ROUND(F88*K88,4))</x:f>
+      </x:c>
+      <x:c r="M88" t="str">
+        <x:f>IF(OR(K88="",I88="",N88=""),"",IF(N88&gt;=I88,ROUND(I88*K88,4),""))</x:f>
+      </x:c>
       <x:c r="N88"/>
-      <x:c r="O88"/>
-      <x:c r="P88"/>
-      <x:c r="Q88"/>
-      <x:c r="R88"/>
-      <x:c r="S88"/>
+      <x:c r="O88" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P88" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q88" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R88" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. A TECH PUBLIC TPS7A2033PDBVR-TP clone is listed as C49452001; TI part chosen.</x:v>
+      </x:c>
+      <x:c r="S88" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C2862740.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
-      <x:c r="A89"/>
-      <x:c r="B89"/>
-      <x:c r="C89"/>
-      <x:c r="D89"/>
-      <x:c r="E89"/>
-      <x:c r="F89"/>
-      <x:c r="G89"/>
-      <x:c r="H89"/>
-      <x:c r="I89"/>
-      <x:c r="J89"/>
+      <x:c r="A89" t="str">
+        <x:v>U23</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>5V_CODEC load switch (SOT-23-6)</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>TI</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>TPS22917DBVR</x:v>
+      </x:c>
+      <x:c r="E89" t="str">
+        <x:v>C2681320</x:v>
+      </x:c>
+      <x:c r="F89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I89" t="n">
+        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D89,$F$11:$F$97),G89)/H89,0)*H89))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J89" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K89"/>
-      <x:c r="L89"/>
-      <x:c r="M89"/>
+      <x:c r="L89" t="str">
+        <x:f>IF(K89="","",ROUND(F89*K89,4))</x:f>
+      </x:c>
+      <x:c r="M89" t="str">
+        <x:f>IF(OR(K89="",I89="",N89=""),"",IF(N89&gt;=I89,ROUND(I89*K89,4),""))</x:f>
+      </x:c>
       <x:c r="N89"/>
-      <x:c r="O89"/>
-      <x:c r="P89"/>
-      <x:c r="Q89"/>
-      <x:c r="R89"/>
-      <x:c r="S89"/>
+      <x:c r="O89" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P89" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q89" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R89" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Pinout checked against SLVSDW8B.</x:v>
+      </x:c>
+      <x:c r="S89" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C2681320.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
+        <x:v>Y200</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>24.576 MHz crystal for PCM1862 (3225-4P, CL 15 pF)</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Lucki</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>L327S240P11L</x:v>
+      </x:c>
+      <x:c r="E90" t="str">
+        <x:v>C5261154</x:v>
+      </x:c>
+      <x:c r="F90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I90" t="n">
+        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D90,$F$11:$F$97),G90)/H90,0)*H90))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K90"/>
+      <x:c r="L90" t="str">
+        <x:f>IF(K90="","",ROUND(F90*K90,4))</x:f>
+      </x:c>
+      <x:c r="M90" t="str">
+        <x:f>IF(OR(K90="",I90="",N90=""),"",IF(N90&gt;=I90,ROUND(I90*K90,4),""))</x:f>
+      </x:c>
+      <x:c r="N90"/>
+      <x:c r="O90" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P90" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q90" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R90" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet not retrieved; pad usage 1/3 assumed. Two 20 pF caps give about 13 pF CL; trim at bring-up.</x:v>
+      </x:c>
+      <x:c r="S90" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C5261154.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>FB200</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>AVDD ferrite bead 600 ohm @100 MHz 0603</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>BLM18AG601SN1D</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>C19330</x:v>
+      </x:c>
+      <x:c r="F91" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H91" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I91" t="n">
+        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D91,$F$11:$F$97),G91)/H91,0)*H91))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K91"/>
+      <x:c r="L91" t="str">
+        <x:f>IF(K91="","",ROUND(F91*K91,4))</x:f>
+      </x:c>
+      <x:c r="M91" t="str">
+        <x:f>IF(OR(K91="",I91="",N91=""),"",IF(N91&gt;=I91,ROUND(I91*K91,4),""))</x:f>
+      </x:c>
+      <x:c r="N91"/>
+      <x:c r="O91" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P91" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q91" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R91" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. 0.5 A, 380 mOhm DCR (search snapshot).</x:v>
+      </x:c>
+      <x:c r="S91" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C19330.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>C200, C201, C202, C203, C204, C205</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>Input AC-coupling 2.2uF X7R 0805</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>CL21B225KAFNNNE</x:v>
+      </x:c>
+      <x:c r="E92" t="str"/>
+      <x:c r="F92" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H92" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I92" t="n">
+        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D92,$F$11:$F$97),G92)/H92,0)*H92))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J92" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K92"/>
+      <x:c r="L92" t="str">
+        <x:f>IF(K92="","",ROUND(F92*K92,4))</x:f>
+      </x:c>
+      <x:c r="M92" t="str">
+        <x:f>IF(OR(K92="",I92="",N92=""),"",IF(N92&gt;=I92,ROUND(I92*K92,4),""))</x:f>
+      </x:c>
+      <x:c r="N92"/>
+      <x:c r="O92" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P92" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q92" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R92" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias.</x:v>
+      </x:c>
+      <x:c r="S92" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>C206, C207, C208, C209, C210, C211</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>Input anti-alias 10nF C0G 0603</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>GRM1885C1H103JA01D</x:v>
+      </x:c>
+      <x:c r="E93" t="str"/>
+      <x:c r="F93" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H93" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I93" t="n">
+        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D93,$F$11:$F$97),G93)/H93,0)*H93))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J93" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K93"/>
+      <x:c r="L93" t="str">
+        <x:f>IF(K93="","",ROUND(F93*K93,4))</x:f>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:f>IF(OR(K93="",I93="",N93=""),"",IF(N93&gt;=I93,ROUND(I93*K93,4),""))</x:f>
+      </x:c>
+      <x:c r="N93"/>
+      <x:c r="O93" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P93" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q93" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R93" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+      </x:c>
+      <x:c r="S93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>C226, C227</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>Crystal load capacitors 20 pF C0G 0603</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>CL10C200JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E94" t="str"/>
+      <x:c r="F94" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H94" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I94" t="n">
+        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D94,$F$11:$F$97),G94)/H94,0)*H94))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J94" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K94"/>
+      <x:c r="L94" t="str">
+        <x:f>IF(K94="","",ROUND(F94*K94,4))</x:f>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:f>IF(OR(K94="",I94="",N94=""),"",IF(N94&gt;=I94,ROUND(I94*K94,4),""))</x:f>
+      </x:c>
+      <x:c r="N94"/>
+      <x:c r="O94" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P94" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q94" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R94" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+      </x:c>
+      <x:c r="S94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>R200, R201, R202, R203, R204, R205</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>Input series 100 ohm 1% 0603</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>RC0603FR-07100RL</x:v>
+      </x:c>
+      <x:c r="E95" t="str"/>
+      <x:c r="F95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H95" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I95" t="n">
+        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D95,$F$11:$F$97),G95)/H95,0)*H95))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K95"/>
+      <x:c r="L95" t="str">
+        <x:f>IF(K95="","",ROUND(F95*K95,4))</x:f>
+      </x:c>
+      <x:c r="M95" t="str">
+        <x:f>IF(OR(K95="",I95="",N95=""),"",IF(N95&gt;=I95,ROUND(I95*K95,4),""))</x:f>
+      </x:c>
+      <x:c r="N95"/>
+      <x:c r="O95" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P95" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q95" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R95" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+      </x:c>
+      <x:c r="S95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>R206, R207, R208</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>I2S series 33 ohm 1% 0603</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>RC0603FR-0733RL</x:v>
+      </x:c>
+      <x:c r="E96" t="str"/>
+      <x:c r="F96" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H96" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I96" t="n">
+        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D96,$F$11:$F$97),G96)/H96,0)*H96))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J96" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K96"/>
+      <x:c r="L96" t="str">
+        <x:f>IF(K96="","",ROUND(F96*K96,4))</x:f>
+      </x:c>
+      <x:c r="M96" t="str">
+        <x:f>IF(OR(K96="",I96="",N96=""),"",IF(N96&gt;=I96,ROUND(I96*K96,4),""))</x:f>
+      </x:c>
+      <x:c r="N96"/>
+      <x:c r="O96" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P96" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q96" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R96" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+      </x:c>
+      <x:c r="S96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>R209, R210</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>Audio I2C pull-ups 2.2k 1% 0603</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>RC0603FR-072K2L</x:v>
+      </x:c>
+      <x:c r="E97" t="str"/>
+      <x:c r="F97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H97" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I97" t="n">
+        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D97,$F$11:$F$97),G97)/H97,0)*H97))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J97" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K97"/>
+      <x:c r="L97" t="str">
+        <x:f>IF(K97="","",ROUND(F97*K97,4))</x:f>
+      </x:c>
+      <x:c r="M97" t="str">
+        <x:f>IF(OR(K97="",I97="",N97=""),"",IF(N97&gt;=I97,ROUND(I97*K97,4),""))</x:f>
+      </x:c>
+      <x:c r="N97"/>
+      <x:c r="O97" t="str">
+        <x:v>LCSC code not looked up</x:v>
+      </x:c>
+      <x:c r="P97" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q97" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R97" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+      </x:c>
+      <x:c r="S97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
+      <x:c r="J98"/>
+      <x:c r="K98"/>
+      <x:c r="L98"/>
+      <x:c r="M98"/>
+      <x:c r="N98"/>
+      <x:c r="O98"/>
+      <x:c r="P98"/>
+      <x:c r="Q98"/>
+      <x:c r="R98"/>
+      <x:c r="S98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
         <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
-      <x:c r="B90"/>
-      <x:c r="C90"/>
-      <x:c r="D90"/>
-      <x:c r="E90"/>
-      <x:c r="F90"/>
-      <x:c r="G90"/>
-      <x:c r="H90"/>
-      <x:c r="I90"/>
-      <x:c r="J90"/>
-      <x:c r="K90"/>
-      <x:c r="L90"/>
-      <x:c r="M90"/>
-      <x:c r="N90"/>
-      <x:c r="O90"/>
-      <x:c r="P90"/>
-      <x:c r="Q90"/>
-      <x:c r="R90"/>
-      <x:c r="S90"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91"/>
-      <x:c r="B91"/>
-      <x:c r="C91"/>
-      <x:c r="D91"/>
-      <x:c r="E91"/>
-      <x:c r="F91"/>
-      <x:c r="G91"/>
-      <x:c r="H91"/>
-      <x:c r="I91"/>
-      <x:c r="J91"/>
-      <x:c r="K91"/>
-      <x:c r="L91"/>
-      <x:c r="M91"/>
-      <x:c r="N91"/>
-      <x:c r="O91"/>
-      <x:c r="P91"/>
-      <x:c r="Q91"/>
-      <x:c r="R91"/>
-      <x:c r="S91"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92"/>
-      <x:c r="B92"/>
-      <x:c r="C92"/>
-      <x:c r="D92"/>
-      <x:c r="E92"/>
-      <x:c r="F92"/>
-      <x:c r="G92"/>
-      <x:c r="H92"/>
-      <x:c r="I92"/>
-      <x:c r="J92"/>
-      <x:c r="K92"/>
-      <x:c r="L92"/>
-      <x:c r="M92"/>
-      <x:c r="N92"/>
-      <x:c r="O92"/>
-      <x:c r="P92"/>
-      <x:c r="Q92"/>
-      <x:c r="R92"/>
-      <x:c r="S92"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93"/>
-      <x:c r="B93"/>
-      <x:c r="C93"/>
-      <x:c r="D93"/>
-      <x:c r="E93"/>
-      <x:c r="F93"/>
-      <x:c r="G93"/>
-      <x:c r="H93"/>
-      <x:c r="I93"/>
-      <x:c r="J93"/>
-      <x:c r="K93"/>
-      <x:c r="L93"/>
-      <x:c r="M93"/>
-      <x:c r="N93"/>
-      <x:c r="O93"/>
-      <x:c r="P93"/>
-      <x:c r="Q93"/>
-      <x:c r="R93"/>
-      <x:c r="S93"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+      <x:c r="I99"/>
+      <x:c r="J99"/>
+      <x:c r="K99"/>
+      <x:c r="L99"/>
+      <x:c r="M99"/>
+      <x:c r="N99"/>
+      <x:c r="O99"/>
+      <x:c r="P99"/>
+      <x:c r="Q99"/>
+      <x:c r="R99"/>
+      <x:c r="S99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
+      <x:c r="I100"/>
+      <x:c r="J100"/>
+      <x:c r="K100"/>
+      <x:c r="L100"/>
+      <x:c r="M100"/>
+      <x:c r="N100"/>
+      <x:c r="O100"/>
+      <x:c r="P100"/>
+      <x:c r="Q100"/>
+      <x:c r="R100"/>
+      <x:c r="S100"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+      <x:c r="G101"/>
+      <x:c r="H101"/>
+      <x:c r="I101"/>
+      <x:c r="J101"/>
+      <x:c r="K101"/>
+      <x:c r="L101"/>
+      <x:c r="M101"/>
+      <x:c r="N101"/>
+      <x:c r="O101"/>
+      <x:c r="P101"/>
+      <x:c r="Q101"/>
+      <x:c r="R101"/>
+      <x:c r="S101"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R25686a9d28eb4ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Rbc74c9e2df1842a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rc1022b5cad4546f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R45a869c7fbae4125"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L97),2)</x:f>
-        <x:v>69.85</x:v>
+        <x:f>ROUND(SUM(L11:L98),2)</x:f>
+        <x:v>70.46</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M97),2)</x:f>
-        <x:v>86.54</x:v>
+        <x:f>ROUND(SUM(M11:M98),2)</x:f>
+        <x:v>86.95</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D11,$F$11:$F$97),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D11,$F$11:$F$98),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D12,$F$11:$F$97),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D12,$F$11:$F$98),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -780,7 +780,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D13,$F$11:$F$97),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D13,$F$11:$F$98),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -829,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D14,$F$11:$F$97),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D14,$F$11:$F$98),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -889,7 +889,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D15,$F$11:$F$97),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D15,$F$11:$F$98),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -949,7 +949,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D16,$F$11:$F$97),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D16,$F$11:$F$98),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1009,7 +1009,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D17,$F$11:$F$97),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D17,$F$11:$F$98),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1069,7 +1069,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D18,$F$11:$F$97),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D18,$F$11:$F$98),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1129,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D19,$F$11:$F$97),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D19,$F$11:$F$98),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1189,7 +1189,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D20,$F$11:$F$97),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D20,$F$11:$F$98),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1249,7 +1249,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D21,$F$11:$F$97),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D21,$F$11:$F$98),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1305,7 +1305,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D22,$F$11:$F$97),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D22,$F$11:$F$98),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1354,7 +1354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D23,$F$11:$F$97),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D23,$F$11:$F$98),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1414,7 +1414,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D24,$F$11:$F$97),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D24,$F$11:$F$98),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1474,7 +1474,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D25,$F$11:$F$97),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D25,$F$11:$F$98),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1534,7 +1534,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D26,$F$11:$F$97),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D26,$F$11:$F$98),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1594,7 +1594,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D27,$F$11:$F$97),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D27,$F$11:$F$98),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1654,7 +1654,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D28,$F$11:$F$97),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D28,$F$11:$F$98),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1710,7 +1710,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D29,$F$11:$F$97),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D29,$F$11:$F$98),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1759,7 +1759,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D30,$F$11:$F$97),G30)/H30,0)*H30))</x:f>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D30,$F$11:$F$98),G30)/H30,0)*H30))</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
@@ -1819,7 +1819,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D31,$F$11:$F$97),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D31,$F$11:$F$98),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1881,7 +1881,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D32,$F$11:$F$97),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D32,$F$11:$F$98),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1919,7 +1919,7 @@
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225</x:v>
+        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
         <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
@@ -1934,7 +1934,7 @@
         <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>10</x:v>
@@ -1943,8 +1943,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D33,$F$11:$F$97),G33)/H33,0)*H33))</x:f>
-        <x:v>20</x:v>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D33,$F$11:$F$98),G33)/H33,0)*H33))</x:f>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J33" t="n">
         <x:v>10</x:v>
@@ -1954,11 +1954,11 @@
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.5642</x:v>
+        <x:v>0.9672</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
-        <x:v>0.806</x:v>
+        <x:v>1.209</x:v>
       </x:c>
       <x:c r="N33" t="n">
         <x:v>1363910</x:v>
@@ -1973,7 +1973,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R33" t="str">
-        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven.</x:v>
+        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven. Headphone_Aux sheet, 2026-10-06. Added C230, C231, C232, C233, C234, C235, C239, C240, C241, C245.</x:v>
       </x:c>
       <x:c r="S33" t="str">
         <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
@@ -1981,7 +1981,7 @@
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="25" t="str">
-        <x:v>C5, C186, C187, C194, C195</x:v>
+        <x:v>C5, C186, C187, C194, C195, C236</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
         <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
@@ -1996,7 +1996,7 @@
         <x:v>C51205</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G34" t="n">
         <x:v>10</x:v>
@@ -2005,7 +2005,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D34,$F$11:$F$97),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D34,$F$11:$F$98),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2016,7 +2016,7 @@
       </x:c>
       <x:c r="L34" s="27" t="n">
         <x:f>IF(K34="","",ROUND(F34*K34,4))</x:f>
-        <x:v>0.3795</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
       <x:c r="M34" s="27" t="n">
         <x:f>IF(OR(K34="",I34="",N34=""),"",IF(N34&gt;=I34,ROUND(I34*K34,4),""))</x:f>
@@ -2034,7 +2034,9 @@
       <x:c r="Q34" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R34"/>
+      <x:c r="R34" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added C236.</x:v>
+      </x:c>
       <x:c r="S34" t="str">
         <x:v>https://www.lcsc.com/product-detail/C51205.html</x:v>
       </x:c>
@@ -2065,7 +2067,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D35,$F$11:$F$97),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D35,$F$11:$F$98),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2112,7 +2114,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D36,$F$11:$F$97),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D36,$F$11:$F$98),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2157,7 +2159,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D37,$F$11:$F$97),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D37,$F$11:$F$98),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2219,7 +2221,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D38,$F$11:$F$97),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D38,$F$11:$F$98),G38)/H38,0)*H38))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2279,7 +2281,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D39,$F$11:$F$97),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D39,$F$11:$F$98),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2339,7 +2341,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D40,$F$11:$F$97),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D40,$F$11:$F$98),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2401,7 +2403,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D41,$F$11:$F$97),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D41,$F$11:$F$98),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2463,7 +2465,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D42,$F$11:$F$97),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D42,$F$11:$F$98),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2520,7 +2522,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D43,$F$11:$F$97),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D43,$F$11:$F$98),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2579,7 +2581,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D44,$F$11:$F$97),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D44,$F$11:$F$98),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2639,7 +2641,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D45,$F$11:$F$97),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D45,$F$11:$F$98),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2699,7 +2701,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D46,$F$11:$F$97),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D46,$F$11:$F$98),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2759,7 +2761,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D47,$F$11:$F$97),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D47,$F$11:$F$98),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2816,7 +2818,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D48,$F$11:$F$97),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D48,$F$11:$F$98),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2876,7 +2878,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D49,$F$11:$F$97),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D49,$F$11:$F$98),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2912,7 +2914,7 @@
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="25" t="str">
-        <x:v>R11, R13, R14, R15, R18, R182, R183</x:v>
+        <x:v>R11, R13, R14, R15, R18, R182, R183, R242, R243, R244</x:v>
       </x:c>
       <x:c r="B50" s="25" t="str">
         <x:v>TPS25730D 10k 1% resistors (CC/ADC, I2C pull-ups R14/R15, pin 36 R18)</x:v>
@@ -2927,7 +2929,7 @@
         <x:v>C98220</x:v>
       </x:c>
       <x:c r="F50" s="25" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>100</x:v>
@@ -2936,7 +2938,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D50,$F$11:$F$97),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D50,$F$11:$F$98),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2947,7 +2949,7 @@
       </x:c>
       <x:c r="L50" s="27" t="n">
         <x:f>IF(K50="","",ROUND(F50*K50,4))</x:f>
-        <x:v>0.0238</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="M50" s="27" t="str">
         <x:f>IF(OR(K50="",I50="",N50=""),"",IF(N50&gt;=I50,ROUND(I50*K50,4),""))</x:f>
@@ -2964,7 +2966,9 @@
       <x:c r="Q50" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R50"/>
+      <x:c r="R50" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R242, R243, R244.</x:v>
+      </x:c>
       <x:c r="S50" t="str">
         <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
       </x:c>
@@ -2995,7 +2999,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D51,$F$11:$F$97),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D51,$F$11:$F$98),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3055,7 +3059,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D52,$F$11:$F$97),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D52,$F$11:$F$98),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3114,7 +3118,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D53,$F$11:$F$97),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D53,$F$11:$F$98),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3173,7 +3177,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D54,$F$11:$F$97),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D54,$F$11:$F$98),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3235,7 +3239,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D55,$F$11:$F$97),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D55,$F$11:$F$98),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3297,7 +3301,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D56,$F$11:$F$97),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D56,$F$11:$F$98),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3348,7 +3352,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D57,$F$11:$F$97),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D57,$F$11:$F$98),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3369,7 +3373,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219, C237, C238, C242, C246</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3384,7 +3388,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3393,7 +3397,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D58,$F$11:$F$97),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D58,$F$11:$F$98),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3404,7 +3408,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.1776</x:v>
+        <x:v>0.222</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3422,7 +3426,9 @@
       <x:c r="Q58" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R58"/>
+      <x:c r="R58" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added C237, C238, C242, C246.</x:v>
+      </x:c>
       <x:c r="S58" t="str">
         <x:v>https://www.lcsc.com/product-detail/C1591.html</x:v>
       </x:c>
@@ -3453,7 +3459,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D59,$F$11:$F$97),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D59,$F$11:$F$98),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3513,7 +3519,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D60,$F$11:$F$97),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D60,$F$11:$F$98),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3548,7 +3554,7 @@
     </x:row>
     <x:row r="61" ht="36" customHeight="1">
       <x:c r="A61" s="25" t="str">
-        <x:v>R122</x:v>
+        <x:v>R122, R232, R233</x:v>
       </x:c>
       <x:c r="B61" s="25" t="str">
         <x:v>Gauge 47k resistor</x:v>
@@ -3563,7 +3569,7 @@
         <x:v>C105579</x:v>
       </x:c>
       <x:c r="F61" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G61" t="n">
         <x:v>100</x:v>
@@ -3572,7 +3578,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D61,$F$11:$F$97),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D61,$F$11:$F$98),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3583,7 +3589,7 @@
       </x:c>
       <x:c r="L61" s="27" t="n">
         <x:f>IF(K61="","",ROUND(F61*K61,4))</x:f>
-        <x:v>0.0012</x:v>
+        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="M61" s="27" t="n">
         <x:f>IF(OR(K61="",I61="",N61=""),"",IF(N61&gt;=I61,ROUND(I61*K61,4),""))</x:f>
@@ -3601,7 +3607,9 @@
       <x:c r="Q61" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R61"/>
+      <x:c r="R61" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R232, R233.</x:v>
+      </x:c>
       <x:c r="S61" t="str">
         <x:v>https://www.lcsc.com/product-detail/C105579.html</x:v>
       </x:c>
@@ -3632,7 +3640,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D62,$F$11:$F$97),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D62,$F$11:$F$98),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3691,7 +3699,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D63,$F$11:$F$97),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D63,$F$11:$F$98),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3753,7 +3761,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D64,$F$11:$F$97),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D64,$F$11:$F$98),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3812,7 +3820,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D65,$F$11:$F$97),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D65,$F$11:$F$98),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3874,7 +3882,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D66,$F$11:$F$97),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D66,$F$11:$F$98),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3936,7 +3944,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D67,$F$11:$F$97),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D67,$F$11:$F$98),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -3996,7 +4004,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D68,$F$11:$F$97),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D68,$F$11:$F$98),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4032,7 +4040,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4047,7 +4055,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4056,7 +4064,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D69,$F$11:$F$97),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D69,$F$11:$F$98),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4067,7 +4075,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0432</x:v>
+        <x:v>0.0864</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4084,7 +4092,9 @@
       <x:c r="Q69" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R69"/>
+      <x:c r="R69" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239.</x:v>
+      </x:c>
       <x:c r="S69" t="str">
         <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
@@ -4115,7 +4125,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D70,$F$11:$F$97),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D70,$F$11:$F$98),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4176,7 +4186,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D71,$F$11:$F$97),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D71,$F$11:$F$98),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4234,7 +4244,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D72,$F$11:$F$97),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D72,$F$11:$F$98),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4283,7 +4293,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D73,$F$11:$F$97),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D73,$F$11:$F$98),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4342,7 +4352,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D74,$F$11:$F$97),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D74,$F$11:$F$98),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4403,7 +4413,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D75,$F$11:$F$97),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D75,$F$11:$F$98),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4439,7 +4449,7 @@
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
       <x:c r="A76" s="25" t="str">
-        <x:v>R126, R127, R174</x:v>
+        <x:v>R126, R127, R174, R241</x:v>
       </x:c>
       <x:c r="B76" s="25" t="str">
         <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
@@ -4454,7 +4464,7 @@
         <x:v>C105578</x:v>
       </x:c>
       <x:c r="F76" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G76" t="n">
         <x:v>100</x:v>
@@ -4463,7 +4473,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D76,$F$11:$F$97),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D76,$F$11:$F$98),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4474,7 +4484,7 @@
       </x:c>
       <x:c r="L76" s="27" t="n">
         <x:f>IF(K76="","",ROUND(F76*K76,4))</x:f>
-        <x:v>0.0168</x:v>
+        <x:v>0.0224</x:v>
       </x:c>
       <x:c r="M76" s="27" t="n">
         <x:f>IF(OR(K76="",I76="",N76=""),"",IF(N76&gt;=I76,ROUND(I76*K76,4),""))</x:f>
@@ -4492,7 +4502,9 @@
       <x:c r="Q76" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R76"/>
+      <x:c r="R76" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R241.</x:v>
+      </x:c>
       <x:c r="S76" t="str">
         <x:v>https://www.lcsc.com/product-detail/C105578.html</x:v>
       </x:c>
@@ -4523,7 +4535,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D77,$F$11:$F$97),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D77,$F$11:$F$98),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4585,7 +4597,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D78,$F$11:$F$97),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D78,$F$11:$F$98),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4641,7 +4653,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D79,$F$11:$F$97),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D79,$F$11:$F$98),G79)/H79,0)*H79))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4703,7 +4715,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D80,$F$11:$F$97),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D80,$F$11:$F$98),G80)/H80,0)*H80))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4759,7 +4771,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D81,$F$11:$F$97),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D81,$F$11:$F$98),G81)/H81,0)*H81))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4815,7 +4827,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D82,$F$11:$F$97),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D82,$F$11:$F$98),G82)/H82,0)*H82))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4871,7 +4883,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D83,$F$11:$F$97),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D83,$F$11:$F$98),G83)/H83,0)*H83))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" t="n">
@@ -4909,7 +4921,7 @@
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
       <x:c r="A84" t="str">
-        <x:v>R185, R186, R187</x:v>
+        <x:v>R185, R186, R187, R226, R227, R228, R229, R230, R231, R240</x:v>
       </x:c>
       <x:c r="B84" t="str">
         <x:v>BM83 RST_N series (R185) and UART_TXD / P0_0 TX_IND series (R186, R187) 1 kohm 1% 0603</x:v>
@@ -4924,7 +4936,7 @@
         <x:v>C22548</x:v>
       </x:c>
       <x:c r="F84" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G84" t="n">
         <x:v>100</x:v>
@@ -4933,7 +4945,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D84,$F$11:$F$97),G84)/H84,0)*H84))</x:f>
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D84,$F$11:$F$98),G84)/H84,0)*H84))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J84" t="n">
@@ -4944,7 +4956,7 @@
       </x:c>
       <x:c r="L84" t="n">
         <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
-        <x:v>0.0033</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="M84" t="n">
         <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
@@ -4963,7 +4975,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R84" t="str">
-        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified.</x:v>
+        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified. Headphone_Aux sheet, 2026-10-06. Added R226, R227, R228, R229, R230, R231, R240.</x:v>
       </x:c>
       <x:c r="S84" t="str">
         <x:v>https://www.lcsc.com/product-detail/C22548.html</x:v>
@@ -4995,7 +5007,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D85,$F$11:$F$97),G85)/H85,0)*H85))</x:f>
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D85,$F$11:$F$98),G85)/H85,0)*H85))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J85" t="n">
@@ -5051,7 +5063,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I86" t="n">
-        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D86,$F$11:$F$97),G86)/H86,0)*H86))</x:f>
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D86,$F$11:$F$98),G86)/H86,0)*H86))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J86" t="n">
@@ -5107,7 +5119,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" t="n">
-        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D87,$F$11:$F$97),G87)/H87,0)*H87))</x:f>
+        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D87,$F$11:$F$98),G87)/H87,0)*H87))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J87" t="n">
@@ -5163,7 +5175,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" t="n">
-        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D88,$F$11:$F$97),G88)/H88,0)*H88))</x:f>
+        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D88,$F$11:$F$98),G88)/H88,0)*H88))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J88" t="n">
@@ -5219,7 +5231,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" t="n">
-        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D89,$F$11:$F$97),G89)/H89,0)*H89))</x:f>
+        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D89,$F$11:$F$98),G89)/H89,0)*H89))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J89" t="n">
@@ -5275,7 +5287,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I90" t="n">
-        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D90,$F$11:$F$97),G90)/H90,0)*H90))</x:f>
+        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D90,$F$11:$F$98),G90)/H90,0)*H90))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J90" t="n">
@@ -5331,7 +5343,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I91" t="n">
-        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D91,$F$11:$F$97),G91)/H91,0)*H91))</x:f>
+        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D91,$F$11:$F$98),G91)/H91,0)*H91))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J91" t="n">
@@ -5363,7 +5375,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>C200, C201, C202, C203, C204, C205</x:v>
+        <x:v>C200, C201, C202, C203, C204, C205, C243, C244</x:v>
       </x:c>
       <x:c r="B92" t="str">
         <x:v>Input AC-coupling 2.2uF X7R 0805</x:v>
@@ -5374,9 +5386,11 @@
       <x:c r="D92" t="str">
         <x:v>CL21B225KAFNNNE</x:v>
       </x:c>
-      <x:c r="E92" t="str"/>
+      <x:c r="E92" t="str">
+        <x:v>C19110</x:v>
+      </x:c>
       <x:c r="F92" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G92" t="n">
         <x:v>10</x:v>
@@ -5385,7 +5399,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I92" t="n">
-        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D92,$F$11:$F$97),G92)/H92,0)*H92))</x:f>
+        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D92,$F$11:$F$98),G92)/H92,0)*H92))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J92" t="n">
@@ -5400,7 +5414,7 @@
       </x:c>
       <x:c r="N92"/>
       <x:c r="O92" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P92" t="n">
         <x:v>46300</x:v>
@@ -5409,9 +5423,11 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R92" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias.</x:v>
-      </x:c>
-      <x:c r="S92" t="str"/>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias. Headphone_Aux sheet, 2026-10-06. Added C243, C244.</x:v>
+      </x:c>
+      <x:c r="S92" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C19110.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
@@ -5437,7 +5453,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I93" t="n">
-        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D93,$F$11:$F$97),G93)/H93,0)*H93))</x:f>
+        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D93,$F$11:$F$98),G93)/H93,0)*H93))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J93" t="n">
@@ -5461,7 +5477,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R93" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget.</x:v>
       </x:c>
       <x:c r="S93" t="str"/>
     </x:row>
@@ -5470,15 +5486,17 @@
         <x:v>C226, C227</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>Crystal load capacitors 20 pF C0G 0603</x:v>
+        <x:v>Crystal load capacitors 22 pF C0G 0603</x:v>
       </x:c>
       <x:c r="C94" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>CL10C200JB8NNNC</x:v>
-      </x:c>
-      <x:c r="E94" t="str"/>
+        <x:v>CL10C220JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>C1653</x:v>
+      </x:c>
       <x:c r="F94" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -5489,7 +5507,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I94" t="n">
-        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D94,$F$11:$F$97),G94)/H94,0)*H94))</x:f>
+        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D94,$F$11:$F$98),G94)/H94,0)*H94))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J94" t="n">
@@ -5504,7 +5522,7 @@
       </x:c>
       <x:c r="N94"/>
       <x:c r="O94" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC number from search 2026-10-06 (JLCPCB C1653 page); price/stock unverified</x:v>
       </x:c>
       <x:c r="P94" t="n">
         <x:v>46300</x:v>
@@ -5513,9 +5531,11 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R94" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
-      </x:c>
-      <x:c r="S94" t="str"/>
+        <x:v>Source_Select_ADC sheet. Changed from 20 pF 2026-10-06: 2 x 22 pF in series plus ~3 pF stray gives about 14 pF for the 15 pF crystal. Unverified: price/stock not checked.</x:v>
+      </x:c>
+      <x:c r="S94" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C1653.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
@@ -5530,7 +5550,9 @@
       <x:c r="D95" t="str">
         <x:v>RC0603FR-07100RL</x:v>
       </x:c>
-      <x:c r="E95" t="str"/>
+      <x:c r="E95" t="str">
+        <x:v>C105588</x:v>
+      </x:c>
       <x:c r="F95" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -5541,22 +5563,27 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I95" t="n">
-        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D95,$F$11:$F$97),G95)/H95,0)*H95))</x:f>
+        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D95,$F$11:$F$98),G95)/H95,0)*H95))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K95"/>
-      <x:c r="L95" t="str">
+      <x:c r="K95" t="n">
+        <x:v>0.0024</x:v>
+      </x:c>
+      <x:c r="L95" t="n">
         <x:f>IF(K95="","",ROUND(F95*K95,4))</x:f>
+        <x:v>0.0144</x:v>
       </x:c>
       <x:c r="M95" t="str">
         <x:f>IF(OR(K95="",I95="",N95=""),"",IF(N95&gt;=I95,ROUND(I95*K95,4),""))</x:f>
       </x:c>
-      <x:c r="N95"/>
+      <x:c r="N95" t="n">
+        <x:v>2943700</x:v>
+      </x:c>
       <x:c r="O95" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC code and price reused from the R112 row (same MPN)</x:v>
       </x:c>
       <x:c r="P95" t="n">
         <x:v>46300</x:v>
@@ -5567,7 +5594,9 @@
       <x:c r="R95" t="str">
         <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
       </x:c>
-      <x:c r="S95" t="str"/>
+      <x:c r="S95" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C105588.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
@@ -5593,7 +5622,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I96" t="n">
-        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D96,$F$11:$F$97),G96)/H96,0)*H96))</x:f>
+        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D96,$F$11:$F$98),G96)/H96,0)*H96))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J96" t="n">
@@ -5617,7 +5646,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R96" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget.</x:v>
       </x:c>
       <x:c r="S96" t="str"/>
     </x:row>
@@ -5634,7 +5663,9 @@
       <x:c r="D97" t="str">
         <x:v>RC0603FR-072K2L</x:v>
       </x:c>
-      <x:c r="E97" t="str"/>
+      <x:c r="E97" t="str">
+        <x:v>C114662</x:v>
+      </x:c>
       <x:c r="F97" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -5645,7 +5676,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I97" t="n">
-        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$97,D97,$F$11:$F$97),G97)/H97,0)*H97))</x:f>
+        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D97,$F$11:$F$98),G97)/H97,0)*H97))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J97" t="n">
@@ -5660,7 +5691,7 @@
       </x:c>
       <x:c r="N97"/>
       <x:c r="O97" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P97" t="n">
         <x:v>46300</x:v>
@@ -5671,33 +5702,68 @@
       <x:c r="R97" t="str">
         <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
       </x:c>
-      <x:c r="S97" t="str"/>
+      <x:c r="S97" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C114662.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98"/>
-      <x:c r="B98"/>
-      <x:c r="C98"/>
-      <x:c r="D98"/>
-      <x:c r="E98"/>
-      <x:c r="F98"/>
-      <x:c r="G98"/>
-      <x:c r="H98"/>
-      <x:c r="I98"/>
-      <x:c r="J98"/>
+      <x:c r="A98" t="str">
+        <x:v>D200, D201</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>Headphone jack / AUX_IN jack ESD, 2-line bidirectional 5 V (SOT-23)</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>DOWO (Nexperia PESD5V0S2BT equivalent)</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>PESD5V0S2BT</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>C5380400</x:v>
+      </x:c>
+      <x:c r="F98" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H98" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I98" t="n">
+        <x:f>IF(OR(D98="",G98="",H98=""),"",IF(COUNTIF($D$11:D98,D98)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D98,$F$11:$F$98),G98)/H98,0)*H98))</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="K98"/>
-      <x:c r="L98"/>
-      <x:c r="M98"/>
+      <x:c r="L98" t="str">
+        <x:f>IF(K98="","",ROUND(F98*K98,4))</x:f>
+      </x:c>
+      <x:c r="M98" t="str">
+        <x:f>IF(OR(K98="",I98="",N98=""),"",IF(N98&gt;=I98,ROUND(I98*K98,4),""))</x:f>
+      </x:c>
       <x:c r="N98"/>
-      <x:c r="O98"/>
-      <x:c r="P98"/>
-      <x:c r="Q98"/>
-      <x:c r="R98"/>
-      <x:c r="S98"/>
+      <x:c r="O98" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P98" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q98" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R98" t="str">
+        <x:v>Headphone_Aux sheet, 2026-10-06. LCSC C5380400 is the DOWO PESD5V0S2BT listing; the Nexperia original was not stock-checked. Pin 3 common (search summary of Nexperia datasheet): VERIFY. Footprint DesktopSpeaker:PESD5V0S2BT (stock SOT-23).</x:v>
+      </x:c>
+      <x:c r="S98" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C5380400.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A99"/>
       <x:c r="B99"/>
       <x:c r="C99"/>
       <x:c r="D99"/>
@@ -5718,7 +5784,9 @@
       <x:c r="S99"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100"/>
+      <x:c r="A100" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
       <x:c r="B100"/>
       <x:c r="C100"/>
       <x:c r="D100"/>
@@ -5739,9 +5807,7 @@
       <x:c r="S100"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A101"/>
       <x:c r="B101"/>
       <x:c r="C101"/>
       <x:c r="D101"/>
@@ -5760,6 +5826,29 @@
       <x:c r="Q101"/>
       <x:c r="R101"/>
       <x:c r="S101"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+      <x:c r="G102"/>
+      <x:c r="H102"/>
+      <x:c r="I102"/>
+      <x:c r="J102"/>
+      <x:c r="K102"/>
+      <x:c r="L102"/>
+      <x:c r="M102"/>
+      <x:c r="N102"/>
+      <x:c r="O102"/>
+      <x:c r="P102"/>
+      <x:c r="Q102"/>
+      <x:c r="R102"/>
+      <x:c r="S102"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rc1022b5cad4546f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R45a869c7fbae4125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R3604e51fcfa94702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R7643382c15d5483c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,8 +433,8 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L98),2)</x:f>
-        <x:v>70.46</x:v>
+        <x:f>ROUND(SUM(L11:L114),2)</x:f>
+        <x:v>78.94</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M98),2)</x:f>
-        <x:v>86.95</x:v>
+        <x:f>ROUND(SUM(M11:M114),2)</x:f>
+        <x:v>95.64</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D11,$F$11:$F$98),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D11,$F$11:$F$114),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D12,$F$11:$F$98),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D12,$F$11:$F$114),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -780,7 +780,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D13,$F$11:$F$98),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D13,$F$11:$F$114),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -829,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D14,$F$11:$F$98),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D14,$F$11:$F$114),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -889,7 +889,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D15,$F$11:$F$98),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D15,$F$11:$F$114),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -949,7 +949,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D16,$F$11:$F$98),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D16,$F$11:$F$114),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1009,7 +1009,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D17,$F$11:$F$98),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D17,$F$11:$F$114),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1069,7 +1069,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D18,$F$11:$F$98),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D18,$F$11:$F$114),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1129,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D19,$F$11:$F$98),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D19,$F$11:$F$114),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1189,7 +1189,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D20,$F$11:$F$98),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D20,$F$11:$F$114),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1249,7 +1249,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D21,$F$11:$F$98),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D21,$F$11:$F$114),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1305,7 +1305,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D22,$F$11:$F$98),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D22,$F$11:$F$114),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1354,7 +1354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D23,$F$11:$F$98),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D23,$F$11:$F$114),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1414,7 +1414,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D24,$F$11:$F$98),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D24,$F$11:$F$114),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1474,7 +1474,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D25,$F$11:$F$98),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D25,$F$11:$F$114),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1534,7 +1534,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D26,$F$11:$F$98),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D26,$F$11:$F$114),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1594,7 +1594,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D27,$F$11:$F$98),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D27,$F$11:$F$114),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1654,7 +1654,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D28,$F$11:$F$98),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D28,$F$11:$F$114),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1710,7 +1710,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D29,$F$11:$F$98),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D29,$F$11:$F$114),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1735,7 +1735,7 @@
     </x:row>
     <x:row r="30" ht="96" customHeight="1">
       <x:c r="A30" s="22" t="str">
-        <x:v>C6, C104, C105, C107, C140, C141, C142, C150, C152, C153, C154</x:v>
+        <x:v>C6, C104, C105, C107, C140, C141, C142, C150, C152, C153, C154, C261, C262, C263, C264</x:v>
       </x:c>
       <x:c r="B30" s="22" t="str">
         <x:v>Charger / regulated-rail 22uF bulk capacitors</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>C907991</x:v>
       </x:c>
       <x:c r="F30" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="1" t="n">
         <x:v>5</x:v>
@@ -1759,8 +1759,8 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D30,$F$11:$F$98),G30)/H30,0)*H30))</x:f>
-        <x:v>15</x:v>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D30,$F$11:$F$114),G30)/H30,0)*H30))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
         <x:v>5</x:v>
@@ -1770,11 +1770,11 @@
       </x:c>
       <x:c r="L30" s="31" t="n">
         <x:f>IF(K30="","",ROUND(F30*K30,4))</x:f>
-        <x:v>2.7973</x:v>
+        <x:v>3.8145</x:v>
       </x:c>
       <x:c r="M30" s="31" t="n">
         <x:f>IF(OR(K30="",I30="",N30=""),"",IF(N30&gt;=I30,ROUND(I30*K30,4),""))</x:f>
-        <x:v>3.8145</x:v>
+        <x:v>5.086</x:v>
       </x:c>
       <x:c r="N30" s="7" t="n">
         <x:v>146915</x:v>
@@ -1788,7 +1788,9 @@
       <x:c r="Q30" s="1" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R30" s="1"/>
+      <x:c r="R30" s="1" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Added C261, C262, C263, C264.</x:v>
+      </x:c>
       <x:c r="S30" s="1" t="str">
         <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
       </x:c>
@@ -1819,7 +1821,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D31,$F$11:$F$98),G31)/H31,0)*H31))</x:f>
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D31,$F$11:$F$114),G31)/H31,0)*H31))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J31" t="n">
@@ -1881,7 +1883,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D32,$F$11:$F$98),G32)/H32,0)*H32))</x:f>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D32,$F$11:$F$114),G32)/H32,0)*H32))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J32" t="n">
@@ -1919,7 +1921,7 @@
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245</x:v>
+        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245, C270, C282, C283, C284, C295, C296, C297</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
         <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
@@ -1934,7 +1936,7 @@
         <x:v>C28323</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G33" t="n">
         <x:v>10</x:v>
@@ -1943,8 +1945,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D33,$F$11:$F$98),G33)/H33,0)*H33))</x:f>
-        <x:v>30</x:v>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D33,$F$11:$F$114),G33)/H33,0)*H33))</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J33" t="n">
         <x:v>10</x:v>
@@ -1954,11 +1956,11 @@
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>0.9672</x:v>
+        <x:v>1.2493</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
-        <x:v>1.209</x:v>
+        <x:v>1.612</x:v>
       </x:c>
       <x:c r="N33" t="n">
         <x:v>1363910</x:v>
@@ -1973,7 +1975,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R33" t="str">
-        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven. Headphone_Aux sheet, 2026-10-06. Added C230, C231, C232, C233, C234, C235, C239, C240, C241, C245.</x:v>
+        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven. Headphone_Aux sheet, 2026-10-06. Added C230, C231, C232, C233, C234, C235, C239, C240, C241, C245. Amplifiers sheet, 2026-10-06. Added C270, C282, C283, C284, C295, C296, C297.</x:v>
       </x:c>
       <x:c r="S33" t="str">
         <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
@@ -2005,7 +2007,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D34,$F$11:$F$98),G34)/H34,0)*H34))</x:f>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D34,$F$11:$F$114),G34)/H34,0)*H34))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J34" t="n">
@@ -2067,7 +2069,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D35,$F$11:$F$98),G35)/H35,0)*H35))</x:f>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D35,$F$11:$F$114),G35)/H35,0)*H35))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J35" t="n">
@@ -2114,7 +2116,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D36,$F$11:$F$98),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D36,$F$11:$F$114),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2159,7 +2161,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D37,$F$11:$F$98),G37)/H37,0)*H37))</x:f>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D37,$F$11:$F$114),G37)/H37,0)*H37))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J37" t="n">
@@ -2221,7 +2223,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D38,$F$11:$F$98),G38)/H38,0)*H38))</x:f>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D38,$F$11:$F$114),G38)/H38,0)*H38))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J38" t="n">
@@ -2257,7 +2259,7 @@
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="25" t="str">
-        <x:v>C103, C110</x:v>
+        <x:v>C103, C110, C266</x:v>
       </x:c>
       <x:c r="B39" s="25" t="str">
         <x:v>47nF X7R / 50V bootstrap capacitors</x:v>
@@ -2272,7 +2274,7 @@
         <x:v>C107093</x:v>
       </x:c>
       <x:c r="F39" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G39" t="n">
         <x:v>50</x:v>
@@ -2281,7 +2283,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D39,$F$11:$F$98),G39)/H39,0)*H39))</x:f>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D39,$F$11:$F$114),G39)/H39,0)*H39))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J39" t="n">
@@ -2292,7 +2294,7 @@
       </x:c>
       <x:c r="L39" s="27" t="n">
         <x:f>IF(K39="","",ROUND(F39*K39,4))</x:f>
-        <x:v>0.0154</x:v>
+        <x:v>0.0231</x:v>
       </x:c>
       <x:c r="M39" s="27" t="n">
         <x:f>IF(OR(K39="",I39="",N39=""),"",IF(N39&gt;=I39,ROUND(I39*K39,4),""))</x:f>
@@ -2310,7 +2312,9 @@
       <x:c r="Q39" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
-      <x:c r="R39"/>
+      <x:c r="R39" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Added C266.</x:v>
+      </x:c>
       <x:c r="S39" t="str">
         <x:v>https://www.lcsc.com/product-detail/C107093.html</x:v>
       </x:c>
@@ -2341,7 +2345,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D40,$F$11:$F$98),G40)/H40,0)*H40))</x:f>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D40,$F$11:$F$114),G40)/H40,0)*H40))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J40" t="n">
@@ -2403,7 +2407,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D41,$F$11:$F$98),G41)/H41,0)*H41))</x:f>
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D41,$F$11:$F$114),G41)/H41,0)*H41))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J41" t="n">
@@ -2465,7 +2469,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D42,$F$11:$F$98),G42)/H42,0)*H42))</x:f>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D42,$F$11:$F$114),G42)/H42,0)*H42))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J42" t="n">
@@ -2522,7 +2526,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D43,$F$11:$F$98),G43)/H43,0)*H43))</x:f>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D43,$F$11:$F$114),G43)/H43,0)*H43))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
@@ -2581,7 +2585,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D44,$F$11:$F$98),G44)/H44,0)*H44))</x:f>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D44,$F$11:$F$114),G44)/H44,0)*H44))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" t="n">
@@ -2641,7 +2645,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D45,$F$11:$F$98),G45)/H45,0)*H45))</x:f>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D45,$F$11:$F$114),G45)/H45,0)*H45))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J45" t="n">
@@ -2701,7 +2705,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D46,$F$11:$F$98),G46)/H46,0)*H46))</x:f>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D46,$F$11:$F$114),G46)/H46,0)*H46))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J46" t="n">
@@ -2761,7 +2765,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D47,$F$11:$F$98),G47)/H47,0)*H47))</x:f>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D47,$F$11:$F$114),G47)/H47,0)*H47))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J47" t="n">
@@ -2818,7 +2822,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D48,$F$11:$F$98),G48)/H48,0)*H48))</x:f>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D48,$F$11:$F$114),G48)/H48,0)*H48))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J48" t="n">
@@ -2878,7 +2882,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D49,$F$11:$F$98),G49)/H49,0)*H49))</x:f>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D49,$F$11:$F$114),G49)/H49,0)*H49))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J49" t="n">
@@ -2914,7 +2918,7 @@
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="25" t="str">
-        <x:v>R11, R13, R14, R15, R18, R182, R183, R242, R243, R244</x:v>
+        <x:v>R11, R13, R14, R15, R18, R182, R183, R242, R243, R244, R262</x:v>
       </x:c>
       <x:c r="B50" s="25" t="str">
         <x:v>TPS25730D 10k 1% resistors (CC/ADC, I2C pull-ups R14/R15, pin 36 R18)</x:v>
@@ -2929,7 +2933,7 @@
         <x:v>C98220</x:v>
       </x:c>
       <x:c r="F50" s="25" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G50" t="n">
         <x:v>100</x:v>
@@ -2938,7 +2942,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D50,$F$11:$F$98),G50)/H50,0)*H50))</x:f>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D50,$F$11:$F$114),G50)/H50,0)*H50))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
@@ -2949,7 +2953,7 @@
       </x:c>
       <x:c r="L50" s="27" t="n">
         <x:f>IF(K50="","",ROUND(F50*K50,4))</x:f>
-        <x:v>0.034</x:v>
+        <x:v>0.0374</x:v>
       </x:c>
       <x:c r="M50" s="27" t="str">
         <x:f>IF(OR(K50="",I50="",N50=""),"",IF(N50&gt;=I50,ROUND(I50*K50,4),""))</x:f>
@@ -2967,7 +2971,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R50" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R242, R243, R244.</x:v>
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R242, R243, R244. Amplifiers sheet, 2026-10-06. Added R262.</x:v>
       </x:c>
       <x:c r="S50" t="str">
         <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
@@ -2999,7 +3003,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D51,$F$11:$F$98),G51)/H51,0)*H51))</x:f>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D51,$F$11:$F$114),G51)/H51,0)*H51))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J51" t="n">
@@ -3059,7 +3063,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D52,$F$11:$F$98),G52)/H52,0)*H52))</x:f>
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D52,$F$11:$F$114),G52)/H52,0)*H52))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
@@ -3118,7 +3122,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D53,$F$11:$F$98),G53)/H53,0)*H53))</x:f>
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D53,$F$11:$F$114),G53)/H53,0)*H53))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" t="n">
@@ -3177,7 +3181,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D54,$F$11:$F$98),G54)/H54,0)*H54))</x:f>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D54,$F$11:$F$114),G54)/H54,0)*H54))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" t="n">
@@ -3239,7 +3243,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D55,$F$11:$F$98),G55)/H55,0)*H55))</x:f>
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D55,$F$11:$F$114),G55)/H55,0)*H55))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
@@ -3301,7 +3305,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D56,$F$11:$F$98),G56)/H56,0)*H56))</x:f>
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D56,$F$11:$F$114),G56)/H56,0)*H56))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" t="n">
@@ -3352,7 +3356,7 @@
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D57,$F$11:$F$98),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D57,$F$11:$F$114),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3373,7 +3377,7 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219, C237, C238, C242, C246</x:v>
+        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219, C237, C238, C242, C246, C260, C267, C276, C278, C281, C289, C291, C294</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
         <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
@@ -3388,7 +3392,7 @@
         <x:v>C1591</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>100</x:v>
@@ -3397,7 +3401,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D58,$F$11:$F$98),G58)/H58,0)*H58))</x:f>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D58,$F$11:$F$114),G58)/H58,0)*H58))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J58" t="n">
@@ -3408,7 +3412,7 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.222</x:v>
+        <x:v>0.3108</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
@@ -3427,7 +3431,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R58" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added C237, C238, C242, C246.</x:v>
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added C237, C238, C242, C246. Amplifiers sheet, 2026-10-06. Added C260, C267, C276, C278, C281, C289, C291, C294.</x:v>
       </x:c>
       <x:c r="S58" t="str">
         <x:v>https://www.lcsc.com/product-detail/C1591.html</x:v>
@@ -3459,7 +3463,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D59,$F$11:$F$98),G59)/H59,0)*H59))</x:f>
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D59,$F$11:$F$114),G59)/H59,0)*H59))</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="J59" t="n">
@@ -3519,7 +3523,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D60,$F$11:$F$98),G60)/H60,0)*H60))</x:f>
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D60,$F$11:$F$114),G60)/H60,0)*H60))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
@@ -3578,7 +3582,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D61,$F$11:$F$98),G61)/H61,0)*H61))</x:f>
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D61,$F$11:$F$114),G61)/H61,0)*H61))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J61" t="n">
@@ -3640,7 +3644,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D62,$F$11:$F$98),G62)/H62,0)*H62))</x:f>
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D62,$F$11:$F$114),G62)/H62,0)*H62))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
@@ -3699,7 +3703,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D63,$F$11:$F$98),G63)/H63,0)*H63))</x:f>
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D63,$F$11:$F$114),G63)/H63,0)*H63))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J63" t="n">
@@ -3761,7 +3765,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D64,$F$11:$F$98),G64)/H64,0)*H64))</x:f>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D64,$F$11:$F$114),G64)/H64,0)*H64))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
@@ -3820,7 +3824,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D65,$F$11:$F$98),G65)/H65,0)*H65))</x:f>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D65,$F$11:$F$114),G65)/H65,0)*H65))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J65" t="n">
@@ -3882,7 +3886,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D66,$F$11:$F$98),G66)/H66,0)*H66))</x:f>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D66,$F$11:$F$114),G66)/H66,0)*H66))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J66" t="n">
@@ -3944,7 +3948,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D67,$F$11:$F$98),G67)/H67,0)*H67))</x:f>
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D67,$F$11:$F$114),G67)/H67,0)*H67))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J67" t="n">
@@ -4004,7 +4008,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D68,$F$11:$F$98),G68)/H68,0)*H68))</x:f>
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D68,$F$11:$F$114),G68)/H68,0)*H68))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J68" t="n">
@@ -4040,7 +4044,7 @@
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239</x:v>
+        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239, R255, R259</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
         <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
@@ -4055,7 +4059,7 @@
         <x:v>C14675</x:v>
       </x:c>
       <x:c r="F69" s="25" t="n">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G69" t="n">
         <x:v>100</x:v>
@@ -4064,7 +4068,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D69,$F$11:$F$98),G69)/H69,0)*H69))</x:f>
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D69,$F$11:$F$114),G69)/H69,0)*H69))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
@@ -4075,7 +4079,7 @@
       </x:c>
       <x:c r="L69" s="27" t="n">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0864</x:v>
+        <x:v>0.0936</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
@@ -4093,7 +4097,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R69" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239.</x:v>
+        <x:v>Headphone_Aux sheet, 2026-10-06. Added R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239. Amplifiers sheet, 2026-10-06. Added R255, R259.</x:v>
       </x:c>
       <x:c r="S69" t="str">
         <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
@@ -4125,7 +4129,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D70,$F$11:$F$98),G70)/H70,0)*H70))</x:f>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D70,$F$11:$F$114),G70)/H70,0)*H70))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
@@ -4186,7 +4190,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D71,$F$11:$F$98),G71)/H71,0)*H71))</x:f>
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D71,$F$11:$F$114),G71)/H71,0)*H71))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
@@ -4244,7 +4248,7 @@
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D72,$F$11:$F$98),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D72,$F$11:$F$114),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4293,7 +4297,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D73,$F$11:$F$98),G73)/H73,0)*H73))</x:f>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D73,$F$11:$F$114),G73)/H73,0)*H73))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" t="n">
@@ -4352,7 +4356,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D74,$F$11:$F$98),G74)/H74,0)*H74))</x:f>
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D74,$F$11:$F$114),G74)/H74,0)*H74))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" t="n">
@@ -4413,7 +4417,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D75,$F$11:$F$98),G75)/H75,0)*H75))</x:f>
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D75,$F$11:$F$114),G75)/H75,0)*H75))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" t="n">
@@ -4473,7 +4477,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D76,$F$11:$F$98),G76)/H76,0)*H76))</x:f>
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D76,$F$11:$F$114),G76)/H76,0)*H76))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J76" t="n">
@@ -4511,7 +4515,7 @@
     </x:row>
     <x:row r="77" ht="36" customHeight="1">
       <x:c r="A77" s="25" t="str">
-        <x:v>C161</x:v>
+        <x:v>C161, C280, C293</x:v>
       </x:c>
       <x:c r="B77" s="25" t="str">
         <x:v>MCU VDD/VDDA 4.7uF bulk (DS12992 fig. 13)</x:v>
@@ -4526,7 +4530,7 @@
         <x:v>C19666</x:v>
       </x:c>
       <x:c r="F77" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G77" t="n">
         <x:v>10</x:v>
@@ -4535,7 +4539,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D77,$F$11:$F$98),G77)/H77,0)*H77))</x:f>
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D77,$F$11:$F$114),G77)/H77,0)*H77))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J77" t="n">
@@ -4546,7 +4550,7 @@
       </x:c>
       <x:c r="L77" s="27" t="n">
         <x:f>IF(K77="","",ROUND(F77*K77,4))</x:f>
-        <x:v>0.0298</x:v>
+        <x:v>0.0894</x:v>
       </x:c>
       <x:c r="M77" s="27" t="n">
         <x:f>IF(OR(K77="",I77="",N77=""),"",IF(N77&gt;=I77,ROUND(I77*K77,4),""))</x:f>
@@ -4565,7 +4569,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R77" t="str">
-        <x:v>LCSC listing 4.7uF/16V X5R 0603; DC-bias derating at 3.0 V not checked.</x:v>
+        <x:v>LCSC listing 4.7uF/16V X5R 0603; DC-bias derating at 3.0 V not checked. Amplifiers sheet, 2026-10-06. Added C280, C293.</x:v>
       </x:c>
       <x:c r="S77" t="str">
         <x:v>https://www.lcsc.com/product-detail/C19666.html</x:v>
@@ -4597,7 +4601,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D78,$F$11:$F$98),G78)/H78,0)*H78))</x:f>
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D78,$F$11:$F$114),G78)/H78,0)*H78))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J78" t="n">
@@ -4653,7 +4657,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D79,$F$11:$F$98),G79)/H79,0)*H79))</x:f>
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D79,$F$11:$F$114),G79)/H79,0)*H79))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J79" t="n">
@@ -4715,7 +4719,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D80,$F$11:$F$98),G80)/H80,0)*H80))</x:f>
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D80,$F$11:$F$114),G80)/H80,0)*H80))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J80" t="n">
@@ -4771,7 +4775,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D81,$F$11:$F$98),G81)/H81,0)*H81))</x:f>
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D81,$F$11:$F$114),G81)/H81,0)*H81))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J81" t="n">
@@ -4827,7 +4831,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D82,$F$11:$F$98),G82)/H82,0)*H82))</x:f>
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D82,$F$11:$F$114),G82)/H82,0)*H82))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J82" t="n">
@@ -4883,7 +4887,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D83,$F$11:$F$98),G83)/H83,0)*H83))</x:f>
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D83,$F$11:$F$114),G83)/H83,0)*H83))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J83" t="n">
@@ -4921,7 +4925,7 @@
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
       <x:c r="A84" t="str">
-        <x:v>R185, R186, R187, R226, R227, R228, R229, R230, R231, R240</x:v>
+        <x:v>R185, R186, R187, R226, R227, R228, R229, R230, R231, R240, R257, R258, R261</x:v>
       </x:c>
       <x:c r="B84" t="str">
         <x:v>BM83 RST_N series (R185) and UART_TXD / P0_0 TX_IND series (R186, R187) 1 kohm 1% 0603</x:v>
@@ -4936,7 +4940,7 @@
         <x:v>C22548</x:v>
       </x:c>
       <x:c r="F84" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G84" t="n">
         <x:v>100</x:v>
@@ -4945,7 +4949,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D84,$F$11:$F$98),G84)/H84,0)*H84))</x:f>
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D84,$F$11:$F$114),G84)/H84,0)*H84))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J84" t="n">
@@ -4956,7 +4960,7 @@
       </x:c>
       <x:c r="L84" t="n">
         <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
-        <x:v>0.011</x:v>
+        <x:v>0.0143</x:v>
       </x:c>
       <x:c r="M84" t="n">
         <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
@@ -4975,7 +4979,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R84" t="str">
-        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified. Headphone_Aux sheet, 2026-10-06. Added R226, R227, R228, R229, R230, R231, R240.</x:v>
+        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified. Headphone_Aux sheet, 2026-10-06. Added R226, R227, R228, R229, R230, R231, R240. Amplifiers sheet, 2026-10-06. Added R257, R258, R261.</x:v>
       </x:c>
       <x:c r="S84" t="str">
         <x:v>https://www.lcsc.com/product-detail/C22548.html</x:v>
@@ -5007,7 +5011,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D85,$F$11:$F$98),G85)/H85,0)*H85))</x:f>
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D85,$F$11:$F$114),G85)/H85,0)*H85))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J85" t="n">
@@ -5063,7 +5067,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I86" t="n">
-        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D86,$F$11:$F$98),G86)/H86,0)*H86))</x:f>
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D86,$F$11:$F$114),G86)/H86,0)*H86))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J86" t="n">
@@ -5119,7 +5123,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" t="n">
-        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D87,$F$11:$F$98),G87)/H87,0)*H87))</x:f>
+        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D87,$F$11:$F$114),G87)/H87,0)*H87))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J87" t="n">
@@ -5175,7 +5179,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" t="n">
-        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D88,$F$11:$F$98),G88)/H88,0)*H88))</x:f>
+        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D88,$F$11:$F$114),G88)/H88,0)*H88))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J88" t="n">
@@ -5231,7 +5235,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" t="n">
-        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D89,$F$11:$F$98),G89)/H89,0)*H89))</x:f>
+        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D89,$F$11:$F$114),G89)/H89,0)*H89))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J89" t="n">
@@ -5287,7 +5291,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I90" t="n">
-        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D90,$F$11:$F$98),G90)/H90,0)*H90))</x:f>
+        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D90,$F$11:$F$114),G90)/H90,0)*H90))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J90" t="n">
@@ -5343,7 +5347,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I91" t="n">
-        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D91,$F$11:$F$98),G91)/H91,0)*H91))</x:f>
+        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D91,$F$11:$F$114),G91)/H91,0)*H91))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J91" t="n">
@@ -5375,7 +5379,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>C200, C201, C202, C203, C204, C205, C243, C244</x:v>
+        <x:v>C200, C201, C202, C203, C204, C205, C243, C244, C265</x:v>
       </x:c>
       <x:c r="B92" t="str">
         <x:v>Input AC-coupling 2.2uF X7R 0805</x:v>
@@ -5390,7 +5394,7 @@
         <x:v>C19110</x:v>
       </x:c>
       <x:c r="F92" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G92" t="n">
         <x:v>10</x:v>
@@ -5399,7 +5403,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I92" t="n">
-        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D92,$F$11:$F$98),G92)/H92,0)*H92))</x:f>
+        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D92,$F$11:$F$114),G92)/H92,0)*H92))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J92" t="n">
@@ -5423,7 +5427,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R92" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias. Headphone_Aux sheet, 2026-10-06. Added C243, C244.</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias. Headphone_Aux sheet, 2026-10-06. Added C243, C244. Amplifiers sheet, 2026-10-06. Added C265.</x:v>
       </x:c>
       <x:c r="S92" t="str">
         <x:v>https://www.lcsc.com/product-detail/C19110.html</x:v>
@@ -5453,7 +5457,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I93" t="n">
-        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D93,$F$11:$F$98),G93)/H93,0)*H93))</x:f>
+        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D93,$F$11:$F$114),G93)/H93,0)*H93))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="J93" t="n">
@@ -5477,7 +5481,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R93" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget.</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget. LCSC code still open after the Amplifiers lookup (search returned distributor listings only).</x:v>
       </x:c>
       <x:c r="S93" t="str"/>
     </x:row>
@@ -5507,7 +5511,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I94" t="n">
-        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D94,$F$11:$F$98),G94)/H94,0)*H94))</x:f>
+        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D94,$F$11:$F$114),G94)/H94,0)*H94))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J94" t="n">
@@ -5563,7 +5567,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I95" t="n">
-        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D95,$F$11:$F$98),G95)/H95,0)*H95))</x:f>
+        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D95,$F$11:$F$114),G95)/H95,0)*H95))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" t="n">
@@ -5622,7 +5626,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I96" t="n">
-        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D96,$F$11:$F$98),G96)/H96,0)*H96))</x:f>
+        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D96,$F$11:$F$114),G96)/H96,0)*H96))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J96" t="n">
@@ -5646,7 +5650,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R96" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget.</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget. LCSC code still open after the Amplifiers lookup (search returned distributor listings only).</x:v>
       </x:c>
       <x:c r="S96" t="str"/>
     </x:row>
@@ -5676,7 +5680,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I97" t="n">
-        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D97,$F$11:$F$98),G97)/H97,0)*H97))</x:f>
+        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D97,$F$11:$F$114),G97)/H97,0)*H97))</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="J97" t="n">
@@ -5732,7 +5736,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I98" t="n">
-        <x:f>IF(OR(D98="",G98="",H98=""),"",IF(COUNTIF($D$11:D98,D98)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$98,D98,$F$11:$F$98),G98)/H98,0)*H98))</x:f>
+        <x:f>IF(OR(D98="",G98="",H98=""),"",IF(COUNTIF($D$11:D98,D98)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D98,$F$11:$F$114),G98)/H98,0)*H98))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J98" t="n">
@@ -5763,92 +5767,867 @@
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99"/>
-      <x:c r="B99"/>
-      <x:c r="C99"/>
-      <x:c r="D99"/>
-      <x:c r="E99"/>
-      <x:c r="F99"/>
-      <x:c r="G99"/>
-      <x:c r="H99"/>
-      <x:c r="I99"/>
-      <x:c r="J99"/>
-      <x:c r="K99"/>
-      <x:c r="L99"/>
-      <x:c r="M99"/>
-      <x:c r="N99"/>
-      <x:c r="O99"/>
-      <x:c r="P99"/>
-      <x:c r="Q99"/>
-      <x:c r="R99"/>
-      <x:c r="S99"/>
+      <x:c r="A99" t="str">
+        <x:v>U25</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>PVDD boost converter 11.9 V (VQFN-20)</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>TI</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>TPS61088RHLR</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>C87357</x:v>
+      </x:c>
+      <x:c r="F99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I99" t="n">
+        <x:f>IF(OR(D99="",G99="",H99=""),"",IF(COUNTIF($D$11:D99,D99)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D99,$F$11:$F$114),G99)/H99,0)*H99))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K99" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="L99" t="n">
+        <x:f>IF(K99="","",ROUND(F99*K99,4))</x:f>
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="M99" t="n">
+        <x:f>IF(OR(K99="",I99="",N99=""),"",IF(N99&gt;=I99,ROUND(I99*K99,4),""))</x:f>
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="N99" t="n">
+        <x:v>1199</x:v>
+      </x:c>
+      <x:c r="O99" t="str">
+        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
+      </x:c>
+      <x:c r="P99" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q99" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R99" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. 499k/56k feedback, 301k RFREQ, 150k ILIM. Pad map and 3D from the EasyEDA official package; verify against TI RHL0020A before PCB.</x:v>
+      </x:c>
+      <x:c r="S99" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C87357.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
-      <x:c r="B100"/>
-      <x:c r="C100"/>
-      <x:c r="D100"/>
-      <x:c r="E100"/>
-      <x:c r="F100"/>
+        <x:v>L200</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>Boost inductor 2.2uH, Isat 19.6 A, Irms 17.8 A, 6.3 mohm</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Coilcraft</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>XAL7070-222MEC</x:v>
+      </x:c>
+      <x:c r="E100" t="str"/>
+      <x:c r="F100" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G100"/>
       <x:c r="H100"/>
-      <x:c r="I100"/>
+      <x:c r="I100" t="str">
+        <x:f>IF(OR(D100="",G100="",H100=""),"",IF(COUNTIF($D$11:D100,D100)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D100,$F$11:$F$114),G100)/H100,0)*H100))</x:f>
+      </x:c>
       <x:c r="J100"/>
       <x:c r="K100"/>
-      <x:c r="L100"/>
-      <x:c r="M100"/>
+      <x:c r="L100" t="str">
+        <x:f>IF(K100="","",ROUND(F100*K100,4))</x:f>
+      </x:c>
+      <x:c r="M100" t="str">
+        <x:f>IF(OR(K100="",I100="",N100=""),"",IF(N100&gt;=I100,ROUND(I100*K100,4),""))</x:f>
+      </x:c>
       <x:c r="N100"/>
-      <x:c r="O100"/>
-      <x:c r="P100"/>
-      <x:c r="Q100"/>
-      <x:c r="R100"/>
+      <x:c r="O100" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P100" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q100" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R100" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Not stocked at LCSC per search; alternatives: Cyntec PIMB104T-2R2MS (datasheet table 2, 18 A / 12 A) or Bourns SRP1265A-2R2M class. Stock KiCad XAL7070 footprint (7.5 x 7.2 mm).</x:v>
+      </x:c>
       <x:c r="S100"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101"/>
-      <x:c r="B101"/>
-      <x:c r="C101"/>
-      <x:c r="D101"/>
-      <x:c r="E101"/>
-      <x:c r="F101"/>
+      <x:c r="A101" t="str">
+        <x:v>L201, L202, L203, L204, L205, L206</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>Speaker output filter inductors 22uH, 5.0 A Isat (peak 2.8 A at 11.1 V into 4 ohm)</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Sunlord</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>MWSA1265S-220MT</x:v>
+      </x:c>
+      <x:c r="E101" t="str"/>
+      <x:c r="F101" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="G101"/>
       <x:c r="H101"/>
-      <x:c r="I101"/>
+      <x:c r="I101" t="str">
+        <x:f>IF(OR(D101="",G101="",H101=""),"",IF(COUNTIF($D$11:D101,D101)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D101,$F$11:$F$114),G101)/H101,0)*H101))</x:f>
+      </x:c>
       <x:c r="J101"/>
       <x:c r="K101"/>
-      <x:c r="L101"/>
-      <x:c r="M101"/>
+      <x:c r="L101" t="str">
+        <x:f>IF(K101="","",ROUND(F101*K101,4))</x:f>
+      </x:c>
+      <x:c r="M101" t="str">
+        <x:f>IF(OR(K101="",I101="",N101=""),"",IF(N101&gt;=I101,ROUND(I101*K101,4),""))</x:f>
+      </x:c>
       <x:c r="N101"/>
-      <x:c r="O101"/>
-      <x:c r="P101"/>
-      <x:c r="Q101"/>
-      <x:c r="R101"/>
+      <x:c r="O101" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P101" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q101" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R101" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Isat 5.0 A from the MWSA1265S series datasheet text; the 22 uH value row and its LCSC code were not confirmed. Stock KiCad MWSA1265S footprint (13.45 x 12.6 x 6.5 mm). OCP trips at about 7.5 A; confirm the saturation margin against measured peak.</x:v>
+      </x:c>
       <x:c r="S101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="str">
+        <x:v>J9, J10, J11</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>Speaker connectors FRONT_L, FRONT_R, WOOFER (JST VH 2-pin, 10 A)</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>JST</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>B2P-VH(LF)(SN)</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>C160315</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I102" t="n">
+        <x:f>IF(OR(D102="",G102="",H102=""),"",IF(COUNTIF($D$11:D102,D102)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D102,$F$11:$F$114),G102)/H102,0)*H102))</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K102" t="n">
+        <x:v>0.2404</x:v>
+      </x:c>
+      <x:c r="L102" t="n">
+        <x:f>IF(K102="","",ROUND(F102*K102,4))</x:f>
+        <x:v>0.7212</x:v>
+      </x:c>
+      <x:c r="M102" t="n">
+        <x:f>IF(OR(K102="",I102="",N102=""),"",IF(N102&gt;=I102,ROUND(I102*K102,4),""))</x:f>
+        <x:v>0.7212</x:v>
+      </x:c>
+      <x:c r="N102" t="n">
+        <x:v>20650</x:v>
+      </x:c>
+      <x:c r="O102" t="str">
+        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
+      </x:c>
+      <x:c r="P102" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q102" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R102" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Pin 1 +, pin 2 -. No 3D model linked (downloaded STEP axes not verified).</x:v>
+      </x:c>
+      <x:c r="S102" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C160315.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>C271, C272, C273, C274, C277, C279, C290, C292</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>PVDD_AMP 22uF 25V X7R 1210 (boost output and TAS5825M PVDD)</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>CL32B226KAJNNNE</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>C309062</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:f>IF(OR(D103="",G103="",H103=""),"",IF(COUNTIF($D$11:D103,D103)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D103,$F$11:$F$114),G103)/H103,0)*H103))</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K103" t="n">
+        <x:v>0.1742</x:v>
+      </x:c>
+      <x:c r="L103" t="n">
+        <x:f>IF(K103="","",ROUND(F103*K103,4))</x:f>
+        <x:v>1.3936</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:f>IF(OR(K103="",I103="",N103=""),"",IF(N103&gt;=I103,ROUND(I103*K103,4),""))</x:f>
+        <x:v>1.3936</x:v>
+      </x:c>
+      <x:c r="N103" t="n">
+        <x:v>9300</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>Search snapshot 2026-10-06; verify at order</x:v>
+      </x:c>
+      <x:c r="P103" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R103" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. 25 V rating on 11.9 V; X7R loses roughly half its capacitance at this bias. TAS datasheet lists 22 uF 35 V 0805: 1210 25 V used instead.</x:v>
+      </x:c>
+      <x:c r="S103" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C309062.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>C285, C286, C287, C288, C298, C299, C300, C301</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>TAS5825M bootstrap 0.47uF 25V X7R 0603</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>CL10B474KA8NNNC</x:v>
+      </x:c>
+      <x:c r="E104" t="str"/>
+      <x:c r="F104" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G104"/>
+      <x:c r="H104"/>
+      <x:c r="I104" t="str">
+        <x:f>IF(OR(D104="",G104="",H104=""),"",IF(COUNTIF($D$11:D104,D104)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D104,$F$11:$F$114),G104)/H104,0)*H104))</x:f>
+      </x:c>
+      <x:c r="J104"/>
+      <x:c r="K104"/>
+      <x:c r="L104" t="str">
+        <x:f>IF(K104="","",ROUND(F104*K104,4))</x:f>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:f>IF(OR(K104="",I104="",N104=""),"",IF(N104&gt;=I104,ROUND(I104*K104,4),""))</x:f>
+      </x:c>
+      <x:c r="N104"/>
+      <x:c r="O104" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P104" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R104" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Table 66 value 0.47 uF 16 V; 25 V part selected for margin.</x:v>
+      </x:c>
+      <x:c r="S104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>C302, C303, C304, C305, C306, C307</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Output filter 0.68uF 50V X7R 0805</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>CL21B684KBFVPNE</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>C472832</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G105"/>
+      <x:c r="H105"/>
+      <x:c r="I105" t="str">
+        <x:f>IF(OR(D105="",G105="",H105=""),"",IF(COUNTIF($D$11:D105,D105)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D105,$F$11:$F$114),G105)/H105,0)*H105))</x:f>
+      </x:c>
+      <x:c r="J105"/>
+      <x:c r="K105"/>
+      <x:c r="L105" t="str">
+        <x:f>IF(K105="","",ROUND(F105*K105,4))</x:f>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:f>IF(OR(K105="",I105="",N105=""),"",IF(N105&gt;=I105,ROUND(I105*K105,4),""))</x:f>
+      </x:c>
+      <x:c r="N105"/>
+      <x:c r="O105" t="str">
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P105" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R105" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Variant suffix per the LCSC listing; confirm voltage/dielectric on the datasheet.</x:v>
+      </x:c>
+      <x:c r="S105" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C472832.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>C268</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Boost COMP capacitor 6.8nF X7R 0603</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>CL10B682KB8NNNC</x:v>
+      </x:c>
+      <x:c r="E106" t="str"/>
+      <x:c r="F106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+      <x:c r="I106" t="str">
+        <x:f>IF(OR(D106="",G106="",H106=""),"",IF(COUNTIF($D$11:D106,D106)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D106,$F$11:$F$114),G106)/H106,0)*H106))</x:f>
+      </x:c>
+      <x:c r="J106"/>
+      <x:c r="K106"/>
+      <x:c r="L106" t="str">
+        <x:f>IF(K106="","",ROUND(F106*K106,4))</x:f>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:f>IF(OR(K106="",I106="",N106=""),"",IF(N106&gt;=I106,ROUND(I106*K106,4),""))</x:f>
+      </x:c>
+      <x:c r="N106"/>
+      <x:c r="O106" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P106" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R106" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Calculated compensation, bench check required.</x:v>
+      </x:c>
+      <x:c r="S106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>C269</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>Boost COMP capacitor 47pF C0G 0603</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>CL10C470JB8NNNC</x:v>
+      </x:c>
+      <x:c r="E107" t="str"/>
+      <x:c r="F107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
+      <x:c r="I107" t="str">
+        <x:f>IF(OR(D107="",G107="",H107=""),"",IF(COUNTIF($D$11:D107,D107)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D107,$F$11:$F$114),G107)/H107,0)*H107))</x:f>
+      </x:c>
+      <x:c r="J107"/>
+      <x:c r="K107"/>
+      <x:c r="L107" t="str">
+        <x:f>IF(K107="","",ROUND(F107*K107,4))</x:f>
+      </x:c>
+      <x:c r="M107" t="str">
+        <x:f>IF(OR(K107="",I107="",N107=""),"",IF(N107&gt;=I107,ROUND(I107*K107,4),""))</x:f>
+      </x:c>
+      <x:c r="N107"/>
+      <x:c r="O107" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P107" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q107" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R107" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Calculated compensation, bench check required.</x:v>
+      </x:c>
+      <x:c r="S107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>C275</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>PVDD_AMP bulk 100uF 25V polymer/hybrid (8x10 mm)</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>Panasonic</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>EEH-ZA1E101P</x:v>
+      </x:c>
+      <x:c r="E108" t="str"/>
+      <x:c r="F108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
+      <x:c r="I108" t="str">
+        <x:f>IF(OR(D108="",G108="",H108=""),"",IF(COUNTIF($D$11:D108,D108)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D108,$F$11:$F$114),G108)/H108,0)*H108))</x:f>
+      </x:c>
+      <x:c r="J108"/>
+      <x:c r="K108"/>
+      <x:c r="L108" t="str">
+        <x:f>IF(K108="","",ROUND(F108*K108,4))</x:f>
+      </x:c>
+      <x:c r="M108" t="str">
+        <x:f>IF(OR(K108="",I108="",N108=""),"",IF(N108&gt;=I108,ROUND(I108*K108,4),""))</x:f>
+      </x:c>
+      <x:c r="N108"/>
+      <x:c r="O108" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified. VERIFY part.</x:v>
+      </x:c>
+      <x:c r="P108" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q108" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R108" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Bass-burst reservoir; part type not verified.</x:v>
+      </x:c>
+      <x:c r="S108"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>R250</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>Boost feedback upper resistor 499k 1%</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>RC0603FR-07499KL</x:v>
+      </x:c>
+      <x:c r="E109" t="str"/>
+      <x:c r="F109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109"/>
+      <x:c r="H109"/>
+      <x:c r="I109" t="str">
+        <x:f>IF(OR(D109="",G109="",H109=""),"",IF(COUNTIF($D$11:D109,D109)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D109,$F$11:$F$114),G109)/H109,0)*H109))</x:f>
+      </x:c>
+      <x:c r="J109"/>
+      <x:c r="K109"/>
+      <x:c r="L109" t="str">
+        <x:f>IF(K109="","",ROUND(F109*K109,4))</x:f>
+      </x:c>
+      <x:c r="M109" t="str">
+        <x:f>IF(OR(K109="",I109="",N109=""),"",IF(N109&gt;=I109,ROUND(I109*K109,4),""))</x:f>
+      </x:c>
+      <x:c r="N109"/>
+      <x:c r="O109" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P109" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q109" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R109" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. VOUT = 1.204 V x (1 + 499k/56k) = 11.93 V.</x:v>
+      </x:c>
+      <x:c r="S109"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>R251</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>Boost feedback lower resistor 56k 1%</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>RC0603FR-0756KL</x:v>
+      </x:c>
+      <x:c r="E110" t="str"/>
+      <x:c r="F110" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110"/>
+      <x:c r="H110"/>
+      <x:c r="I110" t="str">
+        <x:f>IF(OR(D110="",G110="",H110=""),"",IF(COUNTIF($D$11:D110,D110)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D110,$F$11:$F$114),G110)/H110,0)*H110))</x:f>
+      </x:c>
+      <x:c r="J110"/>
+      <x:c r="K110"/>
+      <x:c r="L110" t="str">
+        <x:f>IF(K110="","",ROUND(F110*K110,4))</x:f>
+      </x:c>
+      <x:c r="M110" t="str">
+        <x:f>IF(OR(K110="",I110="",N110=""),"",IF(N110&gt;=I110,ROUND(I110*K110,4),""))</x:f>
+      </x:c>
+      <x:c r="N110"/>
+      <x:c r="O110" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P110" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q110" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R110" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. </x:v>
+      </x:c>
+      <x:c r="S110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>R252</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>Boost RFREQ 301k 1%</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>RC0603FR-07301KL</x:v>
+      </x:c>
+      <x:c r="E111" t="str"/>
+      <x:c r="F111" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111"/>
+      <x:c r="H111"/>
+      <x:c r="I111" t="str">
+        <x:f>IF(OR(D111="",G111="",H111=""),"",IF(COUNTIF($D$11:D111,D111)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D111,$F$11:$F$114),G111)/H111,0)*H111))</x:f>
+      </x:c>
+      <x:c r="J111"/>
+      <x:c r="K111"/>
+      <x:c r="L111" t="str">
+        <x:f>IF(K111="","",ROUND(F111*K111,4))</x:f>
+      </x:c>
+      <x:c r="M111" t="str">
+        <x:f>IF(OR(K111="",I111="",N111=""),"",IF(N111&gt;=I111,ROUND(I111*K111,4),""))</x:f>
+      </x:c>
+      <x:c r="N111"/>
+      <x:c r="O111" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P111" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q111" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R111" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. About 494 kHz at 3.6 V in.</x:v>
+      </x:c>
+      <x:c r="S111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>R253</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>Boost ILIM 150k 1%</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>RC0603FR-07150KL</x:v>
+      </x:c>
+      <x:c r="E112" t="str"/>
+      <x:c r="F112" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112"/>
+      <x:c r="H112"/>
+      <x:c r="I112" t="str">
+        <x:f>IF(OR(D112="",G112="",H112=""),"",IF(COUNTIF($D$11:D112,D112)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D112,$F$11:$F$114),G112)/H112,0)*H112))</x:f>
+      </x:c>
+      <x:c r="J112"/>
+      <x:c r="K112"/>
+      <x:c r="L112" t="str">
+        <x:f>IF(K112="","",ROUND(F112*K112,4))</x:f>
+      </x:c>
+      <x:c r="M112" t="str">
+        <x:f>IF(OR(K112="",I112="",N112=""),"",IF(N112&gt;=I112,ROUND(I112*K112,4),""))</x:f>
+      </x:c>
+      <x:c r="N112"/>
+      <x:c r="O112" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P112" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q112" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R112" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. 7.9 A typical, 6.6 A minimum peak limit (PFM).</x:v>
+      </x:c>
+      <x:c r="S112"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>R254</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Boost COMP resistor 82k 1%</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>RC0603FR-0782KL</x:v>
+      </x:c>
+      <x:c r="E113" t="str"/>
+      <x:c r="F113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
+      <x:c r="I113" t="str">
+        <x:f>IF(OR(D113="",G113="",H113=""),"",IF(COUNTIF($D$11:D113,D113)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D113,$F$11:$F$114),G113)/H113,0)*H113))</x:f>
+      </x:c>
+      <x:c r="J113"/>
+      <x:c r="K113"/>
+      <x:c r="L113" t="str">
+        <x:f>IF(K113="","",ROUND(F113*K113,4))</x:f>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:f>IF(OR(K113="",I113="",N113=""),"",IF(N113&gt;=I113,ROUND(I113*K113,4),""))</x:f>
+      </x:c>
+      <x:c r="N113"/>
+      <x:c r="O113" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P113" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q113" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R113" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. </x:v>
+      </x:c>
+      <x:c r="S113"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>R260 (R256 DNP)</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>TAS5825M U6 ADR 0 ohm (R256 = boost MODE option, not fitted)</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>RC0603FR-070RL</x:v>
+      </x:c>
+      <x:c r="E114" t="str"/>
+      <x:c r="F114" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114"/>
+      <x:c r="H114"/>
+      <x:c r="I114" t="str">
+        <x:f>IF(OR(D114="",G114="",H114=""),"",IF(COUNTIF($D$11:D114,D114)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D114,$F$11:$F$114),G114)/H114,0)*H114))</x:f>
+      </x:c>
+      <x:c r="J114"/>
+      <x:c r="K114"/>
+      <x:c r="L114" t="str">
+        <x:f>IF(K114="","",ROUND(F114*K114,4))</x:f>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:f>IF(OR(K114="",I114="",N114=""),"",IF(N114&gt;=I114,ROUND(I114*K114,4),""))</x:f>
+      </x:c>
+      <x:c r="N114"/>
+      <x:c r="O114" t="str">
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+      </x:c>
+      <x:c r="P114" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q114" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R114" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. R256 is DNP: fit to force PWM mode.</x:v>
+      </x:c>
+      <x:c r="S114"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
+      <x:c r="I115"/>
+      <x:c r="J115"/>
+      <x:c r="K115"/>
+      <x:c r="L115"/>
+      <x:c r="M115"/>
+      <x:c r="N115"/>
+      <x:c r="O115"/>
+      <x:c r="P115"/>
+      <x:c r="Q115"/>
+      <x:c r="R115"/>
+      <x:c r="S115"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
         <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
       </x:c>
-      <x:c r="B102"/>
-      <x:c r="C102"/>
-      <x:c r="D102"/>
-      <x:c r="E102"/>
-      <x:c r="F102"/>
-      <x:c r="G102"/>
-      <x:c r="H102"/>
-      <x:c r="I102"/>
-      <x:c r="J102"/>
-      <x:c r="K102"/>
-      <x:c r="L102"/>
-      <x:c r="M102"/>
-      <x:c r="N102"/>
-      <x:c r="O102"/>
-      <x:c r="P102"/>
-      <x:c r="Q102"/>
-      <x:c r="R102"/>
-      <x:c r="S102"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+      <x:c r="G116"/>
+      <x:c r="H116"/>
+      <x:c r="I116"/>
+      <x:c r="J116"/>
+      <x:c r="K116"/>
+      <x:c r="L116"/>
+      <x:c r="M116"/>
+      <x:c r="N116"/>
+      <x:c r="O116"/>
+      <x:c r="P116"/>
+      <x:c r="Q116"/>
+      <x:c r="R116"/>
+      <x:c r="S116"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
+      <x:c r="I117"/>
+      <x:c r="J117"/>
+      <x:c r="K117"/>
+      <x:c r="L117"/>
+      <x:c r="M117"/>
+      <x:c r="N117"/>
+      <x:c r="O117"/>
+      <x:c r="P117"/>
+      <x:c r="Q117"/>
+      <x:c r="R117"/>
+      <x:c r="S117"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
+      </x:c>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+      <x:c r="G118"/>
+      <x:c r="H118"/>
+      <x:c r="I118"/>
+      <x:c r="J118"/>
+      <x:c r="K118"/>
+      <x:c r="L118"/>
+      <x:c r="M118"/>
+      <x:c r="N118"/>
+      <x:c r="O118"/>
+      <x:c r="P118"/>
+      <x:c r="Q118"/>
+      <x:c r="R118"/>
+      <x:c r="S118"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R3604e51fcfa94702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R7643382c15d5483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R00ddba4ed26d4a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R0cb85783551548f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6055,7 +6055,9 @@
       <x:c r="D104" t="str">
         <x:v>CL10B474KA8NNNC</x:v>
       </x:c>
-      <x:c r="E104" t="str"/>
+      <x:c r="E104" t="str">
+        <x:v>C1623</x:v>
+      </x:c>
       <x:c r="F104" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -6074,7 +6076,7 @@
       </x:c>
       <x:c r="N104"/>
       <x:c r="O104" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+        <x:v>LCSC/JLCPCB code C1623 confirmed for this MPN (jlcpcb.com/partdetail/C1623, 2026-10-06); price/stock not retrieved.</x:v>
       </x:c>
       <x:c r="P104" t="n">
         <x:v>46300</x:v>
@@ -6083,9 +6085,11 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R104" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Table 66 value 0.47 uF 16 V; 25 V part selected for margin.</x:v>
-      </x:c>
-      <x:c r="S104"/>
+        <x:v>Amplifiers sheet, 2026-10-06. Table 66 value 0.47 uF 16 V; 25 V part selected for margin. Remaining Amplifiers-sheet codes (L200, L201-206, C268, C269, C275, R250-R254, R260, C206-C211 C0G 10 nF, R206-R208 33R) not found within the 8-lookup budget; LCSC search is not reachable by the agent (HTTP 403).</x:v>
+      </x:c>
+      <x:c r="S104" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C1623.html</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="str">
@@ -6563,9 +6567,7 @@
       <x:c r="S115"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A116"/>
       <x:c r="B116"/>
       <x:c r="C116"/>
       <x:c r="D116"/>
@@ -6607,9 +6609,7 @@
       <x:c r="S117"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" t="str">
-        <x:v>U18 links a derived STEP with corrected exposed pad; manufacturer exact model remains unavailable.</x:v>
-      </x:c>
+      <x:c r="A118"/>
       <x:c r="B118"/>
       <x:c r="C118"/>
       <x:c r="D118"/>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R00ddba4ed26d4a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R0cb85783551548f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R88769a16ef424944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R15cd418c244a4278"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -433,12 +433,12 @@
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
-        <x:f>ROUND(SUM(L11:L114),2)</x:f>
-        <x:v>78.94</x:v>
+        <x:f>ROUND(SUM(L11:L102),2)</x:f>
+        <x:v>74.53</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
-        <x:v>BOM updated 2026-10-05: TPS25730D USB_PD and BQ25792 charger integrated; stock/prices are listing snapshots or marked unverified.</x:v>
+        <x:v>BOM updated 2026-10-06: all R/C repackaged to hand-solder 0402 (0805 for large/high-voltage capacitors); many new passive MPNs and LCSC codes are unverified, so subtotal is partial.</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
@@ -461,8 +461,8 @@
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
-        <x:f>ROUND(SUM(M11:M114),2)</x:f>
-        <x:v>95.64</x:v>
+        <x:f>ROUND(SUM(M11:M102),2)</x:f>
+        <x:v>84.5</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -662,7 +662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="14" t="n">
-        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D11,$F$11:$F$114),G11)/H11,0)*H11))</x:f>
+        <x:f>IF(OR(D11="",G11="",H11=""),"",IF(COUNTIF($D$11:D11,D11)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D11,$F$11:$F$102),G11)/H11,0)*H11))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="6" t="n">
@@ -722,7 +722,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="14" t="n">
-        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D12,$F$11:$F$114),G12)/H12,0)*H12))</x:f>
+        <x:f>IF(OR(D12="",G12="",H12=""),"",IF(COUNTIF($D$11:D12,D12)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D12,$F$11:$F$102),G12)/H12,0)*H12))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="6" t="n">
@@ -780,7 +780,7 @@
       <x:c r="G13" s="13"/>
       <x:c r="H13" s="13"/>
       <x:c r="I13" s="14" t="str">
-        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D13,$F$11:$F$114),G13)/H13,0)*H13))</x:f>
+        <x:f>IF(OR(D13="",G13="",H13=""),"",IF(COUNTIF($D$11:D13,D13)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D13,$F$11:$F$102),G13)/H13,0)*H13))</x:f>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="28"/>
@@ -829,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="14" t="n">
-        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D14,$F$11:$F$114),G14)/H14,0)*H14))</x:f>
+        <x:f>IF(OR(D14="",G14="",H14=""),"",IF(COUNTIF($D$11:D14,D14)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D14,$F$11:$F$102),G14)/H14,0)*H14))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
@@ -889,7 +889,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="14" t="n">
-        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D15,$F$11:$F$114),G15)/H15,0)*H15))</x:f>
+        <x:f>IF(OR(D15="",G15="",H15=""),"",IF(COUNTIF($D$11:D15,D15)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D15,$F$11:$F$102),G15)/H15,0)*H15))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
@@ -949,7 +949,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="14" t="n">
-        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D16,$F$11:$F$114),G16)/H16,0)*H16))</x:f>
+        <x:f>IF(OR(D16="",G16="",H16=""),"",IF(COUNTIF($D$11:D16,D16)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D16,$F$11:$F$102),G16)/H16,0)*H16))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="n">
@@ -1009,7 +1009,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I17" s="14" t="n">
-        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D17,$F$11:$F$114),G17)/H17,0)*H17))</x:f>
+        <x:f>IF(OR(D17="",G17="",H17=""),"",IF(COUNTIF($D$11:D17,D17)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D17,$F$11:$F$102),G17)/H17,0)*H17))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J17" s="6" t="n">
@@ -1069,7 +1069,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="14" t="n">
-        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D18,$F$11:$F$114),G18)/H18,0)*H18))</x:f>
+        <x:f>IF(OR(D18="",G18="",H18=""),"",IF(COUNTIF($D$11:D18,D18)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D18,$F$11:$F$102),G18)/H18,0)*H18))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J18" s="6" t="n">
@@ -1129,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="14" t="n">
-        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D19,$F$11:$F$114),G19)/H19,0)*H19))</x:f>
+        <x:f>IF(OR(D19="",G19="",H19=""),"",IF(COUNTIF($D$11:D19,D19)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D19,$F$11:$F$102),G19)/H19,0)*H19))</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="6" t="n">
@@ -1189,7 +1189,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="14" t="n">
-        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D20,$F$11:$F$114),G20)/H20,0)*H20))</x:f>
+        <x:f>IF(OR(D20="",G20="",H20=""),"",IF(COUNTIF($D$11:D20,D20)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D20,$F$11:$F$102),G20)/H20,0)*H20))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
@@ -1249,7 +1249,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="14" t="n">
-        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D21,$F$11:$F$114),G21)/H21,0)*H21))</x:f>
+        <x:f>IF(OR(D21="",G21="",H21=""),"",IF(COUNTIF($D$11:D21,D21)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D21,$F$11:$F$102),G21)/H21,0)*H21))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J21" s="6" t="n">
@@ -1305,7 +1305,7 @@
       <x:c r="G22" s="1"/>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="str">
-        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D22,$F$11:$F$114),G22)/H22,0)*H22))</x:f>
+        <x:f>IF(OR(D22="",G22="",H22=""),"",IF(COUNTIF($D$11:D22,D22)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D22,$F$11:$F$102),G22)/H22,0)*H22))</x:f>
       </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="28"/>
@@ -1354,7 +1354,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="1" t="n">
-        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D23,$F$11:$F$114),G23)/H23,0)*H23))</x:f>
+        <x:f>IF(OR(D23="",G23="",H23=""),"",IF(COUNTIF($D$11:D23,D23)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D23,$F$11:$F$102),G23)/H23,0)*H23))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="1" t="n">
@@ -1414,7 +1414,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="1" t="n">
-        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D24,$F$11:$F$114),G24)/H24,0)*H24))</x:f>
+        <x:f>IF(OR(D24="",G24="",H24=""),"",IF(COUNTIF($D$11:D24,D24)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D24,$F$11:$F$102),G24)/H24,0)*H24))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J24" s="1" t="n">
@@ -1474,7 +1474,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I25" s="1" t="n">
-        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D25,$F$11:$F$114),G25)/H25,0)*H25))</x:f>
+        <x:f>IF(OR(D25="",G25="",H25=""),"",IF(COUNTIF($D$11:D25,D25)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D25,$F$11:$F$102),G25)/H25,0)*H25))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="J25" s="1" t="n">
@@ -1534,7 +1534,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="1" t="n">
-        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D26,$F$11:$F$114),G26)/H26,0)*H26))</x:f>
+        <x:f>IF(OR(D26="",G26="",H26=""),"",IF(COUNTIF($D$11:D26,D26)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D26,$F$11:$F$102),G26)/H26,0)*H26))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="n">
@@ -1594,7 +1594,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I27" s="1" t="n">
-        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D27,$F$11:$F$114),G27)/H27,0)*H27))</x:f>
+        <x:f>IF(OR(D27="",G27="",H27=""),"",IF(COUNTIF($D$11:D27,D27)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D27,$F$11:$F$102),G27)/H27,0)*H27))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J27" s="1" t="n">
@@ -1654,7 +1654,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I28" s="1" t="n">
-        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D28,$F$11:$F$114),G28)/H28,0)*H28))</x:f>
+        <x:f>IF(OR(D28="",G28="",H28=""),"",IF(COUNTIF($D$11:D28,D28)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D28,$F$11:$F$102),G28)/H28,0)*H28))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="J28" s="1" t="n">
@@ -1710,7 +1710,7 @@
       <x:c r="G29" s="1"/>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="str">
-        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D29,$F$11:$F$114),G29)/H29,0)*H29))</x:f>
+        <x:f>IF(OR(D29="",G29="",H29=""),"",IF(COUNTIF($D$11:D29,D29)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D29,$F$11:$F$102),G29)/H29,0)*H29))</x:f>
       </x:c>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="28"/>
@@ -1735,173 +1735,146 @@
     </x:row>
     <x:row r="30" ht="96" customHeight="1">
       <x:c r="A30" s="22" t="str">
-        <x:v>C6, C104, C105, C107, C140, C141, C142, C150, C152, C153, C154, C261, C262, C263, C264</x:v>
+        <x:v>U14</x:v>
       </x:c>
       <x:c r="B30" s="22" t="str">
-        <x:v>Charger / regulated-rail 22uF bulk capacitors</x:v>
+        <x:v>5 V codec logic buck-boost regulator</x:v>
       </x:c>
       <x:c r="C30" s="22" t="str">
-        <x:v>Murata</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D30" s="22" t="str">
-        <x:v>GRM21BZ71A226ME15L</x:v>
+        <x:v>TPS63802DLAR</x:v>
       </x:c>
       <x:c r="E30" s="22" t="str">
-        <x:v>C907991</x:v>
+        <x:v>C2845237</x:v>
       </x:c>
       <x:c r="F30" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H30" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="1" t="n">
-        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D30,$F$11:$F$114),G30)/H30,0)*H30))</x:f>
-        <x:v>20</x:v>
+        <x:f>IF(OR(D30="",G30="",H30=""),"",IF(COUNTIF($D$11:D30,D30)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D30,$F$11:$F$102),G30)/H30,0)*H30))</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J30" s="1" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K30" s="28" t="n">
-        <x:v>0.2543</x:v>
+        <x:v>0.9773</x:v>
       </x:c>
       <x:c r="L30" s="31" t="n">
         <x:f>IF(K30="","",ROUND(F30*K30,4))</x:f>
-        <x:v>3.8145</x:v>
+        <x:v>0.9773</x:v>
       </x:c>
       <x:c r="M30" s="31" t="n">
         <x:f>IF(OR(K30="",I30="",N30=""),"",IF(N30&gt;=I30,ROUND(I30*K30,4),""))</x:f>
-        <x:v>5.086</x:v>
+        <x:v>1.9546</x:v>
       </x:c>
       <x:c r="N30" s="7" t="n">
-        <x:v>146915</x:v>
+        <x:v>16705</x:v>
       </x:c>
       <x:c r="O30" s="1" t="str">
-        <x:v>Selected; price/stock open</x:v>
+        <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P30" s="4" t="n">
-        <x:v>46300</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="Q30" s="1" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-04</x:v>
       </x:c>
       <x:c r="R30" s="1" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Added C261, C262, C263, C264.</x:v>
+        <x:v>Same selected part and listing snapshot as U15; stock/price snapshot, not quote.</x:v>
       </x:c>
       <x:c r="S30" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2845237.html</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="36" customHeight="1">
       <x:c r="A31" s="25" t="str">
-        <x:v>U14</x:v>
+        <x:v>J4</x:v>
       </x:c>
       <x:c r="B31" s="25" t="str">
-        <x:v>5 V codec logic buck-boost regulator</x:v>
-      </x:c>
-      <x:c r="C31" s="25" t="str">
-        <x:v>Texas Instruments</x:v>
-      </x:c>
-      <x:c r="D31" s="25" t="str">
-        <x:v>TPS63802DLAR</x:v>
-      </x:c>
-      <x:c r="E31" s="25" t="str">
-        <x:v>C2845237</x:v>
-      </x:c>
+        <x:v>PD I2C service header</x:v>
+      </x:c>
+      <x:c r="C31" s="25"/>
+      <x:c r="D31" s="25"/>
+      <x:c r="E31" s="25"/>
       <x:c r="F31" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I31" t="n">
-        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D31,$F$11:$F$114),G31)/H31,0)*H31))</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K31" s="26" t="n">
-        <x:v>0.9773</x:v>
-      </x:c>
-      <x:c r="L31" s="27" t="n">
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+      <x:c r="I31" t="str">
+        <x:f>IF(OR(D31="",G31="",H31=""),"",IF(COUNTIF($D$11:D31,D31)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D31,$F$11:$F$102),G31)/H31,0)*H31))</x:f>
+      </x:c>
+      <x:c r="J31"/>
+      <x:c r="K31" s="26"/>
+      <x:c r="L31" s="27" t="str">
         <x:f>IF(K31="","",ROUND(F31*K31,4))</x:f>
-        <x:v>0.9773</x:v>
-      </x:c>
-      <x:c r="M31" s="27" t="n">
+      </x:c>
+      <x:c r="M31" s="27" t="str">
         <x:f>IF(OR(K31="",I31="",N31=""),"",IF(N31&gt;=I31,ROUND(I31*K31,4),""))</x:f>
-        <x:v>1.9546</x:v>
-      </x:c>
-      <x:c r="N31" s="17" t="n">
-        <x:v>16705</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N31" s="17"/>
       <x:c r="O31" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P31" s="16" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="Q31" t="str">
-        <x:v>2026-10-04</x:v>
-      </x:c>
-      <x:c r="R31" t="str">
-        <x:v>Same selected part and listing snapshot as U15; stock/price snapshot, not quote.</x:v>
-      </x:c>
-      <x:c r="S31" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2845237.html</x:v>
-      </x:c>
+        <x:v>MPN open</x:v>
+      </x:c>
+      <x:c r="P31" s="16"/>
+      <x:c r="Q31"/>
+      <x:c r="R31"/>
+      <x:c r="S31"/>
     </x:row>
     <x:row r="32" ht="36" customHeight="1">
       <x:c r="A32" s="25" t="str">
-        <x:v>C2</x:v>
+        <x:v>D7</x:v>
       </x:c>
       <x:c r="B32" s="25" t="str">
-        <x:v>TPS25730D CVBUS 4.7uF / 50V X7R 1210</x:v>
+        <x:v>TPS25730D VBUS-to-GND Schottky</x:v>
       </x:c>
       <x:c r="C32" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Diodes Incorporated</x:v>
       </x:c>
       <x:c r="D32" s="25" t="str">
-        <x:v>CL32B475KBUYNNE</x:v>
+        <x:v>1N5819HW-7-F</x:v>
       </x:c>
       <x:c r="E32" s="25" t="str">
-        <x:v>C170099</x:v>
+        <x:v>C82544</x:v>
       </x:c>
       <x:c r="F32" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D32,$F$11:$F$114),G32)/H32,0)*H32))</x:f>
-        <x:v>5</x:v>
+        <x:f>IF(OR(D32="",G32="",H32=""),"",IF(COUNTIF($D$11:D32,D32)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D32,$F$11:$F$102),G32)/H32,0)*H32))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J32" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K32" s="26" t="n">
-        <x:v>0.1367</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="L32" s="27" t="n">
         <x:f>IF(K32="","",ROUND(F32*K32,4))</x:f>
-        <x:v>0.1367</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="M32" s="27" t="n">
         <x:f>IF(OR(K32="",I32="",N32=""),"",IF(N32&gt;=I32,ROUND(I32*K32,4),""))</x:f>
-        <x:v>0.6835</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="N32" t="n">
-        <x:v>57880</x:v>
+        <x:v>137330</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>Listing snapshot</x:v>
@@ -1913,181 +1886,183 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R32" t="str">
-        <x:v>Alt: GRM32ER71H475KA88L C86052</x:v>
+        <x:v>40V/1A SOD-123; leakage not bench-checked; alt B5819W SL C8598</x:v>
       </x:c>
       <x:c r="S32" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C170099.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C82544.html</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="36" customHeight="1">
       <x:c r="A33" s="25" t="str">
-        <x:v>C184, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245, C270, C282, C283, C284, C295, C296, C297</x:v>
+        <x:v>J5</x:v>
       </x:c>
       <x:c r="B33" s="25" t="str">
-        <x:v>1uF / 50V capacitor; effective capacitance open</x:v>
+        <x:v>Three-contact protected pack connector</x:v>
       </x:c>
       <x:c r="C33" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Molex</x:v>
       </x:c>
       <x:c r="D33" s="25" t="str">
-        <x:v>CL21B105KBFNNNE</x:v>
+        <x:v>43650-0300</x:v>
       </x:c>
       <x:c r="E33" s="25" t="str">
-        <x:v>C28323</x:v>
+        <x:v>C503478</x:v>
       </x:c>
       <x:c r="F33" s="25" t="n">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D33,$F$11:$F$114),G33)/H33,0)*H33))</x:f>
-        <x:v>40</x:v>
+        <x:f>IF(OR(D33="",G33="",H33=""),"",IF(COUNTIF($D$11:D33,D33)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D33,$F$11:$F$102),G33)/H33,0)*H33))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J33" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K33" s="26" t="n">
-        <x:v>0.0403</x:v>
+        <x:v>0.5485</x:v>
       </x:c>
       <x:c r="L33" s="27" t="n">
         <x:f>IF(K33="","",ROUND(F33*K33,4))</x:f>
-        <x:v>1.2493</x:v>
+        <x:v>0.5485</x:v>
       </x:c>
       <x:c r="M33" s="27" t="n">
         <x:f>IF(OR(K33="",I33="",N33=""),"",IF(N33&gt;=I33,ROUND(I33*K33,4),""))</x:f>
-        <x:v>1.612</x:v>
+        <x:v>0.5485</x:v>
       </x:c>
       <x:c r="N33" t="n">
-        <x:v>1363910</x:v>
+        <x:v>9368</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Listing snapshot, unverified</x:v>
       </x:c>
       <x:c r="P33" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q33" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R33" t="str">
-        <x:v>CL21B105KBFNNNE; effective capacitance at bias not proven. Headphone_Aux sheet, 2026-10-06. Added C230, C231, C232, C233, C234, C235, C239, C240, C241, C245. Amplifiers sheet, 2026-10-06. Added C270, C282, C283, C284, C295, C296, C297.</x:v>
+        <x:v>Selected 2026-10-06: Micro-Fit 3.0 3-pos right-angle header, 8.5 A/contact (LCSC listing); mates 43645-0300 housing + 43030 crimps (not yet in BOM). LCSC datasheet file is an LXW 5 A drawing; use Molex PS-43650. Price/stock from 2026-10-06 LCSC page, not a quote.</x:v>
       </x:c>
       <x:c r="S33" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C503478.html</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="25" t="str">
-        <x:v>C5, C186, C187, C194, C195, C236</x:v>
+        <x:v>SW100</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
-        <x:v>4.7uF / 50V U19 input capacitor; prove effective capacitance meets TI minimum at worst DC bias/tolerance/temp.</x:v>
+        <x:v>QON wake pushbutton</x:v>
       </x:c>
       <x:c r="C34" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>TE Connectivity</x:v>
       </x:c>
       <x:c r="D34" s="25" t="str">
-        <x:v>CL31B475KBHNNNE</x:v>
+        <x:v>1977066-1</x:v>
       </x:c>
       <x:c r="E34" s="25" t="str">
-        <x:v>C51205</x:v>
+        <x:v>C2972219</x:v>
       </x:c>
       <x:c r="F34" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G34" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H34" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D34,$F$11:$F$114),G34)/H34,0)*H34))</x:f>
-        <x:v>10</x:v>
+        <x:f>IF(OR(D34="",G34="",H34=""),"",IF(COUNTIF($D$11:D34,D34)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D34,$F$11:$F$102),G34)/H34,0)*H34))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J34" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K34" s="26" t="n">
-        <x:v>0.0759</x:v>
+        <x:v>0.6291</x:v>
       </x:c>
       <x:c r="L34" s="27" t="n">
         <x:f>IF(K34="","",ROUND(F34*K34,4))</x:f>
-        <x:v>0.4554</x:v>
+        <x:v>0.6291</x:v>
       </x:c>
       <x:c r="M34" s="27" t="n">
         <x:f>IF(OR(K34="",I34="",N34=""),"",IF(N34&gt;=I34,ROUND(I34*K34,4),""))</x:f>
-        <x:v>0.759</x:v>
+        <x:v>0.6291</x:v>
       </x:c>
       <x:c r="N34" t="n">
-        <x:v>302170</x:v>
+        <x:v>2009</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Listing snapshot, unverified</x:v>
       </x:c>
       <x:c r="P34" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q34" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R34" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added C236.</x:v>
+        <x:v>Selected 2026-10-06: right-angle SMT tact, 50 mA @12 V. LCSC number confirmed. Price/stock from LCSC page 2026-10-06, not a quote.</x:v>
       </x:c>
       <x:c r="S34" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C51205.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2972219.html</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="36" customHeight="1">
       <x:c r="A35" s="25" t="str">
-        <x:v>R10</x:v>
+        <x:v>SW101</x:v>
       </x:c>
       <x:c r="B35" s="25" t="str">
-        <x:v>PD 200k 1% resistor</x:v>
+        <x:v>Pack-positive disconnect switch</x:v>
       </x:c>
       <x:c r="C35" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>SHOU HAN</x:v>
       </x:c>
       <x:c r="D35" s="25" t="str">
-        <x:v>RC0603FR-07200KL</x:v>
+        <x:v>KCD1-201-R</x:v>
       </x:c>
       <x:c r="E35" s="25" t="str">
-        <x:v>C105604</x:v>
+        <x:v>C5884429</x:v>
       </x:c>
       <x:c r="F35" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H35" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D35,$F$11:$F$114),G35)/H35,0)*H35))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D35="",G35="",H35=""),"",IF(COUNTIF($D$11:D35,D35)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D35,$F$11:$F$102),G35)/H35,0)*H35))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J35" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K35" s="26" t="n">
-        <x:v>0.0024</x:v>
+        <x:v>0.338</x:v>
       </x:c>
       <x:c r="L35" s="27" t="n">
         <x:f>IF(K35="","",ROUND(F35*K35,4))</x:f>
-        <x:v>0.0024</x:v>
+        <x:v>0.338</x:v>
       </x:c>
       <x:c r="M35" s="27" t="str">
         <x:f>IF(OR(K35="",I35="",N35=""),"",IF(N35&gt;=I35,ROUND(I35*K35,4),""))</x:f>
       </x:c>
-      <x:c r="N35"/>
+      <x:c r="N35" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="O35" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Listing snapshot, unverified</x:v>
       </x:c>
       <x:c r="P35" s="16" t="n">
         <x:v>46300</x:v>
@@ -2095,17 +2070,19 @@
       <x:c r="Q35" t="str">
         <x:v>2026-10-06</x:v>
       </x:c>
-      <x:c r="R35" t="str"/>
+      <x:c r="R35" t="str">
+        <x:v>Selected 2026-10-06: 20 mm round SPST rocker, 10 A @12 VDC (datasheet), 6 A 250 VAC. LCSC stock 0 at 2026-10-06: availability and 3-terminal mapping UNVERIFIED; peak 15-20 A exceeds rating, see HANDOVER.</x:v>
+      </x:c>
       <x:c r="S35" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105604.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5884429.html</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="36" customHeight="1">
       <x:c r="A36" s="25" t="str">
-        <x:v>J4</x:v>
+        <x:v>PACK</x:v>
       </x:c>
       <x:c r="B36" s="25" t="str">
-        <x:v>PD I2C service header</x:v>
+        <x:v>Protected 1S Li-ion pack with 10k NTC; capacity/curve/lead open</x:v>
       </x:c>
       <x:c r="C36" s="25"/>
       <x:c r="D36" s="25"/>
@@ -2116,7 +2093,7 @@
       <x:c r="G36"/>
       <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D36,$F$11:$F$114),G36)/H36,0)*H36))</x:f>
+        <x:f>IF(OR(D36="",G36="",H36=""),"",IF(COUNTIF($D$11:D36,D36)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D36,$F$11:$F$102),G36)/H36,0)*H36))</x:f>
       </x:c>
       <x:c r="J36"/>
       <x:c r="K36" s="26"/>
@@ -2137,22 +2114,22 @@
     </x:row>
     <x:row r="37" ht="36" customHeight="1">
       <x:c r="A37" s="25" t="str">
-        <x:v>C100, C101, C108, C111, C112</x:v>
+        <x:v>U15</x:v>
       </x:c>
       <x:c r="B37" s="25" t="str">
-        <x:v>BQ25792 VBUS/PMID 10uF / 50V X7R 1210 bank</x:v>
+        <x:v>3.8V Bluetooth buck-boost</x:v>
       </x:c>
       <x:c r="C37" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D37" s="25" t="str">
-        <x:v>CL32B106KBJNNNE</x:v>
+        <x:v>TPS63802DLAR</x:v>
       </x:c>
       <x:c r="E37" s="25" t="str">
-        <x:v>C138687</x:v>
+        <x:v>C2845237</x:v>
       </x:c>
       <x:c r="F37" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G37" t="n">
         <x:v>1</x:v>
@@ -2161,209 +2138,205 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D37,$F$11:$F$114),G37)/H37,0)*H37))</x:f>
-        <x:v>5</x:v>
+        <x:f>IF(OR(D37="",G37="",H37=""),"",IF(COUNTIF($D$11:D37,D37)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D37,$F$11:$F$102),G37)/H37,0)*H37))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="26" t="n">
-        <x:v>0.1571</x:v>
+        <x:v>0.9773</x:v>
       </x:c>
       <x:c r="L37" s="27" t="n">
         <x:f>IF(K37="","",ROUND(F37*K37,4))</x:f>
-        <x:v>0.7855</x:v>
-      </x:c>
-      <x:c r="M37" s="27" t="n">
+        <x:v>0.9773</x:v>
+      </x:c>
+      <x:c r="M37" s="27" t="str">
         <x:f>IF(OR(K37="",I37="",N37=""),"",IF(N37&gt;=I37,ROUND(I37*K37,4),""))</x:f>
-        <x:v>0.7855</x:v>
       </x:c>
       <x:c r="N37" t="n">
-        <x:v>183897</x:v>
+        <x:v>16705</x:v>
       </x:c>
       <x:c r="O37" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P37" s="16" t="n">
-        <x:v>46300</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="Q37" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R37" t="str">
-        <x:v>Review snapshot 2026-10-05; effective capacitance at bias per bq25792 ceramic review.</x:v>
-      </x:c>
+        <x:v>2026-10-04</x:v>
+      </x:c>
+      <x:c r="R37"/>
       <x:c r="S37" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138687.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2845237.html</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
       <x:c r="A38" s="25" t="str">
-        <x:v>C102, C109, C181, C185, C175, C176, C190, C214, C216, C218, C223</x:v>
+        <x:v>L2</x:v>
       </x:c>
       <x:c r="B38" s="25" t="str">
-        <x:v>10uF / 10V X7R 0805 capacitors (charger REGN/PD CVIN_3V3)</x:v>
+        <x:v>0.47uH codec buck-boost inductor</x:v>
       </x:c>
       <x:c r="C38" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Coilcraft</x:v>
       </x:c>
       <x:c r="D38" s="25" t="str">
-        <x:v>CL21B106KPQNNNE</x:v>
+        <x:v>XFL4015-471MEC</x:v>
       </x:c>
       <x:c r="E38" s="25" t="str">
-        <x:v>C32635</x:v>
+        <x:v>C18221164</x:v>
       </x:c>
       <x:c r="F38" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D38,$F$11:$F$114),G38)/H38,0)*H38))</x:f>
-        <x:v>20</x:v>
+        <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D38,$F$11:$F$102),G38)/H38,0)*H38))</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J38" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K38" s="26" t="n">
-        <x:v>0.093</x:v>
+        <x:v>4.2515</x:v>
       </x:c>
       <x:c r="L38" s="27" t="n">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v>1.023</x:v>
+        <x:v>4.2515</x:v>
       </x:c>
       <x:c r="M38" s="27" t="n">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
-        <x:v>1.86</x:v>
+        <x:v>8.503</x:v>
       </x:c>
       <x:c r="N38" t="n">
-        <x:v>230700</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="O38" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P38" s="16" t="n">
-        <x:v>46300</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="Q38" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R38"/>
+        <x:v>2026-10-04</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Same MPN as L3; listing stock and tier are shared.</x:v>
+      </x:c>
       <x:c r="S38" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C18221164.html</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="36" customHeight="1">
       <x:c r="A39" s="25" t="str">
-        <x:v>C103, C110, C266</x:v>
+        <x:v>L3</x:v>
       </x:c>
       <x:c r="B39" s="25" t="str">
-        <x:v>47nF X7R / 50V bootstrap capacitors</x:v>
+        <x:v>Bluetooth buck-boost 0.47uH inductor</x:v>
       </x:c>
       <x:c r="C39" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Coilcraft</x:v>
       </x:c>
       <x:c r="D39" s="25" t="str">
-        <x:v>CC0603KRX7R9BB473</x:v>
+        <x:v>XFL4015-471MEC</x:v>
       </x:c>
       <x:c r="E39" s="25" t="str">
-        <x:v>C107093</x:v>
+        <x:v>C18221164</x:v>
       </x:c>
       <x:c r="F39" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D39,$F$11:$F$114),G39)/H39,0)*H39))</x:f>
-        <x:v>50</x:v>
+        <x:f>IF(OR(D39="",G39="",H39=""),"",IF(COUNTIF($D$11:D39,D39)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D39,$F$11:$F$102),G39)/H39,0)*H39))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J39" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K39" s="26" t="n">
-        <x:v>0.0077</x:v>
+        <x:v>4.2515</x:v>
       </x:c>
       <x:c r="L39" s="27" t="n">
         <x:f>IF(K39="","",ROUND(F39*K39,4))</x:f>
-        <x:v>0.0231</x:v>
-      </x:c>
-      <x:c r="M39" s="27" t="n">
+        <x:v>4.2515</x:v>
+      </x:c>
+      <x:c r="M39" s="27" t="str">
         <x:f>IF(OR(K39="",I39="",N39=""),"",IF(N39&gt;=I39,ROUND(I39*K39,4),""))</x:f>
-        <x:v>0.385</x:v>
       </x:c>
       <x:c r="N39" t="n">
-        <x:v>1537650</x:v>
+        <x:v>2773</x:v>
       </x:c>
       <x:c r="O39" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P39" s="16" t="n">
-        <x:v>46300</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="Q39" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R39" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Added C266.</x:v>
-      </x:c>
+        <x:v>2026-10-04</x:v>
+      </x:c>
+      <x:c r="R39"/>
       <x:c r="S39" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C107093.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C18221164.html</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="36" customHeight="1">
       <x:c r="A40" s="25" t="str">
-        <x:v>C113, C114, C115</x:v>
+        <x:v>U19</x:v>
       </x:c>
       <x:c r="B40" s="25" t="str">
-        <x:v>BQ25792 VBUS/PMID/SYS 100nF/50V X7R 0402 bypass</x:v>
+        <x:v>USB auxiliary 5V / PD controller VDD LDO</x:v>
       </x:c>
       <x:c r="C40" s="25" t="str">
-        <x:v>Murata</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D40" s="25" t="str">
-        <x:v>GRM155R71H104KE14D</x:v>
+        <x:v>TPS7B8450QWDRBRQ1</x:v>
       </x:c>
       <x:c r="E40" s="25" t="str">
-        <x:v>C77020</x:v>
+        <x:v>C3751394</x:v>
       </x:c>
       <x:c r="F40" s="25" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D40,$F$11:$F$114),G40)/H40,0)*H40))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D40="",G40="",H40=""),"",IF(COUNTIF($D$11:D40,D40)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D40,$F$11:$F$102),G40)/H40,0)*H40))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J40" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K40" s="26" t="n">
-        <x:v>0.007</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="L40" s="27" t="n">
         <x:f>IF(K40="","",ROUND(F40*K40,4))</x:f>
-        <x:v>0.021</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="M40" s="27" t="n">
         <x:f>IF(OR(K40="",I40="",N40=""),"",IF(N40&gt;=I40,ROUND(I40*K40,4),""))</x:f>
-        <x:v>0.7</x:v>
+        <x:v>1.3452</x:v>
       </x:c>
       <x:c r="N40" t="n">
-        <x:v>777000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O40" t="str">
         <x:v>Listing snapshot</x:v>
@@ -2375,117 +2348,103 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R40" t="str">
-        <x:v>Footprint DesktopSpeaker:PD_C_0402 (no 3D model)</x:v>
+        <x:v>LCSC snapshot 2026-10-05: 1 pc in stock; $1.3452 at 1+, MOQ/multiple 1 (standard pack 3000; LCSC allows single-piece purchase). Stock is thin and may sell before ordering. TI TPS7B84-Q1: fixed 5V, 150mA, 40V input; startup/surge/dropout and thermal qualification open. Datasheet: ../datasheets/TPS7B84-Q1.pdf.</x:v>
       </x:c>
       <x:c r="S40" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3751394.html</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="36" customHeight="1">
       <x:c r="A41" s="25" t="str">
-        <x:v>D7</x:v>
+        <x:v>U20</x:v>
       </x:c>
       <x:c r="B41" s="25" t="str">
-        <x:v>TPS25730D VBUS-to-GND Schottky</x:v>
+        <x:v>USB and system logic priority mux</x:v>
       </x:c>
       <x:c r="C41" s="25" t="str">
-        <x:v>Diodes Incorporated</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D41" s="25" t="str">
-        <x:v>1N5819HW-7-F</x:v>
+        <x:v>TPS2116DRLR</x:v>
       </x:c>
       <x:c r="E41" s="25" t="str">
-        <x:v>C82544</x:v>
+        <x:v>C3235557</x:v>
       </x:c>
       <x:c r="F41" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G41" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H41" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I41" t="n">
-        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D41,$F$11:$F$114),G41)/H41,0)*H41))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J41" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K41" s="26" t="n">
-        <x:v>0.057</x:v>
-      </x:c>
-      <x:c r="L41" s="27" t="n">
+      <x:c r="G41"/>
+      <x:c r="H41"/>
+      <x:c r="I41" t="str">
+        <x:f>IF(OR(D41="",G41="",H41=""),"",IF(COUNTIF($D$11:D41,D41)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D41,$F$11:$F$102),G41)/H41,0)*H41))</x:f>
+      </x:c>
+      <x:c r="J41"/>
+      <x:c r="K41" s="26"/>
+      <x:c r="L41" s="27" t="str">
         <x:f>IF(K41="","",ROUND(F41*K41,4))</x:f>
-        <x:v>0.057</x:v>
-      </x:c>
-      <x:c r="M41" s="27" t="n">
+      </x:c>
+      <x:c r="M41" s="27" t="str">
         <x:f>IF(OR(K41="",I41="",N41=""),"",IF(N41&gt;=I41,ROUND(I41*K41,4),""))</x:f>
-        <x:v>0.57</x:v>
-      </x:c>
-      <x:c r="N41" t="n">
-        <x:v>137330</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N41"/>
       <x:c r="O41" t="str">
-        <x:v>Listing snapshot</x:v>
-      </x:c>
-      <x:c r="P41" s="16" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q41" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
+        <x:v>Stock/price unverified</x:v>
+      </x:c>
+      <x:c r="P41" s="16"/>
+      <x:c r="Q41"/>
       <x:c r="R41" t="str">
-        <x:v>40V/1A SOD-123; leakage not bench-checked; alt B5819W SL C8598</x:v>
+        <x:v>Selected MPN/LCSC mapping; current stock and price not verified.</x:v>
       </x:c>
       <x:c r="S41" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C82544.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3235557.html</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="36" customHeight="1">
       <x:c r="A42" s="25" t="str">
-        <x:v>C182, C183</x:v>
+        <x:v>U21</x:v>
       </x:c>
       <x:c r="B42" s="25" t="str">
-        <x:v>TPS25730D CC1/CC2 330pF C0G filters</x:v>
+        <x:v>Gauge undervoltage supervisor</x:v>
       </x:c>
       <x:c r="C42" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Texas Instruments</x:v>
       </x:c>
       <x:c r="D42" s="25" t="str">
-        <x:v>CL10C331JB8NNNC</x:v>
+        <x:v>TPS3839G33DBZR</x:v>
       </x:c>
       <x:c r="E42" s="25" t="str">
-        <x:v>C1578</x:v>
+        <x:v>C485802</x:v>
       </x:c>
       <x:c r="F42" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D42,$F$11:$F$114),G42)/H42,0)*H42))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D42="",G42="",H42=""),"",IF(COUNTIF($D$11:D42,D42)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D42,$F$11:$F$102),G42)/H42,0)*H42))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J42" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K42" s="26" t="n">
-        <x:v>0.0089</x:v>
+        <x:v>0.439</x:v>
       </x:c>
       <x:c r="L42" s="27" t="n">
         <x:f>IF(K42="","",ROUND(F42*K42,4))</x:f>
-        <x:v>0.0178</x:v>
-      </x:c>
-      <x:c r="M42" s="27" t="str">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="M42" s="27" t="n">
         <x:f>IF(OR(K42="",I42="",N42=""),"",IF(N42&gt;=I42,ROUND(I42*K42,4),""))</x:f>
-      </x:c>
-      <x:c r="N42"/>
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="N42" t="n">
+        <x:v>3444</x:v>
+      </x:c>
       <x:c r="O42" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
@@ -2493,686 +2452,637 @@
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q42" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R42" t="str"/>
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R42"/>
       <x:c r="S42" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1578.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C485802.html</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="36" customHeight="1">
       <x:c r="A43" s="25" t="str">
-        <x:v>C106</x:v>
+        <x:v>J6</x:v>
       </x:c>
       <x:c r="B43" s="25" t="str">
-        <x:v>Charger BAT 22uF / 10V capacitor</x:v>
+        <x:v>MCU SWD header 1x4 2.54 mm (J7 Tag-Connect TC2030 is PCB pads only, no BOM part)</x:v>
       </x:c>
       <x:c r="C43" s="25" t="str">
-        <x:v>Murata</x:v>
+        <x:v>Ckmtw</x:v>
       </x:c>
       <x:c r="D43" s="25" t="str">
-        <x:v>GRM21BZ71A226ME15L</x:v>
+        <x:v>B-2100S04P-A110</x:v>
       </x:c>
       <x:c r="E43" s="25" t="str">
-        <x:v>C907991</x:v>
+        <x:v>C124378</x:v>
       </x:c>
       <x:c r="F43" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D43,$F$11:$F$114),G43)/H43,0)*H43))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D43="",G43="",H43=""),"",IF(COUNTIF($D$11:D43,D43)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D43,$F$11:$F$102),G43)/H43,0)*H43))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J43" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K43" s="26" t="n">
-        <x:v>0.2543</x:v>
-      </x:c>
-      <x:c r="L43" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K43" s="26"/>
+      <x:c r="L43" s="27" t="str">
         <x:f>IF(K43="","",ROUND(F43*K43,4))</x:f>
-        <x:v>0.2543</x:v>
       </x:c>
       <x:c r="M43" s="27" t="str">
         <x:f>IF(OR(K43="",I43="",N43=""),"",IF(N43&gt;=I43,ROUND(I43*K43,4),""))</x:f>
       </x:c>
-      <x:c r="N43" t="n">
-        <x:v>146915</x:v>
-      </x:c>
+      <x:c r="N43"/>
       <x:c r="O43" t="str">
-        <x:v>Selected; price/stock open</x:v>
+        <x:v>LCSC number from search; price/stock unverified</x:v>
       </x:c>
       <x:c r="P43" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q43" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R43"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>1x4 straight THT header; footprint PinHeader_1x04_P2.54mm_Vertical (stock KiCad STEP). Pin order 1 SWDIO 2 SWCLK 3 NRST 4 GND. Programmer cable TC2030-IDC (legged footprint J7) is a tool, not fitted.</x:v>
+      </x:c>
       <x:c r="S43" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C124378.html</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="36" customHeight="1">
       <x:c r="A44" s="25" t="str">
-        <x:v>R100</x:v>
+        <x:v>Y170</x:v>
       </x:c>
       <x:c r="B44" s="25" t="str">
-        <x:v>Charger 5.23k resistor</x:v>
+        <x:v>12 MHz crystal for PCM2902C (3225-4P, CL 20 pF, +/-10 ppm)</x:v>
       </x:c>
       <x:c r="C44" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>YXC</x:v>
       </x:c>
       <x:c r="D44" s="25" t="str">
-        <x:v>1RC0603F5231</x:v>
+        <x:v>X322512MSB4SI</x:v>
       </x:c>
       <x:c r="E44" s="25" t="str">
-        <x:v>C54531489</x:v>
+        <x:v>C9002</x:v>
       </x:c>
       <x:c r="F44" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D44,$F$11:$F$114),G44)/H44,0)*H44))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D44="",G44="",H44=""),"",IF(COUNTIF($D$11:D44,D44)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D44,$F$11:$F$102),G44)/H44,0)*H44))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K44" s="26" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.0371</x:v>
       </x:c>
       <x:c r="L44" s="27" t="n">
         <x:f>IF(K44="","",ROUND(F44*K44,4))</x:f>
-        <x:v>0.002</x:v>
+        <x:v>0.0371</x:v>
       </x:c>
       <x:c r="M44" s="27" t="n">
         <x:f>IF(OR(K44="",I44="",N44=""),"",IF(N44&gt;=I44,ROUND(I44*K44,4),""))</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.371</x:v>
       </x:c>
       <x:c r="N44" t="n">
-        <x:v>9900</x:v>
+        <x:v>312110</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Listing snapshot, 2026-10-06</x:v>
       </x:c>
       <x:c r="P44" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q44" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R44"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Search-result snapshot; datasheet not retrieved. Pads 1/3 crystal, 2/4 GND assumed (generic 3225-4P) - verify. 33 pF load caps (C177/C178) give ~19.5 pF effective CL incl. stray, vs 20 pF rating.</x:v>
+      </x:c>
       <x:c r="S44" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531489.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C9002.html</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="36" customHeight="1">
       <x:c r="A45" s="25" t="str">
-        <x:v>R101</x:v>
+        <x:v>J8</x:v>
       </x:c>
       <x:c r="B45" s="25" t="str">
-        <x:v>Charger 30.1k resistor</x:v>
+        <x:v>BM83 test/programming header 1x5 2.54 mm (RST_N, P3_4, UART RX/TX, GND)</x:v>
       </x:c>
       <x:c r="C45" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>XYECONN</x:v>
       </x:c>
       <x:c r="D45" s="25" t="str">
-        <x:v>1RC0603F3012</x:v>
+        <x:v>XY-MTP254-1X5</x:v>
       </x:c>
       <x:c r="E45" s="25" t="str">
-        <x:v>C54531365</x:v>
+        <x:v>C54110162</x:v>
       </x:c>
       <x:c r="F45" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D45,$F$11:$F$114),G45)/H45,0)*H45))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D45="",G45="",H45=""),"",IF(COUNTIF($D$11:D45,D45)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D45,$F$11:$F$102),G45)/H45,0)*H45))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J45" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K45" s="26" t="n">
-        <x:v>0.002</x:v>
-      </x:c>
-      <x:c r="L45" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K45" s="26"/>
+      <x:c r="L45" s="27" t="str">
         <x:f>IF(K45="","",ROUND(F45*K45,4))</x:f>
-        <x:v>0.002</x:v>
-      </x:c>
-      <x:c r="M45" s="27" t="n">
+      </x:c>
+      <x:c r="M45" s="27" t="str">
         <x:f>IF(OR(K45="",I45="",N45=""),"",IF(N45&gt;=I45,ROUND(I45*K45,4),""))</x:f>
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="N45" t="n">
-        <x:v>3700</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N45"/>
       <x:c r="O45" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Stock/price unverified</x:v>
       </x:c>
       <x:c r="P45" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q45" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R45"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Bluetooth sheet; part number carried from the earlier 1x5 SWD header selection, not re-verified.</x:v>
+      </x:c>
       <x:c r="S45" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531365.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C54110162.html</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="36" customHeight="1">
       <x:c r="A46" s="25" t="str">
-        <x:v>R102</x:v>
+        <x:v>U24</x:v>
       </x:c>
       <x:c r="B46" s="25" t="str">
-        <x:v>Charger 4.7k resistor</x:v>
+        <x:v>Audio ADC 4:1 input, I2S master (TSSOP-30)</x:v>
       </x:c>
       <x:c r="C46" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D46" s="25" t="str">
-        <x:v>RC0603FR-074K7L</x:v>
+        <x:v>PCM1862DBTR</x:v>
       </x:c>
       <x:c r="E46" s="25" t="str">
-        <x:v>C99782</x:v>
+        <x:v>C544647</x:v>
       </x:c>
       <x:c r="F46" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H46" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D46,$F$11:$F$114),G46)/H46,0)*H46))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D46="",G46="",H46=""),"",IF(COUNTIF($D$11:D46,D46)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D46,$F$11:$F$102),G46)/H46,0)*H46))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J46" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K46" s="26" t="n">
-        <x:v>0.0011</x:v>
-      </x:c>
-      <x:c r="L46" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K46" s="26"/>
+      <x:c r="L46" s="27" t="str">
         <x:f>IF(K46="","",ROUND(F46*K46,4))</x:f>
-        <x:v>0.0011</x:v>
-      </x:c>
-      <x:c r="M46" s="27" t="n">
+      </x:c>
+      <x:c r="M46" s="27" t="str">
         <x:f>IF(OR(K46="",I46="",N46=""),"",IF(N46&gt;=I46,ROUND(I46*K46,4),""))</x:f>
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="N46" t="n">
-        <x:v>1575400</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N46"/>
       <x:c r="O46" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P46" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q46" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R46"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet SLAS831D.</x:v>
+      </x:c>
       <x:c r="S46" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C99782.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C544647.html</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="36" customHeight="1">
       <x:c r="A47" s="25" t="str">
-        <x:v>R108</x:v>
+        <x:v>U22</x:v>
       </x:c>
       <x:c r="B47" s="25" t="str">
-        <x:v>Charger 180k threshold resistor</x:v>
+        <x:v>3V3_AUDIO 300 mA ultra-low-noise LDO</x:v>
       </x:c>
       <x:c r="C47" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D47" s="25" t="str">
-        <x:v>RC0603FR-07180KL</x:v>
+        <x:v>TPS7A2033PDBVR</x:v>
       </x:c>
       <x:c r="E47" s="25" t="str">
-        <x:v>C123419</x:v>
+        <x:v>C2862740</x:v>
       </x:c>
       <x:c r="F47" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G47" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H47" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D47,$F$11:$F$114),G47)/H47,0)*H47))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D47="",G47="",H47=""),"",IF(COUNTIF($D$11:D47,D47)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D47,$F$11:$F$102),G47)/H47,0)*H47))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J47" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K47" s="26" t="n">
-        <x:v>0.0012</x:v>
-      </x:c>
-      <x:c r="L47" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K47" s="26"/>
+      <x:c r="L47" s="27" t="str">
         <x:f>IF(K47="","",ROUND(F47*K47,4))</x:f>
-        <x:v>0.0012</x:v>
       </x:c>
       <x:c r="M47" s="27" t="str">
         <x:f>IF(OR(K47="",I47="",N47=""),"",IF(N47&gt;=I47,ROUND(I47*K47,4),""))</x:f>
       </x:c>
       <x:c r="N47"/>
       <x:c r="O47" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P47" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q47" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R47"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. A TECH PUBLIC TPS7A2033PDBVR-TP clone is listed as C49452001; TI part chosen.</x:v>
+      </x:c>
       <x:c r="S47" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2862740.html</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="36" customHeight="1">
       <x:c r="A48" s="25" t="str">
-        <x:v>R112</x:v>
+        <x:v>U23</x:v>
       </x:c>
       <x:c r="B48" s="25" t="str">
-        <x:v>Charger 100R resistor</x:v>
+        <x:v>5V_CODEC load switch (SOT-23-6)</x:v>
       </x:c>
       <x:c r="C48" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D48" s="25" t="str">
-        <x:v>RC0603FR-07100RL</x:v>
+        <x:v>TPS22917DBVR</x:v>
       </x:c>
       <x:c r="E48" s="25" t="str">
-        <x:v>C105588</x:v>
+        <x:v>C2681320</x:v>
       </x:c>
       <x:c r="F48" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H48" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D48,$F$11:$F$114),G48)/H48,0)*H48))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D48="",G48="",H48=""),"",IF(COUNTIF($D$11:D48,D48)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D48,$F$11:$F$102),G48)/H48,0)*H48))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J48" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K48" s="26" t="n">
-        <x:v>0.0024</x:v>
-      </x:c>
-      <x:c r="L48" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K48" s="26"/>
+      <x:c r="L48" s="27" t="str">
         <x:f>IF(K48="","",ROUND(F48*K48,4))</x:f>
-        <x:v>0.0024</x:v>
-      </x:c>
-      <x:c r="M48" s="27" t="n">
+      </x:c>
+      <x:c r="M48" s="27" t="str">
         <x:f>IF(OR(K48="",I48="",N48=""),"",IF(N48&gt;=I48,ROUND(I48*K48,4),""))</x:f>
-        <x:v>0.24</x:v>
-      </x:c>
-      <x:c r="N48" t="n">
-        <x:v>2943700</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N48"/>
       <x:c r="O48" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P48" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q48" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R48"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R48" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Pinout checked against SLVSDW8B.</x:v>
+      </x:c>
       <x:c r="S48" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105588.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2681320.html</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="36" customHeight="1">
       <x:c r="A49" s="25" t="str">
-        <x:v>R106</x:v>
+        <x:v>Y200</x:v>
       </x:c>
       <x:c r="B49" s="25" t="str">
-        <x:v>Charger INT pull-up 10k</x:v>
+        <x:v>24.576 MHz crystal for PCM1862 (3225-4P, CL 15 pF)</x:v>
       </x:c>
       <x:c r="C49" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Lucki</x:v>
       </x:c>
       <x:c r="D49" s="25" t="str">
-        <x:v>RC0603FR-0710KL</x:v>
+        <x:v>L327S240P11L</x:v>
       </x:c>
       <x:c r="E49" s="25" t="str">
-        <x:v>C98220</x:v>
+        <x:v>C5261154</x:v>
       </x:c>
       <x:c r="F49" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G49" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H49" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D49,$F$11:$F$114),G49)/H49,0)*H49))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D49="",G49="",H49=""),"",IF(COUNTIF($D$11:D49,D49)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D49,$F$11:$F$102),G49)/H49,0)*H49))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J49" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K49" s="26" t="n">
-        <x:v>0.0035</x:v>
-      </x:c>
-      <x:c r="L49" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K49" s="26"/>
+      <x:c r="L49" s="27" t="str">
         <x:f>IF(K49="","",ROUND(F49*K49,4))</x:f>
-        <x:v>0.0035</x:v>
-      </x:c>
-      <x:c r="M49" s="27" t="n">
+      </x:c>
+      <x:c r="M49" s="27" t="str">
         <x:f>IF(OR(K49="",I49="",N49=""),"",IF(N49&gt;=I49,ROUND(I49*K49,4),""))</x:f>
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="N49" t="n">
-        <x:v>11102500</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N49"/>
       <x:c r="O49" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P49" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q49" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R49"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R49" t="str">
+        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet not retrieved; pad usage 1/3 assumed. Two 20 pF caps give about 13 pF CL; trim at bring-up.</x:v>
+      </x:c>
       <x:c r="S49" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5261154.html</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="36" customHeight="1">
       <x:c r="A50" s="25" t="str">
-        <x:v>R11, R13, R14, R15, R18, R182, R183, R242, R243, R244, R262</x:v>
+        <x:v>D200, D201</x:v>
       </x:c>
       <x:c r="B50" s="25" t="str">
-        <x:v>TPS25730D 10k 1% resistors (CC/ADC, I2C pull-ups R14/R15, pin 36 R18)</x:v>
+        <x:v>Headphone jack / AUX_IN jack ESD, 2-line bidirectional 5 V (SOT-23)</x:v>
       </x:c>
       <x:c r="C50" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>DOWO (Nexperia PESD5V0S2BT equivalent)</x:v>
       </x:c>
       <x:c r="D50" s="25" t="str">
-        <x:v>RC0603FR-0710KL</x:v>
+        <x:v>PESD5V0S2BT</x:v>
       </x:c>
       <x:c r="E50" s="25" t="str">
-        <x:v>C98220</x:v>
+        <x:v>C5380400</x:v>
       </x:c>
       <x:c r="F50" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H50" t="n">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D50,$F$11:$F$114),G50)/H50,0)*H50))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D50="",G50="",H50=""),"",IF(COUNTIF($D$11:D50,D50)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D50,$F$11:$F$102),G50)/H50,0)*H50))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J50" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K50" s="26" t="n">
-        <x:v>0.0034</x:v>
-      </x:c>
-      <x:c r="L50" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K50" s="26"/>
+      <x:c r="L50" s="27" t="str">
         <x:f>IF(K50="","",ROUND(F50*K50,4))</x:f>
-        <x:v>0.0374</x:v>
       </x:c>
       <x:c r="M50" s="27" t="str">
         <x:f>IF(OR(K50="",I50="",N50=""),"",IF(N50&gt;=I50,ROUND(I50*K50,4),""))</x:f>
       </x:c>
-      <x:c r="N50" t="n">
-        <x:v>7736700</x:v>
-      </x:c>
+      <x:c r="N50"/>
       <x:c r="O50" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P50" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q50" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R50" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R242, R243, R244. Amplifiers sheet, 2026-10-06. Added R262.</x:v>
+        <x:v>Headphone_Aux sheet, 2026-10-06. LCSC C5380400 is the DOWO PESD5V0S2BT listing; the Nexperia original was not stock-checked. Pin 3 common (search summary of Nexperia datasheet): VERIFY. Footprint DesktopSpeaker:PESD5V0S2BT (stock SOT-23).</x:v>
       </x:c>
       <x:c r="S50" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C98220.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5380400.html</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="36" customHeight="1">
       <x:c r="A51" s="25" t="str">
-        <x:v>R107</x:v>
+        <x:v>U25</x:v>
       </x:c>
       <x:c r="B51" s="25" t="str">
-        <x:v>Charger 100k resistor</x:v>
+        <x:v>PVDD boost converter 11.9 V (VQFN-20)</x:v>
       </x:c>
       <x:c r="C51" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>TI</x:v>
       </x:c>
       <x:c r="D51" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>TPS61088RHLR</x:v>
       </x:c>
       <x:c r="E51" s="25" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C87357</x:v>
       </x:c>
       <x:c r="F51" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H51" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D51,$F$11:$F$114),G51)/H51,0)*H51))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D51="",G51="",H51=""),"",IF(COUNTIF($D$11:D51,D51)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D51,$F$11:$F$102),G51)/H51,0)*H51))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J51" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K51" s="26" t="n">
-        <x:v>0.0036</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="L51" s="27" t="n">
         <x:f>IF(K51="","",ROUND(F51*K51,4))</x:f>
-        <x:v>0.0036</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="M51" s="27" t="n">
         <x:f>IF(OR(K51="",I51="",N51=""),"",IF(N51&gt;=I51,ROUND(I51*K51,4),""))</x:f>
-        <x:v>0.36</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="N51" t="n">
-        <x:v>7813400</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
       </x:c>
       <x:c r="P51" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q51" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R51"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R51" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. 499k/56k feedback, 301k RFREQ, 150k ILIM. Pad map and 3D from the EasyEDA official package; verify against TI RHL0020A before PCB.</x:v>
+      </x:c>
       <x:c r="S51" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C87357.html</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="36" customHeight="1">
       <x:c r="A52" s="25" t="str">
-        <x:v>R12, R16, R17</x:v>
+        <x:v>L200</x:v>
       </x:c>
       <x:c r="B52" s="25" t="str">
-        <x:v>TPS25730D 100k pull-ups / VIN_3V3 resistor</x:v>
+        <x:v>Boost inductor 2.2uH, Isat 19.6 A, Irms 17.8 A, 6.3 mohm</x:v>
       </x:c>
       <x:c r="C52" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Coilcraft</x:v>
       </x:c>
       <x:c r="D52" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E52" s="25" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
+        <x:v>XAL7070-222MEC</x:v>
+      </x:c>
+      <x:c r="E52" s="25"/>
       <x:c r="F52" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G52" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H52" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I52" t="n">
-        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D52,$F$11:$F$114),G52)/H52,0)*H52))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J52" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K52" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L52" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+      <x:c r="I52" t="str">
+        <x:f>IF(OR(D52="",G52="",H52=""),"",IF(COUNTIF($D$11:D52,D52)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D52,$F$11:$F$102),G52)/H52,0)*H52))</x:f>
+      </x:c>
+      <x:c r="J52"/>
+      <x:c r="K52" s="26"/>
+      <x:c r="L52" s="27" t="str">
         <x:f>IF(K52="","",ROUND(F52*K52,4))</x:f>
-        <x:v>0.0108</x:v>
       </x:c>
       <x:c r="M52" s="27" t="str">
         <x:f>IF(OR(K52="",I52="",N52=""),"",IF(N52&gt;=I52,ROUND(I52*K52,4),""))</x:f>
       </x:c>
-      <x:c r="N52" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
+      <x:c r="N52"/>
       <x:c r="O52" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
       </x:c>
       <x:c r="P52" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q52" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R52"/>
-      <x:c r="S52" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R52" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Not stocked at LCSC per search; alternatives: Cyntec PIMB104T-2R2MS (datasheet table 2, 18 A / 12 A) or Bourns SRP1265A-2R2M class. Stock KiCad XAL7070 footprint (7.5 x 7.2 mm).</x:v>
+      </x:c>
+      <x:c r="S52"/>
     </x:row>
     <x:row r="53" ht="36" customHeight="1">
       <x:c r="A53" s="25" t="str">
-        <x:v>R103, R109, R110, R111</x:v>
+        <x:v>L201, L202, L203, L204, L205, L206</x:v>
       </x:c>
       <x:c r="B53" s="25" t="str">
-        <x:v>Charger 100k pull-up/down resistors</x:v>
+        <x:v>Speaker output filter inductors 22uH, 5.0 A Isat (peak 2.8 A at 11.1 V into 4 ohm)</x:v>
       </x:c>
       <x:c r="C53" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Sunlord</x:v>
       </x:c>
       <x:c r="D53" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E53" s="25" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
+        <x:v>MWSA1265S-220MT</x:v>
+      </x:c>
+      <x:c r="E53" s="25"/>
       <x:c r="F53" s="25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G53" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H53" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I53" t="n">
-        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D53,$F$11:$F$114),G53)/H53,0)*H53))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J53" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K53" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L53" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53" t="str">
+        <x:f>IF(OR(D53="",G53="",H53=""),"",IF(COUNTIF($D$11:D53,D53)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D53,$F$11:$F$102),G53)/H53,0)*H53))</x:f>
+      </x:c>
+      <x:c r="J53"/>
+      <x:c r="K53" s="26"/>
+      <x:c r="L53" s="27" t="str">
         <x:f>IF(K53="","",ROUND(F53*K53,4))</x:f>
-        <x:v>0.0144</x:v>
       </x:c>
       <x:c r="M53" s="27" t="str">
         <x:f>IF(OR(K53="",I53="",N53=""),"",IF(N53&gt;=I53,ROUND(I53*K53,4),""))</x:f>
       </x:c>
-      <x:c r="N53" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
+      <x:c r="N53"/>
       <x:c r="O53" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
       </x:c>
       <x:c r="P53" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q53" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R53"/>
-      <x:c r="S53" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R53" t="str">
+        <x:v>Amplifiers sheet, 2026-10-06. Isat 5.0 A from the MWSA1265S series datasheet text; the 22 uH value row and its LCSC code were not confirmed. Stock KiCad MWSA1265S footprint (13.45 x 12.6 x 6.5 mm). OCP trips at about 7.5 A; confirm the saturation margin against measured peak.</x:v>
+      </x:c>
+      <x:c r="S53"/>
     </x:row>
     <x:row r="54" ht="36" customHeight="1">
       <x:c r="A54" s="25" t="str">
-        <x:v>J5</x:v>
+        <x:v>J9, J10, J11</x:v>
       </x:c>
       <x:c r="B54" s="25" t="str">
-        <x:v>Three-contact protected pack connector</x:v>
+        <x:v>Speaker connectors FRONT_L, FRONT_R, WOOFER (JST VH 2-pin, 10 A)</x:v>
       </x:c>
       <x:c r="C54" s="25" t="str">
-        <x:v>Molex</x:v>
+        <x:v>JST</x:v>
       </x:c>
       <x:c r="D54" s="25" t="str">
-        <x:v>43650-0300</x:v>
+        <x:v>B2P-VH(LF)(SN)</x:v>
       </x:c>
       <x:c r="E54" s="25" t="str">
-        <x:v>C503478</x:v>
+        <x:v>C160315</x:v>
       </x:c>
       <x:c r="F54" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G54" t="n">
         <x:v>1</x:v>
@@ -3181,28 +3091,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D54,$F$11:$F$114),G54)/H54,0)*H54))</x:f>
-        <x:v>1</x:v>
+        <x:f>IF(OR(D54="",G54="",H54=""),"",IF(COUNTIF($D$11:D54,D54)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D54,$F$11:$F$102),G54)/H54,0)*H54))</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J54" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K54" s="26" t="n">
-        <x:v>0.5485</x:v>
+        <x:v>0.2404</x:v>
       </x:c>
       <x:c r="L54" s="27" t="n">
         <x:f>IF(K54="","",ROUND(F54*K54,4))</x:f>
-        <x:v>0.5485</x:v>
+        <x:v>0.7212</x:v>
       </x:c>
       <x:c r="M54" s="27" t="n">
         <x:f>IF(OR(K54="",I54="",N54=""),"",IF(N54&gt;=I54,ROUND(I54*K54,4),""))</x:f>
-        <x:v>0.5485</x:v>
+        <x:v>0.7212</x:v>
       </x:c>
       <x:c r="N54" t="n">
-        <x:v>9368</x:v>
+        <x:v>20650</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>Listing snapshot, unverified</x:v>
+        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
       </x:c>
       <x:c r="P54" s="16" t="n">
         <x:v>46300</x:v>
@@ -3211,60 +3121,45 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R54" t="str">
-        <x:v>Selected 2026-10-06: Micro-Fit 3.0 3-pos right-angle header, 8.5 A/contact (LCSC listing); mates 43645-0300 housing + 43030 crimps (not yet in BOM). LCSC datasheet file is an LXW 5 A drawing; use Molex PS-43650. Price/stock from 2026-10-06 LCSC page, not a quote.</x:v>
+        <x:v>Amplifiers sheet, 2026-10-06. Pin 1 +, pin 2 -. No 3D model linked (downloaded STEP axes not verified).</x:v>
       </x:c>
       <x:c r="S54" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C503478.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C160315.html</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="36" customHeight="1">
       <x:c r="A55" s="25" t="str">
-        <x:v>SW100</x:v>
+        <x:v>C275</x:v>
       </x:c>
       <x:c r="B55" s="25" t="str">
-        <x:v>QON wake pushbutton</x:v>
+        <x:v>PVDD_AMP bulk 100uF 25V polymer/hybrid (8x10 mm)</x:v>
       </x:c>
       <x:c r="C55" s="25" t="str">
-        <x:v>TE Connectivity</x:v>
+        <x:v>Panasonic</x:v>
       </x:c>
       <x:c r="D55" s="25" t="str">
-        <x:v>1977066-1</x:v>
-      </x:c>
-      <x:c r="E55" s="25" t="str">
-        <x:v>C2972219</x:v>
-      </x:c>
+        <x:v>EEH-ZA1E101P</x:v>
+      </x:c>
+      <x:c r="E55" s="25"/>
       <x:c r="F55" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G55" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H55" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I55" t="n">
-        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D55,$F$11:$F$114),G55)/H55,0)*H55))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J55" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K55" s="26" t="n">
-        <x:v>0.6291</x:v>
-      </x:c>
-      <x:c r="L55" s="27" t="n">
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+      <x:c r="I55" t="str">
+        <x:f>IF(OR(D55="",G55="",H55=""),"",IF(COUNTIF($D$11:D55,D55)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D55,$F$11:$F$102),G55)/H55,0)*H55))</x:f>
+      </x:c>
+      <x:c r="J55"/>
+      <x:c r="K55" s="26"/>
+      <x:c r="L55" s="27" t="str">
         <x:f>IF(K55="","",ROUND(F55*K55,4))</x:f>
-        <x:v>0.6291</x:v>
-      </x:c>
-      <x:c r="M55" s="27" t="n">
+      </x:c>
+      <x:c r="M55" s="27" t="str">
         <x:f>IF(OR(K55="",I55="",N55=""),"",IF(N55&gt;=I55,ROUND(I55*K55,4),""))</x:f>
-        <x:v>0.6291</x:v>
-      </x:c>
-      <x:c r="N55" t="n">
-        <x:v>2009</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N55"/>
       <x:c r="O55" t="str">
-        <x:v>Listing snapshot, unverified</x:v>
+        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified. VERIFY part.</x:v>
       </x:c>
       <x:c r="P55" s="16" t="n">
         <x:v>46300</x:v>
@@ -3273,59 +3168,43 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R55" t="str">
-        <x:v>Selected 2026-10-06: right-angle SMT tact, 50 mA @12 V. LCSC number confirmed. Price/stock from LCSC page 2026-10-06, not a quote.</x:v>
-      </x:c>
-      <x:c r="S55" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2972219.html</x:v>
-      </x:c>
+        <x:v>Amplifiers sheet, 2026-10-06. Bass-burst reservoir; part type not verified.</x:v>
+      </x:c>
+      <x:c r="S55"/>
     </x:row>
     <x:row r="56" ht="36" customHeight="1">
       <x:c r="A56" s="25" t="str">
-        <x:v>SW101</x:v>
+        <x:v>C2, C5</x:v>
       </x:c>
       <x:c r="B56" s="25" t="str">
-        <x:v>Pack-positive disconnect switch</x:v>
+        <x:v>4.7uF X7R 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C56" s="25" t="str">
-        <x:v>SHOU HAN</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D56" s="25" t="str">
-        <x:v>KCD1-201-R</x:v>
-      </x:c>
-      <x:c r="E56" s="25" t="str">
-        <x:v>C5884429</x:v>
-      </x:c>
+        <x:v>C2012X7R1H475K125AC</x:v>
+      </x:c>
+      <x:c r="E56" s="25"/>
       <x:c r="F56" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G56" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H56" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I56" t="n">
-        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D56,$F$11:$F$114),G56)/H56,0)*H56))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J56" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K56" s="26" t="n">
-        <x:v>0.338</x:v>
-      </x:c>
-      <x:c r="L56" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+      <x:c r="I56" t="str">
+        <x:f>IF(OR(D56="",G56="",H56=""),"",IF(COUNTIF($D$11:D56,D56)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D56,$F$11:$F$102),G56)/H56,0)*H56))</x:f>
+      </x:c>
+      <x:c r="J56"/>
+      <x:c r="K56" s="26"/>
+      <x:c r="L56" s="27" t="str">
         <x:f>IF(K56="","",ROUND(F56*K56,4))</x:f>
-        <x:v>0.338</x:v>
       </x:c>
       <x:c r="M56" s="27" t="str">
         <x:f>IF(OR(K56="",I56="",N56=""),"",IF(N56&gt;=I56,ROUND(I56*K56,4),""))</x:f>
       </x:c>
-      <x:c r="N56" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="N56"/>
       <x:c r="O56" t="str">
-        <x:v>Listing snapshot, unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P56" s="16" t="n">
         <x:v>46300</x:v>
@@ -3334,29 +3213,31 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R56" t="str">
-        <x:v>Selected 2026-10-06: 20 mm round SPST rocker, 10 A @12 VDC (datasheet), 6 A 250 VAC. LCSC stock 0 at 2026-10-06: availability and 3-terminal mapping UNVERIFIED; peak 15-20 A exceeds rating, see HANDOVER.</x:v>
-      </x:c>
-      <x:c r="S56" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5884429.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_1210/C_1206 using CL32B475KBUYNNE, (none). See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S56"/>
     </x:row>
     <x:row r="57" ht="36" customHeight="1">
       <x:c r="A57" s="25" t="str">
-        <x:v>PACK</x:v>
+        <x:v>C100, C101, C108, C111, C112</x:v>
       </x:c>
       <x:c r="B57" s="25" t="str">
-        <x:v>Protected 1S Li-ion pack with 10k NTC; capacity/curve/lead open</x:v>
-      </x:c>
-      <x:c r="C57" s="25"/>
-      <x:c r="D57" s="25"/>
+        <x:v>10uF / 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
+      </x:c>
+      <x:c r="C57" s="25" t="str">
+        <x:v>Murata</x:v>
+      </x:c>
+      <x:c r="D57" s="25" t="str">
+        <x:v>GRM21BR61H106KE43L</x:v>
+      </x:c>
       <x:c r="E57" s="25"/>
       <x:c r="F57" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57" t="str">
-        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D57,$F$11:$F$114),G57)/H57,0)*H57))</x:f>
+        <x:f>IF(OR(D57="",G57="",H57=""),"",IF(COUNTIF($D$11:D57,D57)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D57,$F$11:$F$102),G57)/H57,0)*H57))</x:f>
       </x:c>
       <x:c r="J57"/>
       <x:c r="K57" s="26"/>
@@ -3368,58 +3249,64 @@
       </x:c>
       <x:c r="N57"/>
       <x:c r="O57" t="str">
-        <x:v>MPN open</x:v>
-      </x:c>
-      <x:c r="P57" s="16"/>
-      <x:c r="Q57"/>
-      <x:c r="R57"/>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P57" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q57" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R57" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_1210 using CL32B106KBJNNNE. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
       <x:c r="S57"/>
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C120, C121, C130, C131, C132, C143, C151, C126, C160, C162, C191, C163, C213, C215, C217, C219, C237, C238, C242, C246, C260, C267, C276, C278, C281, C289, C291, C294</x:v>
+        <x:v>C102, C109, C175, C176, C181, C185, C190, C214, C216, C218, C223</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
-        <x:v>100nF / 10V-or-higher 0603 decoupling; supervisor C126</x:v>
+        <x:v>10uF / 10uF / 10V / 10uF X7R 10V / 10uF X7R 10V CVIN_3V3 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C58" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D58" s="25" t="str">
-        <x:v>CL10B104KB8NNNC</x:v>
+        <x:v>CL21B106KPQNNNE</x:v>
       </x:c>
       <x:c r="E58" s="25" t="str">
-        <x:v>C1591</x:v>
+        <x:v>C32635</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G58" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H58" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D58,$F$11:$F$114),G58)/H58,0)*H58))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D58,$F$11:$F$102),G58)/H58,0)*H58))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J58" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K58" s="26" t="n">
-        <x:v>0.0111</x:v>
+        <x:v>0.093</x:v>
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>0.3108</x:v>
+        <x:v>1.023</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
-        <x:v>1.11</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="N58" t="n">
-        <x:v>1192600</x:v>
+        <x:v>230700</x:v>
       </x:c>
       <x:c r="O58" t="str">
         <x:v>Listing snapshot</x:v>
@@ -3431,421 +3318,347 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R58" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added C237, C238, C242, C246. Amplifiers sheet, 2026-10-06. Added C260, C267, C276, C278, C281, C289, C291, C294.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B106KPQNNNE. See reports/passive-repackage-2026-10-06.md. </x:v>
       </x:c>
       <x:c r="S58" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1591.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="36" customHeight="1">
       <x:c r="A59" s="25" t="str">
-        <x:v>C122, C123, C124, C125</x:v>
+        <x:v>C177, C178</x:v>
       </x:c>
       <x:c r="B59" s="25" t="str">
-        <x:v>AO LDO 1uF X7R 10V capacitors</x:v>
+        <x:v>33pF 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C59" s="25" t="str">
-        <x:v>Taiyo Yuden</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D59" s="25" t="str">
-        <x:v>LMK107B7105KA-T</x:v>
-      </x:c>
-      <x:c r="E59" s="25" t="str">
-        <x:v>C92806</x:v>
-      </x:c>
+        <x:v>GRM1555C1H330JA01D</x:v>
+      </x:c>
+      <x:c r="E59" s="25"/>
       <x:c r="F59" s="25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G59" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H59" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I59" t="n">
-        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D59,$F$11:$F$114),G59)/H59,0)*H59))</x:f>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J59" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K59" s="26" t="n">
-        <x:v>0.0231</x:v>
-      </x:c>
-      <x:c r="L59" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
+      <x:c r="I59" t="str">
+        <x:f>IF(OR(D59="",G59="",H59=""),"",IF(COUNTIF($D$11:D59,D59)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D59,$F$11:$F$102),G59)/H59,0)*H59))</x:f>
+      </x:c>
+      <x:c r="J59"/>
+      <x:c r="K59" s="26"/>
+      <x:c r="L59" s="27" t="str">
         <x:f>IF(K59="","",ROUND(F59*K59,4))</x:f>
-        <x:v>0.0924</x:v>
-      </x:c>
-      <x:c r="M59" s="27" t="n">
+      </x:c>
+      <x:c r="M59" s="27" t="str">
         <x:f>IF(OR(K59="",I59="",N59=""),"",IF(N59&gt;=I59,ROUND(I59*K59,4),""))</x:f>
-        <x:v>1.155</x:v>
-      </x:c>
-      <x:c r="N59" t="n">
-        <x:v>3650</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N59"/>
       <x:c r="O59" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P59" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q59" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R59"/>
-      <x:c r="S59" t="str">
-        <x:v>https://www.lcsc.com/es/product-detail/C92806.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R59" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C330JB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S59"/>
     </x:row>
     <x:row r="60" ht="36" customHeight="1">
       <x:c r="A60" s="25" t="str">
-        <x:v>R120, R121</x:v>
+        <x:v>C182, C183</x:v>
       </x:c>
       <x:c r="B60" s="25" t="str">
-        <x:v>Gauge I2C 4.7k resistors</x:v>
+        <x:v>330pF C0G CC1 filter / 330pF C0G CC2 filter 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C60" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D60" s="25" t="str">
-        <x:v>RC0603FR-074K7L</x:v>
-      </x:c>
-      <x:c r="E60" s="25" t="str">
-        <x:v>C99782</x:v>
-      </x:c>
+        <x:v>GRM1555C1H331JA01D</x:v>
+      </x:c>
+      <x:c r="E60" s="25"/>
       <x:c r="F60" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G60" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H60" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I60" t="n">
-        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D60,$F$11:$F$114),G60)/H60,0)*H60))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J60" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K60" s="26" t="n">
-        <x:v>0.0011</x:v>
-      </x:c>
-      <x:c r="L60" s="27" t="n">
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+      <x:c r="I60" t="str">
+        <x:f>IF(OR(D60="",G60="",H60=""),"",IF(COUNTIF($D$11:D60,D60)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D60,$F$11:$F$102),G60)/H60,0)*H60))</x:f>
+      </x:c>
+      <x:c r="J60"/>
+      <x:c r="K60" s="26"/>
+      <x:c r="L60" s="27" t="str">
         <x:f>IF(K60="","",ROUND(F60*K60,4))</x:f>
-        <x:v>0.0022</x:v>
       </x:c>
       <x:c r="M60" s="27" t="str">
         <x:f>IF(OR(K60="",I60="",N60=""),"",IF(N60&gt;=I60,ROUND(I60*K60,4),""))</x:f>
       </x:c>
-      <x:c r="N60" t="n">
-        <x:v>1575400</x:v>
-      </x:c>
+      <x:c r="N60"/>
       <x:c r="O60" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P60" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q60" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R60"/>
-      <x:c r="S60" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C99782.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R60" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C331JB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S60"/>
     </x:row>
     <x:row r="61" ht="36" customHeight="1">
       <x:c r="A61" s="25" t="str">
-        <x:v>R122, R232, R233</x:v>
+        <x:v>C206, C207, C208, C209, C210, C211</x:v>
       </x:c>
       <x:c r="B61" s="25" t="str">
-        <x:v>Gauge 47k resistor</x:v>
+        <x:v>10nF C0G 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C61" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D61" s="25" t="str">
-        <x:v>RC0603FR-0747KL</x:v>
-      </x:c>
-      <x:c r="E61" s="25" t="str">
-        <x:v>C105579</x:v>
-      </x:c>
+        <x:v>GRM1555C1H103JA01D</x:v>
+      </x:c>
+      <x:c r="E61" s="25"/>
       <x:c r="F61" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G61" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H61" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I61" t="n">
-        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D61,$F$11:$F$114),G61)/H61,0)*H61))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J61" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K61" s="26" t="n">
-        <x:v>0.0012</x:v>
-      </x:c>
-      <x:c r="L61" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
+      <x:c r="I61" t="str">
+        <x:f>IF(OR(D61="",G61="",H61=""),"",IF(COUNTIF($D$11:D61,D61)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D61,$F$11:$F$102),G61)/H61,0)*H61))</x:f>
+      </x:c>
+      <x:c r="J61"/>
+      <x:c r="K61" s="26"/>
+      <x:c r="L61" s="27" t="str">
         <x:f>IF(K61="","",ROUND(F61*K61,4))</x:f>
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="M61" s="27" t="n">
+      </x:c>
+      <x:c r="M61" s="27" t="str">
         <x:f>IF(OR(K61="",I61="",N61=""),"",IF(N61&gt;=I61,ROUND(I61*K61,4),""))</x:f>
-        <x:v>0.12</x:v>
-      </x:c>
-      <x:c r="N61" t="n">
-        <x:v>887500</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N61"/>
       <x:c r="O61" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P61" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q61" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R61" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R232, R233.</x:v>
-      </x:c>
-      <x:c r="S61" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105579.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using GRM1885C1H103JA01D. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S61"/>
     </x:row>
     <x:row r="62" ht="36" customHeight="1">
       <x:c r="A62" s="25" t="str">
-        <x:v>U15</x:v>
+        <x:v>C226, C227</x:v>
       </x:c>
       <x:c r="B62" s="25" t="str">
-        <x:v>3.8V Bluetooth buck-boost</x:v>
+        <x:v>22pF C0G 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C62" s="25" t="str">
-        <x:v>TI</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D62" s="25" t="str">
-        <x:v>TPS63802DLAR</x:v>
-      </x:c>
-      <x:c r="E62" s="25" t="str">
-        <x:v>C2845237</x:v>
-      </x:c>
+        <x:v>GRM1555C1H220JA01D</x:v>
+      </x:c>
+      <x:c r="E62" s="25"/>
       <x:c r="F62" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G62" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H62" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I62" t="n">
-        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D62,$F$11:$F$114),G62)/H62,0)*H62))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J62" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K62" s="26" t="n">
-        <x:v>0.9773</x:v>
-      </x:c>
-      <x:c r="L62" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62" t="str">
+        <x:f>IF(OR(D62="",G62="",H62=""),"",IF(COUNTIF($D$11:D62,D62)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D62,$F$11:$F$102),G62)/H62,0)*H62))</x:f>
+      </x:c>
+      <x:c r="J62"/>
+      <x:c r="K62" s="26"/>
+      <x:c r="L62" s="27" t="str">
         <x:f>IF(K62="","",ROUND(F62*K62,4))</x:f>
-        <x:v>0.9773</x:v>
       </x:c>
       <x:c r="M62" s="27" t="str">
         <x:f>IF(OR(K62="",I62="",N62=""),"",IF(N62&gt;=I62,ROUND(I62*K62,4),""))</x:f>
       </x:c>
-      <x:c r="N62" t="n">
-        <x:v>16705</x:v>
-      </x:c>
+      <x:c r="N62"/>
       <x:c r="O62" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P62" s="16" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q62" t="str">
-        <x:v>2026-10-04</x:v>
-      </x:c>
-      <x:c r="R62"/>
-      <x:c r="S62" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2845237.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R62" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C220JB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S62"/>
     </x:row>
     <x:row r="63" ht="36" customHeight="1">
       <x:c r="A63" s="25" t="str">
-        <x:v>L2</x:v>
+        <x:v>C200, C201, C202, C203, C204, C205, C243, C244</x:v>
       </x:c>
       <x:c r="B63" s="25" t="str">
-        <x:v>0.47uH codec buck-boost inductor</x:v>
+        <x:v>2.2uF 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C63" s="25" t="str">
-        <x:v>Coilcraft</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D63" s="25" t="str">
-        <x:v>XFL4015-471MEC</x:v>
-      </x:c>
-      <x:c r="E63" s="25" t="str">
-        <x:v>C18221164</x:v>
-      </x:c>
+        <x:v>CL05A225KP5NNNC</x:v>
+      </x:c>
+      <x:c r="E63" s="25"/>
       <x:c r="F63" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G63" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H63" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I63" t="n">
-        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D63,$F$11:$F$114),G63)/H63,0)*H63))</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J63" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K63" s="26" t="n">
-        <x:v>4.2515</x:v>
-      </x:c>
-      <x:c r="L63" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63" t="str">
+        <x:f>IF(OR(D63="",G63="",H63=""),"",IF(COUNTIF($D$11:D63,D63)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D63,$F$11:$F$102),G63)/H63,0)*H63))</x:f>
+      </x:c>
+      <x:c r="J63"/>
+      <x:c r="K63" s="26"/>
+      <x:c r="L63" s="27" t="str">
         <x:f>IF(K63="","",ROUND(F63*K63,4))</x:f>
-        <x:v>4.2515</x:v>
-      </x:c>
-      <x:c r="M63" s="27" t="n">
+      </x:c>
+      <x:c r="M63" s="27" t="str">
         <x:f>IF(OR(K63="",I63="",N63=""),"",IF(N63&gt;=I63,ROUND(I63*K63,4),""))</x:f>
-        <x:v>8.503</x:v>
-      </x:c>
-      <x:c r="N63" t="n">
-        <x:v>2773</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N63"/>
       <x:c r="O63" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P63" s="16" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q63" t="str">
-        <x:v>2026-10-04</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R63" t="str">
-        <x:v>Same MPN as L3; listing stock and tier are shared.</x:v>
-      </x:c>
-      <x:c r="S63" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C18221164.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B225KAFNNNE. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S63"/>
     </x:row>
     <x:row r="64" ht="36" customHeight="1">
       <x:c r="A64" s="25" t="str">
-        <x:v>L3</x:v>
+        <x:v>C113, C114, C115, C120, C121, C126, C130, C131, C132, C143, C151, C160, C162, C163, C191, C213, C215, C217, C219, C237, C238, C242, C246, C260, C267, C276, C278, C281, C289, C291, C294</x:v>
       </x:c>
       <x:c r="B64" s="25" t="str">
-        <x:v>Bluetooth buck-boost 0.47uH inductor</x:v>
+        <x:v>0.1uF / 50V / 100nF / 100nF 10V X7R / 100nF X7R 10V 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C64" s="25" t="str">
-        <x:v>Coilcraft</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D64" s="25" t="str">
-        <x:v>XFL4015-471MEC</x:v>
+        <x:v>GRM155R71H104KE14D</x:v>
       </x:c>
       <x:c r="E64" s="25" t="str">
-        <x:v>C18221164</x:v>
+        <x:v>C77020</x:v>
       </x:c>
       <x:c r="F64" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G64" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H64" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D64,$F$11:$F$114),G64)/H64,0)*H64))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D64="",G64="",H64=""),"",IF(COUNTIF($D$11:D64,D64)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D64,$F$11:$F$102),G64)/H64,0)*H64))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J64" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K64" s="26" t="n">
-        <x:v>4.2515</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="L64" s="27" t="n">
         <x:f>IF(K64="","",ROUND(F64*K64,4))</x:f>
-        <x:v>4.2515</x:v>
-      </x:c>
-      <x:c r="M64" s="27" t="str">
+        <x:v>0.217</x:v>
+      </x:c>
+      <x:c r="M64" s="27" t="n">
         <x:f>IF(OR(K64="",I64="",N64=""),"",IF(N64&gt;=I64,ROUND(I64*K64,4),""))</x:f>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="N64" t="n">
-        <x:v>2773</x:v>
+        <x:v>777000</x:v>
       </x:c>
       <x:c r="O64" t="str">
         <x:v>Listing snapshot</x:v>
       </x:c>
       <x:c r="P64" s="16" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="Q64" t="str">
-        <x:v>2026-10-04</x:v>
-      </x:c>
-      <x:c r="R64"/>
+        <x:v>2026-10-05</x:v>
+      </x:c>
+      <x:c r="R64" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603/C_0402 using CL10B104KB8NNNC, GRM155R71H104KE14D. See reports/passive-repackage-2026-10-06.md. Footprint DesktopSpeaker:PD_C_0402 (no 3D model)</x:v>
+      </x:c>
       <x:c r="S64" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C18221164.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="36" customHeight="1">
       <x:c r="A65" s="25" t="str">
-        <x:v>R140</x:v>
+        <x:v>C6, C104, C105, C106, C107, C140, C141, C142, C150, C152, C153, C154, C261, C262, C263, C264</x:v>
       </x:c>
       <x:c r="B65" s="25" t="str">
-        <x:v>78.7k 1% codec feedback divider resistor</x:v>
+        <x:v>22uF / 10V / 22uF 10V / 22uF 10V X7R / 22uF X7R 10V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C65" s="25" t="str">
-        <x:v>SAE</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D65" s="25" t="str">
-        <x:v>1RC0603F7872</x:v>
+        <x:v>GRM21BZ71A226ME15L</x:v>
       </x:c>
       <x:c r="E65" s="25" t="str">
-        <x:v>C54531588</x:v>
+        <x:v>C907991</x:v>
       </x:c>
       <x:c r="F65" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H65" t="n">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D65,$F$11:$F$114),G65)/H65,0)*H65))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D65="",G65="",H65=""),"",IF(COUNTIF($D$11:D65,D65)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D65,$F$11:$F$102),G65)/H65,0)*H65))</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J65" t="n">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K65" s="26" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.2543</x:v>
       </x:c>
       <x:c r="L65" s="27" t="n">
         <x:f>IF(K65="","",ROUND(F65*K65,4))</x:f>
-        <x:v>0.002</x:v>
+        <x:v>4.0688</x:v>
       </x:c>
       <x:c r="M65" s="27" t="n">
         <x:f>IF(OR(K65="",I65="",N65=""),"",IF(N65&gt;=I65,ROUND(I65*K65,4),""))</x:f>
-        <x:v>0.2</x:v>
+        <x:v>5.086</x:v>
       </x:c>
       <x:c r="N65" t="n">
-        <x:v>4700</x:v>
+        <x:v>146915</x:v>
       </x:c>
       <x:c r="O65" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>Selected; price/stock open</x:v>
       </x:c>
       <x:c r="P65" s="16" t="n">
         <x:v>46300</x:v>
@@ -3854,299 +3667,248 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R65" t="str">
-        <x:v>In stock 4,700; tier $0.002 at 100+. Datasheet confirms 0603, ±1%, ±100ppm/°C and −55 to +155°C.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using GRM21BZ71A226ME15L. See reports/passive-repackage-2026-10-06.md. Amplifiers sheet, 2026-10-06. Added C261, C262, C263, C264.</x:v>
       </x:c>
       <x:c r="S65" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54531588.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C907991.html</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="36" customHeight="1">
       <x:c r="A66" s="25" t="str">
-        <x:v>R141</x:v>
+        <x:v>C265</x:v>
       </x:c>
       <x:c r="B66" s="25" t="str">
-        <x:v>9.1k 1% codec feedback divider resistor</x:v>
+        <x:v>2.2uF 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C66" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D66" s="25" t="str">
-        <x:v>RC0603FR-079K1L</x:v>
+        <x:v>CL21B225KAFNNNE</x:v>
       </x:c>
       <x:c r="E66" s="25" t="str">
-        <x:v>C114639</x:v>
+        <x:v>C19110</x:v>
       </x:c>
       <x:c r="F66" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D66,$F$11:$F$114),G66)/H66,0)*H66))</x:f>
-        <x:v>100</x:v>
+        <x:f>IF(OR(D66="",G66="",H66=""),"",IF(COUNTIF($D$11:D66,D66)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D66,$F$11:$F$102),G66)/H66,0)*H66))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J66" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K66" s="26" t="n">
-        <x:v>0.0034</x:v>
-      </x:c>
-      <x:c r="L66" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K66" s="26"/>
+      <x:c r="L66" s="27" t="str">
         <x:f>IF(K66="","",ROUND(F66*K66,4))</x:f>
-        <x:v>0.0034</x:v>
-      </x:c>
-      <x:c r="M66" s="27" t="n">
+      </x:c>
+      <x:c r="M66" s="27" t="str">
         <x:f>IF(OR(K66="",I66="",N66=""),"",IF(N66&gt;=I66,ROUND(I66*K66,4),""))</x:f>
-        <x:v>0.34</x:v>
-      </x:c>
-      <x:c r="N66" t="n">
-        <x:v>296500</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N66"/>
       <x:c r="O66" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P66" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q66" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R66" t="str">
-        <x:v>In stock 296,500; tier $0.0034 at 100+. 0603, ±1%, ±100ppm/°C, −55 to +155°C. Distinct MPN from R151.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B225KAFNNNE. See reports/passive-repackage-2026-10-06.md. Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias. Headphone_Aux sheet, 2026-10-06. Added C243, C244. Amplifiers sheet, 2026-10-06. Added C265.</x:v>
       </x:c>
       <x:c r="S66" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114639.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C19110.html</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="36" customHeight="1">
       <x:c r="A67" s="25" t="str">
-        <x:v>R150</x:v>
+        <x:v>C103, C110, C266</x:v>
       </x:c>
       <x:c r="B67" s="25" t="str">
-        <x:v>604k 1% feedback resistor</x:v>
+        <x:v>47nF / 47nF / 50V 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C67" s="25" t="str">
-        <x:v>FOJAN</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D67" s="25" t="str">
-        <x:v>FRC0603F6043TS</x:v>
-      </x:c>
-      <x:c r="E67" s="25" t="str">
-        <x:v>C2933246</x:v>
-      </x:c>
+        <x:v>GRM155R71H473KA12D</x:v>
+      </x:c>
+      <x:c r="E67" s="25"/>
       <x:c r="F67" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G67" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H67" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I67" t="n">
-        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D67,$F$11:$F$114),G67)/H67,0)*H67))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J67" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K67" s="26" t="n">
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="L67" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67" t="str">
+        <x:f>IF(OR(D67="",G67="",H67=""),"",IF(COUNTIF($D$11:D67,D67)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D67,$F$11:$F$102),G67)/H67,0)*H67))</x:f>
+      </x:c>
+      <x:c r="J67"/>
+      <x:c r="K67" s="26"/>
+      <x:c r="L67" s="27" t="str">
         <x:f>IF(K67="","",ROUND(F67*K67,4))</x:f>
-        <x:v>0.0025</x:v>
-      </x:c>
-      <x:c r="M67" s="27" t="n">
+      </x:c>
+      <x:c r="M67" s="27" t="str">
         <x:f>IF(OR(K67="",I67="",N67=""),"",IF(N67&gt;=I67,ROUND(I67*K67,4),""))</x:f>
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="N67" t="n">
-        <x:v>54400</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N67"/>
       <x:c r="O67" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P67" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q67" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R67"/>
-      <x:c r="S67" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2933246.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R67" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CC0603KRX7R9BB473. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S67"/>
     </x:row>
     <x:row r="68" ht="36" customHeight="1">
       <x:c r="A68" s="25" t="str">
-        <x:v>R151</x:v>
+        <x:v>C268</x:v>
       </x:c>
       <x:c r="B68" s="25" t="str">
-        <x:v>91k 1% feedback resistor</x:v>
+        <x:v>6.8nF 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C68" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D68" s="25" t="str">
-        <x:v>AC0603FR-0791KL</x:v>
-      </x:c>
-      <x:c r="E68" s="25" t="str">
-        <x:v>C228098</x:v>
-      </x:c>
+        <x:v>GRM155R71H682KA01D</x:v>
+      </x:c>
+      <x:c r="E68" s="25"/>
       <x:c r="F68" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G68" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H68" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I68" t="n">
-        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D68,$F$11:$F$114),G68)/H68,0)*H68))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J68" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K68" s="26" t="n">
-        <x:v>0.0061</x:v>
-      </x:c>
-      <x:c r="L68" s="27" t="n">
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68" t="str">
+        <x:f>IF(OR(D68="",G68="",H68=""),"",IF(COUNTIF($D$11:D68,D68)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D68,$F$11:$F$102),G68)/H68,0)*H68))</x:f>
+      </x:c>
+      <x:c r="J68"/>
+      <x:c r="K68" s="26"/>
+      <x:c r="L68" s="27" t="str">
         <x:f>IF(K68="","",ROUND(F68*K68,4))</x:f>
-        <x:v>0.0061</x:v>
-      </x:c>
-      <x:c r="M68" s="27" t="n">
+      </x:c>
+      <x:c r="M68" s="27" t="str">
         <x:f>IF(OR(K68="",I68="",N68=""),"",IF(N68&gt;=I68,ROUND(I68*K68,4),""))</x:f>
-        <x:v>0.61</x:v>
-      </x:c>
-      <x:c r="N68" t="n">
-        <x:v>700</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N68"/>
       <x:c r="O68" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P68" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q68" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R68"/>
-      <x:c r="S68" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C228098.html</x:v>
-      </x:c>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R68" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10B682KB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S68"/>
     </x:row>
     <x:row r="69" ht="36" customHeight="1">
       <x:c r="A69" s="25" t="str">
-        <x:v>R152, R153, R154, R160, R175, R176, R180, R181, R184, R113, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239, R255, R259</x:v>
+        <x:v>C269</x:v>
       </x:c>
       <x:c r="B69" s="25" t="str">
-        <x:v>100k EN / MODE / bleeder / BOOT0 pull-down resistors</x:v>
+        <x:v>47pF 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C69" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D69" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E69" s="25" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
+        <x:v>GRM1555C1H470JA01D</x:v>
+      </x:c>
+      <x:c r="E69" s="25"/>
       <x:c r="F69" s="25" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G69" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H69" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I69" t="n">
-        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D69,$F$11:$F$114),G69)/H69,0)*H69))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J69" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K69" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L69" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
+      <x:c r="I69" t="str">
+        <x:f>IF(OR(D69="",G69="",H69=""),"",IF(COUNTIF($D$11:D69,D69)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D69,$F$11:$F$102),G69)/H69,0)*H69))</x:f>
+      </x:c>
+      <x:c r="J69"/>
+      <x:c r="K69" s="26"/>
+      <x:c r="L69" s="27" t="str">
         <x:f>IF(K69="","",ROUND(F69*K69,4))</x:f>
-        <x:v>0.0936</x:v>
       </x:c>
       <x:c r="M69" s="27" t="str">
         <x:f>IF(OR(K69="",I69="",N69=""),"",IF(N69&gt;=I69,ROUND(I69*K69,4),""))</x:f>
       </x:c>
-      <x:c r="N69" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
+      <x:c r="N69"/>
       <x:c r="O69" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P69" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q69" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R69" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239. Amplifiers sheet, 2026-10-06. Added R255, R259.</x:v>
-      </x:c>
-      <x:c r="S69" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C470JB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S69"/>
     </x:row>
     <x:row r="70" ht="36" customHeight="1">
       <x:c r="A70" s="25" t="str">
-        <x:v>R142</x:v>
+        <x:v>C184, C270</x:v>
       </x:c>
       <x:c r="B70" s="25" t="str">
-        <x:v>100k EN pulldown resistor</x:v>
+        <x:v>1uF / 1uF X7R 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C70" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D70" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>CL21B105KBFNNNE</x:v>
       </x:c>
       <x:c r="E70" s="25" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C28323</x:v>
       </x:c>
       <x:c r="F70" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G70" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H70" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D70,$F$11:$F$114),G70)/H70,0)*H70))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D70="",G70="",H70=""),"",IF(COUNTIF($D$11:D70,D70)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D70,$F$11:$F$102),G70)/H70,0)*H70))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J70" t="n">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K70" s="26" t="n">
-        <x:v>0.0036</x:v>
+        <x:v>0.0403</x:v>
       </x:c>
       <x:c r="L70" s="27" t="n">
         <x:f>IF(K70="","",ROUND(F70*K70,4))</x:f>
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="M70" s="27" t="str">
+        <x:v>0.0806</x:v>
+      </x:c>
+      <x:c r="M70" s="27" t="n">
         <x:f>IF(OR(K70="",I70="",N70=""),"",IF(N70&gt;=I70,ROUND(I70*K70,4),""))</x:f>
+        <x:v>0.403</x:v>
       </x:c>
       <x:c r="N70" t="n">
-        <x:v>7813400</x:v>
+        <x:v>1363910</x:v>
       </x:c>
       <x:c r="O70" t="str">
         <x:v>Listing snapshot</x:v>
@@ -4158,97 +3920,78 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R70" t="str">
-        <x:v>Existing selected resistor; separated from R141 after divider value change.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B105KBFNNNE. See reports/passive-repackage-2026-10-06.md. CL21B105KBFNNNE; effective capacitance at bias not proven. Headphone_Aux sheet, 2026-10-06. Added C230, C231, C232, C233, C234, C235, C239, C240, C241, C245. Amplifiers sheet, 2026-10-06. Added C270, C282, C283, C284, C295, C296, C297.</x:v>
       </x:c>
       <x:c r="S70" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C28323.html</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="36" customHeight="1">
       <x:c r="A71" s="25" t="str">
-        <x:v>U19</x:v>
+        <x:v>C271, C272, C273, C274, C277, C279, C290, C292</x:v>
       </x:c>
       <x:c r="B71" s="25" t="str">
-        <x:v>USB auxiliary 5V / PD controller VDD LDO</x:v>
+        <x:v>22uF 25V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C71" s="25" t="str">
-        <x:v>Texas Instruments</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D71" s="25" t="str">
-        <x:v>TPS7B8450QWDRBRQ1</x:v>
-      </x:c>
-      <x:c r="E71" s="25" t="str">
-        <x:v>C3751394</x:v>
-      </x:c>
+        <x:v>CL21A226MAQNNNE</x:v>
+      </x:c>
+      <x:c r="E71" s="25"/>
       <x:c r="F71" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I71" t="n">
-        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D71,$F$11:$F$114),G71)/H71,0)*H71))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K71" s="26" t="n">
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="L71" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71" t="str">
+        <x:f>IF(OR(D71="",G71="",H71=""),"",IF(COUNTIF($D$11:D71,D71)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D71,$F$11:$F$102),G71)/H71,0)*H71))</x:f>
+      </x:c>
+      <x:c r="J71"/>
+      <x:c r="K71" s="26"/>
+      <x:c r="L71" s="27" t="str">
         <x:f>IF(K71="","",ROUND(F71*K71,4))</x:f>
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="M71" s="27" t="n">
+      </x:c>
+      <x:c r="M71" s="27" t="str">
         <x:f>IF(OR(K71="",I71="",N71=""),"",IF(N71&gt;=I71,ROUND(I71*K71,4),""))</x:f>
-        <x:v>1.3452</x:v>
-      </x:c>
-      <x:c r="N71" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N71"/>
       <x:c r="O71" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P71" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q71" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R71" t="str">
-        <x:v>LCSC snapshot 2026-10-05: 1 pc in stock; $1.3452 at 1+, MOQ/multiple 1 (standard pack 3000; LCSC allows single-piece purchase). Stock is thin and may sell before ordering. TI TPS7B84-Q1: fixed 5V, 150mA, 40V input; startup/surge/dropout and thermal qualification open. Datasheet: ../datasheets/TPS7B84-Q1.pdf.</x:v>
-      </x:c>
-      <x:c r="S71" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3751394.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_1210 using CL32B226KAJNNNE. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S71"/>
     </x:row>
     <x:row r="72" ht="36" customHeight="1">
       <x:c r="A72" s="25" t="str">
-        <x:v>U20</x:v>
+        <x:v>C161, C186, C187, C194, C195, C236, C280, C293</x:v>
       </x:c>
       <x:c r="B72" s="25" t="str">
-        <x:v>USB and system logic priority mux</x:v>
+        <x:v>4.7uF 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C72" s="25" t="str">
-        <x:v>Texas Instruments</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D72" s="25" t="str">
-        <x:v>TPS2116DRLR</x:v>
-      </x:c>
-      <x:c r="E72" s="25" t="str">
-        <x:v>C3235557</x:v>
-      </x:c>
+        <x:v>CL21A475KAQNNNE</x:v>
+      </x:c>
+      <x:c r="E72" s="25"/>
       <x:c r="F72" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" t="str">
-        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D72,$F$11:$F$114),G72)/H72,0)*H72))</x:f>
+        <x:f>IF(OR(D72="",G72="",H72=""),"",IF(COUNTIF($D$11:D72,D72)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D72,$F$11:$F$102),G72)/H72,0)*H72))</x:f>
       </x:c>
       <x:c r="J72"/>
       <x:c r="K72" s="26"/>
@@ -4260,35 +4003,37 @@
       </x:c>
       <x:c r="N72"/>
       <x:c r="O72" t="str">
-        <x:v>Stock/price unverified</x:v>
-      </x:c>
-      <x:c r="P72" s="16"/>
-      <x:c r="Q72"/>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
+      </x:c>
+      <x:c r="P72" s="16" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="Q72" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
       <x:c r="R72" t="str">
-        <x:v>Selected MPN/LCSC mapping; current stock and price not verified.</x:v>
-      </x:c>
-      <x:c r="S72" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3235557.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603/C_1206 using CL10A475KO8NNNC, CL31B475KBHNNNE. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S72"/>
     </x:row>
     <x:row r="73" ht="36" customHeight="1">
       <x:c r="A73" s="25" t="str">
-        <x:v>R124</x:v>
+        <x:v>C122, C123, C124, C125, C164, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245, C282, C283, C284, C295, C296, C297</x:v>
       </x:c>
       <x:c r="B73" s="25" t="str">
-        <x:v>180k 1% USB-priority threshold divider resistor</x:v>
+        <x:v>1uF / 1uF X7R 10V 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C73" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D73" s="25" t="str">
-        <x:v>RC0603FR-07180KL</x:v>
+        <x:v>CL05A105KO5NNNC</x:v>
       </x:c>
       <x:c r="E73" s="25" t="str">
-        <x:v>C123419</x:v>
+        <x:v>C29266</x:v>
       </x:c>
       <x:c r="F73" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G73" t="n">
         <x:v>100</x:v>
@@ -4297,270 +4042,214 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D73,$F$11:$F$114),G73)/H73,0)*H73))</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(OR(D73="",G73="",H73=""),"",IF(COUNTIF($D$11:D73,D73)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D73,$F$11:$F$102),G73)/H73,0)*H73))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J73" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K73" s="26" t="n">
-        <x:v>0.0012</x:v>
+        <x:v>0.0023</x:v>
       </x:c>
       <x:c r="L73" s="27" t="n">
         <x:f>IF(K73="","",ROUND(F73*K73,4))</x:f>
-        <x:v>0.0012</x:v>
-      </x:c>
-      <x:c r="M73" s="27" t="str">
+        <x:v>0.0782</x:v>
+      </x:c>
+      <x:c r="M73" s="27" t="n">
         <x:f>IF(OR(K73="",I73="",N73=""),"",IF(N73&gt;=I73,ROUND(I73*K73,4),""))</x:f>
-      </x:c>
-      <x:c r="N73"/>
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="N73" t="n">
+        <x:v>4764100</x:v>
+      </x:c>
       <x:c r="O73" t="str">
-        <x:v>Stock unverified; price snapshot</x:v>
+        <x:v>LCSC search 2026-10-06 (price is the quoted tier, stock as listed); re-verify at order</x:v>
       </x:c>
       <x:c r="P73" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q73" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R73" t="str">
-        <x:v>Observed listing tier: $0.0012 at MOQ100. Product page may be stale; stock is unverified.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805/C_0603 using CL21B105KBFNNNE, LMK107B7105KA-T, CL10A105KB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S73" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C123419.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C29266.html</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="36" customHeight="1">
       <x:c r="A74" s="25" t="str">
-        <x:v>R125</x:v>
+        <x:v>C285, C286, C287, C288, C298, C299, C300, C301</x:v>
       </x:c>
       <x:c r="B74" s="25" t="str">
-        <x:v>100k PR1 divider resistor</x:v>
+        <x:v>0.47uF 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C74" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D74" s="25" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
-      </x:c>
-      <x:c r="E74" s="25" t="str">
-        <x:v>C14675</x:v>
-      </x:c>
+        <x:v>CL05B474KO5NNNC</x:v>
+      </x:c>
+      <x:c r="E74" s="25"/>
       <x:c r="F74" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G74" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H74" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I74" t="n">
-        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D74,$F$11:$F$114),G74)/H74,0)*H74))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J74" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K74" s="26" t="n">
-        <x:v>0.0036</x:v>
-      </x:c>
-      <x:c r="L74" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74" t="str">
+        <x:f>IF(OR(D74="",G74="",H74=""),"",IF(COUNTIF($D$11:D74,D74)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D74,$F$11:$F$102),G74)/H74,0)*H74))</x:f>
+      </x:c>
+      <x:c r="J74"/>
+      <x:c r="K74" s="26"/>
+      <x:c r="L74" s="27" t="str">
         <x:f>IF(K74="","",ROUND(F74*K74,4))</x:f>
-        <x:v>0.0036</x:v>
       </x:c>
       <x:c r="M74" s="27" t="str">
         <x:f>IF(OR(K74="",I74="",N74=""),"",IF(N74&gt;=I74,ROUND(I74*K74,4),""))</x:f>
       </x:c>
-      <x:c r="N74" t="n">
-        <x:v>7813400</x:v>
-      </x:c>
+      <x:c r="N74"/>
       <x:c r="O74" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P74" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q74" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R74" t="str">
-        <x:v>Reuse same selected MPN/LCSC mapping as existing 100k BOM rows; no additional MOQ order.</x:v>
-      </x:c>
-      <x:c r="S74" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10B474KA8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S74"/>
     </x:row>
     <x:row r="75" ht="36" customHeight="1">
       <x:c r="A75" s="25" t="str">
-        <x:v>U21</x:v>
+        <x:v>C302, C303, C304, C305, C306, C307</x:v>
       </x:c>
       <x:c r="B75" s="25" t="str">
-        <x:v>Gauge undervoltage supervisor</x:v>
+        <x:v>0.68uF 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C75" s="25" t="str">
-        <x:v>Texas Instruments</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D75" s="25" t="str">
-        <x:v>TPS3839G33DBZR</x:v>
+        <x:v>CL21B684KBFVPNE</x:v>
       </x:c>
       <x:c r="E75" s="25" t="str">
-        <x:v>C485802</x:v>
+        <x:v>C472832</x:v>
       </x:c>
       <x:c r="F75" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G75" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H75" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I75" t="n">
-        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D75,$F$11:$F$114),G75)/H75,0)*H75))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J75" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K75" s="26" t="n">
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="L75" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75" t="str">
+        <x:f>IF(OR(D75="",G75="",H75=""),"",IF(COUNTIF($D$11:D75,D75)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D75,$F$11:$F$102),G75)/H75,0)*H75))</x:f>
+      </x:c>
+      <x:c r="J75"/>
+      <x:c r="K75" s="26"/>
+      <x:c r="L75" s="27" t="str">
         <x:f>IF(K75="","",ROUND(F75*K75,4))</x:f>
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="M75" s="27" t="n">
+      </x:c>
+      <x:c r="M75" s="27" t="str">
         <x:f>IF(OR(K75="",I75="",N75=""),"",IF(N75&gt;=I75,ROUND(I75*K75,4),""))</x:f>
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="N75" t="n">
-        <x:v>3444</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N75"/>
       <x:c r="O75" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
       </x:c>
       <x:c r="P75" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q75" t="str">
-        <x:v>2026-10-05</x:v>
-      </x:c>
-      <x:c r="R75"/>
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="R75" t="str">
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B684KBFVPNE. See reports/passive-repackage-2026-10-06.md. Amplifiers sheet, 2026-10-06. Variant suffix per the LCSC listing; confirm voltage/dielectric on the datasheet.</x:v>
+      </x:c>
       <x:c r="S75" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C485802.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C472832.html</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
       <x:c r="A76" s="25" t="str">
-        <x:v>R126, R127, R174, R241</x:v>
+        <x:v>FB200</x:v>
       </x:c>
       <x:c r="B76" s="25" t="str">
-        <x:v>Gauge signal-switch and supervisor gate pull-up/pull-down resistors</x:v>
+        <x:v>BLM18AG601SN1D 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C76" s="25" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Murata</x:v>
       </x:c>
       <x:c r="D76" s="25" t="str">
-        <x:v>RC0603FR-071ML</x:v>
-      </x:c>
-      <x:c r="E76" s="25" t="str">
-        <x:v>C105578</x:v>
-      </x:c>
+        <x:v>BLM15AG601SN1D</x:v>
+      </x:c>
+      <x:c r="E76" s="25"/>
       <x:c r="F76" s="25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G76" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H76" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I76" t="n">
-        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D76,$F$11:$F$114),G76)/H76,0)*H76))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J76" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K76" s="26" t="n">
-        <x:v>0.0056</x:v>
-      </x:c>
-      <x:c r="L76" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
+      <x:c r="I76" t="str">
+        <x:f>IF(OR(D76="",G76="",H76=""),"",IF(COUNTIF($D$11:D76,D76)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D76,$F$11:$F$102),G76)/H76,0)*H76))</x:f>
+      </x:c>
+      <x:c r="J76"/>
+      <x:c r="K76" s="26"/>
+      <x:c r="L76" s="27" t="str">
         <x:f>IF(K76="","",ROUND(F76*K76,4))</x:f>
-        <x:v>0.0224</x:v>
-      </x:c>
-      <x:c r="M76" s="27" t="n">
+      </x:c>
+      <x:c r="M76" s="27" t="str">
         <x:f>IF(OR(K76="",I76="",N76=""),"",IF(N76&gt;=I76,ROUND(I76*K76,4),""))</x:f>
-        <x:v>0.56</x:v>
-      </x:c>
-      <x:c r="N76" t="n">
-        <x:v>359600</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N76"/>
       <x:c r="O76" t="str">
-        <x:v>Listing snapshot</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P76" s="16" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="Q76" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R76" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. Added R241.</x:v>
-      </x:c>
-      <x:c r="S76" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105578.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using BLM18AG601SN1D. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S76"/>
     </x:row>
     <x:row r="77" ht="36" customHeight="1">
       <x:c r="A77" s="25" t="str">
-        <x:v>C161, C280, C293</x:v>
+        <x:v>R10</x:v>
       </x:c>
       <x:c r="B77" s="25" t="str">
-        <x:v>MCU VDD/VDDA 4.7uF bulk (DS12992 fig. 13)</x:v>
+        <x:v>200k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C77" s="25" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D77" s="25" t="str">
-        <x:v>CL10A475KO8NNNC</x:v>
-      </x:c>
-      <x:c r="E77" s="25" t="str">
-        <x:v>C19666</x:v>
-      </x:c>
+        <x:v>RC0402FR-07200KL</x:v>
+      </x:c>
+      <x:c r="E77" s="25"/>
       <x:c r="F77" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G77" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H77" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I77" t="n">
-        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D77,$F$11:$F$114),G77)/H77,0)*H77))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J77" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K77" s="26" t="n">
-        <x:v>0.0298</x:v>
-      </x:c>
-      <x:c r="L77" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77" t="str">
+        <x:f>IF(OR(D77="",G77="",H77=""),"",IF(COUNTIF($D$11:D77,D77)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D77,$F$11:$F$102),G77)/H77,0)*H77))</x:f>
+      </x:c>
+      <x:c r="J77"/>
+      <x:c r="K77" s="26"/>
+      <x:c r="L77" s="27" t="str">
         <x:f>IF(K77="","",ROUND(F77*K77,4))</x:f>
-        <x:v>0.0894</x:v>
-      </x:c>
-      <x:c r="M77" s="27" t="n">
+      </x:c>
+      <x:c r="M77" s="27" t="str">
         <x:f>IF(OR(K77="",I77="",N77=""),"",IF(N77&gt;=I77,ROUND(I77*K77,4),""))</x:f>
-        <x:v>0.298</x:v>
-      </x:c>
-      <x:c r="N77" t="n">
-        <x:v>138390</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N77"/>
       <x:c r="O77" t="str">
-        <x:v>Listing snapshot, 2026-10-06</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P77" s="16" t="n">
         <x:v>46300</x:v>
@@ -4569,44 +4258,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R77" t="str">
-        <x:v>LCSC listing 4.7uF/16V X5R 0603; DC-bias derating at 3.0 V not checked. Amplifiers sheet, 2026-10-06. Added C280, C293.</x:v>
-      </x:c>
-      <x:c r="S77" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C19666.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07200KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S77"/>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="21" t="str">
-        <x:v>J6</x:v>
+        <x:v>R100</x:v>
       </x:c>
       <x:c r="B78" s="21" t="str">
-        <x:v>MCU SWD header 1x4 2.54 mm (J7 Tag-Connect TC2030 is PCB pads only, no BOM part)</x:v>
+        <x:v>5.23k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C78" s="21" t="str">
-        <x:v>Ckmtw</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D78" s="21" t="str">
-        <x:v>B-2100S04P-A110</x:v>
-      </x:c>
-      <x:c r="E78" s="21" t="str">
-        <x:v>C124378</x:v>
-      </x:c>
+        <x:v>RC0402FR-075K23L</x:v>
+      </x:c>
+      <x:c r="E78" s="21"/>
       <x:c r="F78" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G78" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H78" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I78" t="n">
-        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D78,$F$11:$F$114),G78)/H78,0)*H78))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J78" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78" t="str">
+        <x:f>IF(OR(D78="",G78="",H78=""),"",IF(COUNTIF($D$11:D78,D78)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D78,$F$11:$F$102),G78)/H78,0)*H78))</x:f>
+      </x:c>
+      <x:c r="J78"/>
       <x:c r="K78" s="26"/>
       <x:c r="L78" s="27" t="str">
         <x:f>IF(K78="","",ROUND(F78*K78,4))</x:f>
@@ -4616,7 +4294,7 @@
       </x:c>
       <x:c r="N78"/>
       <x:c r="O78" t="str">
-        <x:v>LCSC number from search; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P78" s="16" t="n">
         <x:v>46300</x:v>
@@ -4625,60 +4303,43 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R78" t="str">
-        <x:v>1x4 straight THT header; footprint PinHeader_1x04_P2.54mm_Vertical (stock KiCad STEP). Pin order 1 SWDIO 2 SWCLK 3 NRST 4 GND. Programmer cable TC2030-IDC (legged footprint J7) is a tool, not fitted.</x:v>
-      </x:c>
-      <x:c r="S78" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C124378.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using 1RC0603F5231. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S78"/>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="21" t="str">
-        <x:v>Y170</x:v>
+        <x:v>R101</x:v>
       </x:c>
       <x:c r="B79" s="21" t="str">
-        <x:v>12 MHz crystal for PCM2902C (3225-4P, CL 20 pF, +/-10 ppm)</x:v>
+        <x:v>30.1k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C79" s="21" t="str">
-        <x:v>YXC</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D79" s="21" t="str">
-        <x:v>X322512MSB4SI</x:v>
-      </x:c>
-      <x:c r="E79" s="21" t="str">
-        <x:v>C9002</x:v>
-      </x:c>
+        <x:v>RC0402FR-0730K1L</x:v>
+      </x:c>
+      <x:c r="E79" s="21"/>
       <x:c r="F79" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G79" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H79" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I79" t="n">
-        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D79,$F$11:$F$114),G79)/H79,0)*H79))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J79" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K79" s="26" t="n">
-        <x:v>0.0371</x:v>
-      </x:c>
-      <x:c r="L79" s="27" t="n">
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79" t="str">
+        <x:f>IF(OR(D79="",G79="",H79=""),"",IF(COUNTIF($D$11:D79,D79)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D79,$F$11:$F$102),G79)/H79,0)*H79))</x:f>
+      </x:c>
+      <x:c r="J79"/>
+      <x:c r="K79" s="26"/>
+      <x:c r="L79" s="27" t="str">
         <x:f>IF(K79="","",ROUND(F79*K79,4))</x:f>
-        <x:v>0.0371</x:v>
-      </x:c>
-      <x:c r="M79" s="27" t="n">
+      </x:c>
+      <x:c r="M79" s="27" t="str">
         <x:f>IF(OR(K79="",I79="",N79=""),"",IF(N79&gt;=I79,ROUND(I79*K79,4),""))</x:f>
-        <x:v>0.371</x:v>
-      </x:c>
-      <x:c r="N79" t="n">
-        <x:v>312110</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N79"/>
       <x:c r="O79" t="str">
-        <x:v>Listing snapshot, 2026-10-06</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P79" s="16" t="n">
         <x:v>46300</x:v>
@@ -4687,44 +4348,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R79" t="str">
-        <x:v>Search-result snapshot; datasheet not retrieved. Pads 1/3 crystal, 2/4 GND assumed (generic 3225-4P) - verify. 33 pF load caps (C177/C178) give ~19.5 pF effective CL incl. stray, vs 20 pF rating.</x:v>
-      </x:c>
-      <x:c r="S79" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C9002.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using 1RC0603F3012. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S79"/>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="21" t="str">
-        <x:v>C177, C178</x:v>
+        <x:v>R102, R120, R121</x:v>
       </x:c>
       <x:c r="B80" s="21" t="str">
-        <x:v>Crystal load capacitors 33 pF C0G 0603</x:v>
+        <x:v>4.7k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C80" s="21" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D80" s="21" t="str">
-        <x:v>CL10C330JB8NNNC</x:v>
-      </x:c>
-      <x:c r="E80" s="21" t="str">
-        <x:v>C1663</x:v>
-      </x:c>
+        <x:v>RC0402FR-074K7L</x:v>
+      </x:c>
+      <x:c r="E80" s="21"/>
       <x:c r="F80" s="21" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G80" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H80" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I80" t="n">
-        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D80,$F$11:$F$114),G80)/H80,0)*H80))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J80" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80" t="str">
+        <x:f>IF(OR(D80="",G80="",H80=""),"",IF(COUNTIF($D$11:D80,D80)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D80,$F$11:$F$102),G80)/H80,0)*H80))</x:f>
+      </x:c>
+      <x:c r="J80"/>
       <x:c r="K80" s="26"/>
       <x:c r="L80" s="27" t="str">
         <x:f>IF(K80="","",ROUND(F80*K80,4))</x:f>
@@ -4734,7 +4384,7 @@
       </x:c>
       <x:c r="N80"/>
       <x:c r="O80" t="str">
-        <x:v>Search snapshot: from ~0.0026 USD, ~517,700 in stock (unverified)</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P80" s="16" t="n">
         <x:v>46300</x:v>
@@ -4743,44 +4393,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R80" t="str">
-        <x:v>33 pF + ~3 pF stray each side gives ~19.5 pF effective vs 20 pF crystal rating (DS: 10-33 pF).</x:v>
-      </x:c>
-      <x:c r="S80" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1663.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-074K7L. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S80"/>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
       <x:c r="A81" t="str">
-        <x:v>R170</x:v>
+        <x:v>R108, R124</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>PCM2902C VBUS filter 2.2 ohm 1% 0603</x:v>
+        <x:v>180k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D81" t="str">
-        <x:v>RC0603FR-072R2L</x:v>
-      </x:c>
-      <x:c r="E81" t="str">
-        <x:v>C112307</x:v>
-      </x:c>
+        <x:v>RC0402FR-07180KL</x:v>
+      </x:c>
+      <x:c r="E81"/>
       <x:c r="F81" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H81" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I81" t="n">
-        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D81,$F$11:$F$114),G81)/H81,0)*H81))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J81" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81" t="str">
+        <x:f>IF(OR(D81="",G81="",H81=""),"",IF(COUNTIF($D$11:D81,D81)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D81,$F$11:$F$102),G81)/H81,0)*H81))</x:f>
+      </x:c>
+      <x:c r="J81"/>
       <x:c r="K81"/>
       <x:c r="L81" t="str">
         <x:f>IF(K81="","",ROUND(F81*K81,4))</x:f>
@@ -4790,7 +4429,7 @@
       </x:c>
       <x:c r="N81"/>
       <x:c r="O81" t="str">
-        <x:v>LCSC number from JLCPCB/LCSC listing; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P81" t="n">
         <x:v>46300</x:v>
@@ -4799,44 +4438,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R81" t="str">
-        <x:v>Yageo RC0603FR-072R2L, 2.2 ohm 1% 0603.</x:v>
-      </x:c>
-      <x:c r="S81" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C112307.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07180KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S81"/>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" t="str">
-        <x:v>R171, R172</x:v>
+        <x:v>R112, R200, R201, R202, R203, R204, R205</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>USB D+/D- 22 ohm series resistors 0603</x:v>
+        <x:v>100 / 100R 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D82" t="str">
-        <x:v>RC0603FR-0722RL</x:v>
-      </x:c>
-      <x:c r="E82" t="str">
-        <x:v>C107701</x:v>
-      </x:c>
+        <x:v>RC0402FR-07100RL</x:v>
+      </x:c>
+      <x:c r="E82"/>
       <x:c r="F82" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G82" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H82" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I82" t="n">
-        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D82,$F$11:$F$114),G82)/H82,0)*H82))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J82" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
+      <x:c r="I82" t="str">
+        <x:f>IF(OR(D82="",G82="",H82=""),"",IF(COUNTIF($D$11:D82,D82)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D82,$F$11:$F$102),G82)/H82,0)*H82))</x:f>
+      </x:c>
+      <x:c r="J82"/>
       <x:c r="K82"/>
       <x:c r="L82" t="str">
         <x:f>IF(K82="","",ROUND(F82*K82,4))</x:f>
@@ -4846,7 +4474,7 @@
       </x:c>
       <x:c r="N82"/>
       <x:c r="O82" t="str">
-        <x:v>Search snapshot: from ~0.0018 USD, ~216,200 in stock (unverified)</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P82" t="n">
         <x:v>46300</x:v>
@@ -4855,60 +4483,43 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R82" t="str">
-        <x:v>Yageo RC0603FR-0722RL, 22 ohm 1% 0603.</x:v>
-      </x:c>
-      <x:c r="S82" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C107701.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07100RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S82"/>
     </x:row>
     <x:row r="83" ht="48" customHeight="1">
       <x:c r="A83" t="str">
-        <x:v>R173</x:v>
+        <x:v>R122, R232, R233</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>D+ pull-up 1.5 kohm 1% 0603 (to VDDI)</x:v>
+        <x:v>47k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D83" t="str">
-        <x:v>RC0603FR-071K5L</x:v>
-      </x:c>
-      <x:c r="E83" t="str">
-        <x:v>C114668</x:v>
-      </x:c>
+        <x:v>RC0402FR-0747KL</x:v>
+      </x:c>
+      <x:c r="E83"/>
       <x:c r="F83" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G83" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H83" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I83" t="n">
-        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D83,$F$11:$F$114),G83)/H83,0)*H83))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J83" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K83" t="n">
-        <x:v>0.0009</x:v>
-      </x:c>
-      <x:c r="L83" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G83"/>
+      <x:c r="H83"/>
+      <x:c r="I83" t="str">
+        <x:f>IF(OR(D83="",G83="",H83=""),"",IF(COUNTIF($D$11:D83,D83)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D83,$F$11:$F$102),G83)/H83,0)*H83))</x:f>
+      </x:c>
+      <x:c r="J83"/>
+      <x:c r="K83"/>
+      <x:c r="L83" t="str">
         <x:f>IF(K83="","",ROUND(F83*K83,4))</x:f>
-        <x:v>0.0009</x:v>
-      </x:c>
-      <x:c r="M83" t="n">
+      </x:c>
+      <x:c r="M83" t="str">
         <x:f>IF(OR(K83="",I83="",N83=""),"",IF(N83&gt;=I83,ROUND(I83*K83,4),""))</x:f>
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="N83" t="n">
-        <x:v>507200</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N83"/>
       <x:c r="O83" t="str">
-        <x:v>Listing snapshot, 2026-10-06</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P83" t="n">
         <x:v>46300</x:v>
@@ -4917,60 +4528,43 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R83" t="str">
-        <x:v>Search-result price/stock.</x:v>
-      </x:c>
-      <x:c r="S83" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114668.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0747KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S83"/>
     </x:row>
     <x:row r="84" ht="48" customHeight="1">
       <x:c r="A84" t="str">
-        <x:v>R185, R186, R187, R226, R227, R228, R229, R230, R231, R240, R257, R258, R261</x:v>
+        <x:v>R126, R127, R174, R241</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>BM83 RST_N series (R185) and UART_TXD / P0_0 TX_IND series (R186, R187) 1 kohm 1% 0603</x:v>
+        <x:v>1M 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D84" t="str">
-        <x:v>RC0603FR-071KL</x:v>
-      </x:c>
-      <x:c r="E84" t="str">
-        <x:v>C22548</x:v>
-      </x:c>
+        <x:v>RC0402FR-071ML</x:v>
+      </x:c>
+      <x:c r="E84"/>
       <x:c r="F84" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I84" t="n">
-        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D84,$F$11:$F$114),G84)/H84,0)*H84))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J84" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K84" t="n">
-        <x:v>0.0011</x:v>
-      </x:c>
-      <x:c r="L84" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84" t="str">
+        <x:f>IF(OR(D84="",G84="",H84=""),"",IF(COUNTIF($D$11:D84,D84)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D84,$F$11:$F$102),G84)/H84,0)*H84))</x:f>
+      </x:c>
+      <x:c r="J84"/>
+      <x:c r="K84"/>
+      <x:c r="L84" t="str">
         <x:f>IF(K84="","",ROUND(F84*K84,4))</x:f>
-        <x:v>0.0143</x:v>
-      </x:c>
-      <x:c r="M84" t="n">
+      </x:c>
+      <x:c r="M84" t="str">
         <x:f>IF(OR(K84="",I84="",N84=""),"",IF(N84&gt;=I84,ROUND(I84*K84,4),""))</x:f>
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="N84" t="n">
-        <x:v>9947200</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="N84"/>
       <x:c r="O84" t="str">
-        <x:v>Search-result price/stock, 2026-10-06</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P84" t="n">
         <x:v>46300</x:v>
@@ -4979,44 +4573,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R84" t="str">
-        <x:v>Bluetooth sheet; LCSC number from search result, price/stock not re-verified. Headphone_Aux sheet, 2026-10-06. Added R226, R227, R228, R229, R230, R231, R240. Amplifiers sheet, 2026-10-06. Added R257, R258, R261.</x:v>
-      </x:c>
-      <x:c r="S84" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C22548.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-071ML. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S84"/>
     </x:row>
     <x:row r="85" ht="48" customHeight="1">
       <x:c r="A85" t="str">
-        <x:v>J8</x:v>
+        <x:v>R140</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>BM83 test/programming header 1x5 2.54 mm (RST_N, P3_4, UART RX/TX, GND)</x:v>
+        <x:v>78.7k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>XYECONN</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>XY-MTP254-1X5</x:v>
-      </x:c>
-      <x:c r="E85" t="str">
-        <x:v>C54110162</x:v>
-      </x:c>
+        <x:v>RC0402FR-0778K7L</x:v>
+      </x:c>
+      <x:c r="E85"/>
       <x:c r="F85" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G85" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H85" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I85" t="n">
-        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D85,$F$11:$F$114),G85)/H85,0)*H85))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J85" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="G85"/>
+      <x:c r="H85"/>
+      <x:c r="I85" t="str">
+        <x:f>IF(OR(D85="",G85="",H85=""),"",IF(COUNTIF($D$11:D85,D85)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D85,$F$11:$F$102),G85)/H85,0)*H85))</x:f>
+      </x:c>
+      <x:c r="J85"/>
       <x:c r="K85"/>
       <x:c r="L85" t="str">
         <x:f>IF(K85="","",ROUND(F85*K85,4))</x:f>
@@ -5026,7 +4609,7 @@
       </x:c>
       <x:c r="N85"/>
       <x:c r="O85" t="str">
-        <x:v>Stock/price unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P85" t="n">
         <x:v>46300</x:v>
@@ -5035,44 +4618,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R85" t="str">
-        <x:v>Bluetooth sheet; part number carried from the earlier 1x5 SWD header selection, not re-verified.</x:v>
-      </x:c>
-      <x:c r="S85" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54110162.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using 1RC0603F7872. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S85"/>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86" t="str">
-        <x:v>C164</x:v>
+        <x:v>R141</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>MCU VREF+ 1uF (DS12232 fig. 13)</x:v>
+        <x:v>9.1k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>CL10A105KB8NNNC</x:v>
-      </x:c>
-      <x:c r="E86" t="str">
-        <x:v>C15849</x:v>
-      </x:c>
+        <x:v>RC0402FR-079K1L</x:v>
+      </x:c>
+      <x:c r="E86"/>
       <x:c r="F86" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G86" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H86" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I86" t="n">
-        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D86,$F$11:$F$114),G86)/H86,0)*H86))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J86" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="G86"/>
+      <x:c r="H86"/>
+      <x:c r="I86" t="str">
+        <x:f>IF(OR(D86="",G86="",H86=""),"",IF(COUNTIF($D$11:D86,D86)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D86,$F$11:$F$102),G86)/H86,0)*H86))</x:f>
+      </x:c>
+      <x:c r="J86"/>
       <x:c r="K86"/>
       <x:c r="L86" t="str">
         <x:f>IF(K86="","",ROUND(F86*K86,4))</x:f>
@@ -5082,7 +4654,7 @@
       </x:c>
       <x:c r="N86"/>
       <x:c r="O86" t="str">
-        <x:v>Stock/price unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P86" t="n">
         <x:v>46300</x:v>
@@ -5091,44 +4663,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R86" t="str">
-        <x:v>LCSC code from memory of the Samsung 1uF 0603 family; verify code, voltage rating and DC-bias at order.</x:v>
-      </x:c>
-      <x:c r="S86" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C15849.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-079K1L. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S86"/>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" t="str">
-        <x:v>U24</x:v>
+        <x:v>R150</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>Audio ADC 4:1 input, I2S master (TSSOP-30)</x:v>
+        <x:v>604k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>TI</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D87" t="str">
-        <x:v>PCM1862DBTR</x:v>
-      </x:c>
-      <x:c r="E87" t="str">
-        <x:v>C544647</x:v>
-      </x:c>
+        <x:v>RC0402FR-07604KL</x:v>
+      </x:c>
+      <x:c r="E87"/>
       <x:c r="F87" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G87" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H87" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I87" t="n">
-        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D87,$F$11:$F$114),G87)/H87,0)*H87))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J87" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
+      <x:c r="I87" t="str">
+        <x:f>IF(OR(D87="",G87="",H87=""),"",IF(COUNTIF($D$11:D87,D87)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D87,$F$11:$F$102),G87)/H87,0)*H87))</x:f>
+      </x:c>
+      <x:c r="J87"/>
       <x:c r="K87"/>
       <x:c r="L87" t="str">
         <x:f>IF(K87="","",ROUND(F87*K87,4))</x:f>
@@ -5138,7 +4699,7 @@
       </x:c>
       <x:c r="N87"/>
       <x:c r="O87" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P87" t="n">
         <x:v>46300</x:v>
@@ -5147,44 +4708,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R87" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet SLAS831D.</x:v>
-      </x:c>
-      <x:c r="S87" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C544647.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using FRC0603F6043TS. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>U22</x:v>
+        <x:v>R151</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>3V3_AUDIO 300 mA ultra-low-noise LDO</x:v>
+        <x:v>91k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>TI</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>TPS7A2033PDBVR</x:v>
-      </x:c>
-      <x:c r="E88" t="str">
-        <x:v>C2862740</x:v>
-      </x:c>
+        <x:v>RC0402FR-0791KL</x:v>
+      </x:c>
+      <x:c r="E88"/>
       <x:c r="F88" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G88" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H88" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I88" t="n">
-        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D88,$F$11:$F$114),G88)/H88,0)*H88))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J88" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G88"/>
+      <x:c r="H88"/>
+      <x:c r="I88" t="str">
+        <x:f>IF(OR(D88="",G88="",H88=""),"",IF(COUNTIF($D$11:D88,D88)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D88,$F$11:$F$102),G88)/H88,0)*H88))</x:f>
+      </x:c>
+      <x:c r="J88"/>
       <x:c r="K88"/>
       <x:c r="L88" t="str">
         <x:f>IF(K88="","",ROUND(F88*K88,4))</x:f>
@@ -5194,7 +4744,7 @@
       </x:c>
       <x:c r="N88"/>
       <x:c r="O88" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P88" t="n">
         <x:v>46300</x:v>
@@ -5203,44 +4753,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R88" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. A TECH PUBLIC TPS7A2033PDBVR-TP clone is listed as C49452001; TI part chosen.</x:v>
-      </x:c>
-      <x:c r="S88" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2862740.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using AC0603FR-0791KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>U23</x:v>
+        <x:v>R170</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>5V_CODEC load switch (SOT-23-6)</x:v>
+        <x:v>2.2 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>TI</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D89" t="str">
-        <x:v>TPS22917DBVR</x:v>
-      </x:c>
-      <x:c r="E89" t="str">
-        <x:v>C2681320</x:v>
-      </x:c>
+        <x:v>RC0402FR-072R2L</x:v>
+      </x:c>
+      <x:c r="E89"/>
       <x:c r="F89" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G89" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H89" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I89" t="n">
-        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D89,$F$11:$F$114),G89)/H89,0)*H89))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J89" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89" t="str">
+        <x:f>IF(OR(D89="",G89="",H89=""),"",IF(COUNTIF($D$11:D89,D89)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D89,$F$11:$F$102),G89)/H89,0)*H89))</x:f>
+      </x:c>
+      <x:c r="J89"/>
       <x:c r="K89"/>
       <x:c r="L89" t="str">
         <x:f>IF(K89="","",ROUND(F89*K89,4))</x:f>
@@ -5250,7 +4789,7 @@
       </x:c>
       <x:c r="N89"/>
       <x:c r="O89" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P89" t="n">
         <x:v>46300</x:v>
@@ -5259,44 +4798,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R89" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Pinout checked against SLVSDW8B.</x:v>
-      </x:c>
-      <x:c r="S89" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2681320.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-072R2L. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>Y200</x:v>
+        <x:v>R171, R172</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>24.576 MHz crystal for PCM1862 (3225-4P, CL 15 pF)</x:v>
+        <x:v>22 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>Lucki</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D90" t="str">
-        <x:v>L327S240P11L</x:v>
-      </x:c>
-      <x:c r="E90" t="str">
-        <x:v>C5261154</x:v>
-      </x:c>
+        <x:v>RC0402FR-0722RL</x:v>
+      </x:c>
+      <x:c r="E90"/>
       <x:c r="F90" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G90" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H90" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I90" t="n">
-        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D90,$F$11:$F$114),G90)/H90,0)*H90))</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J90" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
+      <x:c r="I90" t="str">
+        <x:f>IF(OR(D90="",G90="",H90=""),"",IF(COUNTIF($D$11:D90,D90)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D90,$F$11:$F$102),G90)/H90,0)*H90))</x:f>
+      </x:c>
+      <x:c r="J90"/>
       <x:c r="K90"/>
       <x:c r="L90" t="str">
         <x:f>IF(K90="","",ROUND(F90*K90,4))</x:f>
@@ -5306,7 +4834,7 @@
       </x:c>
       <x:c r="N90"/>
       <x:c r="O90" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P90" t="n">
         <x:v>46300</x:v>
@@ -5315,44 +4843,35 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R90" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet not retrieved; pad usage 1/3 assumed. Two 20 pF caps give about 13 pF CL; trim at bring-up.</x:v>
-      </x:c>
-      <x:c r="S90" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5261154.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0722RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>FB200</x:v>
+        <x:v>R173</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>AVDD ferrite bead 600 ohm @100 MHz 0603</x:v>
+        <x:v>1.5k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>Murata</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D91" t="str">
-        <x:v>BLM18AG601SN1D</x:v>
+        <x:v>RC0402FR-071K5L</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>C19330</x:v>
+        <x:v>C114759</x:v>
       </x:c>
       <x:c r="F91" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G91" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H91" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I91" t="n">
-        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D91,$F$11:$F$114),G91)/H91,0)*H91))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J91" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
+      <x:c r="I91" t="str">
+        <x:f>IF(OR(D91="",G91="",H91=""),"",IF(COUNTIF($D$11:D91,D91)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D91,$F$11:$F$102),G91)/H91,0)*H91))</x:f>
+      </x:c>
+      <x:c r="J91"/>
       <x:c r="K91"/>
       <x:c r="L91" t="str">
         <x:f>IF(K91="","",ROUND(F91*K91,4))</x:f>
@@ -5362,7 +4881,7 @@
       </x:c>
       <x:c r="N91"/>
       <x:c r="O91" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC number from family knowledge; unverified; price/stock unverified</x:v>
       </x:c>
       <x:c r="P91" t="n">
         <x:v>46300</x:v>
@@ -5371,44 +4890,35 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R91" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. 0.5 A, 380 mOhm DCR (search snapshot).</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-071K5L. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S91" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C19330.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C114759.html</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>C200, C201, C202, C203, C204, C205, C243, C244, C265</x:v>
+        <x:v>R206, R207, R208</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>Input AC-coupling 2.2uF X7R 0805</x:v>
+        <x:v>33 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D92" t="str">
-        <x:v>CL21B225KAFNNNE</x:v>
-      </x:c>
-      <x:c r="E92" t="str">
-        <x:v>C19110</x:v>
-      </x:c>
+        <x:v>RC0402FR-0733RL</x:v>
+      </x:c>
+      <x:c r="E92"/>
       <x:c r="F92" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G92" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H92" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I92" t="n">
-        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D92,$F$11:$F$114),G92)/H92,0)*H92))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J92" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
+      <x:c r="I92" t="str">
+        <x:f>IF(OR(D92="",G92="",H92=""),"",IF(COUNTIF($D$11:D92,D92)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D92,$F$11:$F$102),G92)/H92,0)*H92))</x:f>
+      </x:c>
+      <x:c r="J92"/>
       <x:c r="K92"/>
       <x:c r="L92" t="str">
         <x:f>IF(K92="","",ROUND(F92*K92,4))</x:f>
@@ -5418,7 +4928,7 @@
       </x:c>
       <x:c r="N92"/>
       <x:c r="O92" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P92" t="n">
         <x:v>46300</x:v>
@@ -5427,42 +4937,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R92" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. Check voltage rating and DC-bias. Headphone_Aux sheet, 2026-10-06. Added C243, C244. Amplifiers sheet, 2026-10-06. Added C265.</x:v>
-      </x:c>
-      <x:c r="S92" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C19110.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0733RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>C206, C207, C208, C209, C210, C211</x:v>
+        <x:v>R209, R210</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>Input anti-alias 10nF C0G 0603</x:v>
+        <x:v>2.2k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>Murata</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D93" t="str">
-        <x:v>GRM1885C1H103JA01D</x:v>
-      </x:c>
-      <x:c r="E93" t="str"/>
+        <x:v>RC0402FR-072K2L</x:v>
+      </x:c>
+      <x:c r="E93"/>
       <x:c r="F93" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G93" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H93" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I93" t="n">
-        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D93,$F$11:$F$114),G93)/H93,0)*H93))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J93" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
+      <x:c r="I93" t="str">
+        <x:f>IF(OR(D93="",G93="",H93=""),"",IF(COUNTIF($D$11:D93,D93)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D93,$F$11:$F$102),G93)/H93,0)*H93))</x:f>
+      </x:c>
+      <x:c r="J93"/>
       <x:c r="K93"/>
       <x:c r="L93" t="str">
         <x:f>IF(K93="","",ROUND(F93*K93,4))</x:f>
@@ -5472,7 +4973,7 @@
       </x:c>
       <x:c r="N93"/>
       <x:c r="O93" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P93" t="n">
         <x:v>46300</x:v>
@@ -5481,42 +4982,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R93" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget. LCSC code still open after the Amplifiers lookup (search returned distributor listings only).</x:v>
-      </x:c>
-      <x:c r="S93" t="str"/>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-072K2L. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>C226, C227</x:v>
+        <x:v>R250</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>Crystal load capacitors 22 pF C0G 0603</x:v>
+        <x:v>499k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>CL10C220JB8NNNC</x:v>
-      </x:c>
-      <x:c r="E94" t="str">
-        <x:v>C1653</x:v>
-      </x:c>
+        <x:v>RC0402FR-07499KL</x:v>
+      </x:c>
+      <x:c r="E94"/>
       <x:c r="F94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G94" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H94" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I94" t="n">
-        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D94,$F$11:$F$114),G94)/H94,0)*H94))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J94" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94"/>
+      <x:c r="H94"/>
+      <x:c r="I94" t="str">
+        <x:f>IF(OR(D94="",G94="",H94=""),"",IF(COUNTIF($D$11:D94,D94)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D94,$F$11:$F$102),G94)/H94,0)*H94))</x:f>
+      </x:c>
+      <x:c r="J94"/>
       <x:c r="K94"/>
       <x:c r="L94" t="str">
         <x:f>IF(K94="","",ROUND(F94*K94,4))</x:f>
@@ -5526,7 +5018,7 @@
       </x:c>
       <x:c r="N94"/>
       <x:c r="O94" t="str">
-        <x:v>LCSC number from search 2026-10-06 (JLCPCB C1653 page); price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P94" t="n">
         <x:v>46300</x:v>
@@ -5535,59 +5027,43 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R94" t="str">
-        <x:v>Source_Select_ADC sheet. Changed from 20 pF 2026-10-06: 2 x 22 pF in series plus ~3 pF stray gives about 14 pF for the 15 pF crystal. Unverified: price/stock not checked.</x:v>
-      </x:c>
-      <x:c r="S94" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1653.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07499KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>R200, R201, R202, R203, R204, R205</x:v>
+        <x:v>R251</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>Input series 100 ohm 1% 0603</x:v>
+        <x:v>56k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>RC0603FR-07100RL</x:v>
-      </x:c>
-      <x:c r="E95" t="str">
-        <x:v>C105588</x:v>
-      </x:c>
+        <x:v>RC0402FR-0756KL</x:v>
+      </x:c>
+      <x:c r="E95"/>
       <x:c r="F95" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G95" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H95" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I95" t="n">
-        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D95,$F$11:$F$114),G95)/H95,0)*H95))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J95" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K95" t="n">
-        <x:v>0.0024</x:v>
-      </x:c>
-      <x:c r="L95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95"/>
+      <x:c r="H95"/>
+      <x:c r="I95" t="str">
+        <x:f>IF(OR(D95="",G95="",H95=""),"",IF(COUNTIF($D$11:D95,D95)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D95,$F$11:$F$102),G95)/H95,0)*H95))</x:f>
+      </x:c>
+      <x:c r="J95"/>
+      <x:c r="K95"/>
+      <x:c r="L95" t="str">
         <x:f>IF(K95="","",ROUND(F95*K95,4))</x:f>
-        <x:v>0.0144</x:v>
       </x:c>
       <x:c r="M95" t="str">
         <x:f>IF(OR(K95="",I95="",N95=""),"",IF(N95&gt;=I95,ROUND(I95*K95,4),""))</x:f>
       </x:c>
-      <x:c r="N95" t="n">
-        <x:v>2943700</x:v>
-      </x:c>
+      <x:c r="N95"/>
       <x:c r="O95" t="str">
-        <x:v>LCSC code and price reused from the R112 row (same MPN)</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P95" t="n">
         <x:v>46300</x:v>
@@ -5596,42 +5072,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R95" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
-      </x:c>
-      <x:c r="S95" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C105588.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0756KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>R206, R207, R208</x:v>
+        <x:v>R252</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>I2S series 33 ohm 1% 0603</x:v>
+        <x:v>301k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>RC0603FR-0733RL</x:v>
-      </x:c>
-      <x:c r="E96" t="str"/>
+        <x:v>RC0402FR-07301KL</x:v>
+      </x:c>
+      <x:c r="E96"/>
       <x:c r="F96" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G96" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H96" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I96" t="n">
-        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D96,$F$11:$F$114),G96)/H96,0)*H96))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J96" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96"/>
+      <x:c r="H96"/>
+      <x:c r="I96" t="str">
+        <x:f>IF(OR(D96="",G96="",H96=""),"",IF(COUNTIF($D$11:D96,D96)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D96,$F$11:$F$102),G96)/H96,0)*H96))</x:f>
+      </x:c>
+      <x:c r="J96"/>
       <x:c r="K96"/>
       <x:c r="L96" t="str">
         <x:f>IF(K96="","",ROUND(F96*K96,4))</x:f>
@@ -5641,7 +5108,7 @@
       </x:c>
       <x:c r="N96"/>
       <x:c r="O96" t="str">
-        <x:v>LCSC code not looked up</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P96" t="n">
         <x:v>46300</x:v>
@@ -5650,42 +5117,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R96" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze. LCSC code still open: no lookups left in the Headphone_Aux task budget. LCSC code still open after the Amplifiers lookup (search returned distributor listings only).</x:v>
-      </x:c>
-      <x:c r="S96" t="str"/>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07301KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>R209, R210</x:v>
+        <x:v>R253</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>Audio I2C pull-ups 2.2k 1% 0603</x:v>
+        <x:v>150k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>RC0603FR-072K2L</x:v>
-      </x:c>
-      <x:c r="E97" t="str">
-        <x:v>C114662</x:v>
-      </x:c>
+        <x:v>RC0402FR-07150KL</x:v>
+      </x:c>
+      <x:c r="E97"/>
       <x:c r="F97" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G97" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H97" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I97" t="n">
-        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D97,$F$11:$F$114),G97)/H97,0)*H97))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J97" t="n">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G97"/>
+      <x:c r="H97"/>
+      <x:c r="I97" t="str">
+        <x:f>IF(OR(D97="",G97="",H97=""),"",IF(COUNTIF($D$11:D97,D97)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D97,$F$11:$F$102),G97)/H97,0)*H97))</x:f>
+      </x:c>
+      <x:c r="J97"/>
       <x:c r="K97"/>
       <x:c r="L97" t="str">
         <x:f>IF(K97="","",ROUND(F97*K97,4))</x:f>
@@ -5695,7 +5153,7 @@
       </x:c>
       <x:c r="N97"/>
       <x:c r="O97" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P97" t="n">
         <x:v>46300</x:v>
@@ -5704,44 +5162,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R97" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Unverified: LCSC code/price/stock not checked at this BOM freeze.</x:v>
-      </x:c>
-      <x:c r="S97" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C114662.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07150KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="str">
-        <x:v>D200, D201</x:v>
+        <x:v>R254</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>Headphone jack / AUX_IN jack ESD, 2-line bidirectional 5 V (SOT-23)</x:v>
+        <x:v>82k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C98" t="str">
-        <x:v>DOWO (Nexperia PESD5V0S2BT equivalent)</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D98" t="str">
-        <x:v>PESD5V0S2BT</x:v>
-      </x:c>
-      <x:c r="E98" t="str">
-        <x:v>C5380400</x:v>
-      </x:c>
+        <x:v>RC0402FR-0782KL</x:v>
+      </x:c>
+      <x:c r="E98"/>
       <x:c r="F98" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G98" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H98" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I98" t="n">
-        <x:f>IF(OR(D98="",G98="",H98=""),"",IF(COUNTIF($D$11:D98,D98)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D98,$F$11:$F$114),G98)/H98,0)*H98))</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J98" t="n">
-        <x:v>5</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98" t="str">
+        <x:f>IF(OR(D98="",G98="",H98=""),"",IF(COUNTIF($D$11:D98,D98)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D98,$F$11:$F$102),G98)/H98,0)*H98))</x:f>
+      </x:c>
+      <x:c r="J98"/>
       <x:c r="K98"/>
       <x:c r="L98" t="str">
         <x:f>IF(K98="","",ROUND(F98*K98,4))</x:f>
@@ -5751,7 +5198,7 @@
       </x:c>
       <x:c r="N98"/>
       <x:c r="O98" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P98" t="n">
         <x:v>46300</x:v>
@@ -5760,60 +5207,58 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R98" t="str">
-        <x:v>Headphone_Aux sheet, 2026-10-06. LCSC C5380400 is the DOWO PESD5V0S2BT listing; the Nexperia original was not stock-checked. Pin 3 common (search summary of Nexperia datasheet): VERIFY. Footprint DesktopSpeaker:PESD5V0S2BT (stock SOT-23).</x:v>
-      </x:c>
-      <x:c r="S98" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5380400.html</x:v>
-      </x:c>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0782KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+      </x:c>
+      <x:c r="S98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="str">
-        <x:v>U25</x:v>
+        <x:v>R12, R16, R17, R103, R107, R109, R110, R111, R113, R125, R142, R152, R153, R154, R160, R175, R176, R180, R181, R184, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239, R255, R259</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>PVDD boost converter 11.9 V (VQFN-20)</x:v>
+        <x:v>100k / 100k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C99" t="str">
-        <x:v>TI</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D99" t="str">
-        <x:v>TPS61088RHLR</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="E99" t="str">
-        <x:v>C87357</x:v>
+        <x:v>C60491</x:v>
       </x:c>
       <x:c r="F99" t="n">
-        <x:v>1</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G99" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H99" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I99" t="n">
-        <x:f>IF(OR(D99="",G99="",H99=""),"",IF(COUNTIF($D$11:D99,D99)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D99,$F$11:$F$114),G99)/H99,0)*H99))</x:f>
-        <x:v>1</x:v>
+        <x:f>IF(OR(D99="",G99="",H99=""),"",IF(COUNTIF($D$11:D99,D99)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D99,$F$11:$F$102),G99)/H99,0)*H99))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J99" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K99" t="n">
-        <x:v>4.9</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="L99" t="n">
         <x:f>IF(K99="","",ROUND(F99*K99,4))</x:f>
-        <x:v>4.9</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="M99" t="n">
         <x:f>IF(OR(K99="",I99="",N99=""),"",IF(N99&gt;=I99,ROUND(I99*K99,4),""))</x:f>
-        <x:v>4.9</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="N99" t="n">
-        <x:v>1199</x:v>
+        <x:v>726500</x:v>
       </x:c>
       <x:c r="O99" t="str">
-        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
+        <x:v>LCSC search 2026-10-06 (price is the quoted tier, stock as listed); re-verify at order</x:v>
       </x:c>
       <x:c r="P99" t="n">
         <x:v>46300</x:v>
@@ -5822,33 +5267,33 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R99" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. 499k/56k feedback, 301k RFREQ, 150k ILIM. Pad map and 3D from the EasyEDA official package; verify against TI RHL0020A before PCB.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-07100KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S99" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C87357.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60491.html</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>L200</x:v>
+        <x:v>R260 (R256 DNP)</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>Boost inductor 2.2uH, Isat 19.6 A, Irms 17.8 A, 6.3 mohm</x:v>
+        <x:v>0R / 0R DNP 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C100" t="str">
-        <x:v>Coilcraft</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D100" t="str">
-        <x:v>XAL7070-222MEC</x:v>
-      </x:c>
-      <x:c r="E100" t="str"/>
+        <x:v>RC0402FR-070RL</x:v>
+      </x:c>
+      <x:c r="E100"/>
       <x:c r="F100" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G100"/>
       <x:c r="H100"/>
       <x:c r="I100" t="str">
-        <x:f>IF(OR(D100="",G100="",H100=""),"",IF(COUNTIF($D$11:D100,D100)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D100,$F$11:$F$114),G100)/H100,0)*H100))</x:f>
+        <x:f>IF(OR(D100="",G100="",H100=""),"",IF(COUNTIF($D$11:D100,D100)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D100,$F$11:$F$102),G100)/H100,0)*H100))</x:f>
       </x:c>
       <x:c r="J100"/>
       <x:c r="K100"/>
@@ -5860,7 +5305,7 @@
       </x:c>
       <x:c r="N100"/>
       <x:c r="O100" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P100" t="n">
         <x:v>46300</x:v>
@@ -5869,31 +5314,31 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R100" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Not stocked at LCSC per search; alternatives: Cyntec PIMB104T-2R2MS (datasheet table 2, 18 A / 12 A) or Bourns SRP1265A-2R2M class. Stock KiCad XAL7070 footprint (7.5 x 7.2 mm).</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-070RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="str">
-        <x:v>L201, L202, L203, L204, L205, L206</x:v>
+        <x:v>R185, R186, R187, R226, R227, R228, R229, R230, R231, R240, R257, R258, R261</x:v>
       </x:c>
       <x:c r="B101" t="str">
-        <x:v>Speaker output filter inductors 22uH, 5.0 A Isat (peak 2.8 A at 11.1 V into 4 ohm)</x:v>
+        <x:v>1k 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C101" t="str">
-        <x:v>Sunlord</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D101" t="str">
-        <x:v>MWSA1265S-220MT</x:v>
-      </x:c>
-      <x:c r="E101" t="str"/>
+        <x:v>RC0402FR-071KL</x:v>
+      </x:c>
+      <x:c r="E101"/>
       <x:c r="F101" t="n">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G101"/>
       <x:c r="H101"/>
       <x:c r="I101" t="str">
-        <x:f>IF(OR(D101="",G101="",H101=""),"",IF(COUNTIF($D$11:D101,D101)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D101,$F$11:$F$114),G101)/H101,0)*H101))</x:f>
+        <x:f>IF(OR(D101="",G101="",H101=""),"",IF(COUNTIF($D$11:D101,D101)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D101,$F$11:$F$102),G101)/H101,0)*H101))</x:f>
       </x:c>
       <x:c r="J101"/>
       <x:c r="K101"/>
@@ -5905,7 +5350,7 @@
       </x:c>
       <x:c r="N101"/>
       <x:c r="O101" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
+        <x:v>LCSC code open: MPN from family knowledge, not looked up; price/stock unverified</x:v>
       </x:c>
       <x:c r="P101" t="n">
         <x:v>46300</x:v>
@@ -5914,58 +5359,58 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R101" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Isat 5.0 A from the MWSA1265S series datasheet text; the 22 uH value row and its LCSC code were not confirmed. Stock KiCad MWSA1265S footprint (13.45 x 12.6 x 6.5 mm). OCP trips at about 7.5 A; confirm the saturation margin against measured peak.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-071KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="str">
-        <x:v>J9, J10, J11</x:v>
+        <x:v>R11, R13, R14, R15, R18, R106, R182, R183, R242, R243, R244, R262</x:v>
       </x:c>
       <x:c r="B102" t="str">
-        <x:v>Speaker connectors FRONT_L, FRONT_R, WOOFER (JST VH 2-pin, 10 A)</x:v>
+        <x:v>10k / 10k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C102" t="str">
-        <x:v>JST</x:v>
+        <x:v>Yageo</x:v>
       </x:c>
       <x:c r="D102" t="str">
-        <x:v>B2P-VH(LF)(SN)</x:v>
+        <x:v>RC0402FR-0710KL</x:v>
       </x:c>
       <x:c r="E102" t="str">
-        <x:v>C160315</x:v>
+        <x:v>C60490</x:v>
       </x:c>
       <x:c r="F102" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G102" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H102" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I102" t="n">
-        <x:f>IF(OR(D102="",G102="",H102=""),"",IF(COUNTIF($D$11:D102,D102)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D102,$F$11:$F$114),G102)/H102,0)*H102))</x:f>
-        <x:v>3</x:v>
+        <x:f>IF(OR(D102="",G102="",H102=""),"",IF(COUNTIF($D$11:D102,D102)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D102,$F$11:$F$102),G102)/H102,0)*H102))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J102" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K102" t="n">
-        <x:v>0.2404</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
       <x:c r="L102" t="n">
         <x:f>IF(K102="","",ROUND(F102*K102,4))</x:f>
-        <x:v>0.7212</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="M102" t="n">
         <x:f>IF(OR(K102="",I102="",N102=""),"",IF(N102&gt;=I102,ROUND(I102*K102,4),""))</x:f>
-        <x:v>0.7212</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="N102" t="n">
-        <x:v>20650</x:v>
+        <x:v>5338600</x:v>
       </x:c>
       <x:c r="O102" t="str">
-        <x:v>EasyEDA/LCSC API 2026-10-06; verify at order</x:v>
+        <x:v>LCSC search 2026-10-06 (price is the quoted tier, stock as listed); re-verify at order</x:v>
       </x:c>
       <x:c r="P102" t="n">
         <x:v>46300</x:v>
@@ -5974,575 +5419,262 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R102" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Pin 1 +, pin 2 -. No 3D model linked (downloaded STEP axes not verified).</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-0710KL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
       </x:c>
       <x:c r="S102" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C160315.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60490.html</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" t="str">
-        <x:v>C271, C272, C273, C274, C277, C279, C290, C292</x:v>
-      </x:c>
-      <x:c r="B103" t="str">
-        <x:v>PVDD_AMP 22uF 25V X7R 1210 (boost output and TAS5825M PVDD)</x:v>
-      </x:c>
-      <x:c r="C103" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D103" t="str">
-        <x:v>CL32B226KAJNNNE</x:v>
-      </x:c>
-      <x:c r="E103" t="str">
-        <x:v>C309062</x:v>
-      </x:c>
-      <x:c r="F103" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G103" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H103" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I103" t="n">
-        <x:f>IF(OR(D103="",G103="",H103=""),"",IF(COUNTIF($D$11:D103,D103)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D103,$F$11:$F$114),G103)/H103,0)*H103))</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J103" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K103" t="n">
-        <x:v>0.1742</x:v>
-      </x:c>
-      <x:c r="L103" t="n">
-        <x:f>IF(K103="","",ROUND(F103*K103,4))</x:f>
-        <x:v>1.3936</x:v>
-      </x:c>
-      <x:c r="M103" t="n">
-        <x:f>IF(OR(K103="",I103="",N103=""),"",IF(N103&gt;=I103,ROUND(I103*K103,4),""))</x:f>
-        <x:v>1.3936</x:v>
-      </x:c>
-      <x:c r="N103" t="n">
-        <x:v>9300</x:v>
-      </x:c>
-      <x:c r="O103" t="str">
-        <x:v>Search snapshot 2026-10-06; verify at order</x:v>
-      </x:c>
-      <x:c r="P103" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q103" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R103" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. 25 V rating on 11.9 V; X7R loses roughly half its capacitance at this bias. TAS datasheet lists 22 uF 35 V 0805: 1210 25 V used instead.</x:v>
-      </x:c>
-      <x:c r="S103" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C309062.html</x:v>
-      </x:c>
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
+      <x:c r="H103"/>
+      <x:c r="I103"/>
+      <x:c r="J103"/>
+      <x:c r="K103"/>
+      <x:c r="L103"/>
+      <x:c r="M103"/>
+      <x:c r="N103"/>
+      <x:c r="O103"/>
+      <x:c r="P103"/>
+      <x:c r="Q103"/>
+      <x:c r="R103"/>
+      <x:c r="S103"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" t="str">
-        <x:v>C285, C286, C287, C288, C298, C299, C300, C301</x:v>
-      </x:c>
-      <x:c r="B104" t="str">
-        <x:v>TAS5825M bootstrap 0.47uF 25V X7R 0603</x:v>
-      </x:c>
-      <x:c r="C104" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D104" t="str">
-        <x:v>CL10B474KA8NNNC</x:v>
-      </x:c>
-      <x:c r="E104" t="str">
-        <x:v>C1623</x:v>
-      </x:c>
-      <x:c r="F104" t="n">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
       <x:c r="G104"/>
       <x:c r="H104"/>
-      <x:c r="I104" t="str">
-        <x:f>IF(OR(D104="",G104="",H104=""),"",IF(COUNTIF($D$11:D104,D104)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D104,$F$11:$F$114),G104)/H104,0)*H104))</x:f>
-      </x:c>
+      <x:c r="I104"/>
       <x:c r="J104"/>
       <x:c r="K104"/>
-      <x:c r="L104" t="str">
-        <x:f>IF(K104="","",ROUND(F104*K104,4))</x:f>
-      </x:c>
-      <x:c r="M104" t="str">
-        <x:f>IF(OR(K104="",I104="",N104=""),"",IF(N104&gt;=I104,ROUND(I104*K104,4),""))</x:f>
-      </x:c>
+      <x:c r="L104"/>
+      <x:c r="M104"/>
       <x:c r="N104"/>
-      <x:c r="O104" t="str">
-        <x:v>LCSC/JLCPCB code C1623 confirmed for this MPN (jlcpcb.com/partdetail/C1623, 2026-10-06); price/stock not retrieved.</x:v>
-      </x:c>
-      <x:c r="P104" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q104" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R104" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Table 66 value 0.47 uF 16 V; 25 V part selected for margin. Remaining Amplifiers-sheet codes (L200, L201-206, C268, C269, C275, R250-R254, R260, C206-C211 C0G 10 nF, R206-R208 33R) not found within the 8-lookup budget; LCSC search is not reachable by the agent (HTTP 403).</x:v>
-      </x:c>
-      <x:c r="S104" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C1623.html</x:v>
-      </x:c>
+      <x:c r="O104"/>
+      <x:c r="P104"/>
+      <x:c r="Q104"/>
+      <x:c r="R104"/>
+      <x:c r="S104"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" t="str">
-        <x:v>C302, C303, C304, C305, C306, C307</x:v>
-      </x:c>
-      <x:c r="B105" t="str">
-        <x:v>Output filter 0.68uF 50V X7R 0805</x:v>
-      </x:c>
-      <x:c r="C105" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D105" t="str">
-        <x:v>CL21B684KBFVPNE</x:v>
-      </x:c>
-      <x:c r="E105" t="str">
-        <x:v>C472832</x:v>
-      </x:c>
-      <x:c r="F105" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
       <x:c r="G105"/>
       <x:c r="H105"/>
-      <x:c r="I105" t="str">
-        <x:f>IF(OR(D105="",G105="",H105=""),"",IF(COUNTIF($D$11:D105,D105)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D105,$F$11:$F$114),G105)/H105,0)*H105))</x:f>
-      </x:c>
+      <x:c r="I105"/>
       <x:c r="J105"/>
       <x:c r="K105"/>
-      <x:c r="L105" t="str">
-        <x:f>IF(K105="","",ROUND(F105*K105,4))</x:f>
-      </x:c>
-      <x:c r="M105" t="str">
-        <x:f>IF(OR(K105="",I105="",N105=""),"",IF(N105&gt;=I105,ROUND(I105*K105,4),""))</x:f>
-      </x:c>
+      <x:c r="L105"/>
+      <x:c r="M105"/>
       <x:c r="N105"/>
-      <x:c r="O105" t="str">
-        <x:v>LCSC number from search 2026-10-06; price/stock unverified</x:v>
-      </x:c>
-      <x:c r="P105" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q105" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R105" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Variant suffix per the LCSC listing; confirm voltage/dielectric on the datasheet.</x:v>
-      </x:c>
-      <x:c r="S105" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C472832.html</x:v>
-      </x:c>
+      <x:c r="O105"/>
+      <x:c r="P105"/>
+      <x:c r="Q105"/>
+      <x:c r="R105"/>
+      <x:c r="S105"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" t="str">
-        <x:v>C268</x:v>
-      </x:c>
-      <x:c r="B106" t="str">
-        <x:v>Boost COMP capacitor 6.8nF X7R 0603</x:v>
-      </x:c>
-      <x:c r="C106" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D106" t="str">
-        <x:v>CL10B682KB8NNNC</x:v>
-      </x:c>
-      <x:c r="E106" t="str"/>
-      <x:c r="F106" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
       <x:c r="G106"/>
       <x:c r="H106"/>
-      <x:c r="I106" t="str">
-        <x:f>IF(OR(D106="",G106="",H106=""),"",IF(COUNTIF($D$11:D106,D106)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D106,$F$11:$F$114),G106)/H106,0)*H106))</x:f>
-      </x:c>
+      <x:c r="I106"/>
       <x:c r="J106"/>
       <x:c r="K106"/>
-      <x:c r="L106" t="str">
-        <x:f>IF(K106="","",ROUND(F106*K106,4))</x:f>
-      </x:c>
-      <x:c r="M106" t="str">
-        <x:f>IF(OR(K106="",I106="",N106=""),"",IF(N106&gt;=I106,ROUND(I106*K106,4),""))</x:f>
-      </x:c>
+      <x:c r="L106"/>
+      <x:c r="M106"/>
       <x:c r="N106"/>
-      <x:c r="O106" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P106" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q106" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R106" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Calculated compensation, bench check required.</x:v>
-      </x:c>
+      <x:c r="O106"/>
+      <x:c r="P106"/>
+      <x:c r="Q106"/>
+      <x:c r="R106"/>
       <x:c r="S106"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" t="str">
-        <x:v>C269</x:v>
-      </x:c>
-      <x:c r="B107" t="str">
-        <x:v>Boost COMP capacitor 47pF C0G 0603</x:v>
-      </x:c>
-      <x:c r="C107" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
-      </x:c>
-      <x:c r="D107" t="str">
-        <x:v>CL10C470JB8NNNC</x:v>
-      </x:c>
-      <x:c r="E107" t="str"/>
-      <x:c r="F107" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
       <x:c r="G107"/>
       <x:c r="H107"/>
-      <x:c r="I107" t="str">
-        <x:f>IF(OR(D107="",G107="",H107=""),"",IF(COUNTIF($D$11:D107,D107)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D107,$F$11:$F$114),G107)/H107,0)*H107))</x:f>
-      </x:c>
+      <x:c r="I107"/>
       <x:c r="J107"/>
       <x:c r="K107"/>
-      <x:c r="L107" t="str">
-        <x:f>IF(K107="","",ROUND(F107*K107,4))</x:f>
-      </x:c>
-      <x:c r="M107" t="str">
-        <x:f>IF(OR(K107="",I107="",N107=""),"",IF(N107&gt;=I107,ROUND(I107*K107,4),""))</x:f>
-      </x:c>
+      <x:c r="L107"/>
+      <x:c r="M107"/>
       <x:c r="N107"/>
-      <x:c r="O107" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P107" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q107" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R107" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Calculated compensation, bench check required.</x:v>
-      </x:c>
+      <x:c r="O107"/>
+      <x:c r="P107"/>
+      <x:c r="Q107"/>
+      <x:c r="R107"/>
       <x:c r="S107"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" t="str">
-        <x:v>C275</x:v>
-      </x:c>
-      <x:c r="B108" t="str">
-        <x:v>PVDD_AMP bulk 100uF 25V polymer/hybrid (8x10 mm)</x:v>
-      </x:c>
-      <x:c r="C108" t="str">
-        <x:v>Panasonic</x:v>
-      </x:c>
-      <x:c r="D108" t="str">
-        <x:v>EEH-ZA1E101P</x:v>
-      </x:c>
-      <x:c r="E108" t="str"/>
-      <x:c r="F108" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
       <x:c r="G108"/>
       <x:c r="H108"/>
-      <x:c r="I108" t="str">
-        <x:f>IF(OR(D108="",G108="",H108=""),"",IF(COUNTIF($D$11:D108,D108)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D108,$F$11:$F$114),G108)/H108,0)*H108))</x:f>
-      </x:c>
+      <x:c r="I108"/>
       <x:c r="J108"/>
       <x:c r="K108"/>
-      <x:c r="L108" t="str">
-        <x:f>IF(K108="","",ROUND(F108*K108,4))</x:f>
-      </x:c>
-      <x:c r="M108" t="str">
-        <x:f>IF(OR(K108="",I108="",N108=""),"",IF(N108&gt;=I108,ROUND(I108*K108,4),""))</x:f>
-      </x:c>
+      <x:c r="L108"/>
+      <x:c r="M108"/>
       <x:c r="N108"/>
-      <x:c r="O108" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified. VERIFY part.</x:v>
-      </x:c>
-      <x:c r="P108" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q108" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R108" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Bass-burst reservoir; part type not verified.</x:v>
-      </x:c>
+      <x:c r="O108"/>
+      <x:c r="P108"/>
+      <x:c r="Q108"/>
+      <x:c r="R108"/>
       <x:c r="S108"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" t="str">
-        <x:v>R250</x:v>
-      </x:c>
-      <x:c r="B109" t="str">
-        <x:v>Boost feedback upper resistor 499k 1%</x:v>
-      </x:c>
-      <x:c r="C109" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D109" t="str">
-        <x:v>RC0603FR-07499KL</x:v>
-      </x:c>
-      <x:c r="E109" t="str"/>
-      <x:c r="F109" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
       <x:c r="G109"/>
       <x:c r="H109"/>
-      <x:c r="I109" t="str">
-        <x:f>IF(OR(D109="",G109="",H109=""),"",IF(COUNTIF($D$11:D109,D109)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D109,$F$11:$F$114),G109)/H109,0)*H109))</x:f>
-      </x:c>
+      <x:c r="I109"/>
       <x:c r="J109"/>
       <x:c r="K109"/>
-      <x:c r="L109" t="str">
-        <x:f>IF(K109="","",ROUND(F109*K109,4))</x:f>
-      </x:c>
-      <x:c r="M109" t="str">
-        <x:f>IF(OR(K109="",I109="",N109=""),"",IF(N109&gt;=I109,ROUND(I109*K109,4),""))</x:f>
-      </x:c>
+      <x:c r="L109"/>
+      <x:c r="M109"/>
       <x:c r="N109"/>
-      <x:c r="O109" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P109" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q109" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R109" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. VOUT = 1.204 V x (1 + 499k/56k) = 11.93 V.</x:v>
-      </x:c>
+      <x:c r="O109"/>
+      <x:c r="P109"/>
+      <x:c r="Q109"/>
+      <x:c r="R109"/>
       <x:c r="S109"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" t="str">
-        <x:v>R251</x:v>
-      </x:c>
-      <x:c r="B110" t="str">
-        <x:v>Boost feedback lower resistor 56k 1%</x:v>
-      </x:c>
-      <x:c r="C110" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D110" t="str">
-        <x:v>RC0603FR-0756KL</x:v>
-      </x:c>
-      <x:c r="E110" t="str"/>
-      <x:c r="F110" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
       <x:c r="G110"/>
       <x:c r="H110"/>
-      <x:c r="I110" t="str">
-        <x:f>IF(OR(D110="",G110="",H110=""),"",IF(COUNTIF($D$11:D110,D110)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D110,$F$11:$F$114),G110)/H110,0)*H110))</x:f>
-      </x:c>
+      <x:c r="I110"/>
       <x:c r="J110"/>
       <x:c r="K110"/>
-      <x:c r="L110" t="str">
-        <x:f>IF(K110="","",ROUND(F110*K110,4))</x:f>
-      </x:c>
-      <x:c r="M110" t="str">
-        <x:f>IF(OR(K110="",I110="",N110=""),"",IF(N110&gt;=I110,ROUND(I110*K110,4),""))</x:f>
-      </x:c>
+      <x:c r="L110"/>
+      <x:c r="M110"/>
       <x:c r="N110"/>
-      <x:c r="O110" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P110" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q110" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R110" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. </x:v>
-      </x:c>
+      <x:c r="O110"/>
+      <x:c r="P110"/>
+      <x:c r="Q110"/>
+      <x:c r="R110"/>
       <x:c r="S110"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" t="str">
-        <x:v>R252</x:v>
-      </x:c>
-      <x:c r="B111" t="str">
-        <x:v>Boost RFREQ 301k 1%</x:v>
-      </x:c>
-      <x:c r="C111" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D111" t="str">
-        <x:v>RC0603FR-07301KL</x:v>
-      </x:c>
-      <x:c r="E111" t="str"/>
-      <x:c r="F111" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
       <x:c r="G111"/>
       <x:c r="H111"/>
-      <x:c r="I111" t="str">
-        <x:f>IF(OR(D111="",G111="",H111=""),"",IF(COUNTIF($D$11:D111,D111)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D111,$F$11:$F$114),G111)/H111,0)*H111))</x:f>
-      </x:c>
+      <x:c r="I111"/>
       <x:c r="J111"/>
       <x:c r="K111"/>
-      <x:c r="L111" t="str">
-        <x:f>IF(K111="","",ROUND(F111*K111,4))</x:f>
-      </x:c>
-      <x:c r="M111" t="str">
-        <x:f>IF(OR(K111="",I111="",N111=""),"",IF(N111&gt;=I111,ROUND(I111*K111,4),""))</x:f>
-      </x:c>
+      <x:c r="L111"/>
+      <x:c r="M111"/>
       <x:c r="N111"/>
-      <x:c r="O111" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P111" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q111" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R111" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. About 494 kHz at 3.6 V in.</x:v>
-      </x:c>
+      <x:c r="O111"/>
+      <x:c r="P111"/>
+      <x:c r="Q111"/>
+      <x:c r="R111"/>
       <x:c r="S111"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" t="str">
-        <x:v>R253</x:v>
-      </x:c>
-      <x:c r="B112" t="str">
-        <x:v>Boost ILIM 150k 1%</x:v>
-      </x:c>
-      <x:c r="C112" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D112" t="str">
-        <x:v>RC0603FR-07150KL</x:v>
-      </x:c>
-      <x:c r="E112" t="str"/>
-      <x:c r="F112" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
       <x:c r="G112"/>
       <x:c r="H112"/>
-      <x:c r="I112" t="str">
-        <x:f>IF(OR(D112="",G112="",H112=""),"",IF(COUNTIF($D$11:D112,D112)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D112,$F$11:$F$114),G112)/H112,0)*H112))</x:f>
-      </x:c>
+      <x:c r="I112"/>
       <x:c r="J112"/>
       <x:c r="K112"/>
-      <x:c r="L112" t="str">
-        <x:f>IF(K112="","",ROUND(F112*K112,4))</x:f>
-      </x:c>
-      <x:c r="M112" t="str">
-        <x:f>IF(OR(K112="",I112="",N112=""),"",IF(N112&gt;=I112,ROUND(I112*K112,4),""))</x:f>
-      </x:c>
+      <x:c r="L112"/>
+      <x:c r="M112"/>
       <x:c r="N112"/>
-      <x:c r="O112" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P112" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q112" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R112" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. 7.9 A typical, 6.6 A minimum peak limit (PFM).</x:v>
-      </x:c>
+      <x:c r="O112"/>
+      <x:c r="P112"/>
+      <x:c r="Q112"/>
+      <x:c r="R112"/>
       <x:c r="S112"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" t="str">
-        <x:v>R254</x:v>
-      </x:c>
-      <x:c r="B113" t="str">
-        <x:v>Boost COMP resistor 82k 1%</x:v>
-      </x:c>
-      <x:c r="C113" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D113" t="str">
-        <x:v>RC0603FR-0782KL</x:v>
-      </x:c>
-      <x:c r="E113" t="str"/>
-      <x:c r="F113" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
       <x:c r="G113"/>
       <x:c r="H113"/>
-      <x:c r="I113" t="str">
-        <x:f>IF(OR(D113="",G113="",H113=""),"",IF(COUNTIF($D$11:D113,D113)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D113,$F$11:$F$114),G113)/H113,0)*H113))</x:f>
-      </x:c>
+      <x:c r="I113"/>
       <x:c r="J113"/>
       <x:c r="K113"/>
-      <x:c r="L113" t="str">
-        <x:f>IF(K113="","",ROUND(F113*K113,4))</x:f>
-      </x:c>
-      <x:c r="M113" t="str">
-        <x:f>IF(OR(K113="",I113="",N113=""),"",IF(N113&gt;=I113,ROUND(I113*K113,4),""))</x:f>
-      </x:c>
+      <x:c r="L113"/>
+      <x:c r="M113"/>
       <x:c r="N113"/>
-      <x:c r="O113" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P113" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q113" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R113" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. </x:v>
-      </x:c>
+      <x:c r="O113"/>
+      <x:c r="P113"/>
+      <x:c r="Q113"/>
+      <x:c r="R113"/>
       <x:c r="S113"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" t="str">
-        <x:v>R260 (R256 DNP)</x:v>
-      </x:c>
-      <x:c r="B114" t="str">
-        <x:v>TAS5825M U6 ADR 0 ohm (R256 = boost MODE option, not fitted)</x:v>
-      </x:c>
-      <x:c r="C114" t="str">
-        <x:v>YAGEO</x:v>
-      </x:c>
-      <x:c r="D114" t="str">
-        <x:v>RC0603FR-070RL</x:v>
-      </x:c>
-      <x:c r="E114" t="str"/>
-      <x:c r="F114" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
       <x:c r="G114"/>
       <x:c r="H114"/>
-      <x:c r="I114" t="str">
-        <x:f>IF(OR(D114="",G114="",H114=""),"",IF(COUNTIF($D$11:D114,D114)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$114,D114,$F$11:$F$114),G114)/H114,0)*H114))</x:f>
-      </x:c>
+      <x:c r="I114"/>
       <x:c r="J114"/>
       <x:c r="K114"/>
-      <x:c r="L114" t="str">
-        <x:f>IF(K114="","",ROUND(F114*K114,4))</x:f>
-      </x:c>
-      <x:c r="M114" t="str">
-        <x:f>IF(OR(K114="",I114="",N114=""),"",IF(N114&gt;=I114,ROUND(I114*K114,4),""))</x:f>
-      </x:c>
+      <x:c r="L114"/>
+      <x:c r="M114"/>
       <x:c r="N114"/>
-      <x:c r="O114" t="str">
-        <x:v>LCSC code open: not found in the Amplifiers task lookup budget; price/stock unverified.</x:v>
-      </x:c>
-      <x:c r="P114" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="Q114" t="str">
-        <x:v>2026-10-06</x:v>
-      </x:c>
-      <x:c r="R114" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. R256 is DNP: fit to force PWM mode.</x:v>
-      </x:c>
+      <x:c r="O114"/>
+      <x:c r="P114"/>
+      <x:c r="Q114"/>
+      <x:c r="R114"/>
       <x:c r="S114"/>
     </x:row>
     <x:row r="115">

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="R88769a16ef424944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R15cd418c244a4278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rbebacaf8831e4228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Ref16ae1543fd4aaf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,11 +434,11 @@
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
         <x:f>ROUND(SUM(L11:L102),2)</x:f>
-        <x:v>74.53</x:v>
+        <x:v>74.38</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
-        <x:v>BOM updated 2026-10-06: all R/C repackaged to hand-solder 0402 (0805 for large/high-voltage capacitors); many new passive MPNs and LCSC codes are unverified, so subtotal is partial.</x:v>
+        <x:v>BOM updated 2026-10-06: all R/C repackaged to hand-solder 0402 (0805 for large/high-voltage capacitors); low-risk cuts applied (C113-C115, C121, C143, C151, C163, C164, C185, C242, R260 removed); many passive MPNs/LCSC codes unverified, so subtotal is partial.</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1"/>
@@ -462,7 +462,7 @@
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
         <x:f>ROUND(SUM(M11:M102),2)</x:f>
-        <x:v>84.5</x:v>
+        <x:v>83.57</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -3222,7 +3222,7 @@
         <x:v>C100, C101, C108, C111, C112</x:v>
       </x:c>
       <x:c r="B57" s="25" t="str">
-        <x:v>10uF / 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
+        <x:v>10uF X7R 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C57" s="25" t="str">
         <x:v>Murata</x:v>
@@ -3264,10 +3264,10 @@
     </x:row>
     <x:row r="58" ht="72" customHeight="1">
       <x:c r="A58" s="25" t="str">
-        <x:v>C102, C109, C175, C176, C181, C185, C190, C214, C216, C218, C223</x:v>
+        <x:v>C102, C109, C175, C176, C181, C190, C214, C216, C218, C223</x:v>
       </x:c>
       <x:c r="B58" s="25" t="str">
-        <x:v>10uF / 10uF / 10V / 10uF X7R 10V / 10uF X7R 10V CVIN_3V3 0805 hand-solder (C_0805_2012Metric)</x:v>
+        <x:v>10uF X7R 10V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C58" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
@@ -3279,7 +3279,7 @@
         <x:v>C32635</x:v>
       </x:c>
       <x:c r="F58" s="25" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G58" t="n">
         <x:v>10</x:v>
@@ -3289,7 +3289,7 @@
       </x:c>
       <x:c r="I58" t="n">
         <x:f>IF(OR(D58="",G58="",H58=""),"",IF(COUNTIF($D$11:D58,D58)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$102,D58,$F$11:$F$102),G58)/H58,0)*H58))</x:f>
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J58" t="n">
         <x:v>10</x:v>
@@ -3299,11 +3299,11 @@
       </x:c>
       <x:c r="L58" s="27" t="n">
         <x:f>IF(K58="","",ROUND(F58*K58,4))</x:f>
-        <x:v>1.023</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="M58" s="27" t="n">
         <x:f>IF(OR(K58="",I58="",N58=""),"",IF(N58&gt;=I58,ROUND(I58*K58,4),""))</x:f>
-        <x:v>1.86</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="N58" t="n">
         <x:v>230700</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R58" t="str">
-        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B106KPQNNNE. See reports/passive-repackage-2026-10-06.md. </x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805 using CL21B106KPQNNNE. See reports/passive-repackage-2026-10-06.md.  Low-risk BOM cut 2026-10-06: removed C185 (reports/bom-reduction-audit.md).</x:v>
       </x:c>
       <x:c r="S58" t="str">
         <x:v>https://www.lcsc.com/product-detail/C32635.html</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>C182, C183</x:v>
       </x:c>
       <x:c r="B60" s="25" t="str">
-        <x:v>330pF C0G CC1 filter / 330pF C0G CC2 filter 0402 hand-solder (C_0402_1005Metric)</x:v>
+        <x:v>330pF C0G (CC1/CC2 filters) 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C60" s="25" t="str">
         <x:v>Murata</x:v>
@@ -3551,10 +3551,10 @@
     </x:row>
     <x:row r="64" ht="36" customHeight="1">
       <x:c r="A64" s="25" t="str">
-        <x:v>C113, C114, C115, C120, C121, C126, C130, C131, C132, C143, C151, C160, C162, C163, C191, C213, C215, C217, C219, C237, C238, C242, C246, C260, C267, C276, C278, C281, C289, C291, C294</x:v>
+        <x:v>C120, C126, C130, C131, C132, C160, C162, C191, C213, C215, C217, C219, C237, C238, C246, C260, C267, C276, C278, C281, C289, C291, C294</x:v>
       </x:c>
       <x:c r="B64" s="25" t="str">
-        <x:v>0.1uF / 50V / 100nF / 100nF 10V X7R / 100nF X7R 10V 0402 hand-solder (C_0402_1005Metric)</x:v>
+        <x:v>100nF X7R 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C64" s="25" t="str">
         <x:v>Murata</x:v>
@@ -3566,7 +3566,7 @@
         <x:v>C77020</x:v>
       </x:c>
       <x:c r="F64" s="25" t="n">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G64" t="n">
         <x:v>100</x:v>
@@ -3586,7 +3586,7 @@
       </x:c>
       <x:c r="L64" s="27" t="n">
         <x:f>IF(K64="","",ROUND(F64*K64,4))</x:f>
-        <x:v>0.217</x:v>
+        <x:v>0.161</x:v>
       </x:c>
       <x:c r="M64" s="27" t="n">
         <x:f>IF(OR(K64="",I64="",N64=""),"",IF(N64&gt;=I64,ROUND(I64*K64,4),""))</x:f>
@@ -3605,7 +3605,7 @@
         <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="R64" t="str">
-        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603/C_0402 using CL10B104KB8NNNC, GRM155R71H104KE14D. See reports/passive-repackage-2026-10-06.md. Footprint DesktopSpeaker:PD_C_0402 (no 3D model)</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603/C_0402 using CL10B104KB8NNNC, GRM155R71H104KE14D. See reports/passive-repackage-2026-10-06.md. Footprint DesktopSpeaker:PD_C_0402 (no 3D model) Low-risk BOM cut 2026-10-06: removed C113, C114, C115, C121, C143, C151, C163, C242 (reports/bom-reduction-audit.md).</x:v>
       </x:c>
       <x:c r="S64" t="str">
         <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
@@ -3616,7 +3616,7 @@
         <x:v>C6, C104, C105, C106, C107, C140, C141, C142, C150, C152, C153, C154, C261, C262, C263, C264</x:v>
       </x:c>
       <x:c r="B65" s="25" t="str">
-        <x:v>22uF / 10V / 22uF 10V / 22uF 10V X7R / 22uF X7R 10V 0805 hand-solder (C_0805_2012Metric)</x:v>
+        <x:v>22uF X7R 10V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C65" s="25" t="str">
         <x:v>Murata</x:v>
@@ -3734,7 +3734,7 @@
         <x:v>C103, C110, C266</x:v>
       </x:c>
       <x:c r="B67" s="25" t="str">
-        <x:v>47nF / 47nF / 50V 0402 hand-solder (C_0402_1005Metric)</x:v>
+        <x:v>47nF X7R 50V 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C67" s="25" t="str">
         <x:v>Murata</x:v>
@@ -3869,7 +3869,7 @@
         <x:v>C184, C270</x:v>
       </x:c>
       <x:c r="B70" s="25" t="str">
-        <x:v>1uF / 1uF X7R 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
+        <x:v>1uF X7R 50V 0805 hand-solder (C_0805_2012Metric)</x:v>
       </x:c>
       <x:c r="C70" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
@@ -4018,10 +4018,10 @@
     </x:row>
     <x:row r="73" ht="36" customHeight="1">
       <x:c r="A73" s="25" t="str">
-        <x:v>C122, C123, C124, C125, C164, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245, C282, C283, C284, C295, C296, C297</x:v>
+        <x:v>C122, C123, C124, C125, C170, C171, C172, C173, C174, C192, C193, C212, C220, C221, C222, C224, C225, C230, C231, C232, C233, C234, C235, C239, C240, C241, C245, C282, C283, C284, C295, C296, C297</x:v>
       </x:c>
       <x:c r="B73" s="25" t="str">
-        <x:v>1uF / 1uF X7R 10V 0402 hand-solder (C_0402_1005Metric)</x:v>
+        <x:v>1uF X7R 10V 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C73" s="25" t="str">
         <x:v>Samsung Electro-Mechanics</x:v>
@@ -4033,7 +4033,7 @@
         <x:v>C29266</x:v>
       </x:c>
       <x:c r="F73" s="25" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G73" t="n">
         <x:v>100</x:v>
@@ -4053,7 +4053,7 @@
       </x:c>
       <x:c r="L73" s="27" t="n">
         <x:f>IF(K73="","",ROUND(F73*K73,4))</x:f>
-        <x:v>0.0782</x:v>
+        <x:v>0.0759</x:v>
       </x:c>
       <x:c r="M73" s="27" t="n">
         <x:f>IF(OR(K73="",I73="",N73=""),"",IF(N73&gt;=I73,ROUND(I73*K73,4),""))</x:f>
@@ -4072,7 +4072,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R73" t="str">
-        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805/C_0603 using CL21B105KBFNNNE, LMK107B7105KA-T, CL10A105KB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0805/C_0603 using CL21B105KBFNNNE, LMK107B7105KA-T, CL10A105KB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown. Low-risk BOM cut 2026-10-06: removed C164 (reports/bom-reduction-audit.md).</x:v>
       </x:c>
       <x:c r="S73" t="str">
         <x:v>https://www.lcsc.com/product-detail/C29266.html</x:v>
@@ -4447,7 +4447,7 @@
         <x:v>R112, R200, R201, R202, R203, R204, R205</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>100 / 100R 0402 hand-solder (R_0402_1005Metric)</x:v>
+        <x:v>100R 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C82" t="str">
         <x:v>Yageo</x:v>
@@ -5216,7 +5216,7 @@
         <x:v>R12, R16, R17, R103, R107, R109, R110, R111, R113, R125, R142, R152, R153, R154, R160, R175, R176, R180, R181, R184, R211, R212, R220, R221, R222, R223, R224, R225, R234, R235, R236, R237, R238, R239, R255, R259</x:v>
       </x:c>
       <x:c r="B99" t="str">
-        <x:v>100k / 100k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
+        <x:v>100k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C99" t="str">
         <x:v>Yageo</x:v>
@@ -5275,10 +5275,10 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>R260 (R256 DNP)</x:v>
+        <x:v>(R256 DNP)</x:v>
       </x:c>
       <x:c r="B100" t="str">
-        <x:v>0R / 0R DNP 0402 hand-solder (R_0402_1005Metric)</x:v>
+        <x:v>0R DNP 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C100" t="str">
         <x:v>Yageo</x:v>
@@ -5288,7 +5288,7 @@
       </x:c>
       <x:c r="E100"/>
       <x:c r="F100" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G100"/>
       <x:c r="H100"/>
@@ -5314,7 +5314,7 @@
         <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="R100" t="str">
-        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-070RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was R_0603 using RC0603FR-070RL. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown. Low-risk BOM cut 2026-10-06: removed R260 (reports/bom-reduction-audit.md).</x:v>
       </x:c>
       <x:c r="S100"/>
     </x:row>
@@ -5368,7 +5368,7 @@
         <x:v>R11, R13, R14, R15, R18, R106, R182, R183, R242, R243, R244, R262</x:v>
       </x:c>
       <x:c r="B102" t="str">
-        <x:v>10k / 10k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
+        <x:v>10k 1% 0402 hand-solder (R_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C102" t="str">
         <x:v>Yageo</x:v>

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -434,7 +434,7 @@
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
         <x:f>ROUND(SUM(L11:L111),2)</x:f>
-        <x:v>101.23</x:v>
+        <x:v>101.21</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -462,7 +462,7 @@
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
         <x:f>ROUND(SUM(M11:M111),2)</x:f>
-        <x:v>133.11</x:v>
+        <x:v>132.88</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -3065,16 +3065,16 @@
         <x:v>Y200</x:v>
       </x:c>
       <x:c r="B51" s="22" t="str">
-        <x:v>24.576 MHz crystal for PCM1862 (3225-4P, CL 15 pF)</x:v>
+        <x:v>24.576 MHz crystal for PCM1862 (3225-4P, CL 12 pF)</x:v>
       </x:c>
       <x:c r="C51" s="22" t="str">
-        <x:v>JYJE</x:v>
+        <x:v>YXC</x:v>
       </x:c>
       <x:c r="D51" s="22" t="str">
-        <x:v>3TJ424576UYFBC</x:v>
+        <x:v>X322524576MOB4SI</x:v>
       </x:c>
       <x:c r="E51" s="22" t="str">
-        <x:v>C2149067</x:v>
+        <x:v>C70568</x:v>
       </x:c>
       <x:c r="F51" s="23" t="n">
         <x:v>1</x:v>
@@ -3093,21 +3093,21 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K51" s="28" t="n">
-        <x:v>0.1237</x:v>
+        <x:v>0.1042</x:v>
       </x:c>
       <x:c r="L51" s="30" t="n">
         <x:f>IF(K51="","",ROUND(F51*K51,4))</x:f>
-        <x:v>0.1237</x:v>
+        <x:v>0.1042</x:v>
       </x:c>
       <x:c r="M51" s="30" t="n">
         <x:f>IF(OR(K51="",I51="",N51=""),"",IF(N51&gt;=I51,ROUND(I51*K51,4),""))</x:f>
-        <x:v>0.6185</x:v>
+        <x:v>0.521</x:v>
       </x:c>
       <x:c r="N51" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>4055</x:v>
       </x:c>
       <x:c r="O51" s="1" t="str">
-        <x:v>In stock; coordinator-approved substitution 2026-10-10 (was L327S240P11L C5261154); verified against LCSC listing C2149067 (JYJE 3TJ424576UYFBC, SMD3225-4P; ±30ppm, 15pF, ±10ppm, 24.576MHz); LCSC stock 135 at lookup vs order qty 5; price is the listed ladder at order qty; re-check at order.</x:v>
+        <x:v>In stock; replacement 2026-10-10 (sync-y200-c275; was JYJE 3TJ424576UYFBC C2149067, 135 in stock); verified against LCSC listing C70568 (YXC X322524576MOB4SI, SMD3225-4P; 24.576MHz, 12pF, ±10ppm, ±20ppm, ESR 50Ω); JLC extended; LCSC stock 4055, JLC list stock 5135 at lookup vs order qty 5; price is the listed ladder at order qty; re-check at order.</x:v>
       </x:c>
       <x:c r="P51" s="4" t="n">
         <x:v>46305</x:v>
@@ -3116,10 +3116,10 @@
         <x:v>2026-10-10</x:v>
       </x:c>
       <x:c r="R51" s="1" t="str">
-        <x:v>Source_Select_ADC sheet, 2026-10-06. Datasheet not retrieved; pad usage 1/3 assumed. Two 20 pF caps give about 13 pF CL; trim at bring-up. SUBSTITUTION 2026-10-10 (coordinator-approved): L327S240P11L C5261154 -&gt; 3TJ424576UYFBC C2149067. Original L327S240P11L stock 0 and LCSC lists it as 24 MHz (not 24.576 MHz - the original code may have been wrong for PCM1862); replacement is a true 24.576 MHz, CL 15 pF, 3225-4P, +/-10 ppm tolerance, +/-30 ppm stability (original stability not published), 135 in stock (low).</x:v>
+        <x:v>Source_Select_ADC sheet, 2026-10-06. REPLACEMENT 2026-10-10 (reports/sync-y200-c275.md): JYJE 3TJ424576UYFBC C2149067 (CL 15 pF, 135 in stock) -&gt; YXC X322524576MOB4SI C70568: 24.576 MHz fundamental, CL 12 pF, +/-10 ppm at 25 C, +/-20 ppm -40..85 C, ESR 50 ohm max (16-31 MHz), C0 3 pF max, 3.2 x 2.5 x 0.7 mm, 4055 in stock. Reason: no 15 pF 24.576 MHz 3225 crystal had more than 1000 in stock; with the 12 pF part, C226/C227 change 22 pF -&gt; 15 pF C0G: CL = 15*15/30 + 3-5 pF stray = 10.5-12.5 pF. Lower CL also lowers the gm needed from the PCM1862 1.8 V XI/XO oscillator. Datasheet datasheets/YXC_YSX321SL_X322524576MOB4SI.pdf: pads 1/3 crystal, 2/4 GND, land 1.4 x 1.2 mm at 2.2 x 1.7 mm pitch, matches Crystal_SMD_3225-4Pin_3.2x2.5mm (pad 1 XI, pad 3 XO). History: Lucki L327S240P11L C5261154 (listed as 24 MHz, wrong frequency; stock 0) -&gt; 3TJ424576UYFBC C2149067 -&gt; this part.</x:v>
       </x:c>
       <x:c r="S51" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2149067.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C70568.html</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="36" customHeight="1">
@@ -3437,7 +3437,7 @@
         <x:v>C275</x:v>
       </x:c>
       <x:c r="B57" s="22" t="str">
-        <x:v>PVDD_AMP bulk 100uF 25V polymer/hybrid (8x10 mm)</x:v>
+        <x:v>PVDD_AMP bulk 100uF 25V hybrid polymer (D6.3 x 7.7 mm part on CP_Elec_8x10 pads)</x:v>
       </x:c>
       <x:c r="C57" s="22" t="str">
         <x:v>PANASONIC</x:v>
@@ -3488,7 +3488,7 @@
         <x:v>2026-10-10</x:v>
       </x:c>
       <x:c r="R57" s="1" t="str">
-        <x:v>Amplifiers sheet, 2026-10-06. Bass-burst reservoir; part type not verified. SUBSTITUTION 2026-10-10 (coordinator-approved): EEH-ZA1E101P unresolved -&gt; EEHZA1E101XP C264047. Original EEH-ZA1E101P not listed; same Panasonic EEH-ZA 100 uF 25 V +/-20% hybrid polymer, standard (P) product XP. Pad fit checked vs CP_Elec_8x10: terminals span about +/-1.1 to +/-3.5 mm (datasheet P 2.2, I 2.4 for size D8), pads at +/-3.25 mm, 3.5 x 2.5 mm cover them; 6.3 mm body is inside the 8x10 courtyard. Datasheet ripple 2000 mA rms (listing text of 300 mA is wrong). 3D model is the 8x10 one, cosmetic only.</x:v>
+        <x:v>Amplifiers sheet, 2026-10-06. Bass-burst reservoir; part type not verified. SUBSTITUTION 2026-10-10 (coordinator-approved): EEH-ZA1E101P unresolved -&gt; EEHZA1E101XP C264047. Original EEH-ZA1E101P not listed; same Panasonic EEH-ZA 100 uF 25 V +/-20% hybrid polymer, standard (P) product XP. Pad fit checked vs CP_Elec_8x10: terminals span about +/-0.9 to +/-3.9 mm (datasheet size D8: P 1.8, I 2.6, H 7.8 max, W 0.65; corrected 2026-10-10), pads at +/-3.25 mm, 3.5 x 2.5 mm cover them; 6.3 mm body is inside the 8x10 courtyard. Datasheet ripple 2000 mA rms (listing text of 300 mA is wrong). 3D model repointed 2026-10-10 (reports/sync-y200-c275.md) to kicad-library/3d/CP_Elec_6.3x7.7.step (KiCad library model; measured body D6.3, base 6.6 x 6.6, height 7.7, terminal span 7.8, terminal width 0.65 mm = datasheet D8); pads and copper unchanged.</x:v>
       </x:c>
       <x:c r="S57" s="1" t="str">
         <x:v>https://www.lcsc.com/product-detail/C264047.html</x:v>
@@ -3871,16 +3871,16 @@
         <x:v>C226, C227</x:v>
       </x:c>
       <x:c r="B64" s="22" t="str">
-        <x:v>22pF C0G 0402 hand-solder (C_0402_1005Metric)</x:v>
+        <x:v>15pF C0G 0402 hand-solder (C_0402_1005Metric)</x:v>
       </x:c>
       <x:c r="C64" s="22" t="str">
         <x:v>Murata</x:v>
       </x:c>
       <x:c r="D64" s="22" t="str">
-        <x:v>GRM1555C1H220JA01D</x:v>
+        <x:v>GRM1555C1H150JA01D</x:v>
       </x:c>
       <x:c r="E64" s="22" t="str">
-        <x:v>C76960</x:v>
+        <x:v>C76950</x:v>
       </x:c>
       <x:c r="F64" s="23" t="n">
         <x:v>2</x:v>
@@ -3899,21 +3899,21 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="K64" s="28" t="n">
-        <x:v>0.0067</x:v>
+        <x:v>0.0054</x:v>
       </x:c>
       <x:c r="L64" s="30" t="n">
         <x:f>IF(K64="","",ROUND(F64*K64,4))</x:f>
-        <x:v>0.0134</x:v>
+        <x:v>0.0108</x:v>
       </x:c>
       <x:c r="M64" s="30" t="n">
         <x:f>IF(OR(K64="",I64="",N64=""),"",IF(N64&gt;=I64,ROUND(I64*K64,4),""))</x:f>
-        <x:v>0.67</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="N64" s="7" t="n">
-        <x:v>8700</x:v>
+        <x:v>55300</x:v>
       </x:c>
       <x:c r="O64" s="1" t="str">
-        <x:v>In stock; part/package/value verified 2026-10-10 against LCSC listing C76960 (muRata GRM1555C1H220JA01D, 0402); JLC extended; LCSC stock 8700, JLC list stock 31294 at lookup vs order qty 100; price is the listed ladder at order qty; re-check at order.</x:v>
+        <x:v>In stock; value change 2026-10-10 (sync-y200-c275; was 22pF GRM1555C1H220JA01D C76960); verified against LCSC listing C76950 (muRata GRM1555C1H150JA01D, 0402; 15pF, ±5%, 50V, C0G); JLC extended; LCSC stock 55300, JLC list stock 60138 at lookup vs order qty 100; price is the listed ladder at order qty; re-check at order.</x:v>
       </x:c>
       <x:c r="P64" s="4" t="n">
         <x:v>46305</x:v>
@@ -3922,10 +3922,10 @@
         <x:v>2026-10-10</x:v>
       </x:c>
       <x:c r="R64" s="1" t="str">
-        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C220JB8NNNC. See reports/passive-repackage-2026-10-06.md. MPN not stock-checked unless an LCSC code with price is shown.</x:v>
+        <x:v>Passive repackage 2026-10-06 (hand-solder policy): was C_0603 using CL10C220JB8NNNC. See reports/passive-repackage-2026-10-06.md. VALUE CHANGE 2026-10-10 (reports/sync-y200-c275.md): 22 pF GRM1555C1H220JA01D C76960 -&gt; 15 pF GRM1555C1H150JA01D C76950 to match the 12 pF Y200 replacement (X322524576MOB4SI): CL = 7.5 pF + 3-5 pF stray = 10.5-12.5 pF. Same Murata C0G 50 V +/-5% 0402 series, same footprint. Trim at bring-up if the measured frequency error exceeds about 20 ppm.</x:v>
       </x:c>
       <x:c r="S64" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C76960.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C76950.html</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="36" customHeight="1">

--- a/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
+++ b/ai-files/bom/DesktopSpeaker_LCSC_Starter_BOM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rbebacaf8831e4228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="Ref16ae1543fd4aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selected BOM" sheetId="1" r:id="Rc8a8dc75f86e4d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open selections" sheetId="2" r:id="R20494eb9f8ab456f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="3" t="n">
         <x:f>ROUND(SUM(L11:L111),2)</x:f>
-        <x:v>101.21</x:v>
+        <x:v>105.98</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1" t="str">
@@ -462,7 +462,7 @@
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="3" t="n">
         <x:f>ROUND(SUM(M11:M111),2)</x:f>
-        <x:v>132.88</x:v>
+        <x:v>140.2</x:v>
       </x:c>
       <x:c r="F5" s="1"/>
       <x:c r="G5" s="1" t="str">
@@ -2226,14 +2226,12 @@
         <x:v>Pack-positive disconnect switch</x:v>
       </x:c>
       <x:c r="C37" s="22" t="str">
-        <x:v>SHOU HAN</x:v>
+        <x:v>CW Industries</x:v>
       </x:c>
       <x:c r="D37" s="22" t="str">
-        <x:v>KCD1-201-R</x:v>
-      </x:c>
-      <x:c r="E37" s="22" t="str">
-        <x:v>C5884429</x:v>
-      </x:c>
+        <x:v>GRB112B802BR1</x:v>
+      </x:c>
+      <x:c r="E37" s="22" t="str"/>
       <x:c r="F37" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2251,33 +2249,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="28" t="n">
-        <x:v>0.338</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="L37" s="30" t="n">
-        <x:f>IF(K37="","",ROUND(F37*K37,4))</x:f>
-        <x:v>0.338</x:v>
-      </x:c>
-      <x:c r="M37" s="30" t="str">
+        <x:v>5.09</x:v>
+      </x:c>
+      <x:c r="M37" s="30" t="n">
         <x:f>IF(OR(K37="",I37="",N37=""),"",IF(N37&gt;=I37,ROUND(I37*K37,4),""))</x:f>
-        <x:v/>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="N37" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>7073</x:v>
       </x:c>
       <x:c r="O37" s="1" t="str">
-        <x:v>OUT OF STOCK - no stock - alternatives: none found with equal rating/footprint (KCD1-101/110/103/2P variants all stock 0 at LCSC and JLC); part/package/value verified 2026-10-10 against LCSC listing C5884429 (SHOU HAN KCD1-201-R, Through Hole,23x20.5mm); JLC type not found; LCSC stock 0 at lookup vs order qty 1; price is the listed ladder at order qty; re-check at order.</x:v>
+        <x:v>Digi-Key 2349683, 7073 in stock at 2026-10-12, $5.09; 20 A 14 VDC SPST round rocker, 20.2 mm hole, 0.187 in fastons, IP65, red LED (lamp pin unused on the 1S rail); snap-in panel 1.5-2.5 mm so the 4 mm lid needs a local pocket (CAD); replaces KCD1-201-R (stock 0). Not an LCSC part; wired, not assembled.</x:v>
       </x:c>
       <x:c r="P37" s="4" t="n">
         <x:v>46305</x:v>
       </x:c>
       <x:c r="Q37" s="1" t="str">
-        <x:v>2026-10-10</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="R37" s="1" t="str">
-        <x:v>Selected 2026-10-06: 20 mm round SPST rocker, 10 A @12 VDC (datasheet), 6 A 250 VAC. LCSC stock 0 at 2026-10-06: availability and 3-terminal mapping UNVERIFIED; peak 15-20 A exceeds rating, see HANDOVER. 2026-10-10 coordinator pass: no in-stock equal part found; left unresolved for stock.</x:v>
+        <x:v>Substituted 2026-10-12 from reports/sourcing-2026-10-12.md (coordinator, self-approved). Previous: SHOU HAN KCD1-201-R C5884429, stock 0.</x:v>
       </x:c>
       <x:c r="S37" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5884429.html</x:v>
+        <x:v>https://www.digikey.com/en/products/detail/cw-industries/GRB112B802BR1/2349683</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
@@ -2297,17 +2294,14 @@
       <x:c r="H38" s="13"/>
       <x:c r="I38" s="14" t="str">
         <x:f>IF(OR(D38="",G38="",H38=""),"",IF(COUNTIF($D$11:D38,D38)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$111,D38,$F$11:$F$111),G38)/H38,0)*H38))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="J38" s="6"/>
       <x:c r="K38" s="28"/>
       <x:c r="L38" s="30" t="str">
         <x:f>IF(K38="","",ROUND(F38*K38,4))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="M38" s="30" t="str">
         <x:f>IF(OR(K38="",I38="",N38=""),"",IF(N38&gt;=I38,ROUND(I38*K38,4),""))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="N38" s="7"/>
       <x:c r="O38" s="1" t="str">
@@ -2361,9 +2355,8 @@
         <x:f>IF(K39="","",ROUND(F39*K39,4))</x:f>
         <x:v>0.9773</x:v>
       </x:c>
-      <x:c r="M39" s="30" t="n">
+      <x:c r="M39" s="30" t="str">
         <x:f>IF(OR(K39="",I39="",N39=""),"",IF(N39&gt;=I39,ROUND(I39*K39,4),""))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="N39" s="7" t="n">
         <x:v>15179</x:v>
@@ -2483,9 +2476,8 @@
         <x:f>IF(K41="","",ROUND(F41*K41,4))</x:f>
         <x:v>4.2515</x:v>
       </x:c>
-      <x:c r="M41" s="30" t="n">
+      <x:c r="M41" s="30" t="str">
         <x:f>IF(OR(K41="",I41="",N41=""),"",IF(N41&gt;=I41,ROUND(I41*K41,4),""))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="N41" s="7" t="n">
         <x:v>2302</x:v>
@@ -2727,9 +2719,8 @@
         <x:f>IF(K45="","",ROUND(F45*K45,4))</x:f>
         <x:v>0.0565</x:v>
       </x:c>
-      <x:c r="M45" s="30" t="n">
+      <x:c r="M45" s="30" t="str">
         <x:f>IF(OR(K45="",I45="",N45=""),"",IF(N45&gt;=I45,ROUND(I45*K45,4),""))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="N45" s="7" t="n">
         <x:v>52690</x:v>
@@ -6419,10 +6410,10 @@
         <x:v>Alps Alpine</x:v>
       </x:c>
       <x:c r="D105" s="22" t="str">
-        <x:v>EC11E15244G1</x:v>
+        <x:v>EC11E18244AU</x:v>
       </x:c>
       <x:c r="E105" s="22" t="str">
-        <x:v>C370970</x:v>
+        <x:v>C202365</x:v>
       </x:c>
       <x:c r="F105" s="23" t="n">
         <x:v>1</x:v>
@@ -6441,33 +6432,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="28" t="n">
-        <x:v>2.2041</x:v>
+        <x:v>2.2213</x:v>
       </x:c>
       <x:c r="L105" s="30" t="n">
-        <x:f>IF(K105="","",ROUND(F105*K105,4))</x:f>
-        <x:v>2.2041</x:v>
-      </x:c>
-      <x:c r="M105" s="30" t="str">
+        <x:v>2.2213</x:v>
+      </x:c>
+      <x:c r="M105" s="30" t="n">
         <x:f>IF(OR(K105="",I105="",N105=""),"",IF(N105&gt;=I105,ROUND(I105*K105,4),""))</x:f>
-        <x:v/>
+        <x:v>2.2213</x:v>
       </x:c>
       <x:c r="N105" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="O105" s="1" t="str">
-        <x:v>OUT OF STOCK - no stock - alternatives: part/package/value verified 2026-10-10 against LCSC listing C370970 (ALPSALPINE EC11E15244G1, Through Hole); JLC extended; LCSC stock 0, JLC list stock 0 at lookup vs order qty 1; price is the listed ladder at order qty; re-check at order.</x:v>
+        <x:v>In stock (398 at 2026-10-12); substitute for EC11E15244G1 (C370970, stock 0): same EC11E vertical body, 20 mm flat shaft, push switch 0.5 mm travel, 18/36 pulses/detents instead of 15/30 (firmware counts per detent unchanged); footprint equivalence by series, body drawing not re-read; see reports/sourcing-2026-10-12.md</x:v>
       </x:c>
       <x:c r="P105" s="4" t="n">
         <x:v>46305</x:v>
       </x:c>
       <x:c r="Q105" s="1" t="str">
-        <x:v>2026-10-10</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="R105" s="1" t="str">
-        <x:v>Listing stock 0 at lookup. In-stock Alps variants are different parts (EC11E18244A5 C255515, 697 in stock; EC11E18244AU C202365, 401): confirm detent/shaft/switch suffix against the MCU footprint before substituting. 2026-10-10 coordinator pass: EC11E18244A5 C255515 (437 in stock) and EC11E18244AU C202365 (401) have 36 detents/18 pulses vs 30/15 of EC11E15244G1 (and a different shaft/switch suffix), so they are not equal; not substituted.</x:v>
+        <x:v>Substituted 2026-10-12 (coordinator, self-approved). Previous: EC11E15244G1 C370970, stock 0.</x:v>
       </x:c>
       <x:c r="S105" s="1" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C370970.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C202365.html</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="36" customHeight="1">
@@ -6551,17 +6541,14 @@
       <x:c r="H107" s="13"/>
       <x:c r="I107" s="14" t="str">
         <x:f>IF(OR(D107="",G107="",H107=""),"",IF(COUNTIF($D$11:D107,D107)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$111,D107,$F$11:$F$111),G107)/H107,0)*H107))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="J107" s="6"/>
       <x:c r="K107" s="28"/>
       <x:c r="L107" s="30" t="str">
         <x:f>IF(K107="","",ROUND(F107*K107,4))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="M107" s="30" t="str">
         <x:f>IF(OR(K107="",I107="",N107=""),"",IF(N107&gt;=I107,ROUND(I107*K107,4),""))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="N107" s="7"/>
       <x:c r="O107" s="1" t="str">
@@ -6615,9 +6602,8 @@
         <x:f>IF(K108="","",ROUND(F108*K108,4))</x:f>
         <x:v>0.028</x:v>
       </x:c>
-      <x:c r="M108" s="30" t="n">
+      <x:c r="M108" s="30" t="str">
         <x:f>IF(OR(K108="",I108="",N108=""),"",IF(N108&gt;=I108,ROUND(I108*K108,4),""))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="N108" s="7" t="n">
         <x:v>10000</x:v>
@@ -6739,9 +6725,8 @@
         <x:f>IF(K110="","",ROUND(F110*K110,4))</x:f>
         <x:v>0.0403</x:v>
       </x:c>
-      <x:c r="M110" s="30" t="n">
+      <x:c r="M110" s="30" t="str">
         <x:f>IF(OR(K110="",I110="",N110=""),"",IF(N110&gt;=I110,ROUND(I110*K110,4),""))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="N110" s="7" t="n">
         <x:v>10</x:v>
@@ -6783,17 +6768,14 @@
       <x:c r="H111" s="13"/>
       <x:c r="I111" s="14" t="str">
         <x:f>IF(OR(D111="",G111="",H111=""),"",IF(COUNTIF($D$11:D111,D111)&gt;1,0,ROUNDUP(MAX(SUMIF($D$11:$D$111,D111,$F$11:$F$111),G111)/H111,0)*H111))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="J111" s="6"/>
       <x:c r="K111" s="28"/>
       <x:c r="L111" s="30" t="str">
         <x:f>IF(K111="","",ROUND(F111*K111,4))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="M111" s="30" t="str">
         <x:f>IF(OR(K111="",I111="",N111=""),"",IF(N111&gt;=I111,ROUND(I111*K111,4),""))</x:f>
-        <x:v/>
       </x:c>
       <x:c r="N111" s="7"/>
       <x:c r="O111" s="1" t="str">
